--- a/form/FSS-Entry-Form.xlsx
+++ b/form/FSS-Entry-Form.xlsx
@@ -68,15 +68,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="180">
   <si>
     <t>PRIJAVA TAKMIČARA</t>
   </si>
   <si>
-    <t>Fudokan savez Srbije · popunjava klub i dostavlja savezu · takmičarska sezona 2026. · izdanje 25.08.2026.</t>
-  </si>
-  <si>
-    <t>Unos počinje godištem: uzrasna grupa i naziv uzrasta popunjavaju se automatski, a padajući meni nudi discipline koje su moguće u odnosu na uzrast. Telesna težina unosi se isključivo uz Fudokan sport kumite, budući da je tradicionalni kumite apsolutna kategorija. Kolona „Provera" služi za proveru kompletnosti prijave. Ekipne prijave se unose na listu „Ekipno".</t>
+    <t>Fudokan savez Srbije · popunjava klub i dostavlja savezu · takmičarska sezona 2026. · izdanje 06.10.2026.</t>
+  </si>
+  <si>
+    <t>Unos počinje godištem: uzrasna grupa i naziv uzrasta popunjavaju se automatski, a padajući meni nudi discipline koje su moguće u odnosu na uzrast. Telesna težina unosi se isključivo uz Fudokan sport kumite, budući da je tradicionalni kumite apsolutna kategorija. U kolonu „FSS ID" upisuje se ID takmičara sa spiska saveza — za 2026. godinu, a dok ga takmičar nema, prošlogodišnji; takmičar koji nastupa prvi put ostaje bez ID-a, nov ID dodeljuje savez. Kolona „Provera" služi za proveru kompletnosti prijave. Ekipne prijave se unose na listu „Ekipno".</t>
   </si>
   <si>
     <t>Klub</t>
@@ -140,6 +140,9 @@
   </si>
   <si>
     <t>Telesna težina</t>
+  </si>
+  <si>
+    <t>FSS ID</t>
   </si>
   <si>
     <t>Provera</t>
@@ -1028,7 +1031,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R130"/>
+  <dimension ref="A1:S130"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -1039,21 +1042,22 @@
     <col min="6" max="6" width="16.7109375" customWidth="1"/>
     <col min="7" max="14" width="20.7109375" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" customWidth="1"/>
-    <col min="16" max="16" width="34.7109375" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" customWidth="1"/>
+    <col min="17" max="17" width="34.7109375" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:19">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="28" customHeight="1">
+    <row r="3" spans="1:19" ht="40" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1072,8 +1076,9 @@
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
       <c r="P3" s="3"/>
-    </row>
-    <row r="4" spans="1:18">
+      <c r="Q3" s="3"/>
+    </row>
+    <row r="4" spans="1:19">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -1082,19 +1087,19 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:19">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:19">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="5"/>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:19">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
@@ -1103,7 +1108,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="30" customHeight="1">
+    <row r="10" spans="1:19" ht="30" customHeight="1">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
@@ -1152,8 +1157,11 @@
       <c r="P10" s="6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="11" spans="1:18">
+      <c r="Q10" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -1175,20 +1183,21 @@
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
       <c r="O11" s="5"/>
-      <c r="P11" s="8">
-        <f>IF(COUNTA($A11:$D11,G11:N11)=0,"",IF($A11="","Nedostaje godište",IF($E11="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B11="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B11&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C11="","Nedostaje pol",IF($D11="","Nedostaje pojas",IF(COUNTA(G11:N11)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G11:N11&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E11),G11:N11)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E11,IF(AND(COUNTIF(G11:N11,"Fudokan sport kumite")&gt;0,O11=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G11:N11,"Fudokan sport kumite")=0,O11&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q11">
+      <c r="P11" s="5"/>
+      <c r="Q11" s="8">
+        <f>IF(COUNTA($A11:$D11,G11:N11,P11)=0,"",IF($A11="","Nedostaje godište",IF($E11="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B11="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B11&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C11="","Nedostaje pol",IF($D11="","Nedostaje pojas",IF(COUNTA(G11:N11)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G11:N11&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E11),G11:N11)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E11,IF(AND(COUNTIF(G11:N11,"Fudokan sport kumite")&gt;0,O11=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G11:N11,"Fudokan sport kumite")=0,O11&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P11&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P11,4))="FSS-",MID(P11,LEN(P11)-2,1)="/",ISNUMBER(VALUE(RIGHT(P11,2))),VALUE(MID(P11,5,LEN(P11)-7))&gt;=1,VALUE(MID(P11,5,LEN(P11)-7))=INT(VALUE(MID(P11,5,LEN(P11)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R11">
         <f>IF($E11="","sve_discipline","disc_"&amp;$E11)</f>
         <v/>
       </c>
-      <c r="R11">
+      <c r="S11">
         <f>IF(OR($E11="",$C11=""),"sve_kilaze","kg_"&amp;$E11&amp;"_"&amp;IF($C11="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:19">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -1210,20 +1219,21 @@
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
       <c r="O12" s="5"/>
-      <c r="P12" s="8">
-        <f>IF(COUNTA($A12:$D12,G12:N12)=0,"",IF($A12="","Nedostaje godište",IF($E12="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B12="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B12&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C12="","Nedostaje pol",IF($D12="","Nedostaje pojas",IF(COUNTA(G12:N12)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G12:N12&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E12),G12:N12)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E12,IF(AND(COUNTIF(G12:N12,"Fudokan sport kumite")&gt;0,O12=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G12:N12,"Fudokan sport kumite")=0,O12&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q12">
+      <c r="P12" s="5"/>
+      <c r="Q12" s="8">
+        <f>IF(COUNTA($A12:$D12,G12:N12,P12)=0,"",IF($A12="","Nedostaje godište",IF($E12="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B12="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B12&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C12="","Nedostaje pol",IF($D12="","Nedostaje pojas",IF(COUNTA(G12:N12)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G12:N12&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E12),G12:N12)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E12,IF(AND(COUNTIF(G12:N12,"Fudokan sport kumite")&gt;0,O12=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G12:N12,"Fudokan sport kumite")=0,O12&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P12&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P12,4))="FSS-",MID(P12,LEN(P12)-2,1)="/",ISNUMBER(VALUE(RIGHT(P12,2))),VALUE(MID(P12,5,LEN(P12)-7))&gt;=1,VALUE(MID(P12,5,LEN(P12)-7))=INT(VALUE(MID(P12,5,LEN(P12)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R12">
         <f>IF($E12="","sve_discipline","disc_"&amp;$E12)</f>
         <v/>
       </c>
-      <c r="R12">
+      <c r="S12">
         <f>IF(OR($E12="",$C12=""),"sve_kilaze","kg_"&amp;$E12&amp;"_"&amp;IF($C12="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:19">
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
@@ -1245,20 +1255,21 @@
       <c r="M13" s="5"/>
       <c r="N13" s="5"/>
       <c r="O13" s="5"/>
-      <c r="P13" s="8">
-        <f>IF(COUNTA($A13:$D13,G13:N13)=0,"",IF($A13="","Nedostaje godište",IF($E13="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B13="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B13&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C13="","Nedostaje pol",IF($D13="","Nedostaje pojas",IF(COUNTA(G13:N13)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G13:N13&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E13),G13:N13)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E13,IF(AND(COUNTIF(G13:N13,"Fudokan sport kumite")&gt;0,O13=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G13:N13,"Fudokan sport kumite")=0,O13&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q13">
+      <c r="P13" s="5"/>
+      <c r="Q13" s="8">
+        <f>IF(COUNTA($A13:$D13,G13:N13,P13)=0,"",IF($A13="","Nedostaje godište",IF($E13="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B13="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B13&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C13="","Nedostaje pol",IF($D13="","Nedostaje pojas",IF(COUNTA(G13:N13)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G13:N13&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E13),G13:N13)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E13,IF(AND(COUNTIF(G13:N13,"Fudokan sport kumite")&gt;0,O13=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G13:N13,"Fudokan sport kumite")=0,O13&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P13&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P13,4))="FSS-",MID(P13,LEN(P13)-2,1)="/",ISNUMBER(VALUE(RIGHT(P13,2))),VALUE(MID(P13,5,LEN(P13)-7))&gt;=1,VALUE(MID(P13,5,LEN(P13)-7))=INT(VALUE(MID(P13,5,LEN(P13)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R13">
         <f>IF($E13="","sve_discipline","disc_"&amp;$E13)</f>
         <v/>
       </c>
-      <c r="R13">
+      <c r="S13">
         <f>IF(OR($E13="",$C13=""),"sve_kilaze","kg_"&amp;$E13&amp;"_"&amp;IF($C13="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:19">
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -1280,20 +1291,21 @@
       <c r="M14" s="5"/>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
-      <c r="P14" s="8">
-        <f>IF(COUNTA($A14:$D14,G14:N14)=0,"",IF($A14="","Nedostaje godište",IF($E14="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B14="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B14&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C14="","Nedostaje pol",IF($D14="","Nedostaje pojas",IF(COUNTA(G14:N14)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G14:N14&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E14),G14:N14)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E14,IF(AND(COUNTIF(G14:N14,"Fudokan sport kumite")&gt;0,O14=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G14:N14,"Fudokan sport kumite")=0,O14&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q14">
+      <c r="P14" s="5"/>
+      <c r="Q14" s="8">
+        <f>IF(COUNTA($A14:$D14,G14:N14,P14)=0,"",IF($A14="","Nedostaje godište",IF($E14="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B14="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B14&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C14="","Nedostaje pol",IF($D14="","Nedostaje pojas",IF(COUNTA(G14:N14)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G14:N14&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E14),G14:N14)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E14,IF(AND(COUNTIF(G14:N14,"Fudokan sport kumite")&gt;0,O14=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G14:N14,"Fudokan sport kumite")=0,O14&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P14&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P14,4))="FSS-",MID(P14,LEN(P14)-2,1)="/",ISNUMBER(VALUE(RIGHT(P14,2))),VALUE(MID(P14,5,LEN(P14)-7))&gt;=1,VALUE(MID(P14,5,LEN(P14)-7))=INT(VALUE(MID(P14,5,LEN(P14)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R14">
         <f>IF($E14="","sve_discipline","disc_"&amp;$E14)</f>
         <v/>
       </c>
-      <c r="R14">
+      <c r="S14">
         <f>IF(OR($E14="",$C14=""),"sve_kilaze","kg_"&amp;$E14&amp;"_"&amp;IF($C14="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:19">
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -1315,20 +1327,21 @@
       <c r="M15" s="5"/>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
-      <c r="P15" s="8">
-        <f>IF(COUNTA($A15:$D15,G15:N15)=0,"",IF($A15="","Nedostaje godište",IF($E15="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B15="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B15&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C15="","Nedostaje pol",IF($D15="","Nedostaje pojas",IF(COUNTA(G15:N15)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G15:N15&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E15),G15:N15)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E15,IF(AND(COUNTIF(G15:N15,"Fudokan sport kumite")&gt;0,O15=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G15:N15,"Fudokan sport kumite")=0,O15&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q15">
+      <c r="P15" s="5"/>
+      <c r="Q15" s="8">
+        <f>IF(COUNTA($A15:$D15,G15:N15,P15)=0,"",IF($A15="","Nedostaje godište",IF($E15="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B15="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B15&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C15="","Nedostaje pol",IF($D15="","Nedostaje pojas",IF(COUNTA(G15:N15)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G15:N15&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E15),G15:N15)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E15,IF(AND(COUNTIF(G15:N15,"Fudokan sport kumite")&gt;0,O15=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G15:N15,"Fudokan sport kumite")=0,O15&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P15&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P15,4))="FSS-",MID(P15,LEN(P15)-2,1)="/",ISNUMBER(VALUE(RIGHT(P15,2))),VALUE(MID(P15,5,LEN(P15)-7))&gt;=1,VALUE(MID(P15,5,LEN(P15)-7))=INT(VALUE(MID(P15,5,LEN(P15)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R15">
         <f>IF($E15="","sve_discipline","disc_"&amp;$E15)</f>
         <v/>
       </c>
-      <c r="R15">
+      <c r="S15">
         <f>IF(OR($E15="",$C15=""),"sve_kilaze","kg_"&amp;$E15&amp;"_"&amp;IF($C15="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:19">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -1350,20 +1363,21 @@
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
       <c r="O16" s="5"/>
-      <c r="P16" s="8">
-        <f>IF(COUNTA($A16:$D16,G16:N16)=0,"",IF($A16="","Nedostaje godište",IF($E16="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B16="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B16&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C16="","Nedostaje pol",IF($D16="","Nedostaje pojas",IF(COUNTA(G16:N16)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G16:N16&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E16),G16:N16)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E16,IF(AND(COUNTIF(G16:N16,"Fudokan sport kumite")&gt;0,O16=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G16:N16,"Fudokan sport kumite")=0,O16&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q16">
+      <c r="P16" s="5"/>
+      <c r="Q16" s="8">
+        <f>IF(COUNTA($A16:$D16,G16:N16,P16)=0,"",IF($A16="","Nedostaje godište",IF($E16="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B16="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B16&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C16="","Nedostaje pol",IF($D16="","Nedostaje pojas",IF(COUNTA(G16:N16)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G16:N16&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E16),G16:N16)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E16,IF(AND(COUNTIF(G16:N16,"Fudokan sport kumite")&gt;0,O16=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G16:N16,"Fudokan sport kumite")=0,O16&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P16&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P16,4))="FSS-",MID(P16,LEN(P16)-2,1)="/",ISNUMBER(VALUE(RIGHT(P16,2))),VALUE(MID(P16,5,LEN(P16)-7))&gt;=1,VALUE(MID(P16,5,LEN(P16)-7))=INT(VALUE(MID(P16,5,LEN(P16)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R16">
         <f>IF($E16="","sve_discipline","disc_"&amp;$E16)</f>
         <v/>
       </c>
-      <c r="R16">
+      <c r="S16">
         <f>IF(OR($E16="",$C16=""),"sve_kilaze","kg_"&amp;$E16&amp;"_"&amp;IF($C16="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:19">
       <c r="A17" s="5"/>
       <c r="B17" s="5"/>
       <c r="C17" s="5"/>
@@ -1385,20 +1399,21 @@
       <c r="M17" s="5"/>
       <c r="N17" s="5"/>
       <c r="O17" s="5"/>
-      <c r="P17" s="8">
-        <f>IF(COUNTA($A17:$D17,G17:N17)=0,"",IF($A17="","Nedostaje godište",IF($E17="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B17="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B17&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C17="","Nedostaje pol",IF($D17="","Nedostaje pojas",IF(COUNTA(G17:N17)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G17:N17&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E17),G17:N17)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E17,IF(AND(COUNTIF(G17:N17,"Fudokan sport kumite")&gt;0,O17=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G17:N17,"Fudokan sport kumite")=0,O17&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q17">
+      <c r="P17" s="5"/>
+      <c r="Q17" s="8">
+        <f>IF(COUNTA($A17:$D17,G17:N17,P17)=0,"",IF($A17="","Nedostaje godište",IF($E17="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B17="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B17&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C17="","Nedostaje pol",IF($D17="","Nedostaje pojas",IF(COUNTA(G17:N17)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G17:N17&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E17),G17:N17)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E17,IF(AND(COUNTIF(G17:N17,"Fudokan sport kumite")&gt;0,O17=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G17:N17,"Fudokan sport kumite")=0,O17&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P17&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P17,4))="FSS-",MID(P17,LEN(P17)-2,1)="/",ISNUMBER(VALUE(RIGHT(P17,2))),VALUE(MID(P17,5,LEN(P17)-7))&gt;=1,VALUE(MID(P17,5,LEN(P17)-7))=INT(VALUE(MID(P17,5,LEN(P17)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R17">
         <f>IF($E17="","sve_discipline","disc_"&amp;$E17)</f>
         <v/>
       </c>
-      <c r="R17">
+      <c r="S17">
         <f>IF(OR($E17="",$C17=""),"sve_kilaze","kg_"&amp;$E17&amp;"_"&amp;IF($C17="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:19">
       <c r="A18" s="5"/>
       <c r="B18" s="5"/>
       <c r="C18" s="5"/>
@@ -1420,20 +1435,21 @@
       <c r="M18" s="5"/>
       <c r="N18" s="5"/>
       <c r="O18" s="5"/>
-      <c r="P18" s="8">
-        <f>IF(COUNTA($A18:$D18,G18:N18)=0,"",IF($A18="","Nedostaje godište",IF($E18="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B18="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B18&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C18="","Nedostaje pol",IF($D18="","Nedostaje pojas",IF(COUNTA(G18:N18)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G18:N18&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E18),G18:N18)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E18,IF(AND(COUNTIF(G18:N18,"Fudokan sport kumite")&gt;0,O18=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G18:N18,"Fudokan sport kumite")=0,O18&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q18">
+      <c r="P18" s="5"/>
+      <c r="Q18" s="8">
+        <f>IF(COUNTA($A18:$D18,G18:N18,P18)=0,"",IF($A18="","Nedostaje godište",IF($E18="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B18="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B18&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C18="","Nedostaje pol",IF($D18="","Nedostaje pojas",IF(COUNTA(G18:N18)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G18:N18&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E18),G18:N18)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E18,IF(AND(COUNTIF(G18:N18,"Fudokan sport kumite")&gt;0,O18=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G18:N18,"Fudokan sport kumite")=0,O18&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P18&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P18,4))="FSS-",MID(P18,LEN(P18)-2,1)="/",ISNUMBER(VALUE(RIGHT(P18,2))),VALUE(MID(P18,5,LEN(P18)-7))&gt;=1,VALUE(MID(P18,5,LEN(P18)-7))=INT(VALUE(MID(P18,5,LEN(P18)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R18">
         <f>IF($E18="","sve_discipline","disc_"&amp;$E18)</f>
         <v/>
       </c>
-      <c r="R18">
+      <c r="S18">
         <f>IF(OR($E18="",$C18=""),"sve_kilaze","kg_"&amp;$E18&amp;"_"&amp;IF($C18="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:19">
       <c r="A19" s="5"/>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -1455,20 +1471,21 @@
       <c r="M19" s="5"/>
       <c r="N19" s="5"/>
       <c r="O19" s="5"/>
-      <c r="P19" s="8">
-        <f>IF(COUNTA($A19:$D19,G19:N19)=0,"",IF($A19="","Nedostaje godište",IF($E19="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B19="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B19&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C19="","Nedostaje pol",IF($D19="","Nedostaje pojas",IF(COUNTA(G19:N19)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G19:N19&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E19),G19:N19)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E19,IF(AND(COUNTIF(G19:N19,"Fudokan sport kumite")&gt;0,O19=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G19:N19,"Fudokan sport kumite")=0,O19&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q19">
+      <c r="P19" s="5"/>
+      <c r="Q19" s="8">
+        <f>IF(COUNTA($A19:$D19,G19:N19,P19)=0,"",IF($A19="","Nedostaje godište",IF($E19="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B19="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B19&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C19="","Nedostaje pol",IF($D19="","Nedostaje pojas",IF(COUNTA(G19:N19)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G19:N19&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E19),G19:N19)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E19,IF(AND(COUNTIF(G19:N19,"Fudokan sport kumite")&gt;0,O19=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G19:N19,"Fudokan sport kumite")=0,O19&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P19&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P19,4))="FSS-",MID(P19,LEN(P19)-2,1)="/",ISNUMBER(VALUE(RIGHT(P19,2))),VALUE(MID(P19,5,LEN(P19)-7))&gt;=1,VALUE(MID(P19,5,LEN(P19)-7))=INT(VALUE(MID(P19,5,LEN(P19)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R19">
         <f>IF($E19="","sve_discipline","disc_"&amp;$E19)</f>
         <v/>
       </c>
-      <c r="R19">
+      <c r="S19">
         <f>IF(OR($E19="",$C19=""),"sve_kilaze","kg_"&amp;$E19&amp;"_"&amp;IF($C19="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:19">
       <c r="A20" s="5"/>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -1490,20 +1507,21 @@
       <c r="M20" s="5"/>
       <c r="N20" s="5"/>
       <c r="O20" s="5"/>
-      <c r="P20" s="8">
-        <f>IF(COUNTA($A20:$D20,G20:N20)=0,"",IF($A20="","Nedostaje godište",IF($E20="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B20="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B20&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C20="","Nedostaje pol",IF($D20="","Nedostaje pojas",IF(COUNTA(G20:N20)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G20:N20&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E20),G20:N20)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E20,IF(AND(COUNTIF(G20:N20,"Fudokan sport kumite")&gt;0,O20=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G20:N20,"Fudokan sport kumite")=0,O20&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q20">
+      <c r="P20" s="5"/>
+      <c r="Q20" s="8">
+        <f>IF(COUNTA($A20:$D20,G20:N20,P20)=0,"",IF($A20="","Nedostaje godište",IF($E20="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B20="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B20&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C20="","Nedostaje pol",IF($D20="","Nedostaje pojas",IF(COUNTA(G20:N20)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G20:N20&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E20),G20:N20)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E20,IF(AND(COUNTIF(G20:N20,"Fudokan sport kumite")&gt;0,O20=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G20:N20,"Fudokan sport kumite")=0,O20&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P20&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P20,4))="FSS-",MID(P20,LEN(P20)-2,1)="/",ISNUMBER(VALUE(RIGHT(P20,2))),VALUE(MID(P20,5,LEN(P20)-7))&gt;=1,VALUE(MID(P20,5,LEN(P20)-7))=INT(VALUE(MID(P20,5,LEN(P20)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R20">
         <f>IF($E20="","sve_discipline","disc_"&amp;$E20)</f>
         <v/>
       </c>
-      <c r="R20">
+      <c r="S20">
         <f>IF(OR($E20="",$C20=""),"sve_kilaze","kg_"&amp;$E20&amp;"_"&amp;IF($C20="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:19">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
       <c r="C21" s="5"/>
@@ -1525,20 +1543,21 @@
       <c r="M21" s="5"/>
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
-      <c r="P21" s="8">
-        <f>IF(COUNTA($A21:$D21,G21:N21)=0,"",IF($A21="","Nedostaje godište",IF($E21="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B21="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B21&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C21="","Nedostaje pol",IF($D21="","Nedostaje pojas",IF(COUNTA(G21:N21)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G21:N21&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E21),G21:N21)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E21,IF(AND(COUNTIF(G21:N21,"Fudokan sport kumite")&gt;0,O21=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G21:N21,"Fudokan sport kumite")=0,O21&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q21">
+      <c r="P21" s="5"/>
+      <c r="Q21" s="8">
+        <f>IF(COUNTA($A21:$D21,G21:N21,P21)=0,"",IF($A21="","Nedostaje godište",IF($E21="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B21="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B21&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C21="","Nedostaje pol",IF($D21="","Nedostaje pojas",IF(COUNTA(G21:N21)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G21:N21&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E21),G21:N21)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E21,IF(AND(COUNTIF(G21:N21,"Fudokan sport kumite")&gt;0,O21=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G21:N21,"Fudokan sport kumite")=0,O21&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P21&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P21,4))="FSS-",MID(P21,LEN(P21)-2,1)="/",ISNUMBER(VALUE(RIGHT(P21,2))),VALUE(MID(P21,5,LEN(P21)-7))&gt;=1,VALUE(MID(P21,5,LEN(P21)-7))=INT(VALUE(MID(P21,5,LEN(P21)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R21">
         <f>IF($E21="","sve_discipline","disc_"&amp;$E21)</f>
         <v/>
       </c>
-      <c r="R21">
+      <c r="S21">
         <f>IF(OR($E21="",$C21=""),"sve_kilaze","kg_"&amp;$E21&amp;"_"&amp;IF($C21="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:19">
       <c r="A22" s="5"/>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -1560,20 +1579,21 @@
       <c r="M22" s="5"/>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
-      <c r="P22" s="8">
-        <f>IF(COUNTA($A22:$D22,G22:N22)=0,"",IF($A22="","Nedostaje godište",IF($E22="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B22="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B22&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C22="","Nedostaje pol",IF($D22="","Nedostaje pojas",IF(COUNTA(G22:N22)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G22:N22&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E22),G22:N22)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E22,IF(AND(COUNTIF(G22:N22,"Fudokan sport kumite")&gt;0,O22=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G22:N22,"Fudokan sport kumite")=0,O22&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q22">
+      <c r="P22" s="5"/>
+      <c r="Q22" s="8">
+        <f>IF(COUNTA($A22:$D22,G22:N22,P22)=0,"",IF($A22="","Nedostaje godište",IF($E22="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B22="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B22&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C22="","Nedostaje pol",IF($D22="","Nedostaje pojas",IF(COUNTA(G22:N22)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G22:N22&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E22),G22:N22)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E22,IF(AND(COUNTIF(G22:N22,"Fudokan sport kumite")&gt;0,O22=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G22:N22,"Fudokan sport kumite")=0,O22&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P22&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P22,4))="FSS-",MID(P22,LEN(P22)-2,1)="/",ISNUMBER(VALUE(RIGHT(P22,2))),VALUE(MID(P22,5,LEN(P22)-7))&gt;=1,VALUE(MID(P22,5,LEN(P22)-7))=INT(VALUE(MID(P22,5,LEN(P22)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R22">
         <f>IF($E22="","sve_discipline","disc_"&amp;$E22)</f>
         <v/>
       </c>
-      <c r="R22">
+      <c r="S22">
         <f>IF(OR($E22="",$C22=""),"sve_kilaze","kg_"&amp;$E22&amp;"_"&amp;IF($C22="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:19">
       <c r="A23" s="5"/>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
@@ -1595,20 +1615,21 @@
       <c r="M23" s="5"/>
       <c r="N23" s="5"/>
       <c r="O23" s="5"/>
-      <c r="P23" s="8">
-        <f>IF(COUNTA($A23:$D23,G23:N23)=0,"",IF($A23="","Nedostaje godište",IF($E23="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B23="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B23&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C23="","Nedostaje pol",IF($D23="","Nedostaje pojas",IF(COUNTA(G23:N23)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G23:N23&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E23),G23:N23)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E23,IF(AND(COUNTIF(G23:N23,"Fudokan sport kumite")&gt;0,O23=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G23:N23,"Fudokan sport kumite")=0,O23&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q23">
+      <c r="P23" s="5"/>
+      <c r="Q23" s="8">
+        <f>IF(COUNTA($A23:$D23,G23:N23,P23)=0,"",IF($A23="","Nedostaje godište",IF($E23="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B23="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B23&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C23="","Nedostaje pol",IF($D23="","Nedostaje pojas",IF(COUNTA(G23:N23)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G23:N23&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E23),G23:N23)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E23,IF(AND(COUNTIF(G23:N23,"Fudokan sport kumite")&gt;0,O23=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G23:N23,"Fudokan sport kumite")=0,O23&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P23&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P23,4))="FSS-",MID(P23,LEN(P23)-2,1)="/",ISNUMBER(VALUE(RIGHT(P23,2))),VALUE(MID(P23,5,LEN(P23)-7))&gt;=1,VALUE(MID(P23,5,LEN(P23)-7))=INT(VALUE(MID(P23,5,LEN(P23)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R23">
         <f>IF($E23="","sve_discipline","disc_"&amp;$E23)</f>
         <v/>
       </c>
-      <c r="R23">
+      <c r="S23">
         <f>IF(OR($E23="",$C23=""),"sve_kilaze","kg_"&amp;$E23&amp;"_"&amp;IF($C23="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:19">
       <c r="A24" s="5"/>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -1630,20 +1651,21 @@
       <c r="M24" s="5"/>
       <c r="N24" s="5"/>
       <c r="O24" s="5"/>
-      <c r="P24" s="8">
-        <f>IF(COUNTA($A24:$D24,G24:N24)=0,"",IF($A24="","Nedostaje godište",IF($E24="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B24="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B24&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C24="","Nedostaje pol",IF($D24="","Nedostaje pojas",IF(COUNTA(G24:N24)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G24:N24&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E24),G24:N24)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E24,IF(AND(COUNTIF(G24:N24,"Fudokan sport kumite")&gt;0,O24=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G24:N24,"Fudokan sport kumite")=0,O24&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q24">
+      <c r="P24" s="5"/>
+      <c r="Q24" s="8">
+        <f>IF(COUNTA($A24:$D24,G24:N24,P24)=0,"",IF($A24="","Nedostaje godište",IF($E24="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B24="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B24&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C24="","Nedostaje pol",IF($D24="","Nedostaje pojas",IF(COUNTA(G24:N24)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G24:N24&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E24),G24:N24)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E24,IF(AND(COUNTIF(G24:N24,"Fudokan sport kumite")&gt;0,O24=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G24:N24,"Fudokan sport kumite")=0,O24&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P24&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P24,4))="FSS-",MID(P24,LEN(P24)-2,1)="/",ISNUMBER(VALUE(RIGHT(P24,2))),VALUE(MID(P24,5,LEN(P24)-7))&gt;=1,VALUE(MID(P24,5,LEN(P24)-7))=INT(VALUE(MID(P24,5,LEN(P24)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R24">
         <f>IF($E24="","sve_discipline","disc_"&amp;$E24)</f>
         <v/>
       </c>
-      <c r="R24">
+      <c r="S24">
         <f>IF(OR($E24="",$C24=""),"sve_kilaze","kg_"&amp;$E24&amp;"_"&amp;IF($C24="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:19">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -1665,20 +1687,21 @@
       <c r="M25" s="5"/>
       <c r="N25" s="5"/>
       <c r="O25" s="5"/>
-      <c r="P25" s="8">
-        <f>IF(COUNTA($A25:$D25,G25:N25)=0,"",IF($A25="","Nedostaje godište",IF($E25="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B25="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B25&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C25="","Nedostaje pol",IF($D25="","Nedostaje pojas",IF(COUNTA(G25:N25)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G25:N25&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E25),G25:N25)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E25,IF(AND(COUNTIF(G25:N25,"Fudokan sport kumite")&gt;0,O25=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G25:N25,"Fudokan sport kumite")=0,O25&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q25">
+      <c r="P25" s="5"/>
+      <c r="Q25" s="8">
+        <f>IF(COUNTA($A25:$D25,G25:N25,P25)=0,"",IF($A25="","Nedostaje godište",IF($E25="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B25="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B25&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C25="","Nedostaje pol",IF($D25="","Nedostaje pojas",IF(COUNTA(G25:N25)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G25:N25&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E25),G25:N25)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E25,IF(AND(COUNTIF(G25:N25,"Fudokan sport kumite")&gt;0,O25=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G25:N25,"Fudokan sport kumite")=0,O25&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P25&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P25,4))="FSS-",MID(P25,LEN(P25)-2,1)="/",ISNUMBER(VALUE(RIGHT(P25,2))),VALUE(MID(P25,5,LEN(P25)-7))&gt;=1,VALUE(MID(P25,5,LEN(P25)-7))=INT(VALUE(MID(P25,5,LEN(P25)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R25">
         <f>IF($E25="","sve_discipline","disc_"&amp;$E25)</f>
         <v/>
       </c>
-      <c r="R25">
+      <c r="S25">
         <f>IF(OR($E25="",$C25=""),"sve_kilaze","kg_"&amp;$E25&amp;"_"&amp;IF($C25="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:19">
       <c r="A26" s="5"/>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -1700,20 +1723,21 @@
       <c r="M26" s="5"/>
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
-      <c r="P26" s="8">
-        <f>IF(COUNTA($A26:$D26,G26:N26)=0,"",IF($A26="","Nedostaje godište",IF($E26="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B26="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B26&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C26="","Nedostaje pol",IF($D26="","Nedostaje pojas",IF(COUNTA(G26:N26)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G26:N26&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E26),G26:N26)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E26,IF(AND(COUNTIF(G26:N26,"Fudokan sport kumite")&gt;0,O26=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G26:N26,"Fudokan sport kumite")=0,O26&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q26">
+      <c r="P26" s="5"/>
+      <c r="Q26" s="8">
+        <f>IF(COUNTA($A26:$D26,G26:N26,P26)=0,"",IF($A26="","Nedostaje godište",IF($E26="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B26="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B26&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C26="","Nedostaje pol",IF($D26="","Nedostaje pojas",IF(COUNTA(G26:N26)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G26:N26&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E26),G26:N26)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E26,IF(AND(COUNTIF(G26:N26,"Fudokan sport kumite")&gt;0,O26=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G26:N26,"Fudokan sport kumite")=0,O26&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P26&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P26,4))="FSS-",MID(P26,LEN(P26)-2,1)="/",ISNUMBER(VALUE(RIGHT(P26,2))),VALUE(MID(P26,5,LEN(P26)-7))&gt;=1,VALUE(MID(P26,5,LEN(P26)-7))=INT(VALUE(MID(P26,5,LEN(P26)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R26">
         <f>IF($E26="","sve_discipline","disc_"&amp;$E26)</f>
         <v/>
       </c>
-      <c r="R26">
+      <c r="S26">
         <f>IF(OR($E26="",$C26=""),"sve_kilaze","kg_"&amp;$E26&amp;"_"&amp;IF($C26="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:19">
       <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -1735,20 +1759,21 @@
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
-      <c r="P27" s="8">
-        <f>IF(COUNTA($A27:$D27,G27:N27)=0,"",IF($A27="","Nedostaje godište",IF($E27="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B27="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B27&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C27="","Nedostaje pol",IF($D27="","Nedostaje pojas",IF(COUNTA(G27:N27)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G27:N27&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E27),G27:N27)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E27,IF(AND(COUNTIF(G27:N27,"Fudokan sport kumite")&gt;0,O27=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G27:N27,"Fudokan sport kumite")=0,O27&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q27">
+      <c r="P27" s="5"/>
+      <c r="Q27" s="8">
+        <f>IF(COUNTA($A27:$D27,G27:N27,P27)=0,"",IF($A27="","Nedostaje godište",IF($E27="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B27="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B27&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C27="","Nedostaje pol",IF($D27="","Nedostaje pojas",IF(COUNTA(G27:N27)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G27:N27&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E27),G27:N27)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E27,IF(AND(COUNTIF(G27:N27,"Fudokan sport kumite")&gt;0,O27=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G27:N27,"Fudokan sport kumite")=0,O27&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P27&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P27,4))="FSS-",MID(P27,LEN(P27)-2,1)="/",ISNUMBER(VALUE(RIGHT(P27,2))),VALUE(MID(P27,5,LEN(P27)-7))&gt;=1,VALUE(MID(P27,5,LEN(P27)-7))=INT(VALUE(MID(P27,5,LEN(P27)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R27">
         <f>IF($E27="","sve_discipline","disc_"&amp;$E27)</f>
         <v/>
       </c>
-      <c r="R27">
+      <c r="S27">
         <f>IF(OR($E27="",$C27=""),"sve_kilaze","kg_"&amp;$E27&amp;"_"&amp;IF($C27="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:19">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
@@ -1770,20 +1795,21 @@
       <c r="M28" s="5"/>
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
-      <c r="P28" s="8">
-        <f>IF(COUNTA($A28:$D28,G28:N28)=0,"",IF($A28="","Nedostaje godište",IF($E28="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B28="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B28&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C28="","Nedostaje pol",IF($D28="","Nedostaje pojas",IF(COUNTA(G28:N28)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G28:N28&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E28),G28:N28)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E28,IF(AND(COUNTIF(G28:N28,"Fudokan sport kumite")&gt;0,O28=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G28:N28,"Fudokan sport kumite")=0,O28&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q28">
+      <c r="P28" s="5"/>
+      <c r="Q28" s="8">
+        <f>IF(COUNTA($A28:$D28,G28:N28,P28)=0,"",IF($A28="","Nedostaje godište",IF($E28="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B28="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B28&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C28="","Nedostaje pol",IF($D28="","Nedostaje pojas",IF(COUNTA(G28:N28)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G28:N28&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E28),G28:N28)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E28,IF(AND(COUNTIF(G28:N28,"Fudokan sport kumite")&gt;0,O28=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G28:N28,"Fudokan sport kumite")=0,O28&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P28&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P28,4))="FSS-",MID(P28,LEN(P28)-2,1)="/",ISNUMBER(VALUE(RIGHT(P28,2))),VALUE(MID(P28,5,LEN(P28)-7))&gt;=1,VALUE(MID(P28,5,LEN(P28)-7))=INT(VALUE(MID(P28,5,LEN(P28)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R28">
         <f>IF($E28="","sve_discipline","disc_"&amp;$E28)</f>
         <v/>
       </c>
-      <c r="R28">
+      <c r="S28">
         <f>IF(OR($E28="",$C28=""),"sve_kilaze","kg_"&amp;$E28&amp;"_"&amp;IF($C28="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:19">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
@@ -1805,20 +1831,21 @@
       <c r="M29" s="5"/>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
-      <c r="P29" s="8">
-        <f>IF(COUNTA($A29:$D29,G29:N29)=0,"",IF($A29="","Nedostaje godište",IF($E29="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B29="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B29&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C29="","Nedostaje pol",IF($D29="","Nedostaje pojas",IF(COUNTA(G29:N29)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G29:N29&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E29),G29:N29)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E29,IF(AND(COUNTIF(G29:N29,"Fudokan sport kumite")&gt;0,O29=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G29:N29,"Fudokan sport kumite")=0,O29&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q29">
+      <c r="P29" s="5"/>
+      <c r="Q29" s="8">
+        <f>IF(COUNTA($A29:$D29,G29:N29,P29)=0,"",IF($A29="","Nedostaje godište",IF($E29="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B29="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B29&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C29="","Nedostaje pol",IF($D29="","Nedostaje pojas",IF(COUNTA(G29:N29)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G29:N29&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E29),G29:N29)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E29,IF(AND(COUNTIF(G29:N29,"Fudokan sport kumite")&gt;0,O29=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G29:N29,"Fudokan sport kumite")=0,O29&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P29&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P29,4))="FSS-",MID(P29,LEN(P29)-2,1)="/",ISNUMBER(VALUE(RIGHT(P29,2))),VALUE(MID(P29,5,LEN(P29)-7))&gt;=1,VALUE(MID(P29,5,LEN(P29)-7))=INT(VALUE(MID(P29,5,LEN(P29)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R29">
         <f>IF($E29="","sve_discipline","disc_"&amp;$E29)</f>
         <v/>
       </c>
-      <c r="R29">
+      <c r="S29">
         <f>IF(OR($E29="",$C29=""),"sve_kilaze","kg_"&amp;$E29&amp;"_"&amp;IF($C29="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:19">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -1840,20 +1867,21 @@
       <c r="M30" s="5"/>
       <c r="N30" s="5"/>
       <c r="O30" s="5"/>
-      <c r="P30" s="8">
-        <f>IF(COUNTA($A30:$D30,G30:N30)=0,"",IF($A30="","Nedostaje godište",IF($E30="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B30="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B30&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C30="","Nedostaje pol",IF($D30="","Nedostaje pojas",IF(COUNTA(G30:N30)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G30:N30&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E30),G30:N30)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E30,IF(AND(COUNTIF(G30:N30,"Fudokan sport kumite")&gt;0,O30=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G30:N30,"Fudokan sport kumite")=0,O30&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q30">
+      <c r="P30" s="5"/>
+      <c r="Q30" s="8">
+        <f>IF(COUNTA($A30:$D30,G30:N30,P30)=0,"",IF($A30="","Nedostaje godište",IF($E30="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B30="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B30&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C30="","Nedostaje pol",IF($D30="","Nedostaje pojas",IF(COUNTA(G30:N30)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G30:N30&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E30),G30:N30)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E30,IF(AND(COUNTIF(G30:N30,"Fudokan sport kumite")&gt;0,O30=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G30:N30,"Fudokan sport kumite")=0,O30&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P30&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P30,4))="FSS-",MID(P30,LEN(P30)-2,1)="/",ISNUMBER(VALUE(RIGHT(P30,2))),VALUE(MID(P30,5,LEN(P30)-7))&gt;=1,VALUE(MID(P30,5,LEN(P30)-7))=INT(VALUE(MID(P30,5,LEN(P30)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R30">
         <f>IF($E30="","sve_discipline","disc_"&amp;$E30)</f>
         <v/>
       </c>
-      <c r="R30">
+      <c r="S30">
         <f>IF(OR($E30="",$C30=""),"sve_kilaze","kg_"&amp;$E30&amp;"_"&amp;IF($C30="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:19">
       <c r="A31" s="5"/>
       <c r="B31" s="5"/>
       <c r="C31" s="5"/>
@@ -1875,20 +1903,21 @@
       <c r="M31" s="5"/>
       <c r="N31" s="5"/>
       <c r="O31" s="5"/>
-      <c r="P31" s="8">
-        <f>IF(COUNTA($A31:$D31,G31:N31)=0,"",IF($A31="","Nedostaje godište",IF($E31="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B31="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B31&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C31="","Nedostaje pol",IF($D31="","Nedostaje pojas",IF(COUNTA(G31:N31)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G31:N31&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E31),G31:N31)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E31,IF(AND(COUNTIF(G31:N31,"Fudokan sport kumite")&gt;0,O31=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G31:N31,"Fudokan sport kumite")=0,O31&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q31">
+      <c r="P31" s="5"/>
+      <c r="Q31" s="8">
+        <f>IF(COUNTA($A31:$D31,G31:N31,P31)=0,"",IF($A31="","Nedostaje godište",IF($E31="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B31="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B31&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C31="","Nedostaje pol",IF($D31="","Nedostaje pojas",IF(COUNTA(G31:N31)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G31:N31&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E31),G31:N31)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E31,IF(AND(COUNTIF(G31:N31,"Fudokan sport kumite")&gt;0,O31=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G31:N31,"Fudokan sport kumite")=0,O31&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P31&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P31,4))="FSS-",MID(P31,LEN(P31)-2,1)="/",ISNUMBER(VALUE(RIGHT(P31,2))),VALUE(MID(P31,5,LEN(P31)-7))&gt;=1,VALUE(MID(P31,5,LEN(P31)-7))=INT(VALUE(MID(P31,5,LEN(P31)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R31">
         <f>IF($E31="","sve_discipline","disc_"&amp;$E31)</f>
         <v/>
       </c>
-      <c r="R31">
+      <c r="S31">
         <f>IF(OR($E31="",$C31=""),"sve_kilaze","kg_"&amp;$E31&amp;"_"&amp;IF($C31="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:19">
       <c r="A32" s="5"/>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -1910,20 +1939,21 @@
       <c r="M32" s="5"/>
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
-      <c r="P32" s="8">
-        <f>IF(COUNTA($A32:$D32,G32:N32)=0,"",IF($A32="","Nedostaje godište",IF($E32="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B32="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B32&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C32="","Nedostaje pol",IF($D32="","Nedostaje pojas",IF(COUNTA(G32:N32)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G32:N32&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E32),G32:N32)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E32,IF(AND(COUNTIF(G32:N32,"Fudokan sport kumite")&gt;0,O32=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G32:N32,"Fudokan sport kumite")=0,O32&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q32">
+      <c r="P32" s="5"/>
+      <c r="Q32" s="8">
+        <f>IF(COUNTA($A32:$D32,G32:N32,P32)=0,"",IF($A32="","Nedostaje godište",IF($E32="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B32="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B32&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C32="","Nedostaje pol",IF($D32="","Nedostaje pojas",IF(COUNTA(G32:N32)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G32:N32&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E32),G32:N32)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E32,IF(AND(COUNTIF(G32:N32,"Fudokan sport kumite")&gt;0,O32=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G32:N32,"Fudokan sport kumite")=0,O32&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P32&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P32,4))="FSS-",MID(P32,LEN(P32)-2,1)="/",ISNUMBER(VALUE(RIGHT(P32,2))),VALUE(MID(P32,5,LEN(P32)-7))&gt;=1,VALUE(MID(P32,5,LEN(P32)-7))=INT(VALUE(MID(P32,5,LEN(P32)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R32">
         <f>IF($E32="","sve_discipline","disc_"&amp;$E32)</f>
         <v/>
       </c>
-      <c r="R32">
+      <c r="S32">
         <f>IF(OR($E32="",$C32=""),"sve_kilaze","kg_"&amp;$E32&amp;"_"&amp;IF($C32="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:18">
+    <row r="33" spans="1:19">
       <c r="A33" s="5"/>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -1945,20 +1975,21 @@
       <c r="M33" s="5"/>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
-      <c r="P33" s="8">
-        <f>IF(COUNTA($A33:$D33,G33:N33)=0,"",IF($A33="","Nedostaje godište",IF($E33="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B33="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B33&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C33="","Nedostaje pol",IF($D33="","Nedostaje pojas",IF(COUNTA(G33:N33)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G33:N33&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E33),G33:N33)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E33,IF(AND(COUNTIF(G33:N33,"Fudokan sport kumite")&gt;0,O33=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G33:N33,"Fudokan sport kumite")=0,O33&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q33">
+      <c r="P33" s="5"/>
+      <c r="Q33" s="8">
+        <f>IF(COUNTA($A33:$D33,G33:N33,P33)=0,"",IF($A33="","Nedostaje godište",IF($E33="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B33="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B33&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C33="","Nedostaje pol",IF($D33="","Nedostaje pojas",IF(COUNTA(G33:N33)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G33:N33&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E33),G33:N33)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E33,IF(AND(COUNTIF(G33:N33,"Fudokan sport kumite")&gt;0,O33=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G33:N33,"Fudokan sport kumite")=0,O33&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P33&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P33,4))="FSS-",MID(P33,LEN(P33)-2,1)="/",ISNUMBER(VALUE(RIGHT(P33,2))),VALUE(MID(P33,5,LEN(P33)-7))&gt;=1,VALUE(MID(P33,5,LEN(P33)-7))=INT(VALUE(MID(P33,5,LEN(P33)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R33">
         <f>IF($E33="","sve_discipline","disc_"&amp;$E33)</f>
         <v/>
       </c>
-      <c r="R33">
+      <c r="S33">
         <f>IF(OR($E33="",$C33=""),"sve_kilaze","kg_"&amp;$E33&amp;"_"&amp;IF($C33="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:18">
+    <row r="34" spans="1:19">
       <c r="A34" s="5"/>
       <c r="B34" s="5"/>
       <c r="C34" s="5"/>
@@ -1980,20 +2011,21 @@
       <c r="M34" s="5"/>
       <c r="N34" s="5"/>
       <c r="O34" s="5"/>
-      <c r="P34" s="8">
-        <f>IF(COUNTA($A34:$D34,G34:N34)=0,"",IF($A34="","Nedostaje godište",IF($E34="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B34="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B34&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C34="","Nedostaje pol",IF($D34="","Nedostaje pojas",IF(COUNTA(G34:N34)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G34:N34&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E34),G34:N34)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E34,IF(AND(COUNTIF(G34:N34,"Fudokan sport kumite")&gt;0,O34=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G34:N34,"Fudokan sport kumite")=0,O34&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q34">
+      <c r="P34" s="5"/>
+      <c r="Q34" s="8">
+        <f>IF(COUNTA($A34:$D34,G34:N34,P34)=0,"",IF($A34="","Nedostaje godište",IF($E34="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B34="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B34&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C34="","Nedostaje pol",IF($D34="","Nedostaje pojas",IF(COUNTA(G34:N34)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G34:N34&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E34),G34:N34)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E34,IF(AND(COUNTIF(G34:N34,"Fudokan sport kumite")&gt;0,O34=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G34:N34,"Fudokan sport kumite")=0,O34&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P34&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P34,4))="FSS-",MID(P34,LEN(P34)-2,1)="/",ISNUMBER(VALUE(RIGHT(P34,2))),VALUE(MID(P34,5,LEN(P34)-7))&gt;=1,VALUE(MID(P34,5,LEN(P34)-7))=INT(VALUE(MID(P34,5,LEN(P34)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R34">
         <f>IF($E34="","sve_discipline","disc_"&amp;$E34)</f>
         <v/>
       </c>
-      <c r="R34">
+      <c r="S34">
         <f>IF(OR($E34="",$C34=""),"sve_kilaze","kg_"&amp;$E34&amp;"_"&amp;IF($C34="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:18">
+    <row r="35" spans="1:19">
       <c r="A35" s="5"/>
       <c r="B35" s="5"/>
       <c r="C35" s="5"/>
@@ -2015,20 +2047,21 @@
       <c r="M35" s="5"/>
       <c r="N35" s="5"/>
       <c r="O35" s="5"/>
-      <c r="P35" s="8">
-        <f>IF(COUNTA($A35:$D35,G35:N35)=0,"",IF($A35="","Nedostaje godište",IF($E35="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B35="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B35&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C35="","Nedostaje pol",IF($D35="","Nedostaje pojas",IF(COUNTA(G35:N35)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G35:N35&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E35),G35:N35)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E35,IF(AND(COUNTIF(G35:N35,"Fudokan sport kumite")&gt;0,O35=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G35:N35,"Fudokan sport kumite")=0,O35&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q35">
+      <c r="P35" s="5"/>
+      <c r="Q35" s="8">
+        <f>IF(COUNTA($A35:$D35,G35:N35,P35)=0,"",IF($A35="","Nedostaje godište",IF($E35="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B35="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B35&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C35="","Nedostaje pol",IF($D35="","Nedostaje pojas",IF(COUNTA(G35:N35)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G35:N35&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E35),G35:N35)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E35,IF(AND(COUNTIF(G35:N35,"Fudokan sport kumite")&gt;0,O35=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G35:N35,"Fudokan sport kumite")=0,O35&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P35&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P35,4))="FSS-",MID(P35,LEN(P35)-2,1)="/",ISNUMBER(VALUE(RIGHT(P35,2))),VALUE(MID(P35,5,LEN(P35)-7))&gt;=1,VALUE(MID(P35,5,LEN(P35)-7))=INT(VALUE(MID(P35,5,LEN(P35)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R35">
         <f>IF($E35="","sve_discipline","disc_"&amp;$E35)</f>
         <v/>
       </c>
-      <c r="R35">
+      <c r="S35">
         <f>IF(OR($E35="",$C35=""),"sve_kilaze","kg_"&amp;$E35&amp;"_"&amp;IF($C35="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:18">
+    <row r="36" spans="1:19">
       <c r="A36" s="5"/>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -2050,20 +2083,21 @@
       <c r="M36" s="5"/>
       <c r="N36" s="5"/>
       <c r="O36" s="5"/>
-      <c r="P36" s="8">
-        <f>IF(COUNTA($A36:$D36,G36:N36)=0,"",IF($A36="","Nedostaje godište",IF($E36="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B36="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B36&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C36="","Nedostaje pol",IF($D36="","Nedostaje pojas",IF(COUNTA(G36:N36)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G36:N36&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E36),G36:N36)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E36,IF(AND(COUNTIF(G36:N36,"Fudokan sport kumite")&gt;0,O36=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G36:N36,"Fudokan sport kumite")=0,O36&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q36">
+      <c r="P36" s="5"/>
+      <c r="Q36" s="8">
+        <f>IF(COUNTA($A36:$D36,G36:N36,P36)=0,"",IF($A36="","Nedostaje godište",IF($E36="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B36="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B36&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C36="","Nedostaje pol",IF($D36="","Nedostaje pojas",IF(COUNTA(G36:N36)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G36:N36&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E36),G36:N36)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E36,IF(AND(COUNTIF(G36:N36,"Fudokan sport kumite")&gt;0,O36=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G36:N36,"Fudokan sport kumite")=0,O36&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P36&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P36,4))="FSS-",MID(P36,LEN(P36)-2,1)="/",ISNUMBER(VALUE(RIGHT(P36,2))),VALUE(MID(P36,5,LEN(P36)-7))&gt;=1,VALUE(MID(P36,5,LEN(P36)-7))=INT(VALUE(MID(P36,5,LEN(P36)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R36">
         <f>IF($E36="","sve_discipline","disc_"&amp;$E36)</f>
         <v/>
       </c>
-      <c r="R36">
+      <c r="S36">
         <f>IF(OR($E36="",$C36=""),"sve_kilaze","kg_"&amp;$E36&amp;"_"&amp;IF($C36="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:18">
+    <row r="37" spans="1:19">
       <c r="A37" s="5"/>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
@@ -2085,20 +2119,21 @@
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
       <c r="O37" s="5"/>
-      <c r="P37" s="8">
-        <f>IF(COUNTA($A37:$D37,G37:N37)=0,"",IF($A37="","Nedostaje godište",IF($E37="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B37="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B37&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C37="","Nedostaje pol",IF($D37="","Nedostaje pojas",IF(COUNTA(G37:N37)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G37:N37&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E37),G37:N37)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E37,IF(AND(COUNTIF(G37:N37,"Fudokan sport kumite")&gt;0,O37=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G37:N37,"Fudokan sport kumite")=0,O37&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q37">
+      <c r="P37" s="5"/>
+      <c r="Q37" s="8">
+        <f>IF(COUNTA($A37:$D37,G37:N37,P37)=0,"",IF($A37="","Nedostaje godište",IF($E37="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B37="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B37&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C37="","Nedostaje pol",IF($D37="","Nedostaje pojas",IF(COUNTA(G37:N37)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G37:N37&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E37),G37:N37)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E37,IF(AND(COUNTIF(G37:N37,"Fudokan sport kumite")&gt;0,O37=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G37:N37,"Fudokan sport kumite")=0,O37&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P37&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P37,4))="FSS-",MID(P37,LEN(P37)-2,1)="/",ISNUMBER(VALUE(RIGHT(P37,2))),VALUE(MID(P37,5,LEN(P37)-7))&gt;=1,VALUE(MID(P37,5,LEN(P37)-7))=INT(VALUE(MID(P37,5,LEN(P37)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R37">
         <f>IF($E37="","sve_discipline","disc_"&amp;$E37)</f>
         <v/>
       </c>
-      <c r="R37">
+      <c r="S37">
         <f>IF(OR($E37="",$C37=""),"sve_kilaze","kg_"&amp;$E37&amp;"_"&amp;IF($C37="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:18">
+    <row r="38" spans="1:19">
       <c r="A38" s="5"/>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -2120,20 +2155,21 @@
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
       <c r="O38" s="5"/>
-      <c r="P38" s="8">
-        <f>IF(COUNTA($A38:$D38,G38:N38)=0,"",IF($A38="","Nedostaje godište",IF($E38="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B38="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B38&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C38="","Nedostaje pol",IF($D38="","Nedostaje pojas",IF(COUNTA(G38:N38)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G38:N38&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E38),G38:N38)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E38,IF(AND(COUNTIF(G38:N38,"Fudokan sport kumite")&gt;0,O38=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G38:N38,"Fudokan sport kumite")=0,O38&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q38">
+      <c r="P38" s="5"/>
+      <c r="Q38" s="8">
+        <f>IF(COUNTA($A38:$D38,G38:N38,P38)=0,"",IF($A38="","Nedostaje godište",IF($E38="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B38="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B38&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C38="","Nedostaje pol",IF($D38="","Nedostaje pojas",IF(COUNTA(G38:N38)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G38:N38&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E38),G38:N38)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E38,IF(AND(COUNTIF(G38:N38,"Fudokan sport kumite")&gt;0,O38=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G38:N38,"Fudokan sport kumite")=0,O38&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P38&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P38,4))="FSS-",MID(P38,LEN(P38)-2,1)="/",ISNUMBER(VALUE(RIGHT(P38,2))),VALUE(MID(P38,5,LEN(P38)-7))&gt;=1,VALUE(MID(P38,5,LEN(P38)-7))=INT(VALUE(MID(P38,5,LEN(P38)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R38">
         <f>IF($E38="","sve_discipline","disc_"&amp;$E38)</f>
         <v/>
       </c>
-      <c r="R38">
+      <c r="S38">
         <f>IF(OR($E38="",$C38=""),"sve_kilaze","kg_"&amp;$E38&amp;"_"&amp;IF($C38="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:18">
+    <row r="39" spans="1:19">
       <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -2155,20 +2191,21 @@
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
       <c r="O39" s="5"/>
-      <c r="P39" s="8">
-        <f>IF(COUNTA($A39:$D39,G39:N39)=0,"",IF($A39="","Nedostaje godište",IF($E39="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B39="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B39&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C39="","Nedostaje pol",IF($D39="","Nedostaje pojas",IF(COUNTA(G39:N39)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G39:N39&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E39),G39:N39)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E39,IF(AND(COUNTIF(G39:N39,"Fudokan sport kumite")&gt;0,O39=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G39:N39,"Fudokan sport kumite")=0,O39&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q39">
+      <c r="P39" s="5"/>
+      <c r="Q39" s="8">
+        <f>IF(COUNTA($A39:$D39,G39:N39,P39)=0,"",IF($A39="","Nedostaje godište",IF($E39="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B39="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B39&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C39="","Nedostaje pol",IF($D39="","Nedostaje pojas",IF(COUNTA(G39:N39)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G39:N39&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E39),G39:N39)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E39,IF(AND(COUNTIF(G39:N39,"Fudokan sport kumite")&gt;0,O39=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G39:N39,"Fudokan sport kumite")=0,O39&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P39&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P39,4))="FSS-",MID(P39,LEN(P39)-2,1)="/",ISNUMBER(VALUE(RIGHT(P39,2))),VALUE(MID(P39,5,LEN(P39)-7))&gt;=1,VALUE(MID(P39,5,LEN(P39)-7))=INT(VALUE(MID(P39,5,LEN(P39)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R39">
         <f>IF($E39="","sve_discipline","disc_"&amp;$E39)</f>
         <v/>
       </c>
-      <c r="R39">
+      <c r="S39">
         <f>IF(OR($E39="",$C39=""),"sve_kilaze","kg_"&amp;$E39&amp;"_"&amp;IF($C39="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:18">
+    <row r="40" spans="1:19">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -2190,20 +2227,21 @@
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
-      <c r="P40" s="8">
-        <f>IF(COUNTA($A40:$D40,G40:N40)=0,"",IF($A40="","Nedostaje godište",IF($E40="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B40="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B40&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C40="","Nedostaje pol",IF($D40="","Nedostaje pojas",IF(COUNTA(G40:N40)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G40:N40&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E40),G40:N40)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E40,IF(AND(COUNTIF(G40:N40,"Fudokan sport kumite")&gt;0,O40=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G40:N40,"Fudokan sport kumite")=0,O40&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q40">
+      <c r="P40" s="5"/>
+      <c r="Q40" s="8">
+        <f>IF(COUNTA($A40:$D40,G40:N40,P40)=0,"",IF($A40="","Nedostaje godište",IF($E40="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B40="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B40&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C40="","Nedostaje pol",IF($D40="","Nedostaje pojas",IF(COUNTA(G40:N40)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G40:N40&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E40),G40:N40)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E40,IF(AND(COUNTIF(G40:N40,"Fudokan sport kumite")&gt;0,O40=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G40:N40,"Fudokan sport kumite")=0,O40&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P40&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P40,4))="FSS-",MID(P40,LEN(P40)-2,1)="/",ISNUMBER(VALUE(RIGHT(P40,2))),VALUE(MID(P40,5,LEN(P40)-7))&gt;=1,VALUE(MID(P40,5,LEN(P40)-7))=INT(VALUE(MID(P40,5,LEN(P40)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R40">
         <f>IF($E40="","sve_discipline","disc_"&amp;$E40)</f>
         <v/>
       </c>
-      <c r="R40">
+      <c r="S40">
         <f>IF(OR($E40="",$C40=""),"sve_kilaze","kg_"&amp;$E40&amp;"_"&amp;IF($C40="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:18">
+    <row r="41" spans="1:19">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -2225,20 +2263,21 @@
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
       <c r="O41" s="5"/>
-      <c r="P41" s="8">
-        <f>IF(COUNTA($A41:$D41,G41:N41)=0,"",IF($A41="","Nedostaje godište",IF($E41="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B41="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B41&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C41="","Nedostaje pol",IF($D41="","Nedostaje pojas",IF(COUNTA(G41:N41)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G41:N41&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E41),G41:N41)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E41,IF(AND(COUNTIF(G41:N41,"Fudokan sport kumite")&gt;0,O41=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G41:N41,"Fudokan sport kumite")=0,O41&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q41">
+      <c r="P41" s="5"/>
+      <c r="Q41" s="8">
+        <f>IF(COUNTA($A41:$D41,G41:N41,P41)=0,"",IF($A41="","Nedostaje godište",IF($E41="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B41="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B41&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C41="","Nedostaje pol",IF($D41="","Nedostaje pojas",IF(COUNTA(G41:N41)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G41:N41&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E41),G41:N41)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E41,IF(AND(COUNTIF(G41:N41,"Fudokan sport kumite")&gt;0,O41=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G41:N41,"Fudokan sport kumite")=0,O41&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P41&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P41,4))="FSS-",MID(P41,LEN(P41)-2,1)="/",ISNUMBER(VALUE(RIGHT(P41,2))),VALUE(MID(P41,5,LEN(P41)-7))&gt;=1,VALUE(MID(P41,5,LEN(P41)-7))=INT(VALUE(MID(P41,5,LEN(P41)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R41">
         <f>IF($E41="","sve_discipline","disc_"&amp;$E41)</f>
         <v/>
       </c>
-      <c r="R41">
+      <c r="S41">
         <f>IF(OR($E41="",$C41=""),"sve_kilaze","kg_"&amp;$E41&amp;"_"&amp;IF($C41="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:18">
+    <row r="42" spans="1:19">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -2260,20 +2299,21 @@
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
       <c r="O42" s="5"/>
-      <c r="P42" s="8">
-        <f>IF(COUNTA($A42:$D42,G42:N42)=0,"",IF($A42="","Nedostaje godište",IF($E42="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B42="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B42&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C42="","Nedostaje pol",IF($D42="","Nedostaje pojas",IF(COUNTA(G42:N42)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G42:N42&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E42),G42:N42)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E42,IF(AND(COUNTIF(G42:N42,"Fudokan sport kumite")&gt;0,O42=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G42:N42,"Fudokan sport kumite")=0,O42&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q42">
+      <c r="P42" s="5"/>
+      <c r="Q42" s="8">
+        <f>IF(COUNTA($A42:$D42,G42:N42,P42)=0,"",IF($A42="","Nedostaje godište",IF($E42="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B42="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B42&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C42="","Nedostaje pol",IF($D42="","Nedostaje pojas",IF(COUNTA(G42:N42)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G42:N42&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E42),G42:N42)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E42,IF(AND(COUNTIF(G42:N42,"Fudokan sport kumite")&gt;0,O42=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G42:N42,"Fudokan sport kumite")=0,O42&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P42&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P42,4))="FSS-",MID(P42,LEN(P42)-2,1)="/",ISNUMBER(VALUE(RIGHT(P42,2))),VALUE(MID(P42,5,LEN(P42)-7))&gt;=1,VALUE(MID(P42,5,LEN(P42)-7))=INT(VALUE(MID(P42,5,LEN(P42)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R42">
         <f>IF($E42="","sve_discipline","disc_"&amp;$E42)</f>
         <v/>
       </c>
-      <c r="R42">
+      <c r="S42">
         <f>IF(OR($E42="",$C42=""),"sve_kilaze","kg_"&amp;$E42&amp;"_"&amp;IF($C42="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:18">
+    <row r="43" spans="1:19">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -2295,20 +2335,21 @@
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
       <c r="O43" s="5"/>
-      <c r="P43" s="8">
-        <f>IF(COUNTA($A43:$D43,G43:N43)=0,"",IF($A43="","Nedostaje godište",IF($E43="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B43="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B43&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C43="","Nedostaje pol",IF($D43="","Nedostaje pojas",IF(COUNTA(G43:N43)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G43:N43&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E43),G43:N43)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E43,IF(AND(COUNTIF(G43:N43,"Fudokan sport kumite")&gt;0,O43=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G43:N43,"Fudokan sport kumite")=0,O43&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q43">
+      <c r="P43" s="5"/>
+      <c r="Q43" s="8">
+        <f>IF(COUNTA($A43:$D43,G43:N43,P43)=0,"",IF($A43="","Nedostaje godište",IF($E43="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B43="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B43&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C43="","Nedostaje pol",IF($D43="","Nedostaje pojas",IF(COUNTA(G43:N43)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G43:N43&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E43),G43:N43)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E43,IF(AND(COUNTIF(G43:N43,"Fudokan sport kumite")&gt;0,O43=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G43:N43,"Fudokan sport kumite")=0,O43&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P43&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P43,4))="FSS-",MID(P43,LEN(P43)-2,1)="/",ISNUMBER(VALUE(RIGHT(P43,2))),VALUE(MID(P43,5,LEN(P43)-7))&gt;=1,VALUE(MID(P43,5,LEN(P43)-7))=INT(VALUE(MID(P43,5,LEN(P43)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R43">
         <f>IF($E43="","sve_discipline","disc_"&amp;$E43)</f>
         <v/>
       </c>
-      <c r="R43">
+      <c r="S43">
         <f>IF(OR($E43="",$C43=""),"sve_kilaze","kg_"&amp;$E43&amp;"_"&amp;IF($C43="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:18">
+    <row r="44" spans="1:19">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -2330,20 +2371,21 @@
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
       <c r="O44" s="5"/>
-      <c r="P44" s="8">
-        <f>IF(COUNTA($A44:$D44,G44:N44)=0,"",IF($A44="","Nedostaje godište",IF($E44="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B44="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B44&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C44="","Nedostaje pol",IF($D44="","Nedostaje pojas",IF(COUNTA(G44:N44)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G44:N44&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E44),G44:N44)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E44,IF(AND(COUNTIF(G44:N44,"Fudokan sport kumite")&gt;0,O44=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G44:N44,"Fudokan sport kumite")=0,O44&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q44">
+      <c r="P44" s="5"/>
+      <c r="Q44" s="8">
+        <f>IF(COUNTA($A44:$D44,G44:N44,P44)=0,"",IF($A44="","Nedostaje godište",IF($E44="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B44="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B44&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C44="","Nedostaje pol",IF($D44="","Nedostaje pojas",IF(COUNTA(G44:N44)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G44:N44&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E44),G44:N44)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E44,IF(AND(COUNTIF(G44:N44,"Fudokan sport kumite")&gt;0,O44=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G44:N44,"Fudokan sport kumite")=0,O44&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P44&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P44,4))="FSS-",MID(P44,LEN(P44)-2,1)="/",ISNUMBER(VALUE(RIGHT(P44,2))),VALUE(MID(P44,5,LEN(P44)-7))&gt;=1,VALUE(MID(P44,5,LEN(P44)-7))=INT(VALUE(MID(P44,5,LEN(P44)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R44">
         <f>IF($E44="","sve_discipline","disc_"&amp;$E44)</f>
         <v/>
       </c>
-      <c r="R44">
+      <c r="S44">
         <f>IF(OR($E44="",$C44=""),"sve_kilaze","kg_"&amp;$E44&amp;"_"&amp;IF($C44="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:18">
+    <row r="45" spans="1:19">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -2365,20 +2407,21 @@
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
       <c r="O45" s="5"/>
-      <c r="P45" s="8">
-        <f>IF(COUNTA($A45:$D45,G45:N45)=0,"",IF($A45="","Nedostaje godište",IF($E45="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B45="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B45&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C45="","Nedostaje pol",IF($D45="","Nedostaje pojas",IF(COUNTA(G45:N45)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G45:N45&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E45),G45:N45)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E45,IF(AND(COUNTIF(G45:N45,"Fudokan sport kumite")&gt;0,O45=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G45:N45,"Fudokan sport kumite")=0,O45&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q45">
+      <c r="P45" s="5"/>
+      <c r="Q45" s="8">
+        <f>IF(COUNTA($A45:$D45,G45:N45,P45)=0,"",IF($A45="","Nedostaje godište",IF($E45="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B45="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B45&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C45="","Nedostaje pol",IF($D45="","Nedostaje pojas",IF(COUNTA(G45:N45)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G45:N45&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E45),G45:N45)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E45,IF(AND(COUNTIF(G45:N45,"Fudokan sport kumite")&gt;0,O45=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G45:N45,"Fudokan sport kumite")=0,O45&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P45&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P45,4))="FSS-",MID(P45,LEN(P45)-2,1)="/",ISNUMBER(VALUE(RIGHT(P45,2))),VALUE(MID(P45,5,LEN(P45)-7))&gt;=1,VALUE(MID(P45,5,LEN(P45)-7))=INT(VALUE(MID(P45,5,LEN(P45)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R45">
         <f>IF($E45="","sve_discipline","disc_"&amp;$E45)</f>
         <v/>
       </c>
-      <c r="R45">
+      <c r="S45">
         <f>IF(OR($E45="",$C45=""),"sve_kilaze","kg_"&amp;$E45&amp;"_"&amp;IF($C45="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:18">
+    <row r="46" spans="1:19">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -2400,20 +2443,21 @@
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
       <c r="O46" s="5"/>
-      <c r="P46" s="8">
-        <f>IF(COUNTA($A46:$D46,G46:N46)=0,"",IF($A46="","Nedostaje godište",IF($E46="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B46="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B46&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C46="","Nedostaje pol",IF($D46="","Nedostaje pojas",IF(COUNTA(G46:N46)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G46:N46&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E46),G46:N46)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E46,IF(AND(COUNTIF(G46:N46,"Fudokan sport kumite")&gt;0,O46=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G46:N46,"Fudokan sport kumite")=0,O46&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q46">
+      <c r="P46" s="5"/>
+      <c r="Q46" s="8">
+        <f>IF(COUNTA($A46:$D46,G46:N46,P46)=0,"",IF($A46="","Nedostaje godište",IF($E46="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B46="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B46&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C46="","Nedostaje pol",IF($D46="","Nedostaje pojas",IF(COUNTA(G46:N46)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G46:N46&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E46),G46:N46)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E46,IF(AND(COUNTIF(G46:N46,"Fudokan sport kumite")&gt;0,O46=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G46:N46,"Fudokan sport kumite")=0,O46&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P46&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P46,4))="FSS-",MID(P46,LEN(P46)-2,1)="/",ISNUMBER(VALUE(RIGHT(P46,2))),VALUE(MID(P46,5,LEN(P46)-7))&gt;=1,VALUE(MID(P46,5,LEN(P46)-7))=INT(VALUE(MID(P46,5,LEN(P46)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R46">
         <f>IF($E46="","sve_discipline","disc_"&amp;$E46)</f>
         <v/>
       </c>
-      <c r="R46">
+      <c r="S46">
         <f>IF(OR($E46="",$C46=""),"sve_kilaze","kg_"&amp;$E46&amp;"_"&amp;IF($C46="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:18">
+    <row r="47" spans="1:19">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -2435,20 +2479,21 @@
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
       <c r="O47" s="5"/>
-      <c r="P47" s="8">
-        <f>IF(COUNTA($A47:$D47,G47:N47)=0,"",IF($A47="","Nedostaje godište",IF($E47="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B47="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B47&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C47="","Nedostaje pol",IF($D47="","Nedostaje pojas",IF(COUNTA(G47:N47)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G47:N47&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E47),G47:N47)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E47,IF(AND(COUNTIF(G47:N47,"Fudokan sport kumite")&gt;0,O47=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G47:N47,"Fudokan sport kumite")=0,O47&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q47">
+      <c r="P47" s="5"/>
+      <c r="Q47" s="8">
+        <f>IF(COUNTA($A47:$D47,G47:N47,P47)=0,"",IF($A47="","Nedostaje godište",IF($E47="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B47="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B47&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C47="","Nedostaje pol",IF($D47="","Nedostaje pojas",IF(COUNTA(G47:N47)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G47:N47&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E47),G47:N47)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E47,IF(AND(COUNTIF(G47:N47,"Fudokan sport kumite")&gt;0,O47=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G47:N47,"Fudokan sport kumite")=0,O47&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P47&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P47,4))="FSS-",MID(P47,LEN(P47)-2,1)="/",ISNUMBER(VALUE(RIGHT(P47,2))),VALUE(MID(P47,5,LEN(P47)-7))&gt;=1,VALUE(MID(P47,5,LEN(P47)-7))=INT(VALUE(MID(P47,5,LEN(P47)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R47">
         <f>IF($E47="","sve_discipline","disc_"&amp;$E47)</f>
         <v/>
       </c>
-      <c r="R47">
+      <c r="S47">
         <f>IF(OR($E47="",$C47=""),"sve_kilaze","kg_"&amp;$E47&amp;"_"&amp;IF($C47="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:18">
+    <row r="48" spans="1:19">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -2470,20 +2515,21 @@
       <c r="M48" s="5"/>
       <c r="N48" s="5"/>
       <c r="O48" s="5"/>
-      <c r="P48" s="8">
-        <f>IF(COUNTA($A48:$D48,G48:N48)=0,"",IF($A48="","Nedostaje godište",IF($E48="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B48="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B48&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C48="","Nedostaje pol",IF($D48="","Nedostaje pojas",IF(COUNTA(G48:N48)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G48:N48&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E48),G48:N48)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E48,IF(AND(COUNTIF(G48:N48,"Fudokan sport kumite")&gt;0,O48=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G48:N48,"Fudokan sport kumite")=0,O48&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q48">
+      <c r="P48" s="5"/>
+      <c r="Q48" s="8">
+        <f>IF(COUNTA($A48:$D48,G48:N48,P48)=0,"",IF($A48="","Nedostaje godište",IF($E48="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B48="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B48&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C48="","Nedostaje pol",IF($D48="","Nedostaje pojas",IF(COUNTA(G48:N48)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G48:N48&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E48),G48:N48)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E48,IF(AND(COUNTIF(G48:N48,"Fudokan sport kumite")&gt;0,O48=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G48:N48,"Fudokan sport kumite")=0,O48&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P48&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P48,4))="FSS-",MID(P48,LEN(P48)-2,1)="/",ISNUMBER(VALUE(RIGHT(P48,2))),VALUE(MID(P48,5,LEN(P48)-7))&gt;=1,VALUE(MID(P48,5,LEN(P48)-7))=INT(VALUE(MID(P48,5,LEN(P48)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R48">
         <f>IF($E48="","sve_discipline","disc_"&amp;$E48)</f>
         <v/>
       </c>
-      <c r="R48">
+      <c r="S48">
         <f>IF(OR($E48="",$C48=""),"sve_kilaze","kg_"&amp;$E48&amp;"_"&amp;IF($C48="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:18">
+    <row r="49" spans="1:19">
       <c r="A49" s="5"/>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
@@ -2505,20 +2551,21 @@
       <c r="M49" s="5"/>
       <c r="N49" s="5"/>
       <c r="O49" s="5"/>
-      <c r="P49" s="8">
-        <f>IF(COUNTA($A49:$D49,G49:N49)=0,"",IF($A49="","Nedostaje godište",IF($E49="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B49="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B49&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C49="","Nedostaje pol",IF($D49="","Nedostaje pojas",IF(COUNTA(G49:N49)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G49:N49&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E49),G49:N49)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E49,IF(AND(COUNTIF(G49:N49,"Fudokan sport kumite")&gt;0,O49=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G49:N49,"Fudokan sport kumite")=0,O49&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q49">
+      <c r="P49" s="5"/>
+      <c r="Q49" s="8">
+        <f>IF(COUNTA($A49:$D49,G49:N49,P49)=0,"",IF($A49="","Nedostaje godište",IF($E49="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B49="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B49&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C49="","Nedostaje pol",IF($D49="","Nedostaje pojas",IF(COUNTA(G49:N49)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G49:N49&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E49),G49:N49)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E49,IF(AND(COUNTIF(G49:N49,"Fudokan sport kumite")&gt;0,O49=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G49:N49,"Fudokan sport kumite")=0,O49&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P49&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P49,4))="FSS-",MID(P49,LEN(P49)-2,1)="/",ISNUMBER(VALUE(RIGHT(P49,2))),VALUE(MID(P49,5,LEN(P49)-7))&gt;=1,VALUE(MID(P49,5,LEN(P49)-7))=INT(VALUE(MID(P49,5,LEN(P49)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R49">
         <f>IF($E49="","sve_discipline","disc_"&amp;$E49)</f>
         <v/>
       </c>
-      <c r="R49">
+      <c r="S49">
         <f>IF(OR($E49="",$C49=""),"sve_kilaze","kg_"&amp;$E49&amp;"_"&amp;IF($C49="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:18">
+    <row r="50" spans="1:19">
       <c r="A50" s="5"/>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -2540,20 +2587,21 @@
       <c r="M50" s="5"/>
       <c r="N50" s="5"/>
       <c r="O50" s="5"/>
-      <c r="P50" s="8">
-        <f>IF(COUNTA($A50:$D50,G50:N50)=0,"",IF($A50="","Nedostaje godište",IF($E50="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B50="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B50&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C50="","Nedostaje pol",IF($D50="","Nedostaje pojas",IF(COUNTA(G50:N50)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G50:N50&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E50),G50:N50)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E50,IF(AND(COUNTIF(G50:N50,"Fudokan sport kumite")&gt;0,O50=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G50:N50,"Fudokan sport kumite")=0,O50&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q50">
+      <c r="P50" s="5"/>
+      <c r="Q50" s="8">
+        <f>IF(COUNTA($A50:$D50,G50:N50,P50)=0,"",IF($A50="","Nedostaje godište",IF($E50="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B50="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B50&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C50="","Nedostaje pol",IF($D50="","Nedostaje pojas",IF(COUNTA(G50:N50)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G50:N50&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E50),G50:N50)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E50,IF(AND(COUNTIF(G50:N50,"Fudokan sport kumite")&gt;0,O50=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G50:N50,"Fudokan sport kumite")=0,O50&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P50&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P50,4))="FSS-",MID(P50,LEN(P50)-2,1)="/",ISNUMBER(VALUE(RIGHT(P50,2))),VALUE(MID(P50,5,LEN(P50)-7))&gt;=1,VALUE(MID(P50,5,LEN(P50)-7))=INT(VALUE(MID(P50,5,LEN(P50)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R50">
         <f>IF($E50="","sve_discipline","disc_"&amp;$E50)</f>
         <v/>
       </c>
-      <c r="R50">
+      <c r="S50">
         <f>IF(OR($E50="",$C50=""),"sve_kilaze","kg_"&amp;$E50&amp;"_"&amp;IF($C50="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:18">
+    <row r="51" spans="1:19">
       <c r="A51" s="5"/>
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
@@ -2575,20 +2623,21 @@
       <c r="M51" s="5"/>
       <c r="N51" s="5"/>
       <c r="O51" s="5"/>
-      <c r="P51" s="8">
-        <f>IF(COUNTA($A51:$D51,G51:N51)=0,"",IF($A51="","Nedostaje godište",IF($E51="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B51="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B51&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C51="","Nedostaje pol",IF($D51="","Nedostaje pojas",IF(COUNTA(G51:N51)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G51:N51&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E51),G51:N51)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E51,IF(AND(COUNTIF(G51:N51,"Fudokan sport kumite")&gt;0,O51=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G51:N51,"Fudokan sport kumite")=0,O51&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q51">
+      <c r="P51" s="5"/>
+      <c r="Q51" s="8">
+        <f>IF(COUNTA($A51:$D51,G51:N51,P51)=0,"",IF($A51="","Nedostaje godište",IF($E51="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B51="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B51&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C51="","Nedostaje pol",IF($D51="","Nedostaje pojas",IF(COUNTA(G51:N51)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G51:N51&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E51),G51:N51)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E51,IF(AND(COUNTIF(G51:N51,"Fudokan sport kumite")&gt;0,O51=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G51:N51,"Fudokan sport kumite")=0,O51&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P51&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P51,4))="FSS-",MID(P51,LEN(P51)-2,1)="/",ISNUMBER(VALUE(RIGHT(P51,2))),VALUE(MID(P51,5,LEN(P51)-7))&gt;=1,VALUE(MID(P51,5,LEN(P51)-7))=INT(VALUE(MID(P51,5,LEN(P51)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R51">
         <f>IF($E51="","sve_discipline","disc_"&amp;$E51)</f>
         <v/>
       </c>
-      <c r="R51">
+      <c r="S51">
         <f>IF(OR($E51="",$C51=""),"sve_kilaze","kg_"&amp;$E51&amp;"_"&amp;IF($C51="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:18">
+    <row r="52" spans="1:19">
       <c r="A52" s="5"/>
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
@@ -2610,20 +2659,21 @@
       <c r="M52" s="5"/>
       <c r="N52" s="5"/>
       <c r="O52" s="5"/>
-      <c r="P52" s="8">
-        <f>IF(COUNTA($A52:$D52,G52:N52)=0,"",IF($A52="","Nedostaje godište",IF($E52="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B52="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B52&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C52="","Nedostaje pol",IF($D52="","Nedostaje pojas",IF(COUNTA(G52:N52)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G52:N52&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E52),G52:N52)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E52,IF(AND(COUNTIF(G52:N52,"Fudokan sport kumite")&gt;0,O52=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G52:N52,"Fudokan sport kumite")=0,O52&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q52">
+      <c r="P52" s="5"/>
+      <c r="Q52" s="8">
+        <f>IF(COUNTA($A52:$D52,G52:N52,P52)=0,"",IF($A52="","Nedostaje godište",IF($E52="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B52="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B52&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C52="","Nedostaje pol",IF($D52="","Nedostaje pojas",IF(COUNTA(G52:N52)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G52:N52&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E52),G52:N52)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E52,IF(AND(COUNTIF(G52:N52,"Fudokan sport kumite")&gt;0,O52=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G52:N52,"Fudokan sport kumite")=0,O52&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P52&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P52,4))="FSS-",MID(P52,LEN(P52)-2,1)="/",ISNUMBER(VALUE(RIGHT(P52,2))),VALUE(MID(P52,5,LEN(P52)-7))&gt;=1,VALUE(MID(P52,5,LEN(P52)-7))=INT(VALUE(MID(P52,5,LEN(P52)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R52">
         <f>IF($E52="","sve_discipline","disc_"&amp;$E52)</f>
         <v/>
       </c>
-      <c r="R52">
+      <c r="S52">
         <f>IF(OR($E52="",$C52=""),"sve_kilaze","kg_"&amp;$E52&amp;"_"&amp;IF($C52="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:18">
+    <row r="53" spans="1:19">
       <c r="A53" s="5"/>
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
@@ -2645,20 +2695,21 @@
       <c r="M53" s="5"/>
       <c r="N53" s="5"/>
       <c r="O53" s="5"/>
-      <c r="P53" s="8">
-        <f>IF(COUNTA($A53:$D53,G53:N53)=0,"",IF($A53="","Nedostaje godište",IF($E53="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B53="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B53&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C53="","Nedostaje pol",IF($D53="","Nedostaje pojas",IF(COUNTA(G53:N53)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G53:N53&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E53),G53:N53)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E53,IF(AND(COUNTIF(G53:N53,"Fudokan sport kumite")&gt;0,O53=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G53:N53,"Fudokan sport kumite")=0,O53&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q53">
+      <c r="P53" s="5"/>
+      <c r="Q53" s="8">
+        <f>IF(COUNTA($A53:$D53,G53:N53,P53)=0,"",IF($A53="","Nedostaje godište",IF($E53="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B53="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B53&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C53="","Nedostaje pol",IF($D53="","Nedostaje pojas",IF(COUNTA(G53:N53)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G53:N53&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E53),G53:N53)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E53,IF(AND(COUNTIF(G53:N53,"Fudokan sport kumite")&gt;0,O53=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G53:N53,"Fudokan sport kumite")=0,O53&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P53&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P53,4))="FSS-",MID(P53,LEN(P53)-2,1)="/",ISNUMBER(VALUE(RIGHT(P53,2))),VALUE(MID(P53,5,LEN(P53)-7))&gt;=1,VALUE(MID(P53,5,LEN(P53)-7))=INT(VALUE(MID(P53,5,LEN(P53)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R53">
         <f>IF($E53="","sve_discipline","disc_"&amp;$E53)</f>
         <v/>
       </c>
-      <c r="R53">
+      <c r="S53">
         <f>IF(OR($E53="",$C53=""),"sve_kilaze","kg_"&amp;$E53&amp;"_"&amp;IF($C53="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:18">
+    <row r="54" spans="1:19">
       <c r="A54" s="5"/>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -2680,20 +2731,21 @@
       <c r="M54" s="5"/>
       <c r="N54" s="5"/>
       <c r="O54" s="5"/>
-      <c r="P54" s="8">
-        <f>IF(COUNTA($A54:$D54,G54:N54)=0,"",IF($A54="","Nedostaje godište",IF($E54="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B54="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B54&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C54="","Nedostaje pol",IF($D54="","Nedostaje pojas",IF(COUNTA(G54:N54)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G54:N54&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E54),G54:N54)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E54,IF(AND(COUNTIF(G54:N54,"Fudokan sport kumite")&gt;0,O54=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G54:N54,"Fudokan sport kumite")=0,O54&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q54">
+      <c r="P54" s="5"/>
+      <c r="Q54" s="8">
+        <f>IF(COUNTA($A54:$D54,G54:N54,P54)=0,"",IF($A54="","Nedostaje godište",IF($E54="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B54="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B54&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C54="","Nedostaje pol",IF($D54="","Nedostaje pojas",IF(COUNTA(G54:N54)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G54:N54&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E54),G54:N54)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E54,IF(AND(COUNTIF(G54:N54,"Fudokan sport kumite")&gt;0,O54=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G54:N54,"Fudokan sport kumite")=0,O54&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P54&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P54,4))="FSS-",MID(P54,LEN(P54)-2,1)="/",ISNUMBER(VALUE(RIGHT(P54,2))),VALUE(MID(P54,5,LEN(P54)-7))&gt;=1,VALUE(MID(P54,5,LEN(P54)-7))=INT(VALUE(MID(P54,5,LEN(P54)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R54">
         <f>IF($E54="","sve_discipline","disc_"&amp;$E54)</f>
         <v/>
       </c>
-      <c r="R54">
+      <c r="S54">
         <f>IF(OR($E54="",$C54=""),"sve_kilaze","kg_"&amp;$E54&amp;"_"&amp;IF($C54="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:18">
+    <row r="55" spans="1:19">
       <c r="A55" s="5"/>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -2715,20 +2767,21 @@
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
       <c r="O55" s="5"/>
-      <c r="P55" s="8">
-        <f>IF(COUNTA($A55:$D55,G55:N55)=0,"",IF($A55="","Nedostaje godište",IF($E55="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B55="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B55&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C55="","Nedostaje pol",IF($D55="","Nedostaje pojas",IF(COUNTA(G55:N55)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G55:N55&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E55),G55:N55)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E55,IF(AND(COUNTIF(G55:N55,"Fudokan sport kumite")&gt;0,O55=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G55:N55,"Fudokan sport kumite")=0,O55&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q55">
+      <c r="P55" s="5"/>
+      <c r="Q55" s="8">
+        <f>IF(COUNTA($A55:$D55,G55:N55,P55)=0,"",IF($A55="","Nedostaje godište",IF($E55="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B55="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B55&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C55="","Nedostaje pol",IF($D55="","Nedostaje pojas",IF(COUNTA(G55:N55)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G55:N55&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E55),G55:N55)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E55,IF(AND(COUNTIF(G55:N55,"Fudokan sport kumite")&gt;0,O55=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G55:N55,"Fudokan sport kumite")=0,O55&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P55&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P55,4))="FSS-",MID(P55,LEN(P55)-2,1)="/",ISNUMBER(VALUE(RIGHT(P55,2))),VALUE(MID(P55,5,LEN(P55)-7))&gt;=1,VALUE(MID(P55,5,LEN(P55)-7))=INT(VALUE(MID(P55,5,LEN(P55)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R55">
         <f>IF($E55="","sve_discipline","disc_"&amp;$E55)</f>
         <v/>
       </c>
-      <c r="R55">
+      <c r="S55">
         <f>IF(OR($E55="",$C55=""),"sve_kilaze","kg_"&amp;$E55&amp;"_"&amp;IF($C55="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:18">
+    <row r="56" spans="1:19">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -2750,20 +2803,21 @@
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
       <c r="O56" s="5"/>
-      <c r="P56" s="8">
-        <f>IF(COUNTA($A56:$D56,G56:N56)=0,"",IF($A56="","Nedostaje godište",IF($E56="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B56="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B56&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C56="","Nedostaje pol",IF($D56="","Nedostaje pojas",IF(COUNTA(G56:N56)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G56:N56&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E56),G56:N56)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E56,IF(AND(COUNTIF(G56:N56,"Fudokan sport kumite")&gt;0,O56=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G56:N56,"Fudokan sport kumite")=0,O56&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q56">
+      <c r="P56" s="5"/>
+      <c r="Q56" s="8">
+        <f>IF(COUNTA($A56:$D56,G56:N56,P56)=0,"",IF($A56="","Nedostaje godište",IF($E56="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B56="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B56&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C56="","Nedostaje pol",IF($D56="","Nedostaje pojas",IF(COUNTA(G56:N56)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G56:N56&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E56),G56:N56)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E56,IF(AND(COUNTIF(G56:N56,"Fudokan sport kumite")&gt;0,O56=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G56:N56,"Fudokan sport kumite")=0,O56&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P56&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P56,4))="FSS-",MID(P56,LEN(P56)-2,1)="/",ISNUMBER(VALUE(RIGHT(P56,2))),VALUE(MID(P56,5,LEN(P56)-7))&gt;=1,VALUE(MID(P56,5,LEN(P56)-7))=INT(VALUE(MID(P56,5,LEN(P56)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R56">
         <f>IF($E56="","sve_discipline","disc_"&amp;$E56)</f>
         <v/>
       </c>
-      <c r="R56">
+      <c r="S56">
         <f>IF(OR($E56="",$C56=""),"sve_kilaze","kg_"&amp;$E56&amp;"_"&amp;IF($C56="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:18">
+    <row r="57" spans="1:19">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -2785,20 +2839,21 @@
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
       <c r="O57" s="5"/>
-      <c r="P57" s="8">
-        <f>IF(COUNTA($A57:$D57,G57:N57)=0,"",IF($A57="","Nedostaje godište",IF($E57="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B57="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B57&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C57="","Nedostaje pol",IF($D57="","Nedostaje pojas",IF(COUNTA(G57:N57)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G57:N57&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E57),G57:N57)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E57,IF(AND(COUNTIF(G57:N57,"Fudokan sport kumite")&gt;0,O57=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G57:N57,"Fudokan sport kumite")=0,O57&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q57">
+      <c r="P57" s="5"/>
+      <c r="Q57" s="8">
+        <f>IF(COUNTA($A57:$D57,G57:N57,P57)=0,"",IF($A57="","Nedostaje godište",IF($E57="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B57="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B57&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C57="","Nedostaje pol",IF($D57="","Nedostaje pojas",IF(COUNTA(G57:N57)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G57:N57&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E57),G57:N57)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E57,IF(AND(COUNTIF(G57:N57,"Fudokan sport kumite")&gt;0,O57=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G57:N57,"Fudokan sport kumite")=0,O57&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P57&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P57,4))="FSS-",MID(P57,LEN(P57)-2,1)="/",ISNUMBER(VALUE(RIGHT(P57,2))),VALUE(MID(P57,5,LEN(P57)-7))&gt;=1,VALUE(MID(P57,5,LEN(P57)-7))=INT(VALUE(MID(P57,5,LEN(P57)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R57">
         <f>IF($E57="","sve_discipline","disc_"&amp;$E57)</f>
         <v/>
       </c>
-      <c r="R57">
+      <c r="S57">
         <f>IF(OR($E57="",$C57=""),"sve_kilaze","kg_"&amp;$E57&amp;"_"&amp;IF($C57="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:18">
+    <row r="58" spans="1:19">
       <c r="A58" s="5"/>
       <c r="B58" s="5"/>
       <c r="C58" s="5"/>
@@ -2820,20 +2875,21 @@
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
       <c r="O58" s="5"/>
-      <c r="P58" s="8">
-        <f>IF(COUNTA($A58:$D58,G58:N58)=0,"",IF($A58="","Nedostaje godište",IF($E58="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B58="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B58&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C58="","Nedostaje pol",IF($D58="","Nedostaje pojas",IF(COUNTA(G58:N58)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G58:N58&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E58),G58:N58)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E58,IF(AND(COUNTIF(G58:N58,"Fudokan sport kumite")&gt;0,O58=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G58:N58,"Fudokan sport kumite")=0,O58&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q58">
+      <c r="P58" s="5"/>
+      <c r="Q58" s="8">
+        <f>IF(COUNTA($A58:$D58,G58:N58,P58)=0,"",IF($A58="","Nedostaje godište",IF($E58="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B58="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B58&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C58="","Nedostaje pol",IF($D58="","Nedostaje pojas",IF(COUNTA(G58:N58)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G58:N58&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E58),G58:N58)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E58,IF(AND(COUNTIF(G58:N58,"Fudokan sport kumite")&gt;0,O58=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G58:N58,"Fudokan sport kumite")=0,O58&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P58&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P58,4))="FSS-",MID(P58,LEN(P58)-2,1)="/",ISNUMBER(VALUE(RIGHT(P58,2))),VALUE(MID(P58,5,LEN(P58)-7))&gt;=1,VALUE(MID(P58,5,LEN(P58)-7))=INT(VALUE(MID(P58,5,LEN(P58)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R58">
         <f>IF($E58="","sve_discipline","disc_"&amp;$E58)</f>
         <v/>
       </c>
-      <c r="R58">
+      <c r="S58">
         <f>IF(OR($E58="",$C58=""),"sve_kilaze","kg_"&amp;$E58&amp;"_"&amp;IF($C58="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:18">
+    <row r="59" spans="1:19">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -2855,20 +2911,21 @@
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
       <c r="O59" s="5"/>
-      <c r="P59" s="8">
-        <f>IF(COUNTA($A59:$D59,G59:N59)=0,"",IF($A59="","Nedostaje godište",IF($E59="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B59="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B59&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C59="","Nedostaje pol",IF($D59="","Nedostaje pojas",IF(COUNTA(G59:N59)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G59:N59&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E59),G59:N59)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E59,IF(AND(COUNTIF(G59:N59,"Fudokan sport kumite")&gt;0,O59=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G59:N59,"Fudokan sport kumite")=0,O59&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q59">
+      <c r="P59" s="5"/>
+      <c r="Q59" s="8">
+        <f>IF(COUNTA($A59:$D59,G59:N59,P59)=0,"",IF($A59="","Nedostaje godište",IF($E59="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B59="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B59&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C59="","Nedostaje pol",IF($D59="","Nedostaje pojas",IF(COUNTA(G59:N59)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G59:N59&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E59),G59:N59)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E59,IF(AND(COUNTIF(G59:N59,"Fudokan sport kumite")&gt;0,O59=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G59:N59,"Fudokan sport kumite")=0,O59&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P59&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P59,4))="FSS-",MID(P59,LEN(P59)-2,1)="/",ISNUMBER(VALUE(RIGHT(P59,2))),VALUE(MID(P59,5,LEN(P59)-7))&gt;=1,VALUE(MID(P59,5,LEN(P59)-7))=INT(VALUE(MID(P59,5,LEN(P59)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R59">
         <f>IF($E59="","sve_discipline","disc_"&amp;$E59)</f>
         <v/>
       </c>
-      <c r="R59">
+      <c r="S59">
         <f>IF(OR($E59="",$C59=""),"sve_kilaze","kg_"&amp;$E59&amp;"_"&amp;IF($C59="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:18">
+    <row r="60" spans="1:19">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -2890,20 +2947,21 @@
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
       <c r="O60" s="5"/>
-      <c r="P60" s="8">
-        <f>IF(COUNTA($A60:$D60,G60:N60)=0,"",IF($A60="","Nedostaje godište",IF($E60="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B60="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B60&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C60="","Nedostaje pol",IF($D60="","Nedostaje pojas",IF(COUNTA(G60:N60)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G60:N60&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E60),G60:N60)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E60,IF(AND(COUNTIF(G60:N60,"Fudokan sport kumite")&gt;0,O60=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G60:N60,"Fudokan sport kumite")=0,O60&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q60">
+      <c r="P60" s="5"/>
+      <c r="Q60" s="8">
+        <f>IF(COUNTA($A60:$D60,G60:N60,P60)=0,"",IF($A60="","Nedostaje godište",IF($E60="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B60="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B60&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C60="","Nedostaje pol",IF($D60="","Nedostaje pojas",IF(COUNTA(G60:N60)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G60:N60&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E60),G60:N60)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E60,IF(AND(COUNTIF(G60:N60,"Fudokan sport kumite")&gt;0,O60=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G60:N60,"Fudokan sport kumite")=0,O60&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P60&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P60,4))="FSS-",MID(P60,LEN(P60)-2,1)="/",ISNUMBER(VALUE(RIGHT(P60,2))),VALUE(MID(P60,5,LEN(P60)-7))&gt;=1,VALUE(MID(P60,5,LEN(P60)-7))=INT(VALUE(MID(P60,5,LEN(P60)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R60">
         <f>IF($E60="","sve_discipline","disc_"&amp;$E60)</f>
         <v/>
       </c>
-      <c r="R60">
+      <c r="S60">
         <f>IF(OR($E60="",$C60=""),"sve_kilaze","kg_"&amp;$E60&amp;"_"&amp;IF($C60="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:18">
+    <row r="61" spans="1:19">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -2925,20 +2983,21 @@
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
       <c r="O61" s="5"/>
-      <c r="P61" s="8">
-        <f>IF(COUNTA($A61:$D61,G61:N61)=0,"",IF($A61="","Nedostaje godište",IF($E61="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B61="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B61&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C61="","Nedostaje pol",IF($D61="","Nedostaje pojas",IF(COUNTA(G61:N61)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G61:N61&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E61),G61:N61)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E61,IF(AND(COUNTIF(G61:N61,"Fudokan sport kumite")&gt;0,O61=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G61:N61,"Fudokan sport kumite")=0,O61&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q61">
+      <c r="P61" s="5"/>
+      <c r="Q61" s="8">
+        <f>IF(COUNTA($A61:$D61,G61:N61,P61)=0,"",IF($A61="","Nedostaje godište",IF($E61="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B61="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B61&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C61="","Nedostaje pol",IF($D61="","Nedostaje pojas",IF(COUNTA(G61:N61)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G61:N61&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E61),G61:N61)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E61,IF(AND(COUNTIF(G61:N61,"Fudokan sport kumite")&gt;0,O61=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G61:N61,"Fudokan sport kumite")=0,O61&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P61&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P61,4))="FSS-",MID(P61,LEN(P61)-2,1)="/",ISNUMBER(VALUE(RIGHT(P61,2))),VALUE(MID(P61,5,LEN(P61)-7))&gt;=1,VALUE(MID(P61,5,LEN(P61)-7))=INT(VALUE(MID(P61,5,LEN(P61)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R61">
         <f>IF($E61="","sve_discipline","disc_"&amp;$E61)</f>
         <v/>
       </c>
-      <c r="R61">
+      <c r="S61">
         <f>IF(OR($E61="",$C61=""),"sve_kilaze","kg_"&amp;$E61&amp;"_"&amp;IF($C61="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:18">
+    <row r="62" spans="1:19">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -2960,20 +3019,21 @@
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
       <c r="O62" s="5"/>
-      <c r="P62" s="8">
-        <f>IF(COUNTA($A62:$D62,G62:N62)=0,"",IF($A62="","Nedostaje godište",IF($E62="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B62="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B62&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C62="","Nedostaje pol",IF($D62="","Nedostaje pojas",IF(COUNTA(G62:N62)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G62:N62&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E62),G62:N62)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E62,IF(AND(COUNTIF(G62:N62,"Fudokan sport kumite")&gt;0,O62=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G62:N62,"Fudokan sport kumite")=0,O62&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q62">
+      <c r="P62" s="5"/>
+      <c r="Q62" s="8">
+        <f>IF(COUNTA($A62:$D62,G62:N62,P62)=0,"",IF($A62="","Nedostaje godište",IF($E62="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B62="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B62&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C62="","Nedostaje pol",IF($D62="","Nedostaje pojas",IF(COUNTA(G62:N62)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G62:N62&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E62),G62:N62)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E62,IF(AND(COUNTIF(G62:N62,"Fudokan sport kumite")&gt;0,O62=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G62:N62,"Fudokan sport kumite")=0,O62&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P62&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P62,4))="FSS-",MID(P62,LEN(P62)-2,1)="/",ISNUMBER(VALUE(RIGHT(P62,2))),VALUE(MID(P62,5,LEN(P62)-7))&gt;=1,VALUE(MID(P62,5,LEN(P62)-7))=INT(VALUE(MID(P62,5,LEN(P62)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R62">
         <f>IF($E62="","sve_discipline","disc_"&amp;$E62)</f>
         <v/>
       </c>
-      <c r="R62">
+      <c r="S62">
         <f>IF(OR($E62="",$C62=""),"sve_kilaze","kg_"&amp;$E62&amp;"_"&amp;IF($C62="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:18">
+    <row r="63" spans="1:19">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -2995,20 +3055,21 @@
       <c r="M63" s="5"/>
       <c r="N63" s="5"/>
       <c r="O63" s="5"/>
-      <c r="P63" s="8">
-        <f>IF(COUNTA($A63:$D63,G63:N63)=0,"",IF($A63="","Nedostaje godište",IF($E63="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B63="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B63&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C63="","Nedostaje pol",IF($D63="","Nedostaje pojas",IF(COUNTA(G63:N63)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G63:N63&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E63),G63:N63)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E63,IF(AND(COUNTIF(G63:N63,"Fudokan sport kumite")&gt;0,O63=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G63:N63,"Fudokan sport kumite")=0,O63&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q63">
+      <c r="P63" s="5"/>
+      <c r="Q63" s="8">
+        <f>IF(COUNTA($A63:$D63,G63:N63,P63)=0,"",IF($A63="","Nedostaje godište",IF($E63="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B63="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B63&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C63="","Nedostaje pol",IF($D63="","Nedostaje pojas",IF(COUNTA(G63:N63)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G63:N63&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E63),G63:N63)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E63,IF(AND(COUNTIF(G63:N63,"Fudokan sport kumite")&gt;0,O63=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G63:N63,"Fudokan sport kumite")=0,O63&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P63&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P63,4))="FSS-",MID(P63,LEN(P63)-2,1)="/",ISNUMBER(VALUE(RIGHT(P63,2))),VALUE(MID(P63,5,LEN(P63)-7))&gt;=1,VALUE(MID(P63,5,LEN(P63)-7))=INT(VALUE(MID(P63,5,LEN(P63)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R63">
         <f>IF($E63="","sve_discipline","disc_"&amp;$E63)</f>
         <v/>
       </c>
-      <c r="R63">
+      <c r="S63">
         <f>IF(OR($E63="",$C63=""),"sve_kilaze","kg_"&amp;$E63&amp;"_"&amp;IF($C63="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:18">
+    <row r="64" spans="1:19">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -3030,20 +3091,21 @@
       <c r="M64" s="5"/>
       <c r="N64" s="5"/>
       <c r="O64" s="5"/>
-      <c r="P64" s="8">
-        <f>IF(COUNTA($A64:$D64,G64:N64)=0,"",IF($A64="","Nedostaje godište",IF($E64="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B64="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B64&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C64="","Nedostaje pol",IF($D64="","Nedostaje pojas",IF(COUNTA(G64:N64)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G64:N64&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E64),G64:N64)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E64,IF(AND(COUNTIF(G64:N64,"Fudokan sport kumite")&gt;0,O64=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G64:N64,"Fudokan sport kumite")=0,O64&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q64">
+      <c r="P64" s="5"/>
+      <c r="Q64" s="8">
+        <f>IF(COUNTA($A64:$D64,G64:N64,P64)=0,"",IF($A64="","Nedostaje godište",IF($E64="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B64="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B64&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C64="","Nedostaje pol",IF($D64="","Nedostaje pojas",IF(COUNTA(G64:N64)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G64:N64&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E64),G64:N64)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E64,IF(AND(COUNTIF(G64:N64,"Fudokan sport kumite")&gt;0,O64=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G64:N64,"Fudokan sport kumite")=0,O64&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P64&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P64,4))="FSS-",MID(P64,LEN(P64)-2,1)="/",ISNUMBER(VALUE(RIGHT(P64,2))),VALUE(MID(P64,5,LEN(P64)-7))&gt;=1,VALUE(MID(P64,5,LEN(P64)-7))=INT(VALUE(MID(P64,5,LEN(P64)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R64">
         <f>IF($E64="","sve_discipline","disc_"&amp;$E64)</f>
         <v/>
       </c>
-      <c r="R64">
+      <c r="S64">
         <f>IF(OR($E64="",$C64=""),"sve_kilaze","kg_"&amp;$E64&amp;"_"&amp;IF($C64="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:18">
+    <row r="65" spans="1:19">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -3065,20 +3127,21 @@
       <c r="M65" s="5"/>
       <c r="N65" s="5"/>
       <c r="O65" s="5"/>
-      <c r="P65" s="8">
-        <f>IF(COUNTA($A65:$D65,G65:N65)=0,"",IF($A65="","Nedostaje godište",IF($E65="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B65="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B65&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C65="","Nedostaje pol",IF($D65="","Nedostaje pojas",IF(COUNTA(G65:N65)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G65:N65&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E65),G65:N65)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E65,IF(AND(COUNTIF(G65:N65,"Fudokan sport kumite")&gt;0,O65=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G65:N65,"Fudokan sport kumite")=0,O65&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q65">
+      <c r="P65" s="5"/>
+      <c r="Q65" s="8">
+        <f>IF(COUNTA($A65:$D65,G65:N65,P65)=0,"",IF($A65="","Nedostaje godište",IF($E65="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B65="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B65&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C65="","Nedostaje pol",IF($D65="","Nedostaje pojas",IF(COUNTA(G65:N65)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G65:N65&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E65),G65:N65)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E65,IF(AND(COUNTIF(G65:N65,"Fudokan sport kumite")&gt;0,O65=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G65:N65,"Fudokan sport kumite")=0,O65&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P65&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P65,4))="FSS-",MID(P65,LEN(P65)-2,1)="/",ISNUMBER(VALUE(RIGHT(P65,2))),VALUE(MID(P65,5,LEN(P65)-7))&gt;=1,VALUE(MID(P65,5,LEN(P65)-7))=INT(VALUE(MID(P65,5,LEN(P65)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R65">
         <f>IF($E65="","sve_discipline","disc_"&amp;$E65)</f>
         <v/>
       </c>
-      <c r="R65">
+      <c r="S65">
         <f>IF(OR($E65="",$C65=""),"sve_kilaze","kg_"&amp;$E65&amp;"_"&amp;IF($C65="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:18">
+    <row r="66" spans="1:19">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -3100,20 +3163,21 @@
       <c r="M66" s="5"/>
       <c r="N66" s="5"/>
       <c r="O66" s="5"/>
-      <c r="P66" s="8">
-        <f>IF(COUNTA($A66:$D66,G66:N66)=0,"",IF($A66="","Nedostaje godište",IF($E66="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B66="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B66&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C66="","Nedostaje pol",IF($D66="","Nedostaje pojas",IF(COUNTA(G66:N66)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G66:N66&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E66),G66:N66)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E66,IF(AND(COUNTIF(G66:N66,"Fudokan sport kumite")&gt;0,O66=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G66:N66,"Fudokan sport kumite")=0,O66&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q66">
+      <c r="P66" s="5"/>
+      <c r="Q66" s="8">
+        <f>IF(COUNTA($A66:$D66,G66:N66,P66)=0,"",IF($A66="","Nedostaje godište",IF($E66="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B66="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B66&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C66="","Nedostaje pol",IF($D66="","Nedostaje pojas",IF(COUNTA(G66:N66)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G66:N66&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E66),G66:N66)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E66,IF(AND(COUNTIF(G66:N66,"Fudokan sport kumite")&gt;0,O66=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G66:N66,"Fudokan sport kumite")=0,O66&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P66&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P66,4))="FSS-",MID(P66,LEN(P66)-2,1)="/",ISNUMBER(VALUE(RIGHT(P66,2))),VALUE(MID(P66,5,LEN(P66)-7))&gt;=1,VALUE(MID(P66,5,LEN(P66)-7))=INT(VALUE(MID(P66,5,LEN(P66)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R66">
         <f>IF($E66="","sve_discipline","disc_"&amp;$E66)</f>
         <v/>
       </c>
-      <c r="R66">
+      <c r="S66">
         <f>IF(OR($E66="",$C66=""),"sve_kilaze","kg_"&amp;$E66&amp;"_"&amp;IF($C66="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:18">
+    <row r="67" spans="1:19">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -3135,20 +3199,21 @@
       <c r="M67" s="5"/>
       <c r="N67" s="5"/>
       <c r="O67" s="5"/>
-      <c r="P67" s="8">
-        <f>IF(COUNTA($A67:$D67,G67:N67)=0,"",IF($A67="","Nedostaje godište",IF($E67="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B67="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B67&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C67="","Nedostaje pol",IF($D67="","Nedostaje pojas",IF(COUNTA(G67:N67)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G67:N67&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E67),G67:N67)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E67,IF(AND(COUNTIF(G67:N67,"Fudokan sport kumite")&gt;0,O67=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G67:N67,"Fudokan sport kumite")=0,O67&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q67">
+      <c r="P67" s="5"/>
+      <c r="Q67" s="8">
+        <f>IF(COUNTA($A67:$D67,G67:N67,P67)=0,"",IF($A67="","Nedostaje godište",IF($E67="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B67="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B67&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C67="","Nedostaje pol",IF($D67="","Nedostaje pojas",IF(COUNTA(G67:N67)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G67:N67&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E67),G67:N67)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E67,IF(AND(COUNTIF(G67:N67,"Fudokan sport kumite")&gt;0,O67=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G67:N67,"Fudokan sport kumite")=0,O67&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P67&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P67,4))="FSS-",MID(P67,LEN(P67)-2,1)="/",ISNUMBER(VALUE(RIGHT(P67,2))),VALUE(MID(P67,5,LEN(P67)-7))&gt;=1,VALUE(MID(P67,5,LEN(P67)-7))=INT(VALUE(MID(P67,5,LEN(P67)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R67">
         <f>IF($E67="","sve_discipline","disc_"&amp;$E67)</f>
         <v/>
       </c>
-      <c r="R67">
+      <c r="S67">
         <f>IF(OR($E67="",$C67=""),"sve_kilaze","kg_"&amp;$E67&amp;"_"&amp;IF($C67="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:18">
+    <row r="68" spans="1:19">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -3170,20 +3235,21 @@
       <c r="M68" s="5"/>
       <c r="N68" s="5"/>
       <c r="O68" s="5"/>
-      <c r="P68" s="8">
-        <f>IF(COUNTA($A68:$D68,G68:N68)=0,"",IF($A68="","Nedostaje godište",IF($E68="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B68="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B68&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C68="","Nedostaje pol",IF($D68="","Nedostaje pojas",IF(COUNTA(G68:N68)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G68:N68&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E68),G68:N68)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E68,IF(AND(COUNTIF(G68:N68,"Fudokan sport kumite")&gt;0,O68=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G68:N68,"Fudokan sport kumite")=0,O68&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q68">
+      <c r="P68" s="5"/>
+      <c r="Q68" s="8">
+        <f>IF(COUNTA($A68:$D68,G68:N68,P68)=0,"",IF($A68="","Nedostaje godište",IF($E68="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B68="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B68&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C68="","Nedostaje pol",IF($D68="","Nedostaje pojas",IF(COUNTA(G68:N68)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G68:N68&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E68),G68:N68)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E68,IF(AND(COUNTIF(G68:N68,"Fudokan sport kumite")&gt;0,O68=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G68:N68,"Fudokan sport kumite")=0,O68&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P68&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P68,4))="FSS-",MID(P68,LEN(P68)-2,1)="/",ISNUMBER(VALUE(RIGHT(P68,2))),VALUE(MID(P68,5,LEN(P68)-7))&gt;=1,VALUE(MID(P68,5,LEN(P68)-7))=INT(VALUE(MID(P68,5,LEN(P68)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R68">
         <f>IF($E68="","sve_discipline","disc_"&amp;$E68)</f>
         <v/>
       </c>
-      <c r="R68">
+      <c r="S68">
         <f>IF(OR($E68="",$C68=""),"sve_kilaze","kg_"&amp;$E68&amp;"_"&amp;IF($C68="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:18">
+    <row r="69" spans="1:19">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -3205,20 +3271,21 @@
       <c r="M69" s="5"/>
       <c r="N69" s="5"/>
       <c r="O69" s="5"/>
-      <c r="P69" s="8">
-        <f>IF(COUNTA($A69:$D69,G69:N69)=0,"",IF($A69="","Nedostaje godište",IF($E69="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B69="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B69&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C69="","Nedostaje pol",IF($D69="","Nedostaje pojas",IF(COUNTA(G69:N69)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G69:N69&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E69),G69:N69)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E69,IF(AND(COUNTIF(G69:N69,"Fudokan sport kumite")&gt;0,O69=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G69:N69,"Fudokan sport kumite")=0,O69&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q69">
+      <c r="P69" s="5"/>
+      <c r="Q69" s="8">
+        <f>IF(COUNTA($A69:$D69,G69:N69,P69)=0,"",IF($A69="","Nedostaje godište",IF($E69="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B69="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B69&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C69="","Nedostaje pol",IF($D69="","Nedostaje pojas",IF(COUNTA(G69:N69)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G69:N69&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E69),G69:N69)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E69,IF(AND(COUNTIF(G69:N69,"Fudokan sport kumite")&gt;0,O69=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G69:N69,"Fudokan sport kumite")=0,O69&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P69&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P69,4))="FSS-",MID(P69,LEN(P69)-2,1)="/",ISNUMBER(VALUE(RIGHT(P69,2))),VALUE(MID(P69,5,LEN(P69)-7))&gt;=1,VALUE(MID(P69,5,LEN(P69)-7))=INT(VALUE(MID(P69,5,LEN(P69)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R69">
         <f>IF($E69="","sve_discipline","disc_"&amp;$E69)</f>
         <v/>
       </c>
-      <c r="R69">
+      <c r="S69">
         <f>IF(OR($E69="",$C69=""),"sve_kilaze","kg_"&amp;$E69&amp;"_"&amp;IF($C69="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:18">
+    <row r="70" spans="1:19">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -3240,20 +3307,21 @@
       <c r="M70" s="5"/>
       <c r="N70" s="5"/>
       <c r="O70" s="5"/>
-      <c r="P70" s="8">
-        <f>IF(COUNTA($A70:$D70,G70:N70)=0,"",IF($A70="","Nedostaje godište",IF($E70="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B70="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B70&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C70="","Nedostaje pol",IF($D70="","Nedostaje pojas",IF(COUNTA(G70:N70)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G70:N70&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E70),G70:N70)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E70,IF(AND(COUNTIF(G70:N70,"Fudokan sport kumite")&gt;0,O70=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G70:N70,"Fudokan sport kumite")=0,O70&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q70">
+      <c r="P70" s="5"/>
+      <c r="Q70" s="8">
+        <f>IF(COUNTA($A70:$D70,G70:N70,P70)=0,"",IF($A70="","Nedostaje godište",IF($E70="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B70="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B70&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C70="","Nedostaje pol",IF($D70="","Nedostaje pojas",IF(COUNTA(G70:N70)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G70:N70&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E70),G70:N70)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E70,IF(AND(COUNTIF(G70:N70,"Fudokan sport kumite")&gt;0,O70=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G70:N70,"Fudokan sport kumite")=0,O70&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P70&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P70,4))="FSS-",MID(P70,LEN(P70)-2,1)="/",ISNUMBER(VALUE(RIGHT(P70,2))),VALUE(MID(P70,5,LEN(P70)-7))&gt;=1,VALUE(MID(P70,5,LEN(P70)-7))=INT(VALUE(MID(P70,5,LEN(P70)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R70">
         <f>IF($E70="","sve_discipline","disc_"&amp;$E70)</f>
         <v/>
       </c>
-      <c r="R70">
+      <c r="S70">
         <f>IF(OR($E70="",$C70=""),"sve_kilaze","kg_"&amp;$E70&amp;"_"&amp;IF($C70="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:18">
+    <row r="71" spans="1:19">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -3275,20 +3343,21 @@
       <c r="M71" s="5"/>
       <c r="N71" s="5"/>
       <c r="O71" s="5"/>
-      <c r="P71" s="8">
-        <f>IF(COUNTA($A71:$D71,G71:N71)=0,"",IF($A71="","Nedostaje godište",IF($E71="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B71="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B71&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C71="","Nedostaje pol",IF($D71="","Nedostaje pojas",IF(COUNTA(G71:N71)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G71:N71&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E71),G71:N71)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E71,IF(AND(COUNTIF(G71:N71,"Fudokan sport kumite")&gt;0,O71=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G71:N71,"Fudokan sport kumite")=0,O71&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q71">
+      <c r="P71" s="5"/>
+      <c r="Q71" s="8">
+        <f>IF(COUNTA($A71:$D71,G71:N71,P71)=0,"",IF($A71="","Nedostaje godište",IF($E71="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B71="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B71&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C71="","Nedostaje pol",IF($D71="","Nedostaje pojas",IF(COUNTA(G71:N71)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G71:N71&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E71),G71:N71)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E71,IF(AND(COUNTIF(G71:N71,"Fudokan sport kumite")&gt;0,O71=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G71:N71,"Fudokan sport kumite")=0,O71&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P71&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P71,4))="FSS-",MID(P71,LEN(P71)-2,1)="/",ISNUMBER(VALUE(RIGHT(P71,2))),VALUE(MID(P71,5,LEN(P71)-7))&gt;=1,VALUE(MID(P71,5,LEN(P71)-7))=INT(VALUE(MID(P71,5,LEN(P71)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R71">
         <f>IF($E71="","sve_discipline","disc_"&amp;$E71)</f>
         <v/>
       </c>
-      <c r="R71">
+      <c r="S71">
         <f>IF(OR($E71="",$C71=""),"sve_kilaze","kg_"&amp;$E71&amp;"_"&amp;IF($C71="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:18">
+    <row r="72" spans="1:19">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -3310,20 +3379,21 @@
       <c r="M72" s="5"/>
       <c r="N72" s="5"/>
       <c r="O72" s="5"/>
-      <c r="P72" s="8">
-        <f>IF(COUNTA($A72:$D72,G72:N72)=0,"",IF($A72="","Nedostaje godište",IF($E72="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B72="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B72&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C72="","Nedostaje pol",IF($D72="","Nedostaje pojas",IF(COUNTA(G72:N72)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G72:N72&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E72),G72:N72)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E72,IF(AND(COUNTIF(G72:N72,"Fudokan sport kumite")&gt;0,O72=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G72:N72,"Fudokan sport kumite")=0,O72&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q72">
+      <c r="P72" s="5"/>
+      <c r="Q72" s="8">
+        <f>IF(COUNTA($A72:$D72,G72:N72,P72)=0,"",IF($A72="","Nedostaje godište",IF($E72="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B72="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B72&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C72="","Nedostaje pol",IF($D72="","Nedostaje pojas",IF(COUNTA(G72:N72)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G72:N72&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E72),G72:N72)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E72,IF(AND(COUNTIF(G72:N72,"Fudokan sport kumite")&gt;0,O72=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G72:N72,"Fudokan sport kumite")=0,O72&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P72&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P72,4))="FSS-",MID(P72,LEN(P72)-2,1)="/",ISNUMBER(VALUE(RIGHT(P72,2))),VALUE(MID(P72,5,LEN(P72)-7))&gt;=1,VALUE(MID(P72,5,LEN(P72)-7))=INT(VALUE(MID(P72,5,LEN(P72)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R72">
         <f>IF($E72="","sve_discipline","disc_"&amp;$E72)</f>
         <v/>
       </c>
-      <c r="R72">
+      <c r="S72">
         <f>IF(OR($E72="",$C72=""),"sve_kilaze","kg_"&amp;$E72&amp;"_"&amp;IF($C72="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:18">
+    <row r="73" spans="1:19">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -3345,20 +3415,21 @@
       <c r="M73" s="5"/>
       <c r="N73" s="5"/>
       <c r="O73" s="5"/>
-      <c r="P73" s="8">
-        <f>IF(COUNTA($A73:$D73,G73:N73)=0,"",IF($A73="","Nedostaje godište",IF($E73="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B73="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B73&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C73="","Nedostaje pol",IF($D73="","Nedostaje pojas",IF(COUNTA(G73:N73)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G73:N73&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E73),G73:N73)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E73,IF(AND(COUNTIF(G73:N73,"Fudokan sport kumite")&gt;0,O73=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G73:N73,"Fudokan sport kumite")=0,O73&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q73">
+      <c r="P73" s="5"/>
+      <c r="Q73" s="8">
+        <f>IF(COUNTA($A73:$D73,G73:N73,P73)=0,"",IF($A73="","Nedostaje godište",IF($E73="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B73="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B73&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C73="","Nedostaje pol",IF($D73="","Nedostaje pojas",IF(COUNTA(G73:N73)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G73:N73&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E73),G73:N73)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E73,IF(AND(COUNTIF(G73:N73,"Fudokan sport kumite")&gt;0,O73=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G73:N73,"Fudokan sport kumite")=0,O73&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P73&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P73,4))="FSS-",MID(P73,LEN(P73)-2,1)="/",ISNUMBER(VALUE(RIGHT(P73,2))),VALUE(MID(P73,5,LEN(P73)-7))&gt;=1,VALUE(MID(P73,5,LEN(P73)-7))=INT(VALUE(MID(P73,5,LEN(P73)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R73">
         <f>IF($E73="","sve_discipline","disc_"&amp;$E73)</f>
         <v/>
       </c>
-      <c r="R73">
+      <c r="S73">
         <f>IF(OR($E73="",$C73=""),"sve_kilaze","kg_"&amp;$E73&amp;"_"&amp;IF($C73="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:18">
+    <row r="74" spans="1:19">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -3380,20 +3451,21 @@
       <c r="M74" s="5"/>
       <c r="N74" s="5"/>
       <c r="O74" s="5"/>
-      <c r="P74" s="8">
-        <f>IF(COUNTA($A74:$D74,G74:N74)=0,"",IF($A74="","Nedostaje godište",IF($E74="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B74="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B74&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C74="","Nedostaje pol",IF($D74="","Nedostaje pojas",IF(COUNTA(G74:N74)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G74:N74&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E74),G74:N74)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E74,IF(AND(COUNTIF(G74:N74,"Fudokan sport kumite")&gt;0,O74=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G74:N74,"Fudokan sport kumite")=0,O74&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q74">
+      <c r="P74" s="5"/>
+      <c r="Q74" s="8">
+        <f>IF(COUNTA($A74:$D74,G74:N74,P74)=0,"",IF($A74="","Nedostaje godište",IF($E74="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B74="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B74&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C74="","Nedostaje pol",IF($D74="","Nedostaje pojas",IF(COUNTA(G74:N74)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G74:N74&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E74),G74:N74)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E74,IF(AND(COUNTIF(G74:N74,"Fudokan sport kumite")&gt;0,O74=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G74:N74,"Fudokan sport kumite")=0,O74&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P74&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P74,4))="FSS-",MID(P74,LEN(P74)-2,1)="/",ISNUMBER(VALUE(RIGHT(P74,2))),VALUE(MID(P74,5,LEN(P74)-7))&gt;=1,VALUE(MID(P74,5,LEN(P74)-7))=INT(VALUE(MID(P74,5,LEN(P74)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R74">
         <f>IF($E74="","sve_discipline","disc_"&amp;$E74)</f>
         <v/>
       </c>
-      <c r="R74">
+      <c r="S74">
         <f>IF(OR($E74="",$C74=""),"sve_kilaze","kg_"&amp;$E74&amp;"_"&amp;IF($C74="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:18">
+    <row r="75" spans="1:19">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -3415,20 +3487,21 @@
       <c r="M75" s="5"/>
       <c r="N75" s="5"/>
       <c r="O75" s="5"/>
-      <c r="P75" s="8">
-        <f>IF(COUNTA($A75:$D75,G75:N75)=0,"",IF($A75="","Nedostaje godište",IF($E75="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B75="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B75&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C75="","Nedostaje pol",IF($D75="","Nedostaje pojas",IF(COUNTA(G75:N75)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G75:N75&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E75),G75:N75)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E75,IF(AND(COUNTIF(G75:N75,"Fudokan sport kumite")&gt;0,O75=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G75:N75,"Fudokan sport kumite")=0,O75&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q75">
+      <c r="P75" s="5"/>
+      <c r="Q75" s="8">
+        <f>IF(COUNTA($A75:$D75,G75:N75,P75)=0,"",IF($A75="","Nedostaje godište",IF($E75="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B75="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B75&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C75="","Nedostaje pol",IF($D75="","Nedostaje pojas",IF(COUNTA(G75:N75)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G75:N75&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E75),G75:N75)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E75,IF(AND(COUNTIF(G75:N75,"Fudokan sport kumite")&gt;0,O75=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G75:N75,"Fudokan sport kumite")=0,O75&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P75&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P75,4))="FSS-",MID(P75,LEN(P75)-2,1)="/",ISNUMBER(VALUE(RIGHT(P75,2))),VALUE(MID(P75,5,LEN(P75)-7))&gt;=1,VALUE(MID(P75,5,LEN(P75)-7))=INT(VALUE(MID(P75,5,LEN(P75)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R75">
         <f>IF($E75="","sve_discipline","disc_"&amp;$E75)</f>
         <v/>
       </c>
-      <c r="R75">
+      <c r="S75">
         <f>IF(OR($E75="",$C75=""),"sve_kilaze","kg_"&amp;$E75&amp;"_"&amp;IF($C75="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:18">
+    <row r="76" spans="1:19">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -3450,20 +3523,21 @@
       <c r="M76" s="5"/>
       <c r="N76" s="5"/>
       <c r="O76" s="5"/>
-      <c r="P76" s="8">
-        <f>IF(COUNTA($A76:$D76,G76:N76)=0,"",IF($A76="","Nedostaje godište",IF($E76="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B76="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B76&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C76="","Nedostaje pol",IF($D76="","Nedostaje pojas",IF(COUNTA(G76:N76)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G76:N76&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E76),G76:N76)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E76,IF(AND(COUNTIF(G76:N76,"Fudokan sport kumite")&gt;0,O76=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G76:N76,"Fudokan sport kumite")=0,O76&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q76">
+      <c r="P76" s="5"/>
+      <c r="Q76" s="8">
+        <f>IF(COUNTA($A76:$D76,G76:N76,P76)=0,"",IF($A76="","Nedostaje godište",IF($E76="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B76="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B76&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C76="","Nedostaje pol",IF($D76="","Nedostaje pojas",IF(COUNTA(G76:N76)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G76:N76&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E76),G76:N76)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E76,IF(AND(COUNTIF(G76:N76,"Fudokan sport kumite")&gt;0,O76=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G76:N76,"Fudokan sport kumite")=0,O76&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P76&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P76,4))="FSS-",MID(P76,LEN(P76)-2,1)="/",ISNUMBER(VALUE(RIGHT(P76,2))),VALUE(MID(P76,5,LEN(P76)-7))&gt;=1,VALUE(MID(P76,5,LEN(P76)-7))=INT(VALUE(MID(P76,5,LEN(P76)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R76">
         <f>IF($E76="","sve_discipline","disc_"&amp;$E76)</f>
         <v/>
       </c>
-      <c r="R76">
+      <c r="S76">
         <f>IF(OR($E76="",$C76=""),"sve_kilaze","kg_"&amp;$E76&amp;"_"&amp;IF($C76="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:18">
+    <row r="77" spans="1:19">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -3485,20 +3559,21 @@
       <c r="M77" s="5"/>
       <c r="N77" s="5"/>
       <c r="O77" s="5"/>
-      <c r="P77" s="8">
-        <f>IF(COUNTA($A77:$D77,G77:N77)=0,"",IF($A77="","Nedostaje godište",IF($E77="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B77="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B77&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C77="","Nedostaje pol",IF($D77="","Nedostaje pojas",IF(COUNTA(G77:N77)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G77:N77&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E77),G77:N77)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E77,IF(AND(COUNTIF(G77:N77,"Fudokan sport kumite")&gt;0,O77=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G77:N77,"Fudokan sport kumite")=0,O77&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q77">
+      <c r="P77" s="5"/>
+      <c r="Q77" s="8">
+        <f>IF(COUNTA($A77:$D77,G77:N77,P77)=0,"",IF($A77="","Nedostaje godište",IF($E77="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B77="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B77&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C77="","Nedostaje pol",IF($D77="","Nedostaje pojas",IF(COUNTA(G77:N77)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G77:N77&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E77),G77:N77)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E77,IF(AND(COUNTIF(G77:N77,"Fudokan sport kumite")&gt;0,O77=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G77:N77,"Fudokan sport kumite")=0,O77&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P77&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P77,4))="FSS-",MID(P77,LEN(P77)-2,1)="/",ISNUMBER(VALUE(RIGHT(P77,2))),VALUE(MID(P77,5,LEN(P77)-7))&gt;=1,VALUE(MID(P77,5,LEN(P77)-7))=INT(VALUE(MID(P77,5,LEN(P77)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R77">
         <f>IF($E77="","sve_discipline","disc_"&amp;$E77)</f>
         <v/>
       </c>
-      <c r="R77">
+      <c r="S77">
         <f>IF(OR($E77="",$C77=""),"sve_kilaze","kg_"&amp;$E77&amp;"_"&amp;IF($C77="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:18">
+    <row r="78" spans="1:19">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -3520,20 +3595,21 @@
       <c r="M78" s="5"/>
       <c r="N78" s="5"/>
       <c r="O78" s="5"/>
-      <c r="P78" s="8">
-        <f>IF(COUNTA($A78:$D78,G78:N78)=0,"",IF($A78="","Nedostaje godište",IF($E78="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B78="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B78&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C78="","Nedostaje pol",IF($D78="","Nedostaje pojas",IF(COUNTA(G78:N78)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G78:N78&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E78),G78:N78)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E78,IF(AND(COUNTIF(G78:N78,"Fudokan sport kumite")&gt;0,O78=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G78:N78,"Fudokan sport kumite")=0,O78&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q78">
+      <c r="P78" s="5"/>
+      <c r="Q78" s="8">
+        <f>IF(COUNTA($A78:$D78,G78:N78,P78)=0,"",IF($A78="","Nedostaje godište",IF($E78="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B78="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B78&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C78="","Nedostaje pol",IF($D78="","Nedostaje pojas",IF(COUNTA(G78:N78)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G78:N78&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E78),G78:N78)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E78,IF(AND(COUNTIF(G78:N78,"Fudokan sport kumite")&gt;0,O78=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G78:N78,"Fudokan sport kumite")=0,O78&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P78&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P78,4))="FSS-",MID(P78,LEN(P78)-2,1)="/",ISNUMBER(VALUE(RIGHT(P78,2))),VALUE(MID(P78,5,LEN(P78)-7))&gt;=1,VALUE(MID(P78,5,LEN(P78)-7))=INT(VALUE(MID(P78,5,LEN(P78)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R78">
         <f>IF($E78="","sve_discipline","disc_"&amp;$E78)</f>
         <v/>
       </c>
-      <c r="R78">
+      <c r="S78">
         <f>IF(OR($E78="",$C78=""),"sve_kilaze","kg_"&amp;$E78&amp;"_"&amp;IF($C78="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:18">
+    <row r="79" spans="1:19">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -3555,20 +3631,21 @@
       <c r="M79" s="5"/>
       <c r="N79" s="5"/>
       <c r="O79" s="5"/>
-      <c r="P79" s="8">
-        <f>IF(COUNTA($A79:$D79,G79:N79)=0,"",IF($A79="","Nedostaje godište",IF($E79="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B79="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B79&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C79="","Nedostaje pol",IF($D79="","Nedostaje pojas",IF(COUNTA(G79:N79)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G79:N79&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E79),G79:N79)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E79,IF(AND(COUNTIF(G79:N79,"Fudokan sport kumite")&gt;0,O79=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G79:N79,"Fudokan sport kumite")=0,O79&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q79">
+      <c r="P79" s="5"/>
+      <c r="Q79" s="8">
+        <f>IF(COUNTA($A79:$D79,G79:N79,P79)=0,"",IF($A79="","Nedostaje godište",IF($E79="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B79="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B79&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C79="","Nedostaje pol",IF($D79="","Nedostaje pojas",IF(COUNTA(G79:N79)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G79:N79&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E79),G79:N79)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E79,IF(AND(COUNTIF(G79:N79,"Fudokan sport kumite")&gt;0,O79=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G79:N79,"Fudokan sport kumite")=0,O79&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P79&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P79,4))="FSS-",MID(P79,LEN(P79)-2,1)="/",ISNUMBER(VALUE(RIGHT(P79,2))),VALUE(MID(P79,5,LEN(P79)-7))&gt;=1,VALUE(MID(P79,5,LEN(P79)-7))=INT(VALUE(MID(P79,5,LEN(P79)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R79">
         <f>IF($E79="","sve_discipline","disc_"&amp;$E79)</f>
         <v/>
       </c>
-      <c r="R79">
+      <c r="S79">
         <f>IF(OR($E79="",$C79=""),"sve_kilaze","kg_"&amp;$E79&amp;"_"&amp;IF($C79="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:18">
+    <row r="80" spans="1:19">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -3590,20 +3667,21 @@
       <c r="M80" s="5"/>
       <c r="N80" s="5"/>
       <c r="O80" s="5"/>
-      <c r="P80" s="8">
-        <f>IF(COUNTA($A80:$D80,G80:N80)=0,"",IF($A80="","Nedostaje godište",IF($E80="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B80="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B80&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C80="","Nedostaje pol",IF($D80="","Nedostaje pojas",IF(COUNTA(G80:N80)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G80:N80&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E80),G80:N80)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E80,IF(AND(COUNTIF(G80:N80,"Fudokan sport kumite")&gt;0,O80=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G80:N80,"Fudokan sport kumite")=0,O80&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q80">
+      <c r="P80" s="5"/>
+      <c r="Q80" s="8">
+        <f>IF(COUNTA($A80:$D80,G80:N80,P80)=0,"",IF($A80="","Nedostaje godište",IF($E80="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B80="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B80&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C80="","Nedostaje pol",IF($D80="","Nedostaje pojas",IF(COUNTA(G80:N80)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G80:N80&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E80),G80:N80)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E80,IF(AND(COUNTIF(G80:N80,"Fudokan sport kumite")&gt;0,O80=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G80:N80,"Fudokan sport kumite")=0,O80&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P80&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P80,4))="FSS-",MID(P80,LEN(P80)-2,1)="/",ISNUMBER(VALUE(RIGHT(P80,2))),VALUE(MID(P80,5,LEN(P80)-7))&gt;=1,VALUE(MID(P80,5,LEN(P80)-7))=INT(VALUE(MID(P80,5,LEN(P80)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R80">
         <f>IF($E80="","sve_discipline","disc_"&amp;$E80)</f>
         <v/>
       </c>
-      <c r="R80">
+      <c r="S80">
         <f>IF(OR($E80="",$C80=""),"sve_kilaze","kg_"&amp;$E80&amp;"_"&amp;IF($C80="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:18">
+    <row r="81" spans="1:19">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -3625,20 +3703,21 @@
       <c r="M81" s="5"/>
       <c r="N81" s="5"/>
       <c r="O81" s="5"/>
-      <c r="P81" s="8">
-        <f>IF(COUNTA($A81:$D81,G81:N81)=0,"",IF($A81="","Nedostaje godište",IF($E81="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B81="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B81&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C81="","Nedostaje pol",IF($D81="","Nedostaje pojas",IF(COUNTA(G81:N81)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G81:N81&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E81),G81:N81)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E81,IF(AND(COUNTIF(G81:N81,"Fudokan sport kumite")&gt;0,O81=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G81:N81,"Fudokan sport kumite")=0,O81&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q81">
+      <c r="P81" s="5"/>
+      <c r="Q81" s="8">
+        <f>IF(COUNTA($A81:$D81,G81:N81,P81)=0,"",IF($A81="","Nedostaje godište",IF($E81="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B81="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B81&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C81="","Nedostaje pol",IF($D81="","Nedostaje pojas",IF(COUNTA(G81:N81)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G81:N81&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E81),G81:N81)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E81,IF(AND(COUNTIF(G81:N81,"Fudokan sport kumite")&gt;0,O81=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G81:N81,"Fudokan sport kumite")=0,O81&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P81&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P81,4))="FSS-",MID(P81,LEN(P81)-2,1)="/",ISNUMBER(VALUE(RIGHT(P81,2))),VALUE(MID(P81,5,LEN(P81)-7))&gt;=1,VALUE(MID(P81,5,LEN(P81)-7))=INT(VALUE(MID(P81,5,LEN(P81)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R81">
         <f>IF($E81="","sve_discipline","disc_"&amp;$E81)</f>
         <v/>
       </c>
-      <c r="R81">
+      <c r="S81">
         <f>IF(OR($E81="",$C81=""),"sve_kilaze","kg_"&amp;$E81&amp;"_"&amp;IF($C81="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:18">
+    <row r="82" spans="1:19">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -3660,20 +3739,21 @@
       <c r="M82" s="5"/>
       <c r="N82" s="5"/>
       <c r="O82" s="5"/>
-      <c r="P82" s="8">
-        <f>IF(COUNTA($A82:$D82,G82:N82)=0,"",IF($A82="","Nedostaje godište",IF($E82="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B82="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B82&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C82="","Nedostaje pol",IF($D82="","Nedostaje pojas",IF(COUNTA(G82:N82)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G82:N82&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E82),G82:N82)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E82,IF(AND(COUNTIF(G82:N82,"Fudokan sport kumite")&gt;0,O82=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G82:N82,"Fudokan sport kumite")=0,O82&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q82">
+      <c r="P82" s="5"/>
+      <c r="Q82" s="8">
+        <f>IF(COUNTA($A82:$D82,G82:N82,P82)=0,"",IF($A82="","Nedostaje godište",IF($E82="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B82="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B82&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C82="","Nedostaje pol",IF($D82="","Nedostaje pojas",IF(COUNTA(G82:N82)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G82:N82&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E82),G82:N82)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E82,IF(AND(COUNTIF(G82:N82,"Fudokan sport kumite")&gt;0,O82=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G82:N82,"Fudokan sport kumite")=0,O82&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P82&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P82,4))="FSS-",MID(P82,LEN(P82)-2,1)="/",ISNUMBER(VALUE(RIGHT(P82,2))),VALUE(MID(P82,5,LEN(P82)-7))&gt;=1,VALUE(MID(P82,5,LEN(P82)-7))=INT(VALUE(MID(P82,5,LEN(P82)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R82">
         <f>IF($E82="","sve_discipline","disc_"&amp;$E82)</f>
         <v/>
       </c>
-      <c r="R82">
+      <c r="S82">
         <f>IF(OR($E82="",$C82=""),"sve_kilaze","kg_"&amp;$E82&amp;"_"&amp;IF($C82="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:18">
+    <row r="83" spans="1:19">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -3695,20 +3775,21 @@
       <c r="M83" s="5"/>
       <c r="N83" s="5"/>
       <c r="O83" s="5"/>
-      <c r="P83" s="8">
-        <f>IF(COUNTA($A83:$D83,G83:N83)=0,"",IF($A83="","Nedostaje godište",IF($E83="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B83="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B83&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C83="","Nedostaje pol",IF($D83="","Nedostaje pojas",IF(COUNTA(G83:N83)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G83:N83&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E83),G83:N83)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E83,IF(AND(COUNTIF(G83:N83,"Fudokan sport kumite")&gt;0,O83=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G83:N83,"Fudokan sport kumite")=0,O83&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q83">
+      <c r="P83" s="5"/>
+      <c r="Q83" s="8">
+        <f>IF(COUNTA($A83:$D83,G83:N83,P83)=0,"",IF($A83="","Nedostaje godište",IF($E83="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B83="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B83&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C83="","Nedostaje pol",IF($D83="","Nedostaje pojas",IF(COUNTA(G83:N83)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G83:N83&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E83),G83:N83)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E83,IF(AND(COUNTIF(G83:N83,"Fudokan sport kumite")&gt;0,O83=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G83:N83,"Fudokan sport kumite")=0,O83&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P83&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P83,4))="FSS-",MID(P83,LEN(P83)-2,1)="/",ISNUMBER(VALUE(RIGHT(P83,2))),VALUE(MID(P83,5,LEN(P83)-7))&gt;=1,VALUE(MID(P83,5,LEN(P83)-7))=INT(VALUE(MID(P83,5,LEN(P83)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R83">
         <f>IF($E83="","sve_discipline","disc_"&amp;$E83)</f>
         <v/>
       </c>
-      <c r="R83">
+      <c r="S83">
         <f>IF(OR($E83="",$C83=""),"sve_kilaze","kg_"&amp;$E83&amp;"_"&amp;IF($C83="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:18">
+    <row r="84" spans="1:19">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -3730,20 +3811,21 @@
       <c r="M84" s="5"/>
       <c r="N84" s="5"/>
       <c r="O84" s="5"/>
-      <c r="P84" s="8">
-        <f>IF(COUNTA($A84:$D84,G84:N84)=0,"",IF($A84="","Nedostaje godište",IF($E84="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B84="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B84&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C84="","Nedostaje pol",IF($D84="","Nedostaje pojas",IF(COUNTA(G84:N84)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G84:N84&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E84),G84:N84)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E84,IF(AND(COUNTIF(G84:N84,"Fudokan sport kumite")&gt;0,O84=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G84:N84,"Fudokan sport kumite")=0,O84&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q84">
+      <c r="P84" s="5"/>
+      <c r="Q84" s="8">
+        <f>IF(COUNTA($A84:$D84,G84:N84,P84)=0,"",IF($A84="","Nedostaje godište",IF($E84="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B84="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B84&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C84="","Nedostaje pol",IF($D84="","Nedostaje pojas",IF(COUNTA(G84:N84)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G84:N84&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E84),G84:N84)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E84,IF(AND(COUNTIF(G84:N84,"Fudokan sport kumite")&gt;0,O84=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G84:N84,"Fudokan sport kumite")=0,O84&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P84&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P84,4))="FSS-",MID(P84,LEN(P84)-2,1)="/",ISNUMBER(VALUE(RIGHT(P84,2))),VALUE(MID(P84,5,LEN(P84)-7))&gt;=1,VALUE(MID(P84,5,LEN(P84)-7))=INT(VALUE(MID(P84,5,LEN(P84)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R84">
         <f>IF($E84="","sve_discipline","disc_"&amp;$E84)</f>
         <v/>
       </c>
-      <c r="R84">
+      <c r="S84">
         <f>IF(OR($E84="",$C84=""),"sve_kilaze","kg_"&amp;$E84&amp;"_"&amp;IF($C84="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:18">
+    <row r="85" spans="1:19">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -3765,20 +3847,21 @@
       <c r="M85" s="5"/>
       <c r="N85" s="5"/>
       <c r="O85" s="5"/>
-      <c r="P85" s="8">
-        <f>IF(COUNTA($A85:$D85,G85:N85)=0,"",IF($A85="","Nedostaje godište",IF($E85="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B85="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B85&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C85="","Nedostaje pol",IF($D85="","Nedostaje pojas",IF(COUNTA(G85:N85)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G85:N85&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E85),G85:N85)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E85,IF(AND(COUNTIF(G85:N85,"Fudokan sport kumite")&gt;0,O85=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G85:N85,"Fudokan sport kumite")=0,O85&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q85">
+      <c r="P85" s="5"/>
+      <c r="Q85" s="8">
+        <f>IF(COUNTA($A85:$D85,G85:N85,P85)=0,"",IF($A85="","Nedostaje godište",IF($E85="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B85="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B85&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C85="","Nedostaje pol",IF($D85="","Nedostaje pojas",IF(COUNTA(G85:N85)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G85:N85&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E85),G85:N85)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E85,IF(AND(COUNTIF(G85:N85,"Fudokan sport kumite")&gt;0,O85=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G85:N85,"Fudokan sport kumite")=0,O85&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P85&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P85,4))="FSS-",MID(P85,LEN(P85)-2,1)="/",ISNUMBER(VALUE(RIGHT(P85,2))),VALUE(MID(P85,5,LEN(P85)-7))&gt;=1,VALUE(MID(P85,5,LEN(P85)-7))=INT(VALUE(MID(P85,5,LEN(P85)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R85">
         <f>IF($E85="","sve_discipline","disc_"&amp;$E85)</f>
         <v/>
       </c>
-      <c r="R85">
+      <c r="S85">
         <f>IF(OR($E85="",$C85=""),"sve_kilaze","kg_"&amp;$E85&amp;"_"&amp;IF($C85="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="86" spans="1:18">
+    <row r="86" spans="1:19">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -3800,20 +3883,21 @@
       <c r="M86" s="5"/>
       <c r="N86" s="5"/>
       <c r="O86" s="5"/>
-      <c r="P86" s="8">
-        <f>IF(COUNTA($A86:$D86,G86:N86)=0,"",IF($A86="","Nedostaje godište",IF($E86="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B86="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B86&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C86="","Nedostaje pol",IF($D86="","Nedostaje pojas",IF(COUNTA(G86:N86)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G86:N86&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E86),G86:N86)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E86,IF(AND(COUNTIF(G86:N86,"Fudokan sport kumite")&gt;0,O86=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G86:N86,"Fudokan sport kumite")=0,O86&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q86">
+      <c r="P86" s="5"/>
+      <c r="Q86" s="8">
+        <f>IF(COUNTA($A86:$D86,G86:N86,P86)=0,"",IF($A86="","Nedostaje godište",IF($E86="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B86="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B86&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C86="","Nedostaje pol",IF($D86="","Nedostaje pojas",IF(COUNTA(G86:N86)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G86:N86&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E86),G86:N86)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E86,IF(AND(COUNTIF(G86:N86,"Fudokan sport kumite")&gt;0,O86=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G86:N86,"Fudokan sport kumite")=0,O86&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P86&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P86,4))="FSS-",MID(P86,LEN(P86)-2,1)="/",ISNUMBER(VALUE(RIGHT(P86,2))),VALUE(MID(P86,5,LEN(P86)-7))&gt;=1,VALUE(MID(P86,5,LEN(P86)-7))=INT(VALUE(MID(P86,5,LEN(P86)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R86">
         <f>IF($E86="","sve_discipline","disc_"&amp;$E86)</f>
         <v/>
       </c>
-      <c r="R86">
+      <c r="S86">
         <f>IF(OR($E86="",$C86=""),"sve_kilaze","kg_"&amp;$E86&amp;"_"&amp;IF($C86="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="87" spans="1:18">
+    <row r="87" spans="1:19">
       <c r="A87" s="5"/>
       <c r="B87" s="5"/>
       <c r="C87" s="5"/>
@@ -3835,20 +3919,21 @@
       <c r="M87" s="5"/>
       <c r="N87" s="5"/>
       <c r="O87" s="5"/>
-      <c r="P87" s="8">
-        <f>IF(COUNTA($A87:$D87,G87:N87)=0,"",IF($A87="","Nedostaje godište",IF($E87="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B87="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B87&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C87="","Nedostaje pol",IF($D87="","Nedostaje pojas",IF(COUNTA(G87:N87)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G87:N87&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E87),G87:N87)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E87,IF(AND(COUNTIF(G87:N87,"Fudokan sport kumite")&gt;0,O87=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G87:N87,"Fudokan sport kumite")=0,O87&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q87">
+      <c r="P87" s="5"/>
+      <c r="Q87" s="8">
+        <f>IF(COUNTA($A87:$D87,G87:N87,P87)=0,"",IF($A87="","Nedostaje godište",IF($E87="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B87="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B87&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C87="","Nedostaje pol",IF($D87="","Nedostaje pojas",IF(COUNTA(G87:N87)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G87:N87&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E87),G87:N87)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E87,IF(AND(COUNTIF(G87:N87,"Fudokan sport kumite")&gt;0,O87=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G87:N87,"Fudokan sport kumite")=0,O87&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P87&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P87,4))="FSS-",MID(P87,LEN(P87)-2,1)="/",ISNUMBER(VALUE(RIGHT(P87,2))),VALUE(MID(P87,5,LEN(P87)-7))&gt;=1,VALUE(MID(P87,5,LEN(P87)-7))=INT(VALUE(MID(P87,5,LEN(P87)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R87">
         <f>IF($E87="","sve_discipline","disc_"&amp;$E87)</f>
         <v/>
       </c>
-      <c r="R87">
+      <c r="S87">
         <f>IF(OR($E87="",$C87=""),"sve_kilaze","kg_"&amp;$E87&amp;"_"&amp;IF($C87="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:18">
+    <row r="88" spans="1:19">
       <c r="A88" s="5"/>
       <c r="B88" s="5"/>
       <c r="C88" s="5"/>
@@ -3870,20 +3955,21 @@
       <c r="M88" s="5"/>
       <c r="N88" s="5"/>
       <c r="O88" s="5"/>
-      <c r="P88" s="8">
-        <f>IF(COUNTA($A88:$D88,G88:N88)=0,"",IF($A88="","Nedostaje godište",IF($E88="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B88="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B88&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C88="","Nedostaje pol",IF($D88="","Nedostaje pojas",IF(COUNTA(G88:N88)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G88:N88&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E88),G88:N88)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E88,IF(AND(COUNTIF(G88:N88,"Fudokan sport kumite")&gt;0,O88=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G88:N88,"Fudokan sport kumite")=0,O88&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q88">
+      <c r="P88" s="5"/>
+      <c r="Q88" s="8">
+        <f>IF(COUNTA($A88:$D88,G88:N88,P88)=0,"",IF($A88="","Nedostaje godište",IF($E88="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B88="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B88&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C88="","Nedostaje pol",IF($D88="","Nedostaje pojas",IF(COUNTA(G88:N88)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G88:N88&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E88),G88:N88)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E88,IF(AND(COUNTIF(G88:N88,"Fudokan sport kumite")&gt;0,O88=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G88:N88,"Fudokan sport kumite")=0,O88&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P88&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P88,4))="FSS-",MID(P88,LEN(P88)-2,1)="/",ISNUMBER(VALUE(RIGHT(P88,2))),VALUE(MID(P88,5,LEN(P88)-7))&gt;=1,VALUE(MID(P88,5,LEN(P88)-7))=INT(VALUE(MID(P88,5,LEN(P88)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R88">
         <f>IF($E88="","sve_discipline","disc_"&amp;$E88)</f>
         <v/>
       </c>
-      <c r="R88">
+      <c r="S88">
         <f>IF(OR($E88="",$C88=""),"sve_kilaze","kg_"&amp;$E88&amp;"_"&amp;IF($C88="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="89" spans="1:18">
+    <row r="89" spans="1:19">
       <c r="A89" s="5"/>
       <c r="B89" s="5"/>
       <c r="C89" s="5"/>
@@ -3905,20 +3991,21 @@
       <c r="M89" s="5"/>
       <c r="N89" s="5"/>
       <c r="O89" s="5"/>
-      <c r="P89" s="8">
-        <f>IF(COUNTA($A89:$D89,G89:N89)=0,"",IF($A89="","Nedostaje godište",IF($E89="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B89="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B89&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C89="","Nedostaje pol",IF($D89="","Nedostaje pojas",IF(COUNTA(G89:N89)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G89:N89&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E89),G89:N89)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E89,IF(AND(COUNTIF(G89:N89,"Fudokan sport kumite")&gt;0,O89=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G89:N89,"Fudokan sport kumite")=0,O89&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q89">
+      <c r="P89" s="5"/>
+      <c r="Q89" s="8">
+        <f>IF(COUNTA($A89:$D89,G89:N89,P89)=0,"",IF($A89="","Nedostaje godište",IF($E89="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B89="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B89&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C89="","Nedostaje pol",IF($D89="","Nedostaje pojas",IF(COUNTA(G89:N89)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G89:N89&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E89),G89:N89)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E89,IF(AND(COUNTIF(G89:N89,"Fudokan sport kumite")&gt;0,O89=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G89:N89,"Fudokan sport kumite")=0,O89&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P89&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P89,4))="FSS-",MID(P89,LEN(P89)-2,1)="/",ISNUMBER(VALUE(RIGHT(P89,2))),VALUE(MID(P89,5,LEN(P89)-7))&gt;=1,VALUE(MID(P89,5,LEN(P89)-7))=INT(VALUE(MID(P89,5,LEN(P89)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R89">
         <f>IF($E89="","sve_discipline","disc_"&amp;$E89)</f>
         <v/>
       </c>
-      <c r="R89">
+      <c r="S89">
         <f>IF(OR($E89="",$C89=""),"sve_kilaze","kg_"&amp;$E89&amp;"_"&amp;IF($C89="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="90" spans="1:18">
+    <row r="90" spans="1:19">
       <c r="A90" s="5"/>
       <c r="B90" s="5"/>
       <c r="C90" s="5"/>
@@ -3940,20 +4027,21 @@
       <c r="M90" s="5"/>
       <c r="N90" s="5"/>
       <c r="O90" s="5"/>
-      <c r="P90" s="8">
-        <f>IF(COUNTA($A90:$D90,G90:N90)=0,"",IF($A90="","Nedostaje godište",IF($E90="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B90="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B90&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C90="","Nedostaje pol",IF($D90="","Nedostaje pojas",IF(COUNTA(G90:N90)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G90:N90&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E90),G90:N90)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E90,IF(AND(COUNTIF(G90:N90,"Fudokan sport kumite")&gt;0,O90=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G90:N90,"Fudokan sport kumite")=0,O90&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q90">
+      <c r="P90" s="5"/>
+      <c r="Q90" s="8">
+        <f>IF(COUNTA($A90:$D90,G90:N90,P90)=0,"",IF($A90="","Nedostaje godište",IF($E90="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B90="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B90&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C90="","Nedostaje pol",IF($D90="","Nedostaje pojas",IF(COUNTA(G90:N90)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G90:N90&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E90),G90:N90)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E90,IF(AND(COUNTIF(G90:N90,"Fudokan sport kumite")&gt;0,O90=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G90:N90,"Fudokan sport kumite")=0,O90&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P90&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P90,4))="FSS-",MID(P90,LEN(P90)-2,1)="/",ISNUMBER(VALUE(RIGHT(P90,2))),VALUE(MID(P90,5,LEN(P90)-7))&gt;=1,VALUE(MID(P90,5,LEN(P90)-7))=INT(VALUE(MID(P90,5,LEN(P90)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R90">
         <f>IF($E90="","sve_discipline","disc_"&amp;$E90)</f>
         <v/>
       </c>
-      <c r="R90">
+      <c r="S90">
         <f>IF(OR($E90="",$C90=""),"sve_kilaze","kg_"&amp;$E90&amp;"_"&amp;IF($C90="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:18">
+    <row r="91" spans="1:19">
       <c r="A91" s="5"/>
       <c r="B91" s="5"/>
       <c r="C91" s="5"/>
@@ -3975,20 +4063,21 @@
       <c r="M91" s="5"/>
       <c r="N91" s="5"/>
       <c r="O91" s="5"/>
-      <c r="P91" s="8">
-        <f>IF(COUNTA($A91:$D91,G91:N91)=0,"",IF($A91="","Nedostaje godište",IF($E91="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B91="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B91&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C91="","Nedostaje pol",IF($D91="","Nedostaje pojas",IF(COUNTA(G91:N91)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G91:N91&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E91),G91:N91)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E91,IF(AND(COUNTIF(G91:N91,"Fudokan sport kumite")&gt;0,O91=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G91:N91,"Fudokan sport kumite")=0,O91&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q91">
+      <c r="P91" s="5"/>
+      <c r="Q91" s="8">
+        <f>IF(COUNTA($A91:$D91,G91:N91,P91)=0,"",IF($A91="","Nedostaje godište",IF($E91="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B91="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B91&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C91="","Nedostaje pol",IF($D91="","Nedostaje pojas",IF(COUNTA(G91:N91)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G91:N91&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E91),G91:N91)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E91,IF(AND(COUNTIF(G91:N91,"Fudokan sport kumite")&gt;0,O91=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G91:N91,"Fudokan sport kumite")=0,O91&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P91&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P91,4))="FSS-",MID(P91,LEN(P91)-2,1)="/",ISNUMBER(VALUE(RIGHT(P91,2))),VALUE(MID(P91,5,LEN(P91)-7))&gt;=1,VALUE(MID(P91,5,LEN(P91)-7))=INT(VALUE(MID(P91,5,LEN(P91)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R91">
         <f>IF($E91="","sve_discipline","disc_"&amp;$E91)</f>
         <v/>
       </c>
-      <c r="R91">
+      <c r="S91">
         <f>IF(OR($E91="",$C91=""),"sve_kilaze","kg_"&amp;$E91&amp;"_"&amp;IF($C91="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:18">
+    <row r="92" spans="1:19">
       <c r="A92" s="5"/>
       <c r="B92" s="5"/>
       <c r="C92" s="5"/>
@@ -4010,20 +4099,21 @@
       <c r="M92" s="5"/>
       <c r="N92" s="5"/>
       <c r="O92" s="5"/>
-      <c r="P92" s="8">
-        <f>IF(COUNTA($A92:$D92,G92:N92)=0,"",IF($A92="","Nedostaje godište",IF($E92="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B92="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B92&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C92="","Nedostaje pol",IF($D92="","Nedostaje pojas",IF(COUNTA(G92:N92)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G92:N92&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E92),G92:N92)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E92,IF(AND(COUNTIF(G92:N92,"Fudokan sport kumite")&gt;0,O92=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G92:N92,"Fudokan sport kumite")=0,O92&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q92">
+      <c r="P92" s="5"/>
+      <c r="Q92" s="8">
+        <f>IF(COUNTA($A92:$D92,G92:N92,P92)=0,"",IF($A92="","Nedostaje godište",IF($E92="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B92="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B92&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C92="","Nedostaje pol",IF($D92="","Nedostaje pojas",IF(COUNTA(G92:N92)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G92:N92&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E92),G92:N92)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E92,IF(AND(COUNTIF(G92:N92,"Fudokan sport kumite")&gt;0,O92=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G92:N92,"Fudokan sport kumite")=0,O92&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P92&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P92,4))="FSS-",MID(P92,LEN(P92)-2,1)="/",ISNUMBER(VALUE(RIGHT(P92,2))),VALUE(MID(P92,5,LEN(P92)-7))&gt;=1,VALUE(MID(P92,5,LEN(P92)-7))=INT(VALUE(MID(P92,5,LEN(P92)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R92">
         <f>IF($E92="","sve_discipline","disc_"&amp;$E92)</f>
         <v/>
       </c>
-      <c r="R92">
+      <c r="S92">
         <f>IF(OR($E92="",$C92=""),"sve_kilaze","kg_"&amp;$E92&amp;"_"&amp;IF($C92="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:18">
+    <row r="93" spans="1:19">
       <c r="A93" s="5"/>
       <c r="B93" s="5"/>
       <c r="C93" s="5"/>
@@ -4045,20 +4135,21 @@
       <c r="M93" s="5"/>
       <c r="N93" s="5"/>
       <c r="O93" s="5"/>
-      <c r="P93" s="8">
-        <f>IF(COUNTA($A93:$D93,G93:N93)=0,"",IF($A93="","Nedostaje godište",IF($E93="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B93="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B93&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C93="","Nedostaje pol",IF($D93="","Nedostaje pojas",IF(COUNTA(G93:N93)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G93:N93&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E93),G93:N93)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E93,IF(AND(COUNTIF(G93:N93,"Fudokan sport kumite")&gt;0,O93=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G93:N93,"Fudokan sport kumite")=0,O93&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q93">
+      <c r="P93" s="5"/>
+      <c r="Q93" s="8">
+        <f>IF(COUNTA($A93:$D93,G93:N93,P93)=0,"",IF($A93="","Nedostaje godište",IF($E93="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B93="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B93&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C93="","Nedostaje pol",IF($D93="","Nedostaje pojas",IF(COUNTA(G93:N93)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G93:N93&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E93),G93:N93)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E93,IF(AND(COUNTIF(G93:N93,"Fudokan sport kumite")&gt;0,O93=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G93:N93,"Fudokan sport kumite")=0,O93&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P93&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P93,4))="FSS-",MID(P93,LEN(P93)-2,1)="/",ISNUMBER(VALUE(RIGHT(P93,2))),VALUE(MID(P93,5,LEN(P93)-7))&gt;=1,VALUE(MID(P93,5,LEN(P93)-7))=INT(VALUE(MID(P93,5,LEN(P93)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R93">
         <f>IF($E93="","sve_discipline","disc_"&amp;$E93)</f>
         <v/>
       </c>
-      <c r="R93">
+      <c r="S93">
         <f>IF(OR($E93="",$C93=""),"sve_kilaze","kg_"&amp;$E93&amp;"_"&amp;IF($C93="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:18">
+    <row r="94" spans="1:19">
       <c r="A94" s="5"/>
       <c r="B94" s="5"/>
       <c r="C94" s="5"/>
@@ -4080,20 +4171,21 @@
       <c r="M94" s="5"/>
       <c r="N94" s="5"/>
       <c r="O94" s="5"/>
-      <c r="P94" s="8">
-        <f>IF(COUNTA($A94:$D94,G94:N94)=0,"",IF($A94="","Nedostaje godište",IF($E94="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B94="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B94&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C94="","Nedostaje pol",IF($D94="","Nedostaje pojas",IF(COUNTA(G94:N94)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G94:N94&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E94),G94:N94)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E94,IF(AND(COUNTIF(G94:N94,"Fudokan sport kumite")&gt;0,O94=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G94:N94,"Fudokan sport kumite")=0,O94&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q94">
+      <c r="P94" s="5"/>
+      <c r="Q94" s="8">
+        <f>IF(COUNTA($A94:$D94,G94:N94,P94)=0,"",IF($A94="","Nedostaje godište",IF($E94="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B94="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B94&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C94="","Nedostaje pol",IF($D94="","Nedostaje pojas",IF(COUNTA(G94:N94)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G94:N94&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E94),G94:N94)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E94,IF(AND(COUNTIF(G94:N94,"Fudokan sport kumite")&gt;0,O94=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G94:N94,"Fudokan sport kumite")=0,O94&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P94&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P94,4))="FSS-",MID(P94,LEN(P94)-2,1)="/",ISNUMBER(VALUE(RIGHT(P94,2))),VALUE(MID(P94,5,LEN(P94)-7))&gt;=1,VALUE(MID(P94,5,LEN(P94)-7))=INT(VALUE(MID(P94,5,LEN(P94)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R94">
         <f>IF($E94="","sve_discipline","disc_"&amp;$E94)</f>
         <v/>
       </c>
-      <c r="R94">
+      <c r="S94">
         <f>IF(OR($E94="",$C94=""),"sve_kilaze","kg_"&amp;$E94&amp;"_"&amp;IF($C94="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="95" spans="1:18">
+    <row r="95" spans="1:19">
       <c r="A95" s="5"/>
       <c r="B95" s="5"/>
       <c r="C95" s="5"/>
@@ -4115,20 +4207,21 @@
       <c r="M95" s="5"/>
       <c r="N95" s="5"/>
       <c r="O95" s="5"/>
-      <c r="P95" s="8">
-        <f>IF(COUNTA($A95:$D95,G95:N95)=0,"",IF($A95="","Nedostaje godište",IF($E95="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B95="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B95&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C95="","Nedostaje pol",IF($D95="","Nedostaje pojas",IF(COUNTA(G95:N95)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G95:N95&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E95),G95:N95)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E95,IF(AND(COUNTIF(G95:N95,"Fudokan sport kumite")&gt;0,O95=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G95:N95,"Fudokan sport kumite")=0,O95&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q95">
+      <c r="P95" s="5"/>
+      <c r="Q95" s="8">
+        <f>IF(COUNTA($A95:$D95,G95:N95,P95)=0,"",IF($A95="","Nedostaje godište",IF($E95="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B95="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B95&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C95="","Nedostaje pol",IF($D95="","Nedostaje pojas",IF(COUNTA(G95:N95)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G95:N95&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E95),G95:N95)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E95,IF(AND(COUNTIF(G95:N95,"Fudokan sport kumite")&gt;0,O95=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G95:N95,"Fudokan sport kumite")=0,O95&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P95&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P95,4))="FSS-",MID(P95,LEN(P95)-2,1)="/",ISNUMBER(VALUE(RIGHT(P95,2))),VALUE(MID(P95,5,LEN(P95)-7))&gt;=1,VALUE(MID(P95,5,LEN(P95)-7))=INT(VALUE(MID(P95,5,LEN(P95)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R95">
         <f>IF($E95="","sve_discipline","disc_"&amp;$E95)</f>
         <v/>
       </c>
-      <c r="R95">
+      <c r="S95">
         <f>IF(OR($E95="",$C95=""),"sve_kilaze","kg_"&amp;$E95&amp;"_"&amp;IF($C95="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="96" spans="1:18">
+    <row r="96" spans="1:19">
       <c r="A96" s="5"/>
       <c r="B96" s="5"/>
       <c r="C96" s="5"/>
@@ -4150,20 +4243,21 @@
       <c r="M96" s="5"/>
       <c r="N96" s="5"/>
       <c r="O96" s="5"/>
-      <c r="P96" s="8">
-        <f>IF(COUNTA($A96:$D96,G96:N96)=0,"",IF($A96="","Nedostaje godište",IF($E96="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B96="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B96&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C96="","Nedostaje pol",IF($D96="","Nedostaje pojas",IF(COUNTA(G96:N96)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G96:N96&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E96),G96:N96)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E96,IF(AND(COUNTIF(G96:N96,"Fudokan sport kumite")&gt;0,O96=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G96:N96,"Fudokan sport kumite")=0,O96&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q96">
+      <c r="P96" s="5"/>
+      <c r="Q96" s="8">
+        <f>IF(COUNTA($A96:$D96,G96:N96,P96)=0,"",IF($A96="","Nedostaje godište",IF($E96="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B96="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B96&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C96="","Nedostaje pol",IF($D96="","Nedostaje pojas",IF(COUNTA(G96:N96)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G96:N96&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E96),G96:N96)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E96,IF(AND(COUNTIF(G96:N96,"Fudokan sport kumite")&gt;0,O96=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G96:N96,"Fudokan sport kumite")=0,O96&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P96&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P96,4))="FSS-",MID(P96,LEN(P96)-2,1)="/",ISNUMBER(VALUE(RIGHT(P96,2))),VALUE(MID(P96,5,LEN(P96)-7))&gt;=1,VALUE(MID(P96,5,LEN(P96)-7))=INT(VALUE(MID(P96,5,LEN(P96)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R96">
         <f>IF($E96="","sve_discipline","disc_"&amp;$E96)</f>
         <v/>
       </c>
-      <c r="R96">
+      <c r="S96">
         <f>IF(OR($E96="",$C96=""),"sve_kilaze","kg_"&amp;$E96&amp;"_"&amp;IF($C96="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:18">
+    <row r="97" spans="1:19">
       <c r="A97" s="5"/>
       <c r="B97" s="5"/>
       <c r="C97" s="5"/>
@@ -4185,20 +4279,21 @@
       <c r="M97" s="5"/>
       <c r="N97" s="5"/>
       <c r="O97" s="5"/>
-      <c r="P97" s="8">
-        <f>IF(COUNTA($A97:$D97,G97:N97)=0,"",IF($A97="","Nedostaje godište",IF($E97="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B97="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B97&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C97="","Nedostaje pol",IF($D97="","Nedostaje pojas",IF(COUNTA(G97:N97)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G97:N97&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E97),G97:N97)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E97,IF(AND(COUNTIF(G97:N97,"Fudokan sport kumite")&gt;0,O97=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G97:N97,"Fudokan sport kumite")=0,O97&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q97">
+      <c r="P97" s="5"/>
+      <c r="Q97" s="8">
+        <f>IF(COUNTA($A97:$D97,G97:N97,P97)=0,"",IF($A97="","Nedostaje godište",IF($E97="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B97="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B97&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C97="","Nedostaje pol",IF($D97="","Nedostaje pojas",IF(COUNTA(G97:N97)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G97:N97&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E97),G97:N97)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E97,IF(AND(COUNTIF(G97:N97,"Fudokan sport kumite")&gt;0,O97=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G97:N97,"Fudokan sport kumite")=0,O97&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P97&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P97,4))="FSS-",MID(P97,LEN(P97)-2,1)="/",ISNUMBER(VALUE(RIGHT(P97,2))),VALUE(MID(P97,5,LEN(P97)-7))&gt;=1,VALUE(MID(P97,5,LEN(P97)-7))=INT(VALUE(MID(P97,5,LEN(P97)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R97">
         <f>IF($E97="","sve_discipline","disc_"&amp;$E97)</f>
         <v/>
       </c>
-      <c r="R97">
+      <c r="S97">
         <f>IF(OR($E97="",$C97=""),"sve_kilaze","kg_"&amp;$E97&amp;"_"&amp;IF($C97="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:18">
+    <row r="98" spans="1:19">
       <c r="A98" s="5"/>
       <c r="B98" s="5"/>
       <c r="C98" s="5"/>
@@ -4220,20 +4315,21 @@
       <c r="M98" s="5"/>
       <c r="N98" s="5"/>
       <c r="O98" s="5"/>
-      <c r="P98" s="8">
-        <f>IF(COUNTA($A98:$D98,G98:N98)=0,"",IF($A98="","Nedostaje godište",IF($E98="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B98="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B98&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C98="","Nedostaje pol",IF($D98="","Nedostaje pojas",IF(COUNTA(G98:N98)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G98:N98&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E98),G98:N98)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E98,IF(AND(COUNTIF(G98:N98,"Fudokan sport kumite")&gt;0,O98=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G98:N98,"Fudokan sport kumite")=0,O98&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q98">
+      <c r="P98" s="5"/>
+      <c r="Q98" s="8">
+        <f>IF(COUNTA($A98:$D98,G98:N98,P98)=0,"",IF($A98="","Nedostaje godište",IF($E98="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B98="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B98&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C98="","Nedostaje pol",IF($D98="","Nedostaje pojas",IF(COUNTA(G98:N98)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G98:N98&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E98),G98:N98)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E98,IF(AND(COUNTIF(G98:N98,"Fudokan sport kumite")&gt;0,O98=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G98:N98,"Fudokan sport kumite")=0,O98&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P98&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P98,4))="FSS-",MID(P98,LEN(P98)-2,1)="/",ISNUMBER(VALUE(RIGHT(P98,2))),VALUE(MID(P98,5,LEN(P98)-7))&gt;=1,VALUE(MID(P98,5,LEN(P98)-7))=INT(VALUE(MID(P98,5,LEN(P98)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R98">
         <f>IF($E98="","sve_discipline","disc_"&amp;$E98)</f>
         <v/>
       </c>
-      <c r="R98">
+      <c r="S98">
         <f>IF(OR($E98="",$C98=""),"sve_kilaze","kg_"&amp;$E98&amp;"_"&amp;IF($C98="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="99" spans="1:18">
+    <row r="99" spans="1:19">
       <c r="A99" s="5"/>
       <c r="B99" s="5"/>
       <c r="C99" s="5"/>
@@ -4255,20 +4351,21 @@
       <c r="M99" s="5"/>
       <c r="N99" s="5"/>
       <c r="O99" s="5"/>
-      <c r="P99" s="8">
-        <f>IF(COUNTA($A99:$D99,G99:N99)=0,"",IF($A99="","Nedostaje godište",IF($E99="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B99="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B99&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C99="","Nedostaje pol",IF($D99="","Nedostaje pojas",IF(COUNTA(G99:N99)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G99:N99&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E99),G99:N99)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E99,IF(AND(COUNTIF(G99:N99,"Fudokan sport kumite")&gt;0,O99=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G99:N99,"Fudokan sport kumite")=0,O99&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q99">
+      <c r="P99" s="5"/>
+      <c r="Q99" s="8">
+        <f>IF(COUNTA($A99:$D99,G99:N99,P99)=0,"",IF($A99="","Nedostaje godište",IF($E99="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B99="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B99&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C99="","Nedostaje pol",IF($D99="","Nedostaje pojas",IF(COUNTA(G99:N99)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G99:N99&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E99),G99:N99)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E99,IF(AND(COUNTIF(G99:N99,"Fudokan sport kumite")&gt;0,O99=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G99:N99,"Fudokan sport kumite")=0,O99&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P99&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P99,4))="FSS-",MID(P99,LEN(P99)-2,1)="/",ISNUMBER(VALUE(RIGHT(P99,2))),VALUE(MID(P99,5,LEN(P99)-7))&gt;=1,VALUE(MID(P99,5,LEN(P99)-7))=INT(VALUE(MID(P99,5,LEN(P99)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R99">
         <f>IF($E99="","sve_discipline","disc_"&amp;$E99)</f>
         <v/>
       </c>
-      <c r="R99">
+      <c r="S99">
         <f>IF(OR($E99="",$C99=""),"sve_kilaze","kg_"&amp;$E99&amp;"_"&amp;IF($C99="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="100" spans="1:18">
+    <row r="100" spans="1:19">
       <c r="A100" s="5"/>
       <c r="B100" s="5"/>
       <c r="C100" s="5"/>
@@ -4290,20 +4387,21 @@
       <c r="M100" s="5"/>
       <c r="N100" s="5"/>
       <c r="O100" s="5"/>
-      <c r="P100" s="8">
-        <f>IF(COUNTA($A100:$D100,G100:N100)=0,"",IF($A100="","Nedostaje godište",IF($E100="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B100="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B100&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C100="","Nedostaje pol",IF($D100="","Nedostaje pojas",IF(COUNTA(G100:N100)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G100:N100&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E100),G100:N100)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E100,IF(AND(COUNTIF(G100:N100,"Fudokan sport kumite")&gt;0,O100=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G100:N100,"Fudokan sport kumite")=0,O100&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q100">
+      <c r="P100" s="5"/>
+      <c r="Q100" s="8">
+        <f>IF(COUNTA($A100:$D100,G100:N100,P100)=0,"",IF($A100="","Nedostaje godište",IF($E100="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B100="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B100&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C100="","Nedostaje pol",IF($D100="","Nedostaje pojas",IF(COUNTA(G100:N100)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G100:N100&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E100),G100:N100)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E100,IF(AND(COUNTIF(G100:N100,"Fudokan sport kumite")&gt;0,O100=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G100:N100,"Fudokan sport kumite")=0,O100&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P100&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P100,4))="FSS-",MID(P100,LEN(P100)-2,1)="/",ISNUMBER(VALUE(RIGHT(P100,2))),VALUE(MID(P100,5,LEN(P100)-7))&gt;=1,VALUE(MID(P100,5,LEN(P100)-7))=INT(VALUE(MID(P100,5,LEN(P100)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R100">
         <f>IF($E100="","sve_discipline","disc_"&amp;$E100)</f>
         <v/>
       </c>
-      <c r="R100">
+      <c r="S100">
         <f>IF(OR($E100="",$C100=""),"sve_kilaze","kg_"&amp;$E100&amp;"_"&amp;IF($C100="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="101" spans="1:18">
+    <row r="101" spans="1:19">
       <c r="A101" s="5"/>
       <c r="B101" s="5"/>
       <c r="C101" s="5"/>
@@ -4325,20 +4423,21 @@
       <c r="M101" s="5"/>
       <c r="N101" s="5"/>
       <c r="O101" s="5"/>
-      <c r="P101" s="8">
-        <f>IF(COUNTA($A101:$D101,G101:N101)=0,"",IF($A101="","Nedostaje godište",IF($E101="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B101="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B101&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C101="","Nedostaje pol",IF($D101="","Nedostaje pojas",IF(COUNTA(G101:N101)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G101:N101&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E101),G101:N101)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E101,IF(AND(COUNTIF(G101:N101,"Fudokan sport kumite")&gt;0,O101=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G101:N101,"Fudokan sport kumite")=0,O101&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q101">
+      <c r="P101" s="5"/>
+      <c r="Q101" s="8">
+        <f>IF(COUNTA($A101:$D101,G101:N101,P101)=0,"",IF($A101="","Nedostaje godište",IF($E101="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B101="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B101&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C101="","Nedostaje pol",IF($D101="","Nedostaje pojas",IF(COUNTA(G101:N101)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G101:N101&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E101),G101:N101)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E101,IF(AND(COUNTIF(G101:N101,"Fudokan sport kumite")&gt;0,O101=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G101:N101,"Fudokan sport kumite")=0,O101&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P101&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P101,4))="FSS-",MID(P101,LEN(P101)-2,1)="/",ISNUMBER(VALUE(RIGHT(P101,2))),VALUE(MID(P101,5,LEN(P101)-7))&gt;=1,VALUE(MID(P101,5,LEN(P101)-7))=INT(VALUE(MID(P101,5,LEN(P101)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R101">
         <f>IF($E101="","sve_discipline","disc_"&amp;$E101)</f>
         <v/>
       </c>
-      <c r="R101">
+      <c r="S101">
         <f>IF(OR($E101="",$C101=""),"sve_kilaze","kg_"&amp;$E101&amp;"_"&amp;IF($C101="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:18">
+    <row r="102" spans="1:19">
       <c r="A102" s="5"/>
       <c r="B102" s="5"/>
       <c r="C102" s="5"/>
@@ -4360,20 +4459,21 @@
       <c r="M102" s="5"/>
       <c r="N102" s="5"/>
       <c r="O102" s="5"/>
-      <c r="P102" s="8">
-        <f>IF(COUNTA($A102:$D102,G102:N102)=0,"",IF($A102="","Nedostaje godište",IF($E102="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B102="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B102&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C102="","Nedostaje pol",IF($D102="","Nedostaje pojas",IF(COUNTA(G102:N102)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G102:N102&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E102),G102:N102)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E102,IF(AND(COUNTIF(G102:N102,"Fudokan sport kumite")&gt;0,O102=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G102:N102,"Fudokan sport kumite")=0,O102&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q102">
+      <c r="P102" s="5"/>
+      <c r="Q102" s="8">
+        <f>IF(COUNTA($A102:$D102,G102:N102,P102)=0,"",IF($A102="","Nedostaje godište",IF($E102="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B102="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B102&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C102="","Nedostaje pol",IF($D102="","Nedostaje pojas",IF(COUNTA(G102:N102)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G102:N102&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E102),G102:N102)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E102,IF(AND(COUNTIF(G102:N102,"Fudokan sport kumite")&gt;0,O102=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G102:N102,"Fudokan sport kumite")=0,O102&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P102&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P102,4))="FSS-",MID(P102,LEN(P102)-2,1)="/",ISNUMBER(VALUE(RIGHT(P102,2))),VALUE(MID(P102,5,LEN(P102)-7))&gt;=1,VALUE(MID(P102,5,LEN(P102)-7))=INT(VALUE(MID(P102,5,LEN(P102)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R102">
         <f>IF($E102="","sve_discipline","disc_"&amp;$E102)</f>
         <v/>
       </c>
-      <c r="R102">
+      <c r="S102">
         <f>IF(OR($E102="",$C102=""),"sve_kilaze","kg_"&amp;$E102&amp;"_"&amp;IF($C102="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:18">
+    <row r="103" spans="1:19">
       <c r="A103" s="5"/>
       <c r="B103" s="5"/>
       <c r="C103" s="5"/>
@@ -4395,20 +4495,21 @@
       <c r="M103" s="5"/>
       <c r="N103" s="5"/>
       <c r="O103" s="5"/>
-      <c r="P103" s="8">
-        <f>IF(COUNTA($A103:$D103,G103:N103)=0,"",IF($A103="","Nedostaje godište",IF($E103="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B103="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B103&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C103="","Nedostaje pol",IF($D103="","Nedostaje pojas",IF(COUNTA(G103:N103)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G103:N103&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E103),G103:N103)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E103,IF(AND(COUNTIF(G103:N103,"Fudokan sport kumite")&gt;0,O103=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G103:N103,"Fudokan sport kumite")=0,O103&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q103">
+      <c r="P103" s="5"/>
+      <c r="Q103" s="8">
+        <f>IF(COUNTA($A103:$D103,G103:N103,P103)=0,"",IF($A103="","Nedostaje godište",IF($E103="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B103="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B103&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C103="","Nedostaje pol",IF($D103="","Nedostaje pojas",IF(COUNTA(G103:N103)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G103:N103&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E103),G103:N103)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E103,IF(AND(COUNTIF(G103:N103,"Fudokan sport kumite")&gt;0,O103=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G103:N103,"Fudokan sport kumite")=0,O103&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P103&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P103,4))="FSS-",MID(P103,LEN(P103)-2,1)="/",ISNUMBER(VALUE(RIGHT(P103,2))),VALUE(MID(P103,5,LEN(P103)-7))&gt;=1,VALUE(MID(P103,5,LEN(P103)-7))=INT(VALUE(MID(P103,5,LEN(P103)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R103">
         <f>IF($E103="","sve_discipline","disc_"&amp;$E103)</f>
         <v/>
       </c>
-      <c r="R103">
+      <c r="S103">
         <f>IF(OR($E103="",$C103=""),"sve_kilaze","kg_"&amp;$E103&amp;"_"&amp;IF($C103="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:18">
+    <row r="104" spans="1:19">
       <c r="A104" s="5"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -4430,20 +4531,21 @@
       <c r="M104" s="5"/>
       <c r="N104" s="5"/>
       <c r="O104" s="5"/>
-      <c r="P104" s="8">
-        <f>IF(COUNTA($A104:$D104,G104:N104)=0,"",IF($A104="","Nedostaje godište",IF($E104="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B104="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B104&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C104="","Nedostaje pol",IF($D104="","Nedostaje pojas",IF(COUNTA(G104:N104)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G104:N104&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E104),G104:N104)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E104,IF(AND(COUNTIF(G104:N104,"Fudokan sport kumite")&gt;0,O104=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G104:N104,"Fudokan sport kumite")=0,O104&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q104">
+      <c r="P104" s="5"/>
+      <c r="Q104" s="8">
+        <f>IF(COUNTA($A104:$D104,G104:N104,P104)=0,"",IF($A104="","Nedostaje godište",IF($E104="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B104="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B104&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C104="","Nedostaje pol",IF($D104="","Nedostaje pojas",IF(COUNTA(G104:N104)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G104:N104&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E104),G104:N104)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E104,IF(AND(COUNTIF(G104:N104,"Fudokan sport kumite")&gt;0,O104=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G104:N104,"Fudokan sport kumite")=0,O104&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P104&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P104,4))="FSS-",MID(P104,LEN(P104)-2,1)="/",ISNUMBER(VALUE(RIGHT(P104,2))),VALUE(MID(P104,5,LEN(P104)-7))&gt;=1,VALUE(MID(P104,5,LEN(P104)-7))=INT(VALUE(MID(P104,5,LEN(P104)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R104">
         <f>IF($E104="","sve_discipline","disc_"&amp;$E104)</f>
         <v/>
       </c>
-      <c r="R104">
+      <c r="S104">
         <f>IF(OR($E104="",$C104=""),"sve_kilaze","kg_"&amp;$E104&amp;"_"&amp;IF($C104="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:18">
+    <row r="105" spans="1:19">
       <c r="A105" s="5"/>
       <c r="B105" s="5"/>
       <c r="C105" s="5"/>
@@ -4465,20 +4567,21 @@
       <c r="M105" s="5"/>
       <c r="N105" s="5"/>
       <c r="O105" s="5"/>
-      <c r="P105" s="8">
-        <f>IF(COUNTA($A105:$D105,G105:N105)=0,"",IF($A105="","Nedostaje godište",IF($E105="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B105="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B105&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C105="","Nedostaje pol",IF($D105="","Nedostaje pojas",IF(COUNTA(G105:N105)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G105:N105&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E105),G105:N105)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E105,IF(AND(COUNTIF(G105:N105,"Fudokan sport kumite")&gt;0,O105=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G105:N105,"Fudokan sport kumite")=0,O105&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q105">
+      <c r="P105" s="5"/>
+      <c r="Q105" s="8">
+        <f>IF(COUNTA($A105:$D105,G105:N105,P105)=0,"",IF($A105="","Nedostaje godište",IF($E105="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B105="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B105&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C105="","Nedostaje pol",IF($D105="","Nedostaje pojas",IF(COUNTA(G105:N105)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G105:N105&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E105),G105:N105)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E105,IF(AND(COUNTIF(G105:N105,"Fudokan sport kumite")&gt;0,O105=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G105:N105,"Fudokan sport kumite")=0,O105&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P105&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P105,4))="FSS-",MID(P105,LEN(P105)-2,1)="/",ISNUMBER(VALUE(RIGHT(P105,2))),VALUE(MID(P105,5,LEN(P105)-7))&gt;=1,VALUE(MID(P105,5,LEN(P105)-7))=INT(VALUE(MID(P105,5,LEN(P105)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R105">
         <f>IF($E105="","sve_discipline","disc_"&amp;$E105)</f>
         <v/>
       </c>
-      <c r="R105">
+      <c r="S105">
         <f>IF(OR($E105="",$C105=""),"sve_kilaze","kg_"&amp;$E105&amp;"_"&amp;IF($C105="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:18">
+    <row r="106" spans="1:19">
       <c r="A106" s="5"/>
       <c r="B106" s="5"/>
       <c r="C106" s="5"/>
@@ -4500,20 +4603,21 @@
       <c r="M106" s="5"/>
       <c r="N106" s="5"/>
       <c r="O106" s="5"/>
-      <c r="P106" s="8">
-        <f>IF(COUNTA($A106:$D106,G106:N106)=0,"",IF($A106="","Nedostaje godište",IF($E106="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B106="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B106&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C106="","Nedostaje pol",IF($D106="","Nedostaje pojas",IF(COUNTA(G106:N106)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G106:N106&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E106),G106:N106)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E106,IF(AND(COUNTIF(G106:N106,"Fudokan sport kumite")&gt;0,O106=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G106:N106,"Fudokan sport kumite")=0,O106&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q106">
+      <c r="P106" s="5"/>
+      <c r="Q106" s="8">
+        <f>IF(COUNTA($A106:$D106,G106:N106,P106)=0,"",IF($A106="","Nedostaje godište",IF($E106="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B106="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B106&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C106="","Nedostaje pol",IF($D106="","Nedostaje pojas",IF(COUNTA(G106:N106)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G106:N106&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E106),G106:N106)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E106,IF(AND(COUNTIF(G106:N106,"Fudokan sport kumite")&gt;0,O106=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G106:N106,"Fudokan sport kumite")=0,O106&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P106&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P106,4))="FSS-",MID(P106,LEN(P106)-2,1)="/",ISNUMBER(VALUE(RIGHT(P106,2))),VALUE(MID(P106,5,LEN(P106)-7))&gt;=1,VALUE(MID(P106,5,LEN(P106)-7))=INT(VALUE(MID(P106,5,LEN(P106)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R106">
         <f>IF($E106="","sve_discipline","disc_"&amp;$E106)</f>
         <v/>
       </c>
-      <c r="R106">
+      <c r="S106">
         <f>IF(OR($E106="",$C106=""),"sve_kilaze","kg_"&amp;$E106&amp;"_"&amp;IF($C106="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="107" spans="1:18">
+    <row r="107" spans="1:19">
       <c r="A107" s="5"/>
       <c r="B107" s="5"/>
       <c r="C107" s="5"/>
@@ -4535,20 +4639,21 @@
       <c r="M107" s="5"/>
       <c r="N107" s="5"/>
       <c r="O107" s="5"/>
-      <c r="P107" s="8">
-        <f>IF(COUNTA($A107:$D107,G107:N107)=0,"",IF($A107="","Nedostaje godište",IF($E107="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B107="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B107&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C107="","Nedostaje pol",IF($D107="","Nedostaje pojas",IF(COUNTA(G107:N107)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G107:N107&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E107),G107:N107)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E107,IF(AND(COUNTIF(G107:N107,"Fudokan sport kumite")&gt;0,O107=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G107:N107,"Fudokan sport kumite")=0,O107&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q107">
+      <c r="P107" s="5"/>
+      <c r="Q107" s="8">
+        <f>IF(COUNTA($A107:$D107,G107:N107,P107)=0,"",IF($A107="","Nedostaje godište",IF($E107="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B107="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B107&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C107="","Nedostaje pol",IF($D107="","Nedostaje pojas",IF(COUNTA(G107:N107)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G107:N107&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E107),G107:N107)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E107,IF(AND(COUNTIF(G107:N107,"Fudokan sport kumite")&gt;0,O107=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G107:N107,"Fudokan sport kumite")=0,O107&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P107&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P107,4))="FSS-",MID(P107,LEN(P107)-2,1)="/",ISNUMBER(VALUE(RIGHT(P107,2))),VALUE(MID(P107,5,LEN(P107)-7))&gt;=1,VALUE(MID(P107,5,LEN(P107)-7))=INT(VALUE(MID(P107,5,LEN(P107)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R107">
         <f>IF($E107="","sve_discipline","disc_"&amp;$E107)</f>
         <v/>
       </c>
-      <c r="R107">
+      <c r="S107">
         <f>IF(OR($E107="",$C107=""),"sve_kilaze","kg_"&amp;$E107&amp;"_"&amp;IF($C107="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="108" spans="1:18">
+    <row r="108" spans="1:19">
       <c r="A108" s="5"/>
       <c r="B108" s="5"/>
       <c r="C108" s="5"/>
@@ -4570,20 +4675,21 @@
       <c r="M108" s="5"/>
       <c r="N108" s="5"/>
       <c r="O108" s="5"/>
-      <c r="P108" s="8">
-        <f>IF(COUNTA($A108:$D108,G108:N108)=0,"",IF($A108="","Nedostaje godište",IF($E108="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B108="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B108&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C108="","Nedostaje pol",IF($D108="","Nedostaje pojas",IF(COUNTA(G108:N108)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G108:N108&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E108),G108:N108)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E108,IF(AND(COUNTIF(G108:N108,"Fudokan sport kumite")&gt;0,O108=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G108:N108,"Fudokan sport kumite")=0,O108&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q108">
+      <c r="P108" s="5"/>
+      <c r="Q108" s="8">
+        <f>IF(COUNTA($A108:$D108,G108:N108,P108)=0,"",IF($A108="","Nedostaje godište",IF($E108="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B108="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B108&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C108="","Nedostaje pol",IF($D108="","Nedostaje pojas",IF(COUNTA(G108:N108)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G108:N108&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E108),G108:N108)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E108,IF(AND(COUNTIF(G108:N108,"Fudokan sport kumite")&gt;0,O108=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G108:N108,"Fudokan sport kumite")=0,O108&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P108&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P108,4))="FSS-",MID(P108,LEN(P108)-2,1)="/",ISNUMBER(VALUE(RIGHT(P108,2))),VALUE(MID(P108,5,LEN(P108)-7))&gt;=1,VALUE(MID(P108,5,LEN(P108)-7))=INT(VALUE(MID(P108,5,LEN(P108)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R108">
         <f>IF($E108="","sve_discipline","disc_"&amp;$E108)</f>
         <v/>
       </c>
-      <c r="R108">
+      <c r="S108">
         <f>IF(OR($E108="",$C108=""),"sve_kilaze","kg_"&amp;$E108&amp;"_"&amp;IF($C108="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:18">
+    <row r="109" spans="1:19">
       <c r="A109" s="5"/>
       <c r="B109" s="5"/>
       <c r="C109" s="5"/>
@@ -4605,20 +4711,21 @@
       <c r="M109" s="5"/>
       <c r="N109" s="5"/>
       <c r="O109" s="5"/>
-      <c r="P109" s="8">
-        <f>IF(COUNTA($A109:$D109,G109:N109)=0,"",IF($A109="","Nedostaje godište",IF($E109="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B109="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B109&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C109="","Nedostaje pol",IF($D109="","Nedostaje pojas",IF(COUNTA(G109:N109)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G109:N109&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E109),G109:N109)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E109,IF(AND(COUNTIF(G109:N109,"Fudokan sport kumite")&gt;0,O109=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G109:N109,"Fudokan sport kumite")=0,O109&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q109">
+      <c r="P109" s="5"/>
+      <c r="Q109" s="8">
+        <f>IF(COUNTA($A109:$D109,G109:N109,P109)=0,"",IF($A109="","Nedostaje godište",IF($E109="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B109="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B109&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C109="","Nedostaje pol",IF($D109="","Nedostaje pojas",IF(COUNTA(G109:N109)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G109:N109&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E109),G109:N109)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E109,IF(AND(COUNTIF(G109:N109,"Fudokan sport kumite")&gt;0,O109=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G109:N109,"Fudokan sport kumite")=0,O109&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P109&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P109,4))="FSS-",MID(P109,LEN(P109)-2,1)="/",ISNUMBER(VALUE(RIGHT(P109,2))),VALUE(MID(P109,5,LEN(P109)-7))&gt;=1,VALUE(MID(P109,5,LEN(P109)-7))=INT(VALUE(MID(P109,5,LEN(P109)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R109">
         <f>IF($E109="","sve_discipline","disc_"&amp;$E109)</f>
         <v/>
       </c>
-      <c r="R109">
+      <c r="S109">
         <f>IF(OR($E109="",$C109=""),"sve_kilaze","kg_"&amp;$E109&amp;"_"&amp;IF($C109="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:18">
+    <row r="110" spans="1:19">
       <c r="A110" s="5"/>
       <c r="B110" s="5"/>
       <c r="C110" s="5"/>
@@ -4640,20 +4747,21 @@
       <c r="M110" s="5"/>
       <c r="N110" s="5"/>
       <c r="O110" s="5"/>
-      <c r="P110" s="8">
-        <f>IF(COUNTA($A110:$D110,G110:N110)=0,"",IF($A110="","Nedostaje godište",IF($E110="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B110="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B110&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C110="","Nedostaje pol",IF($D110="","Nedostaje pojas",IF(COUNTA(G110:N110)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G110:N110&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E110),G110:N110)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E110,IF(AND(COUNTIF(G110:N110,"Fudokan sport kumite")&gt;0,O110=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G110:N110,"Fudokan sport kumite")=0,O110&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q110">
+      <c r="P110" s="5"/>
+      <c r="Q110" s="8">
+        <f>IF(COUNTA($A110:$D110,G110:N110,P110)=0,"",IF($A110="","Nedostaje godište",IF($E110="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B110="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B110&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C110="","Nedostaje pol",IF($D110="","Nedostaje pojas",IF(COUNTA(G110:N110)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G110:N110&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E110),G110:N110)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E110,IF(AND(COUNTIF(G110:N110,"Fudokan sport kumite")&gt;0,O110=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G110:N110,"Fudokan sport kumite")=0,O110&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P110&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P110,4))="FSS-",MID(P110,LEN(P110)-2,1)="/",ISNUMBER(VALUE(RIGHT(P110,2))),VALUE(MID(P110,5,LEN(P110)-7))&gt;=1,VALUE(MID(P110,5,LEN(P110)-7))=INT(VALUE(MID(P110,5,LEN(P110)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R110">
         <f>IF($E110="","sve_discipline","disc_"&amp;$E110)</f>
         <v/>
       </c>
-      <c r="R110">
+      <c r="S110">
         <f>IF(OR($E110="",$C110=""),"sve_kilaze","kg_"&amp;$E110&amp;"_"&amp;IF($C110="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="111" spans="1:18">
+    <row r="111" spans="1:19">
       <c r="A111" s="5"/>
       <c r="B111" s="5"/>
       <c r="C111" s="5"/>
@@ -4675,20 +4783,21 @@
       <c r="M111" s="5"/>
       <c r="N111" s="5"/>
       <c r="O111" s="5"/>
-      <c r="P111" s="8">
-        <f>IF(COUNTA($A111:$D111,G111:N111)=0,"",IF($A111="","Nedostaje godište",IF($E111="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B111="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B111&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C111="","Nedostaje pol",IF($D111="","Nedostaje pojas",IF(COUNTA(G111:N111)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G111:N111&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E111),G111:N111)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E111,IF(AND(COUNTIF(G111:N111,"Fudokan sport kumite")&gt;0,O111=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G111:N111,"Fudokan sport kumite")=0,O111&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q111">
+      <c r="P111" s="5"/>
+      <c r="Q111" s="8">
+        <f>IF(COUNTA($A111:$D111,G111:N111,P111)=0,"",IF($A111="","Nedostaje godište",IF($E111="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B111="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B111&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C111="","Nedostaje pol",IF($D111="","Nedostaje pojas",IF(COUNTA(G111:N111)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G111:N111&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E111),G111:N111)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E111,IF(AND(COUNTIF(G111:N111,"Fudokan sport kumite")&gt;0,O111=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G111:N111,"Fudokan sport kumite")=0,O111&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P111&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P111,4))="FSS-",MID(P111,LEN(P111)-2,1)="/",ISNUMBER(VALUE(RIGHT(P111,2))),VALUE(MID(P111,5,LEN(P111)-7))&gt;=1,VALUE(MID(P111,5,LEN(P111)-7))=INT(VALUE(MID(P111,5,LEN(P111)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R111">
         <f>IF($E111="","sve_discipline","disc_"&amp;$E111)</f>
         <v/>
       </c>
-      <c r="R111">
+      <c r="S111">
         <f>IF(OR($E111="",$C111=""),"sve_kilaze","kg_"&amp;$E111&amp;"_"&amp;IF($C111="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="112" spans="1:18">
+    <row r="112" spans="1:19">
       <c r="A112" s="5"/>
       <c r="B112" s="5"/>
       <c r="C112" s="5"/>
@@ -4710,20 +4819,21 @@
       <c r="M112" s="5"/>
       <c r="N112" s="5"/>
       <c r="O112" s="5"/>
-      <c r="P112" s="8">
-        <f>IF(COUNTA($A112:$D112,G112:N112)=0,"",IF($A112="","Nedostaje godište",IF($E112="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B112="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B112&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C112="","Nedostaje pol",IF($D112="","Nedostaje pojas",IF(COUNTA(G112:N112)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G112:N112&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E112),G112:N112)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E112,IF(AND(COUNTIF(G112:N112,"Fudokan sport kumite")&gt;0,O112=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G112:N112,"Fudokan sport kumite")=0,O112&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q112">
+      <c r="P112" s="5"/>
+      <c r="Q112" s="8">
+        <f>IF(COUNTA($A112:$D112,G112:N112,P112)=0,"",IF($A112="","Nedostaje godište",IF($E112="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B112="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B112&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C112="","Nedostaje pol",IF($D112="","Nedostaje pojas",IF(COUNTA(G112:N112)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G112:N112&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E112),G112:N112)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E112,IF(AND(COUNTIF(G112:N112,"Fudokan sport kumite")&gt;0,O112=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G112:N112,"Fudokan sport kumite")=0,O112&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P112&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P112,4))="FSS-",MID(P112,LEN(P112)-2,1)="/",ISNUMBER(VALUE(RIGHT(P112,2))),VALUE(MID(P112,5,LEN(P112)-7))&gt;=1,VALUE(MID(P112,5,LEN(P112)-7))=INT(VALUE(MID(P112,5,LEN(P112)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R112">
         <f>IF($E112="","sve_discipline","disc_"&amp;$E112)</f>
         <v/>
       </c>
-      <c r="R112">
+      <c r="S112">
         <f>IF(OR($E112="",$C112=""),"sve_kilaze","kg_"&amp;$E112&amp;"_"&amp;IF($C112="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="113" spans="1:18">
+    <row r="113" spans="1:19">
       <c r="A113" s="5"/>
       <c r="B113" s="5"/>
       <c r="C113" s="5"/>
@@ -4745,20 +4855,21 @@
       <c r="M113" s="5"/>
       <c r="N113" s="5"/>
       <c r="O113" s="5"/>
-      <c r="P113" s="8">
-        <f>IF(COUNTA($A113:$D113,G113:N113)=0,"",IF($A113="","Nedostaje godište",IF($E113="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B113="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B113&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C113="","Nedostaje pol",IF($D113="","Nedostaje pojas",IF(COUNTA(G113:N113)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G113:N113&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E113),G113:N113)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E113,IF(AND(COUNTIF(G113:N113,"Fudokan sport kumite")&gt;0,O113=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G113:N113,"Fudokan sport kumite")=0,O113&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q113">
+      <c r="P113" s="5"/>
+      <c r="Q113" s="8">
+        <f>IF(COUNTA($A113:$D113,G113:N113,P113)=0,"",IF($A113="","Nedostaje godište",IF($E113="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B113="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B113&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C113="","Nedostaje pol",IF($D113="","Nedostaje pojas",IF(COUNTA(G113:N113)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G113:N113&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E113),G113:N113)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E113,IF(AND(COUNTIF(G113:N113,"Fudokan sport kumite")&gt;0,O113=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G113:N113,"Fudokan sport kumite")=0,O113&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P113&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P113,4))="FSS-",MID(P113,LEN(P113)-2,1)="/",ISNUMBER(VALUE(RIGHT(P113,2))),VALUE(MID(P113,5,LEN(P113)-7))&gt;=1,VALUE(MID(P113,5,LEN(P113)-7))=INT(VALUE(MID(P113,5,LEN(P113)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R113">
         <f>IF($E113="","sve_discipline","disc_"&amp;$E113)</f>
         <v/>
       </c>
-      <c r="R113">
+      <c r="S113">
         <f>IF(OR($E113="",$C113=""),"sve_kilaze","kg_"&amp;$E113&amp;"_"&amp;IF($C113="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:18">
+    <row r="114" spans="1:19">
       <c r="A114" s="5"/>
       <c r="B114" s="5"/>
       <c r="C114" s="5"/>
@@ -4780,20 +4891,21 @@
       <c r="M114" s="5"/>
       <c r="N114" s="5"/>
       <c r="O114" s="5"/>
-      <c r="P114" s="8">
-        <f>IF(COUNTA($A114:$D114,G114:N114)=0,"",IF($A114="","Nedostaje godište",IF($E114="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B114="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B114&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C114="","Nedostaje pol",IF($D114="","Nedostaje pojas",IF(COUNTA(G114:N114)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G114:N114&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E114),G114:N114)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E114,IF(AND(COUNTIF(G114:N114,"Fudokan sport kumite")&gt;0,O114=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G114:N114,"Fudokan sport kumite")=0,O114&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q114">
+      <c r="P114" s="5"/>
+      <c r="Q114" s="8">
+        <f>IF(COUNTA($A114:$D114,G114:N114,P114)=0,"",IF($A114="","Nedostaje godište",IF($E114="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B114="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B114&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C114="","Nedostaje pol",IF($D114="","Nedostaje pojas",IF(COUNTA(G114:N114)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G114:N114&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E114),G114:N114)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E114,IF(AND(COUNTIF(G114:N114,"Fudokan sport kumite")&gt;0,O114=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G114:N114,"Fudokan sport kumite")=0,O114&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P114&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P114,4))="FSS-",MID(P114,LEN(P114)-2,1)="/",ISNUMBER(VALUE(RIGHT(P114,2))),VALUE(MID(P114,5,LEN(P114)-7))&gt;=1,VALUE(MID(P114,5,LEN(P114)-7))=INT(VALUE(MID(P114,5,LEN(P114)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R114">
         <f>IF($E114="","sve_discipline","disc_"&amp;$E114)</f>
         <v/>
       </c>
-      <c r="R114">
+      <c r="S114">
         <f>IF(OR($E114="",$C114=""),"sve_kilaze","kg_"&amp;$E114&amp;"_"&amp;IF($C114="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:18">
+    <row r="115" spans="1:19">
       <c r="A115" s="5"/>
       <c r="B115" s="5"/>
       <c r="C115" s="5"/>
@@ -4815,20 +4927,21 @@
       <c r="M115" s="5"/>
       <c r="N115" s="5"/>
       <c r="O115" s="5"/>
-      <c r="P115" s="8">
-        <f>IF(COUNTA($A115:$D115,G115:N115)=0,"",IF($A115="","Nedostaje godište",IF($E115="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B115="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B115&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C115="","Nedostaje pol",IF($D115="","Nedostaje pojas",IF(COUNTA(G115:N115)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G115:N115&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E115),G115:N115)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E115,IF(AND(COUNTIF(G115:N115,"Fudokan sport kumite")&gt;0,O115=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G115:N115,"Fudokan sport kumite")=0,O115&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q115">
+      <c r="P115" s="5"/>
+      <c r="Q115" s="8">
+        <f>IF(COUNTA($A115:$D115,G115:N115,P115)=0,"",IF($A115="","Nedostaje godište",IF($E115="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B115="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B115&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C115="","Nedostaje pol",IF($D115="","Nedostaje pojas",IF(COUNTA(G115:N115)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G115:N115&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E115),G115:N115)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E115,IF(AND(COUNTIF(G115:N115,"Fudokan sport kumite")&gt;0,O115=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G115:N115,"Fudokan sport kumite")=0,O115&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P115&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P115,4))="FSS-",MID(P115,LEN(P115)-2,1)="/",ISNUMBER(VALUE(RIGHT(P115,2))),VALUE(MID(P115,5,LEN(P115)-7))&gt;=1,VALUE(MID(P115,5,LEN(P115)-7))=INT(VALUE(MID(P115,5,LEN(P115)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R115">
         <f>IF($E115="","sve_discipline","disc_"&amp;$E115)</f>
         <v/>
       </c>
-      <c r="R115">
+      <c r="S115">
         <f>IF(OR($E115="",$C115=""),"sve_kilaze","kg_"&amp;$E115&amp;"_"&amp;IF($C115="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="116" spans="1:18">
+    <row r="116" spans="1:19">
       <c r="A116" s="5"/>
       <c r="B116" s="5"/>
       <c r="C116" s="5"/>
@@ -4850,20 +4963,21 @@
       <c r="M116" s="5"/>
       <c r="N116" s="5"/>
       <c r="O116" s="5"/>
-      <c r="P116" s="8">
-        <f>IF(COUNTA($A116:$D116,G116:N116)=0,"",IF($A116="","Nedostaje godište",IF($E116="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B116="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B116&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C116="","Nedostaje pol",IF($D116="","Nedostaje pojas",IF(COUNTA(G116:N116)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G116:N116&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E116),G116:N116)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E116,IF(AND(COUNTIF(G116:N116,"Fudokan sport kumite")&gt;0,O116=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G116:N116,"Fudokan sport kumite")=0,O116&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q116">
+      <c r="P116" s="5"/>
+      <c r="Q116" s="8">
+        <f>IF(COUNTA($A116:$D116,G116:N116,P116)=0,"",IF($A116="","Nedostaje godište",IF($E116="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B116="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B116&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C116="","Nedostaje pol",IF($D116="","Nedostaje pojas",IF(COUNTA(G116:N116)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G116:N116&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E116),G116:N116)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E116,IF(AND(COUNTIF(G116:N116,"Fudokan sport kumite")&gt;0,O116=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G116:N116,"Fudokan sport kumite")=0,O116&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P116&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P116,4))="FSS-",MID(P116,LEN(P116)-2,1)="/",ISNUMBER(VALUE(RIGHT(P116,2))),VALUE(MID(P116,5,LEN(P116)-7))&gt;=1,VALUE(MID(P116,5,LEN(P116)-7))=INT(VALUE(MID(P116,5,LEN(P116)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R116">
         <f>IF($E116="","sve_discipline","disc_"&amp;$E116)</f>
         <v/>
       </c>
-      <c r="R116">
+      <c r="S116">
         <f>IF(OR($E116="",$C116=""),"sve_kilaze","kg_"&amp;$E116&amp;"_"&amp;IF($C116="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:18">
+    <row r="117" spans="1:19">
       <c r="A117" s="5"/>
       <c r="B117" s="5"/>
       <c r="C117" s="5"/>
@@ -4885,20 +4999,21 @@
       <c r="M117" s="5"/>
       <c r="N117" s="5"/>
       <c r="O117" s="5"/>
-      <c r="P117" s="8">
-        <f>IF(COUNTA($A117:$D117,G117:N117)=0,"",IF($A117="","Nedostaje godište",IF($E117="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B117="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B117&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C117="","Nedostaje pol",IF($D117="","Nedostaje pojas",IF(COUNTA(G117:N117)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G117:N117&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E117),G117:N117)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E117,IF(AND(COUNTIF(G117:N117,"Fudokan sport kumite")&gt;0,O117=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G117:N117,"Fudokan sport kumite")=0,O117&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q117">
+      <c r="P117" s="5"/>
+      <c r="Q117" s="8">
+        <f>IF(COUNTA($A117:$D117,G117:N117,P117)=0,"",IF($A117="","Nedostaje godište",IF($E117="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B117="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B117&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C117="","Nedostaje pol",IF($D117="","Nedostaje pojas",IF(COUNTA(G117:N117)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G117:N117&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E117),G117:N117)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E117,IF(AND(COUNTIF(G117:N117,"Fudokan sport kumite")&gt;0,O117=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G117:N117,"Fudokan sport kumite")=0,O117&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P117&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P117,4))="FSS-",MID(P117,LEN(P117)-2,1)="/",ISNUMBER(VALUE(RIGHT(P117,2))),VALUE(MID(P117,5,LEN(P117)-7))&gt;=1,VALUE(MID(P117,5,LEN(P117)-7))=INT(VALUE(MID(P117,5,LEN(P117)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R117">
         <f>IF($E117="","sve_discipline","disc_"&amp;$E117)</f>
         <v/>
       </c>
-      <c r="R117">
+      <c r="S117">
         <f>IF(OR($E117="",$C117=""),"sve_kilaze","kg_"&amp;$E117&amp;"_"&amp;IF($C117="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:18">
+    <row r="118" spans="1:19">
       <c r="A118" s="5"/>
       <c r="B118" s="5"/>
       <c r="C118" s="5"/>
@@ -4920,20 +5035,21 @@
       <c r="M118" s="5"/>
       <c r="N118" s="5"/>
       <c r="O118" s="5"/>
-      <c r="P118" s="8">
-        <f>IF(COUNTA($A118:$D118,G118:N118)=0,"",IF($A118="","Nedostaje godište",IF($E118="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B118="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B118&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C118="","Nedostaje pol",IF($D118="","Nedostaje pojas",IF(COUNTA(G118:N118)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G118:N118&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E118),G118:N118)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E118,IF(AND(COUNTIF(G118:N118,"Fudokan sport kumite")&gt;0,O118=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G118:N118,"Fudokan sport kumite")=0,O118&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q118">
+      <c r="P118" s="5"/>
+      <c r="Q118" s="8">
+        <f>IF(COUNTA($A118:$D118,G118:N118,P118)=0,"",IF($A118="","Nedostaje godište",IF($E118="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B118="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B118&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C118="","Nedostaje pol",IF($D118="","Nedostaje pojas",IF(COUNTA(G118:N118)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G118:N118&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E118),G118:N118)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E118,IF(AND(COUNTIF(G118:N118,"Fudokan sport kumite")&gt;0,O118=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G118:N118,"Fudokan sport kumite")=0,O118&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P118&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P118,4))="FSS-",MID(P118,LEN(P118)-2,1)="/",ISNUMBER(VALUE(RIGHT(P118,2))),VALUE(MID(P118,5,LEN(P118)-7))&gt;=1,VALUE(MID(P118,5,LEN(P118)-7))=INT(VALUE(MID(P118,5,LEN(P118)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R118">
         <f>IF($E118="","sve_discipline","disc_"&amp;$E118)</f>
         <v/>
       </c>
-      <c r="R118">
+      <c r="S118">
         <f>IF(OR($E118="",$C118=""),"sve_kilaze","kg_"&amp;$E118&amp;"_"&amp;IF($C118="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:18">
+    <row r="119" spans="1:19">
       <c r="A119" s="5"/>
       <c r="B119" s="5"/>
       <c r="C119" s="5"/>
@@ -4955,20 +5071,21 @@
       <c r="M119" s="5"/>
       <c r="N119" s="5"/>
       <c r="O119" s="5"/>
-      <c r="P119" s="8">
-        <f>IF(COUNTA($A119:$D119,G119:N119)=0,"",IF($A119="","Nedostaje godište",IF($E119="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B119="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B119&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C119="","Nedostaje pol",IF($D119="","Nedostaje pojas",IF(COUNTA(G119:N119)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G119:N119&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E119),G119:N119)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E119,IF(AND(COUNTIF(G119:N119,"Fudokan sport kumite")&gt;0,O119=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G119:N119,"Fudokan sport kumite")=0,O119&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q119">
+      <c r="P119" s="5"/>
+      <c r="Q119" s="8">
+        <f>IF(COUNTA($A119:$D119,G119:N119,P119)=0,"",IF($A119="","Nedostaje godište",IF($E119="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B119="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B119&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C119="","Nedostaje pol",IF($D119="","Nedostaje pojas",IF(COUNTA(G119:N119)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G119:N119&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E119),G119:N119)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E119,IF(AND(COUNTIF(G119:N119,"Fudokan sport kumite")&gt;0,O119=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G119:N119,"Fudokan sport kumite")=0,O119&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P119&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P119,4))="FSS-",MID(P119,LEN(P119)-2,1)="/",ISNUMBER(VALUE(RIGHT(P119,2))),VALUE(MID(P119,5,LEN(P119)-7))&gt;=1,VALUE(MID(P119,5,LEN(P119)-7))=INT(VALUE(MID(P119,5,LEN(P119)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R119">
         <f>IF($E119="","sve_discipline","disc_"&amp;$E119)</f>
         <v/>
       </c>
-      <c r="R119">
+      <c r="S119">
         <f>IF(OR($E119="",$C119=""),"sve_kilaze","kg_"&amp;$E119&amp;"_"&amp;IF($C119="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:18">
+    <row r="120" spans="1:19">
       <c r="A120" s="5"/>
       <c r="B120" s="5"/>
       <c r="C120" s="5"/>
@@ -4990,20 +5107,21 @@
       <c r="M120" s="5"/>
       <c r="N120" s="5"/>
       <c r="O120" s="5"/>
-      <c r="P120" s="8">
-        <f>IF(COUNTA($A120:$D120,G120:N120)=0,"",IF($A120="","Nedostaje godište",IF($E120="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B120="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B120&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C120="","Nedostaje pol",IF($D120="","Nedostaje pojas",IF(COUNTA(G120:N120)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G120:N120&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E120),G120:N120)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E120,IF(AND(COUNTIF(G120:N120,"Fudokan sport kumite")&gt;0,O120=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G120:N120,"Fudokan sport kumite")=0,O120&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q120">
+      <c r="P120" s="5"/>
+      <c r="Q120" s="8">
+        <f>IF(COUNTA($A120:$D120,G120:N120,P120)=0,"",IF($A120="","Nedostaje godište",IF($E120="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B120="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B120&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C120="","Nedostaje pol",IF($D120="","Nedostaje pojas",IF(COUNTA(G120:N120)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G120:N120&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E120),G120:N120)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E120,IF(AND(COUNTIF(G120:N120,"Fudokan sport kumite")&gt;0,O120=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G120:N120,"Fudokan sport kumite")=0,O120&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P120&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P120,4))="FSS-",MID(P120,LEN(P120)-2,1)="/",ISNUMBER(VALUE(RIGHT(P120,2))),VALUE(MID(P120,5,LEN(P120)-7))&gt;=1,VALUE(MID(P120,5,LEN(P120)-7))=INT(VALUE(MID(P120,5,LEN(P120)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R120">
         <f>IF($E120="","sve_discipline","disc_"&amp;$E120)</f>
         <v/>
       </c>
-      <c r="R120">
+      <c r="S120">
         <f>IF(OR($E120="",$C120=""),"sve_kilaze","kg_"&amp;$E120&amp;"_"&amp;IF($C120="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:18">
+    <row r="121" spans="1:19">
       <c r="A121" s="5"/>
       <c r="B121" s="5"/>
       <c r="C121" s="5"/>
@@ -5025,20 +5143,21 @@
       <c r="M121" s="5"/>
       <c r="N121" s="5"/>
       <c r="O121" s="5"/>
-      <c r="P121" s="8">
-        <f>IF(COUNTA($A121:$D121,G121:N121)=0,"",IF($A121="","Nedostaje godište",IF($E121="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B121="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B121&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C121="","Nedostaje pol",IF($D121="","Nedostaje pojas",IF(COUNTA(G121:N121)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G121:N121&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E121),G121:N121)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E121,IF(AND(COUNTIF(G121:N121,"Fudokan sport kumite")&gt;0,O121=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G121:N121,"Fudokan sport kumite")=0,O121&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q121">
+      <c r="P121" s="5"/>
+      <c r="Q121" s="8">
+        <f>IF(COUNTA($A121:$D121,G121:N121,P121)=0,"",IF($A121="","Nedostaje godište",IF($E121="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B121="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B121&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C121="","Nedostaje pol",IF($D121="","Nedostaje pojas",IF(COUNTA(G121:N121)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G121:N121&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E121),G121:N121)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E121,IF(AND(COUNTIF(G121:N121,"Fudokan sport kumite")&gt;0,O121=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G121:N121,"Fudokan sport kumite")=0,O121&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P121&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P121,4))="FSS-",MID(P121,LEN(P121)-2,1)="/",ISNUMBER(VALUE(RIGHT(P121,2))),VALUE(MID(P121,5,LEN(P121)-7))&gt;=1,VALUE(MID(P121,5,LEN(P121)-7))=INT(VALUE(MID(P121,5,LEN(P121)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R121">
         <f>IF($E121="","sve_discipline","disc_"&amp;$E121)</f>
         <v/>
       </c>
-      <c r="R121">
+      <c r="S121">
         <f>IF(OR($E121="",$C121=""),"sve_kilaze","kg_"&amp;$E121&amp;"_"&amp;IF($C121="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="122" spans="1:18">
+    <row r="122" spans="1:19">
       <c r="A122" s="5"/>
       <c r="B122" s="5"/>
       <c r="C122" s="5"/>
@@ -5060,20 +5179,21 @@
       <c r="M122" s="5"/>
       <c r="N122" s="5"/>
       <c r="O122" s="5"/>
-      <c r="P122" s="8">
-        <f>IF(COUNTA($A122:$D122,G122:N122)=0,"",IF($A122="","Nedostaje godište",IF($E122="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B122="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B122&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C122="","Nedostaje pol",IF($D122="","Nedostaje pojas",IF(COUNTA(G122:N122)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G122:N122&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E122),G122:N122)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E122,IF(AND(COUNTIF(G122:N122,"Fudokan sport kumite")&gt;0,O122=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G122:N122,"Fudokan sport kumite")=0,O122&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q122">
+      <c r="P122" s="5"/>
+      <c r="Q122" s="8">
+        <f>IF(COUNTA($A122:$D122,G122:N122,P122)=0,"",IF($A122="","Nedostaje godište",IF($E122="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B122="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B122&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C122="","Nedostaje pol",IF($D122="","Nedostaje pojas",IF(COUNTA(G122:N122)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G122:N122&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E122),G122:N122)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E122,IF(AND(COUNTIF(G122:N122,"Fudokan sport kumite")&gt;0,O122=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G122:N122,"Fudokan sport kumite")=0,O122&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P122&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P122,4))="FSS-",MID(P122,LEN(P122)-2,1)="/",ISNUMBER(VALUE(RIGHT(P122,2))),VALUE(MID(P122,5,LEN(P122)-7))&gt;=1,VALUE(MID(P122,5,LEN(P122)-7))=INT(VALUE(MID(P122,5,LEN(P122)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R122">
         <f>IF($E122="","sve_discipline","disc_"&amp;$E122)</f>
         <v/>
       </c>
-      <c r="R122">
+      <c r="S122">
         <f>IF(OR($E122="",$C122=""),"sve_kilaze","kg_"&amp;$E122&amp;"_"&amp;IF($C122="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="123" spans="1:18">
+    <row r="123" spans="1:19">
       <c r="A123" s="5"/>
       <c r="B123" s="5"/>
       <c r="C123" s="5"/>
@@ -5095,20 +5215,21 @@
       <c r="M123" s="5"/>
       <c r="N123" s="5"/>
       <c r="O123" s="5"/>
-      <c r="P123" s="8">
-        <f>IF(COUNTA($A123:$D123,G123:N123)=0,"",IF($A123="","Nedostaje godište",IF($E123="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B123="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B123&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C123="","Nedostaje pol",IF($D123="","Nedostaje pojas",IF(COUNTA(G123:N123)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G123:N123&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E123),G123:N123)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E123,IF(AND(COUNTIF(G123:N123,"Fudokan sport kumite")&gt;0,O123=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G123:N123,"Fudokan sport kumite")=0,O123&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q123">
+      <c r="P123" s="5"/>
+      <c r="Q123" s="8">
+        <f>IF(COUNTA($A123:$D123,G123:N123,P123)=0,"",IF($A123="","Nedostaje godište",IF($E123="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B123="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B123&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C123="","Nedostaje pol",IF($D123="","Nedostaje pojas",IF(COUNTA(G123:N123)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G123:N123&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E123),G123:N123)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E123,IF(AND(COUNTIF(G123:N123,"Fudokan sport kumite")&gt;0,O123=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G123:N123,"Fudokan sport kumite")=0,O123&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P123&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P123,4))="FSS-",MID(P123,LEN(P123)-2,1)="/",ISNUMBER(VALUE(RIGHT(P123,2))),VALUE(MID(P123,5,LEN(P123)-7))&gt;=1,VALUE(MID(P123,5,LEN(P123)-7))=INT(VALUE(MID(P123,5,LEN(P123)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R123">
         <f>IF($E123="","sve_discipline","disc_"&amp;$E123)</f>
         <v/>
       </c>
-      <c r="R123">
+      <c r="S123">
         <f>IF(OR($E123="",$C123=""),"sve_kilaze","kg_"&amp;$E123&amp;"_"&amp;IF($C123="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="124" spans="1:18">
+    <row r="124" spans="1:19">
       <c r="A124" s="5"/>
       <c r="B124" s="5"/>
       <c r="C124" s="5"/>
@@ -5130,20 +5251,21 @@
       <c r="M124" s="5"/>
       <c r="N124" s="5"/>
       <c r="O124" s="5"/>
-      <c r="P124" s="8">
-        <f>IF(COUNTA($A124:$D124,G124:N124)=0,"",IF($A124="","Nedostaje godište",IF($E124="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B124="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B124&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C124="","Nedostaje pol",IF($D124="","Nedostaje pojas",IF(COUNTA(G124:N124)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G124:N124&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E124),G124:N124)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E124,IF(AND(COUNTIF(G124:N124,"Fudokan sport kumite")&gt;0,O124=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G124:N124,"Fudokan sport kumite")=0,O124&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q124">
+      <c r="P124" s="5"/>
+      <c r="Q124" s="8">
+        <f>IF(COUNTA($A124:$D124,G124:N124,P124)=0,"",IF($A124="","Nedostaje godište",IF($E124="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B124="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B124&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C124="","Nedostaje pol",IF($D124="","Nedostaje pojas",IF(COUNTA(G124:N124)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G124:N124&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E124),G124:N124)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E124,IF(AND(COUNTIF(G124:N124,"Fudokan sport kumite")&gt;0,O124=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G124:N124,"Fudokan sport kumite")=0,O124&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P124&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P124,4))="FSS-",MID(P124,LEN(P124)-2,1)="/",ISNUMBER(VALUE(RIGHT(P124,2))),VALUE(MID(P124,5,LEN(P124)-7))&gt;=1,VALUE(MID(P124,5,LEN(P124)-7))=INT(VALUE(MID(P124,5,LEN(P124)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R124">
         <f>IF($E124="","sve_discipline","disc_"&amp;$E124)</f>
         <v/>
       </c>
-      <c r="R124">
+      <c r="S124">
         <f>IF(OR($E124="",$C124=""),"sve_kilaze","kg_"&amp;$E124&amp;"_"&amp;IF($C124="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:18">
+    <row r="125" spans="1:19">
       <c r="A125" s="5"/>
       <c r="B125" s="5"/>
       <c r="C125" s="5"/>
@@ -5165,20 +5287,21 @@
       <c r="M125" s="5"/>
       <c r="N125" s="5"/>
       <c r="O125" s="5"/>
-      <c r="P125" s="8">
-        <f>IF(COUNTA($A125:$D125,G125:N125)=0,"",IF($A125="","Nedostaje godište",IF($E125="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B125="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B125&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C125="","Nedostaje pol",IF($D125="","Nedostaje pojas",IF(COUNTA(G125:N125)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G125:N125&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E125),G125:N125)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E125,IF(AND(COUNTIF(G125:N125,"Fudokan sport kumite")&gt;0,O125=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G125:N125,"Fudokan sport kumite")=0,O125&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q125">
+      <c r="P125" s="5"/>
+      <c r="Q125" s="8">
+        <f>IF(COUNTA($A125:$D125,G125:N125,P125)=0,"",IF($A125="","Nedostaje godište",IF($E125="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B125="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B125&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C125="","Nedostaje pol",IF($D125="","Nedostaje pojas",IF(COUNTA(G125:N125)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G125:N125&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E125),G125:N125)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E125,IF(AND(COUNTIF(G125:N125,"Fudokan sport kumite")&gt;0,O125=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G125:N125,"Fudokan sport kumite")=0,O125&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P125&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P125,4))="FSS-",MID(P125,LEN(P125)-2,1)="/",ISNUMBER(VALUE(RIGHT(P125,2))),VALUE(MID(P125,5,LEN(P125)-7))&gt;=1,VALUE(MID(P125,5,LEN(P125)-7))=INT(VALUE(MID(P125,5,LEN(P125)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R125">
         <f>IF($E125="","sve_discipline","disc_"&amp;$E125)</f>
         <v/>
       </c>
-      <c r="R125">
+      <c r="S125">
         <f>IF(OR($E125="",$C125=""),"sve_kilaze","kg_"&amp;$E125&amp;"_"&amp;IF($C125="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:18">
+    <row r="126" spans="1:19">
       <c r="A126" s="5"/>
       <c r="B126" s="5"/>
       <c r="C126" s="5"/>
@@ -5200,20 +5323,21 @@
       <c r="M126" s="5"/>
       <c r="N126" s="5"/>
       <c r="O126" s="5"/>
-      <c r="P126" s="8">
-        <f>IF(COUNTA($A126:$D126,G126:N126)=0,"",IF($A126="","Nedostaje godište",IF($E126="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B126="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B126&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C126="","Nedostaje pol",IF($D126="","Nedostaje pojas",IF(COUNTA(G126:N126)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G126:N126&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E126),G126:N126)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E126,IF(AND(COUNTIF(G126:N126,"Fudokan sport kumite")&gt;0,O126=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G126:N126,"Fudokan sport kumite")=0,O126&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q126">
+      <c r="P126" s="5"/>
+      <c r="Q126" s="8">
+        <f>IF(COUNTA($A126:$D126,G126:N126,P126)=0,"",IF($A126="","Nedostaje godište",IF($E126="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B126="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B126&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C126="","Nedostaje pol",IF($D126="","Nedostaje pojas",IF(COUNTA(G126:N126)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G126:N126&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E126),G126:N126)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E126,IF(AND(COUNTIF(G126:N126,"Fudokan sport kumite")&gt;0,O126=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G126:N126,"Fudokan sport kumite")=0,O126&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P126&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P126,4))="FSS-",MID(P126,LEN(P126)-2,1)="/",ISNUMBER(VALUE(RIGHT(P126,2))),VALUE(MID(P126,5,LEN(P126)-7))&gt;=1,VALUE(MID(P126,5,LEN(P126)-7))=INT(VALUE(MID(P126,5,LEN(P126)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R126">
         <f>IF($E126="","sve_discipline","disc_"&amp;$E126)</f>
         <v/>
       </c>
-      <c r="R126">
+      <c r="S126">
         <f>IF(OR($E126="",$C126=""),"sve_kilaze","kg_"&amp;$E126&amp;"_"&amp;IF($C126="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:18">
+    <row r="127" spans="1:19">
       <c r="A127" s="5"/>
       <c r="B127" s="5"/>
       <c r="C127" s="5"/>
@@ -5235,20 +5359,21 @@
       <c r="M127" s="5"/>
       <c r="N127" s="5"/>
       <c r="O127" s="5"/>
-      <c r="P127" s="8">
-        <f>IF(COUNTA($A127:$D127,G127:N127)=0,"",IF($A127="","Nedostaje godište",IF($E127="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B127="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B127&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C127="","Nedostaje pol",IF($D127="","Nedostaje pojas",IF(COUNTA(G127:N127)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G127:N127&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E127),G127:N127)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E127,IF(AND(COUNTIF(G127:N127,"Fudokan sport kumite")&gt;0,O127=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G127:N127,"Fudokan sport kumite")=0,O127&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q127">
+      <c r="P127" s="5"/>
+      <c r="Q127" s="8">
+        <f>IF(COUNTA($A127:$D127,G127:N127,P127)=0,"",IF($A127="","Nedostaje godište",IF($E127="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B127="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B127&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C127="","Nedostaje pol",IF($D127="","Nedostaje pojas",IF(COUNTA(G127:N127)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G127:N127&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E127),G127:N127)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E127,IF(AND(COUNTIF(G127:N127,"Fudokan sport kumite")&gt;0,O127=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G127:N127,"Fudokan sport kumite")=0,O127&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P127&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P127,4))="FSS-",MID(P127,LEN(P127)-2,1)="/",ISNUMBER(VALUE(RIGHT(P127,2))),VALUE(MID(P127,5,LEN(P127)-7))&gt;=1,VALUE(MID(P127,5,LEN(P127)-7))=INT(VALUE(MID(P127,5,LEN(P127)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R127">
         <f>IF($E127="","sve_discipline","disc_"&amp;$E127)</f>
         <v/>
       </c>
-      <c r="R127">
+      <c r="S127">
         <f>IF(OR($E127="",$C127=""),"sve_kilaze","kg_"&amp;$E127&amp;"_"&amp;IF($C127="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="128" spans="1:18">
+    <row r="128" spans="1:19">
       <c r="A128" s="5"/>
       <c r="B128" s="5"/>
       <c r="C128" s="5"/>
@@ -5270,20 +5395,21 @@
       <c r="M128" s="5"/>
       <c r="N128" s="5"/>
       <c r="O128" s="5"/>
-      <c r="P128" s="8">
-        <f>IF(COUNTA($A128:$D128,G128:N128)=0,"",IF($A128="","Nedostaje godište",IF($E128="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B128="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B128&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C128="","Nedostaje pol",IF($D128="","Nedostaje pojas",IF(COUNTA(G128:N128)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G128:N128&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E128),G128:N128)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E128,IF(AND(COUNTIF(G128:N128,"Fudokan sport kumite")&gt;0,O128=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G128:N128,"Fudokan sport kumite")=0,O128&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q128">
+      <c r="P128" s="5"/>
+      <c r="Q128" s="8">
+        <f>IF(COUNTA($A128:$D128,G128:N128,P128)=0,"",IF($A128="","Nedostaje godište",IF($E128="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B128="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B128&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C128="","Nedostaje pol",IF($D128="","Nedostaje pojas",IF(COUNTA(G128:N128)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G128:N128&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E128),G128:N128)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E128,IF(AND(COUNTIF(G128:N128,"Fudokan sport kumite")&gt;0,O128=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G128:N128,"Fudokan sport kumite")=0,O128&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P128&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P128,4))="FSS-",MID(P128,LEN(P128)-2,1)="/",ISNUMBER(VALUE(RIGHT(P128,2))),VALUE(MID(P128,5,LEN(P128)-7))&gt;=1,VALUE(MID(P128,5,LEN(P128)-7))=INT(VALUE(MID(P128,5,LEN(P128)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R128">
         <f>IF($E128="","sve_discipline","disc_"&amp;$E128)</f>
         <v/>
       </c>
-      <c r="R128">
+      <c r="S128">
         <f>IF(OR($E128="",$C128=""),"sve_kilaze","kg_"&amp;$E128&amp;"_"&amp;IF($C128="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="129" spans="1:18">
+    <row r="129" spans="1:19">
       <c r="A129" s="5"/>
       <c r="B129" s="5"/>
       <c r="C129" s="5"/>
@@ -5305,20 +5431,21 @@
       <c r="M129" s="5"/>
       <c r="N129" s="5"/>
       <c r="O129" s="5"/>
-      <c r="P129" s="8">
-        <f>IF(COUNTA($A129:$D129,G129:N129)=0,"",IF($A129="","Nedostaje godište",IF($E129="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B129="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B129&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C129="","Nedostaje pol",IF($D129="","Nedostaje pojas",IF(COUNTA(G129:N129)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G129:N129&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E129),G129:N129)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E129,IF(AND(COUNTIF(G129:N129,"Fudokan sport kumite")&gt;0,O129=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G129:N129,"Fudokan sport kumite")=0,O129&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q129">
+      <c r="P129" s="5"/>
+      <c r="Q129" s="8">
+        <f>IF(COUNTA($A129:$D129,G129:N129,P129)=0,"",IF($A129="","Nedostaje godište",IF($E129="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B129="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B129&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C129="","Nedostaje pol",IF($D129="","Nedostaje pojas",IF(COUNTA(G129:N129)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G129:N129&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E129),G129:N129)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E129,IF(AND(COUNTIF(G129:N129,"Fudokan sport kumite")&gt;0,O129=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G129:N129,"Fudokan sport kumite")=0,O129&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P129&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P129,4))="FSS-",MID(P129,LEN(P129)-2,1)="/",ISNUMBER(VALUE(RIGHT(P129,2))),VALUE(MID(P129,5,LEN(P129)-7))&gt;=1,VALUE(MID(P129,5,LEN(P129)-7))=INT(VALUE(MID(P129,5,LEN(P129)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R129">
         <f>IF($E129="","sve_discipline","disc_"&amp;$E129)</f>
         <v/>
       </c>
-      <c r="R129">
+      <c r="S129">
         <f>IF(OR($E129="",$C129=""),"sve_kilaze","kg_"&amp;$E129&amp;"_"&amp;IF($C129="ženski","Z","M"))</f>
         <v/>
       </c>
     </row>
-    <row r="130" spans="1:18">
+    <row r="130" spans="1:19">
       <c r="A130" s="5"/>
       <c r="B130" s="5"/>
       <c r="C130" s="5"/>
@@ -5340,15 +5467,16 @@
       <c r="M130" s="5"/>
       <c r="N130" s="5"/>
       <c r="O130" s="5"/>
-      <c r="P130" s="8">
-        <f>IF(COUNTA($A130:$D130,G130:N130)=0,"",IF($A130="","Nedostaje godište",IF($E130="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B130="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B130&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C130="","Nedostaje pol",IF($D130="","Nedostaje pojas",IF(COUNTA(G130:N130)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G130:N130&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E130),G130:N130)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E130,IF(AND(COUNTIF(G130:N130,"Fudokan sport kumite")&gt;0,O130=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G130:N130,"Fudokan sport kumite")=0,O130&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))</f>
-        <v/>
-      </c>
-      <c r="Q130">
+      <c r="P130" s="5"/>
+      <c r="Q130" s="8">
+        <f>IF(COUNTA($A130:$D130,G130:N130,P130)=0,"",IF($A130="","Nedostaje godište",IF($E130="","Godište nije obuhvaćeno uzrasnom tabelom",IF($B130="","Nedostaje ime i prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B130&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C130="","Nedostaje pol",IF($D130="","Nedostaje pojas",IF(COUNTA(G130:N130)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(G130:N130&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$E130),G130:N130)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$E130,IF(AND(COUNTIF(G130:N130,"Fudokan sport kumite")&gt;0,O130=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(G130:N130,"Fudokan sport kumite")=0,O130&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite",IF(AND(P130&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT(P130,4))="FSS-",MID(P130,LEN(P130)-2,1)="/",ISNUMBER(VALUE(RIGHT(P130,2))),VALUE(MID(P130,5,LEN(P130)-7))&gt;=1,VALUE(MID(P130,5,LEN(P130)-7))=INT(VALUE(MID(P130,5,LEN(P130)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26","prijava je kompletna"))))))))))))</f>
+        <v/>
+      </c>
+      <c r="R130">
         <f>IF($E130="","sve_discipline","disc_"&amp;$E130)</f>
         <v/>
       </c>
-      <c r="R130">
+      <c r="S130">
         <f>IF(OR($E130="",$C130=""),"sve_kilaze","kg_"&amp;$E130&amp;"_"&amp;IF($C130="ženski","Z","M"))</f>
         <v/>
       </c>
@@ -5356,7 +5484,7 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <mergeCells count="1">
-    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="A3:Q3"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Godište" error="Godište se bira iz padajućeg menija." sqref="A11:A130">
@@ -5369,10 +5497,10 @@
       <formula1>pojasevi</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Disciplina" error="Godište se unosi pre discipline. Padajući meni nudi discipline koje su moguće u odnosu na uzrast." sqref="G11:N130">
-      <formula1>INDIRECT($Q11)</formula1>
+      <formula1>INDIRECT($R11)</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Telesna težina" error="Godište i pol unose se pre telesne težine. Telesna težina unosi se isključivo uz Fudokan sport kumite, budući da je tradicionalni kumite apsolutna kategorija." sqref="O11:O130">
-      <formula1>INDIRECT($R11)</formula1>
+      <formula1>INDIRECT($S11)</formula1>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Ime i prezime" error="Polje prima isključivo slova, razmak, crticu i apostrof; cifre nisu dozvoljene." sqref="B11:B130">
       <formula1>AND(ISERROR(FIND("0",B11)),ISERROR(FIND("1",B11)),ISERROR(FIND("2",B11)),ISERROR(FIND("3",B11)),ISERROR(FIND("4",B11)),ISERROR(FIND("5",B11)),ISERROR(FIND("6",B11)),ISERROR(FIND("7",B11)),ISERROR(FIND("8",B11)),ISERROR(FIND("9",B11)))</formula1>
@@ -5413,17 +5541,17 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="28" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -5451,7 +5579,7 @@
         <v/>
       </c>
       <c r="D4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -5474,10 +5602,10 @@
     </row>
     <row r="9" spans="1:18" ht="30" customHeight="1">
       <c r="A9" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>13</v>
@@ -5486,43 +5614,43 @@
         <v>14</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -9426,163 +9554,163 @@
   <sheetData>
     <row r="1" spans="1:54">
       <c r="A1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="R1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="S1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="T1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="U1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="V1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="W1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="X1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Y1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Z1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AA1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AB1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AC1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AD1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AE1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AF1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AH1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AI1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AJ1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AK1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AL1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AM1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AN1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AO1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AP1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AQ1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AR1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AS1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AT1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AU1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AV1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AW1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AX1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AY1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AZ1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="BA1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="BB1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" spans="1:54">
@@ -9590,148 +9718,148 @@
         <v>1906</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E2">
         <v>2026</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M2" t="s">
+        <v>101</v>
+      </c>
+      <c r="N2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O2" t="s">
+        <v>80</v>
+      </c>
+      <c r="P2" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>104</v>
+      </c>
+      <c r="R2" t="s">
+        <v>104</v>
+      </c>
+      <c r="S2" t="s">
+        <v>80</v>
+      </c>
+      <c r="T2" t="s">
         <v>94</v>
       </c>
-      <c r="M2" t="s">
-        <v>100</v>
-      </c>
-      <c r="N2" t="s">
-        <v>100</v>
-      </c>
-      <c r="O2" t="s">
-        <v>79</v>
-      </c>
-      <c r="P2" t="s">
+      <c r="U2" t="s">
+        <v>104</v>
+      </c>
+      <c r="V2" t="s">
+        <v>108</v>
+      </c>
+      <c r="W2" t="s">
+        <v>80</v>
+      </c>
+      <c r="X2" t="s">
         <v>94</v>
       </c>
-      <c r="Q2" t="s">
-        <v>103</v>
-      </c>
-      <c r="R2" t="s">
-        <v>103</v>
-      </c>
-      <c r="S2" t="s">
-        <v>79</v>
-      </c>
-      <c r="T2" t="s">
-        <v>93</v>
-      </c>
-      <c r="U2" t="s">
-        <v>103</v>
-      </c>
-      <c r="V2" t="s">
-        <v>107</v>
-      </c>
-      <c r="W2" t="s">
-        <v>79</v>
-      </c>
-      <c r="X2" t="s">
-        <v>93</v>
-      </c>
       <c r="Y2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Z2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AA2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AB2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>115</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>113</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>126</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>95</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>131</v>
+      </c>
+      <c r="AY2" t="s">
         <v>94</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>117</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AG2" t="s">
-        <v>120</v>
-      </c>
-      <c r="AH2" t="s">
-        <v>112</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>125</v>
-      </c>
-      <c r="AL2" t="s">
-        <v>128</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AN2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AO2" t="s">
-        <v>130</v>
-      </c>
-      <c r="AP2" t="s">
-        <v>130</v>
-      </c>
-      <c r="AQ2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AR2" t="s">
-        <v>94</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>130</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>130</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>79</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>130</v>
-      </c>
-      <c r="AX2" t="s">
-        <v>130</v>
-      </c>
-      <c r="AY2" t="s">
-        <v>93</v>
       </c>
       <c r="AZ2">
         <v>3</v>
@@ -9740,7 +9868,7 @@
         <v>4</v>
       </c>
       <c r="BB2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:54">
@@ -9748,130 +9876,130 @@
         <v>1977</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E3">
         <v>2025</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L3" t="s">
+        <v>98</v>
+      </c>
+      <c r="M3" t="s">
+        <v>102</v>
+      </c>
+      <c r="N3" t="s">
+        <v>104</v>
+      </c>
+      <c r="O3" t="s">
+        <v>82</v>
+      </c>
+      <c r="P3" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>102</v>
+      </c>
+      <c r="R3" t="s">
+        <v>102</v>
+      </c>
+      <c r="S3" t="s">
+        <v>82</v>
+      </c>
+      <c r="T3" t="s">
+        <v>95</v>
+      </c>
+      <c r="U3" t="s">
+        <v>106</v>
+      </c>
+      <c r="V3" t="s">
+        <v>109</v>
+      </c>
+      <c r="W3" t="s">
+        <v>82</v>
+      </c>
+      <c r="X3" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AJ3" t="s">
         <v>97</v>
       </c>
-      <c r="M3" t="s">
-        <v>101</v>
-      </c>
-      <c r="N3" t="s">
-        <v>103</v>
-      </c>
-      <c r="O3" t="s">
-        <v>81</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="AK3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AN3" t="s">
         <v>97</v>
       </c>
-      <c r="Q3" t="s">
-        <v>101</v>
-      </c>
-      <c r="R3" t="s">
-        <v>101</v>
-      </c>
-      <c r="S3" t="s">
-        <v>81</v>
-      </c>
-      <c r="T3" t="s">
-        <v>94</v>
-      </c>
-      <c r="U3" t="s">
-        <v>105</v>
-      </c>
-      <c r="V3" t="s">
-        <v>108</v>
-      </c>
-      <c r="W3" t="s">
-        <v>81</v>
-      </c>
-      <c r="X3" t="s">
-        <v>94</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>110</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>112</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB3" t="s">
+      <c r="AQ3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>97</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>86</v>
+      </c>
+      <c r="AY3" t="s">
         <v>95</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>115</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>118</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>84</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>95</v>
-      </c>
-      <c r="AG3" t="s">
-        <v>121</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>123</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>126</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>120</v>
-      </c>
-      <c r="AM3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AN3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>85</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>94</v>
       </c>
       <c r="AZ3">
         <v>2</v>
@@ -9880,7 +10008,7 @@
         <v>2</v>
       </c>
       <c r="BB3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:54">
@@ -9888,127 +10016,127 @@
         <v>1992</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E4">
         <v>2024</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L4" t="s">
+        <v>99</v>
+      </c>
+      <c r="M4" t="s">
+        <v>103</v>
+      </c>
+      <c r="N4" t="s">
+        <v>105</v>
+      </c>
+      <c r="O4" t="s">
+        <v>83</v>
+      </c>
+      <c r="P4" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>103</v>
+      </c>
+      <c r="R4" t="s">
+        <v>103</v>
+      </c>
+      <c r="S4" t="s">
+        <v>84</v>
+      </c>
+      <c r="T4" t="s">
         <v>98</v>
       </c>
-      <c r="M4" t="s">
-        <v>102</v>
-      </c>
-      <c r="N4" t="s">
-        <v>104</v>
-      </c>
-      <c r="O4" t="s">
-        <v>82</v>
-      </c>
-      <c r="P4" t="s">
+      <c r="U4" t="s">
+        <v>107</v>
+      </c>
+      <c r="V4" t="s">
+        <v>110</v>
+      </c>
+      <c r="W4" t="s">
+        <v>84</v>
+      </c>
+      <c r="X4" t="s">
         <v>98</v>
       </c>
-      <c r="Q4" t="s">
-        <v>102</v>
-      </c>
-      <c r="R4" t="s">
-        <v>102</v>
-      </c>
-      <c r="S4" t="s">
-        <v>83</v>
-      </c>
-      <c r="T4" t="s">
-        <v>97</v>
-      </c>
-      <c r="U4" t="s">
-        <v>106</v>
-      </c>
-      <c r="V4" t="s">
-        <v>109</v>
-      </c>
-      <c r="W4" t="s">
-        <v>83</v>
-      </c>
-      <c r="X4" t="s">
-        <v>97</v>
-      </c>
       <c r="Y4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AA4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AB4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AC4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AD4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AE4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AF4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AH4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AI4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AJ4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AL4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AN4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AQ4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AR4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AU4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AZ4">
         <v>3</v>
@@ -10017,7 +10145,7 @@
         <v>4</v>
       </c>
       <c r="BB4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:54">
@@ -10025,79 +10153,79 @@
         <v>2006</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E5">
         <v>2023</v>
       </c>
       <c r="F5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O5" t="s">
+        <v>91</v>
+      </c>
+      <c r="S5" t="s">
+        <v>91</v>
+      </c>
+      <c r="T5" t="s">
+        <v>99</v>
+      </c>
+      <c r="W5" t="s">
+        <v>91</v>
+      </c>
+      <c r="X5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>91</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE5" t="s">
         <v>90</v>
       </c>
-      <c r="S5" t="s">
-        <v>90</v>
-      </c>
-      <c r="T5" t="s">
-        <v>98</v>
-      </c>
-      <c r="W5" t="s">
-        <v>90</v>
-      </c>
-      <c r="X5" t="s">
-        <v>98</v>
-      </c>
-      <c r="AA5" t="s">
-        <v>90</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>98</v>
-      </c>
-      <c r="AE5" t="s">
+      <c r="AF5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AI5" t="s">
         <v>89</v>
       </c>
-      <c r="AF5" t="s">
-        <v>98</v>
-      </c>
-      <c r="AI5" t="s">
+      <c r="AJ5" t="s">
+        <v>99</v>
+      </c>
+      <c r="AM5" t="s">
         <v>88</v>
       </c>
-      <c r="AJ5" t="s">
-        <v>98</v>
-      </c>
-      <c r="AM5" t="s">
-        <v>87</v>
-      </c>
       <c r="AN5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AQ5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AR5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AU5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AY5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AZ5">
         <v>3</v>
@@ -10106,7 +10234,7 @@
         <v>4</v>
       </c>
       <c r="BB5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:54">
@@ -10114,58 +10242,58 @@
         <v>2008</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6">
         <v>2022</v>
       </c>
       <c r="F6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K6" t="s">
+        <v>91</v>
+      </c>
+      <c r="O6" t="s">
+        <v>92</v>
+      </c>
+      <c r="S6" t="s">
+        <v>92</v>
+      </c>
+      <c r="W6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>91</v>
+      </c>
+      <c r="AI6" t="s">
         <v>90</v>
       </c>
-      <c r="O6" t="s">
-        <v>91</v>
-      </c>
-      <c r="S6" t="s">
-        <v>91</v>
-      </c>
-      <c r="W6" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA6" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE6" t="s">
-        <v>90</v>
-      </c>
-      <c r="AI6" t="s">
+      <c r="AM6" t="s">
         <v>89</v>
       </c>
-      <c r="AM6" t="s">
-        <v>88</v>
-      </c>
       <c r="AQ6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AU6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AY6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AZ6">
         <v>3</v>
@@ -10179,46 +10307,46 @@
         <v>2011</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7">
         <v>2021</v>
       </c>
       <c r="F7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AI7" t="s">
         <v>91</v>
       </c>
-      <c r="AE7" t="s">
-        <v>91</v>
-      </c>
-      <c r="AI7" t="s">
+      <c r="AM7" t="s">
         <v>90</v>
       </c>
-      <c r="AM7" t="s">
-        <v>89</v>
-      </c>
       <c r="AQ7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AU7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AY7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AZ7">
         <v>3</v>
@@ -10232,34 +10360,34 @@
         <v>2013</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8">
         <v>2020</v>
       </c>
       <c r="F8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AI8" t="s">
+        <v>92</v>
+      </c>
+      <c r="AM8" t="s">
         <v>91</v>
       </c>
-      <c r="AM8" t="s">
-        <v>90</v>
-      </c>
       <c r="AQ8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AU8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:54">
@@ -10267,28 +10395,28 @@
         <v>2015</v>
       </c>
       <c r="B9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E9">
         <v>2019</v>
       </c>
       <c r="H9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AM9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AQ9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AU9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:54">
@@ -10296,19 +10424,19 @@
         <v>2017</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E10">
         <v>2018</v>
       </c>
       <c r="H10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:54">
@@ -10316,19 +10444,19 @@
         <v>2019</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E11">
         <v>2017</v>
       </c>
       <c r="H11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:54">
@@ -10336,10 +10464,10 @@
         <v>2016</v>
       </c>
       <c r="H12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:54">
@@ -10347,10 +10475,10 @@
         <v>2015</v>
       </c>
       <c r="H13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:54">
@@ -10358,10 +10486,10 @@
         <v>2014</v>
       </c>
       <c r="H14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:54">
@@ -10369,7 +10497,7 @@
         <v>2013</v>
       </c>
       <c r="J15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:54">
@@ -10377,7 +10505,7 @@
         <v>2012</v>
       </c>
       <c r="J16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="5:10">
@@ -10385,7 +10513,7 @@
         <v>2011</v>
       </c>
       <c r="J17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="5:10">
@@ -10393,7 +10521,7 @@
         <v>2010</v>
       </c>
       <c r="J18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="5:10">
@@ -10401,7 +10529,7 @@
         <v>2009</v>
       </c>
       <c r="J19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20" spans="5:10">
@@ -10409,7 +10537,7 @@
         <v>2008</v>
       </c>
       <c r="J20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="5:10">
@@ -10417,7 +10545,7 @@
         <v>2007</v>
       </c>
       <c r="J21" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="22" spans="5:10">
@@ -10425,7 +10553,7 @@
         <v>2006</v>
       </c>
       <c r="J22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="5:10">
@@ -10433,7 +10561,7 @@
         <v>2005</v>
       </c>
       <c r="J23" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="5:10">
@@ -10441,7 +10569,7 @@
         <v>2004</v>
       </c>
       <c r="J24" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="25" spans="5:10">
@@ -10449,7 +10577,7 @@
         <v>2003</v>
       </c>
       <c r="J25" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="5:10">
@@ -10457,7 +10585,7 @@
         <v>2002</v>
       </c>
       <c r="J26" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="5:10">
@@ -10465,7 +10593,7 @@
         <v>2001</v>
       </c>
       <c r="J27" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="5:10">
@@ -10473,7 +10601,7 @@
         <v>2000</v>
       </c>
       <c r="J28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="5:10">
@@ -10481,7 +10609,7 @@
         <v>1999</v>
       </c>
       <c r="J29" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="5:10">
@@ -10489,7 +10617,7 @@
         <v>1998</v>
       </c>
       <c r="J30" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31" spans="5:10">
@@ -10497,7 +10625,7 @@
         <v>1997</v>
       </c>
       <c r="J31" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="32" spans="5:10">
@@ -10505,7 +10633,7 @@
         <v>1996</v>
       </c>
       <c r="J32" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="33" spans="5:5">

--- a/form/FSS-Entry-Form.xlsx
+++ b/form/FSS-Entry-Form.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Prijava" sheetId="1" r:id="rId1"/>
     <sheet name="Ekipno" sheetId="2" r:id="rId2"/>
     <sheet name="Pravilnik" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Spisak" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="disc_A">Pravilnik!$K$2:$K$7</definedName>
@@ -45,10 +46,18 @@
     <definedName name="kg_I_Z">Pravilnik!$AT$2:$AT$2</definedName>
     <definedName name="kg_J_M">Pravilnik!$AW$2:$AW$2</definedName>
     <definedName name="kg_J_Z">Pravilnik!$AX$2:$AX$2</definedName>
+    <definedName name="klubovi">OFFSET(Spisak!$I$2,0,0,MAX(1,COUNTA(Spisak!$I$2:$I$501)),1)</definedName>
     <definedName name="pojasevi">Pravilnik!$F$2:$F$8</definedName>
     <definedName name="polovi">Pravilnik!$G$2:$G$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">Ekipno!$9:$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">Prijava!$10:$10</definedName>
+    <definedName name="spisak_godiste">Spisak!$D$2:$D$5001</definedName>
+    <definedName name="spisak_id">Spisak!$A$2:$A$5001</definedName>
+    <definedName name="spisak_ime">Spisak!$B$2:$B$5001</definedName>
+    <definedName name="spisak_klub">Spisak!$G$2:$G$5001</definedName>
+    <definedName name="spisak_pojas">Spisak!$F$2:$F$5001</definedName>
+    <definedName name="spisak_pol">Spisak!$E$2:$E$5001</definedName>
+    <definedName name="spisak_prezime">Spisak!$C$2:$C$5001</definedName>
     <definedName name="sve_discipline">Pravilnik!$H$2:$H$14</definedName>
     <definedName name="sve_ekipne">Pravilnik!$I$2:$I$7</definedName>
     <definedName name="sve_kilaze">Pravilnik!$J$2:$J$32</definedName>
@@ -68,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="199">
   <si>
     <t>PRIJAVA TAKMIČARA</t>
   </si>
@@ -76,13 +85,13 @@
     <t>Fudokan savez Srbije · popunjava klub i dostavlja savezu · takmičarska sezona 2026. · izdanje 06.10.2026.</t>
   </si>
   <si>
-    <t>U prvu kolonu upisuje se FSS ID takmičara sa spiska saveza — za 2026. godinu, a dok ga takmičar nema, prošlogodišnji; takmičar koji nastupa prvi put ostaje bez ID-a, nov ID dodeljuje savez. Ime i prezime upisuju se svako u svoju kolonu. Uzrasna grupa i naziv uzrasta popunjavaju se automatski iz godišta, a padajući meni nudi discipline koje su moguće u odnosu na uzrast. Telesna težina unosi se isključivo uz Fudokan sport kumite, budući da je tradicionalni kumite apsolutna kategorija. Kolona „Provera" služi za proveru kompletnosti prijave. Ekipne prijave se unose na listu „Ekipno".</t>
+    <t>Klub se bira u zaglavlju. Za takmičara koji već ima FSS ID dovoljno je upisati ID — za 2026. godinu, a dok ga takmičar nema, prošlogodišnji: ime, prezime, godište, pol i pojas popunjavaju se sami sa spiska saveza, a bira se samo disciplina. Pojas treba ispraviti ako je takmičar u međuvremenu polagao. Takmičar koji nastupa prvi put nema ID: njemu se upisuju ime i prezime, svako u svoju kolonu, i ostali podaci, a nov ID dodeljuje savez. Uzrasna grupa i naziv uzrasta izvode se iz godišta, a padajući meni nudi discipline koje su moguće u odnosu na uzrast. Telesna težina unosi se isključivo uz Fudokan sport kumite, budući da je tradicionalni kumite apsolutna kategorija. Kolona „Provera" služi za proveru kompletnosti prijave. Ekipne prijave se unose na listu „Ekipno".</t>
   </si>
   <si>
     <t>Klub</t>
   </si>
   <si>
-    <t>pun naziv kluba, onako kako se navodi u rezultatima</t>
+    <t>bira se sa spiska; nov klub upisuje pun naziv, onako kako se navodi u rezultatima</t>
   </si>
   <si>
     <t>Grad</t>
@@ -623,6 +632,48 @@
   </si>
   <si>
     <t>mešoviti par</t>
+  </si>
+  <si>
+    <t>Klubovi</t>
+  </si>
+  <si>
+    <t>KK Fudokan Beograd</t>
+  </si>
+  <si>
+    <t>KK Vojvodina</t>
+  </si>
+  <si>
+    <t>KK Zemun</t>
+  </si>
+  <si>
+    <t>KK Niš</t>
+  </si>
+  <si>
+    <t>KK Vračar</t>
+  </si>
+  <si>
+    <t>KK Kragujevac</t>
+  </si>
+  <si>
+    <t>KK Subotica</t>
+  </si>
+  <si>
+    <t>KK Čačak</t>
+  </si>
+  <si>
+    <t>KK Zvezdara</t>
+  </si>
+  <si>
+    <t>KK Sombor</t>
+  </si>
+  <si>
+    <t>KK Užice</t>
+  </si>
+  <si>
+    <t>KK Leskovac</t>
+  </si>
+  <si>
+    <t>KK Banatski cvet</t>
   </si>
 </sst>
 </file>
@@ -1046,7 +1097,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T130"/>
+  <dimension ref="A1:V130"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -1059,20 +1110,20 @@
     <col min="9" max="16" width="20.7109375" customWidth="1"/>
     <col min="17" max="17" width="12.7109375" customWidth="1"/>
     <col min="18" max="18" width="34.7109375" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" hidden="1" customWidth="1"/>
+    <col min="19" max="22" width="14.7109375" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:22">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:22">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="40" customHeight="1">
+    <row r="3" spans="1:22" ht="52" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -1094,7 +1145,7 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:22">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -1103,19 +1154,19 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:22">
       <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:22">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="5"/>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:22">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
@@ -1124,7 +1175,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="30" customHeight="1">
+    <row r="10" spans="1:22" ht="30" customHeight="1">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
@@ -1180,13 +1231,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:22">
       <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="B11" s="5">
+        <f>IF($V11=0,"",INDEX(spisak_ime,$V11)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C11" s="5">
+        <f>IF($V11=0,"",INDEX(spisak_prezime,$V11)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D11" s="5">
+        <f>IF($V11=0,"",INDEX(spisak_godiste,$V11))</f>
+        <v/>
+      </c>
+      <c r="E11" s="5">
+        <f>IF($V11=0,"",INDEX(spisak_pol,$V11)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="5">
+        <f>IF($V11=0,"",INDEX(spisak_pojas,$V11)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G11" s="7">
         <f>IF($D11="","",LOOKUP($D11,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1205,7 +1271,7 @@
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
       <c r="R11" s="8">
-        <f>IF(COUNTA($A11:$F11,I11:P11,Q11)=0,"",IF(AND($A11&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A11,4))="FSS-",MID($A11,LEN($A11)-2,1)="/",ISNUMBER(VALUE(RIGHT($A11,2))),VALUE(MID($A11,5,LEN($A11)-7))&gt;=1,VALUE(MID($A11,5,LEN($A11)-7))=INT(VALUE(MID($A11,5,LEN($A11)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B11="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B11&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C11="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C11&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D11="","Nedostaje godište",IF($G11="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E11="","Nedostaje pol",IF($F11="","Nedostaje pojas",IF(COUNTA(I11:P11)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I11:P11&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G11),I11:P11)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G11,IF(AND(COUNTIF(I11:P11,"Fudokan sport kumite")&gt;0,Q11=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I11:P11,"Fudokan sport kumite")=0,Q11&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A11:$F11))+SUMPRODUCT(LEN(I11:P11))+LEN(Q11)=0,"",IF(AND($A11&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A11,4))="FSS-",MID($A11,LEN($A11)-2,1)="/",ISNUMBER(VALUE(RIGHT($A11,2))),VALUE(MID($A11,5,LEN($A11)-7))&gt;=1,VALUE(MID($A11,5,LEN($A11)-7))=INT(VALUE(MID($A11,5,LEN($A11)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A11&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A11&lt;&gt;"",$U11=0,$B11=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U11&gt;0,$V11=0,$B11=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U11)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B11="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B11&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C11="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C11&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D11="","Nedostaje godište",IF($G11="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E11="","Nedostaje pol",IF($F11="","Nedostaje pojas",IF(COUNTA(I11:P11)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I11:P11&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G11),I11:P11)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G11,IF(AND(COUNTIF(I11:P11,"Fudokan sport kumite")&gt;0,Q11=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I11:P11,"Fudokan sport kumite")=0,Q11&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S11">
@@ -1216,14 +1282,37 @@
         <f>IF(OR($G11="",$E11=""),"sve_kilaze","kg_"&amp;$G11&amp;"_"&amp;IF($E11="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="12" spans="1:20">
+      <c r="U11">
+        <f>IF($A11="",0,IFERROR(MATCH(TRIM($A11),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <f>IF($U11=0,0,IF(TRIM(INDEX(spisak_klub,$U11))=TRIM($B$4),$U11,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="B12" s="5">
+        <f>IF($V12=0,"",INDEX(spisak_ime,$V12)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="5">
+        <f>IF($V12=0,"",INDEX(spisak_prezime,$V12)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="5">
+        <f>IF($V12=0,"",INDEX(spisak_godiste,$V12))</f>
+        <v/>
+      </c>
+      <c r="E12" s="5">
+        <f>IF($V12=0,"",INDEX(spisak_pol,$V12)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="5">
+        <f>IF($V12=0,"",INDEX(spisak_pojas,$V12)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G12" s="7">
         <f>IF($D12="","",LOOKUP($D12,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1242,7 +1331,7 @@
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
       <c r="R12" s="8">
-        <f>IF(COUNTA($A12:$F12,I12:P12,Q12)=0,"",IF(AND($A12&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A12,4))="FSS-",MID($A12,LEN($A12)-2,1)="/",ISNUMBER(VALUE(RIGHT($A12,2))),VALUE(MID($A12,5,LEN($A12)-7))&gt;=1,VALUE(MID($A12,5,LEN($A12)-7))=INT(VALUE(MID($A12,5,LEN($A12)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B12="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B12&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C12="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C12&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D12="","Nedostaje godište",IF($G12="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E12="","Nedostaje pol",IF($F12="","Nedostaje pojas",IF(COUNTA(I12:P12)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I12:P12&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G12),I12:P12)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G12,IF(AND(COUNTIF(I12:P12,"Fudokan sport kumite")&gt;0,Q12=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I12:P12,"Fudokan sport kumite")=0,Q12&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A12:$F12))+SUMPRODUCT(LEN(I12:P12))+LEN(Q12)=0,"",IF(AND($A12&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A12,4))="FSS-",MID($A12,LEN($A12)-2,1)="/",ISNUMBER(VALUE(RIGHT($A12,2))),VALUE(MID($A12,5,LEN($A12)-7))&gt;=1,VALUE(MID($A12,5,LEN($A12)-7))=INT(VALUE(MID($A12,5,LEN($A12)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A12&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A12&lt;&gt;"",$U12=0,$B12=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U12&gt;0,$V12=0,$B12=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U12)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B12="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B12&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C12="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C12&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D12="","Nedostaje godište",IF($G12="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E12="","Nedostaje pol",IF($F12="","Nedostaje pojas",IF(COUNTA(I12:P12)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I12:P12&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G12),I12:P12)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G12,IF(AND(COUNTIF(I12:P12,"Fudokan sport kumite")&gt;0,Q12=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I12:P12,"Fudokan sport kumite")=0,Q12&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S12">
@@ -1253,14 +1342,37 @@
         <f>IF(OR($G12="",$E12=""),"sve_kilaze","kg_"&amp;$G12&amp;"_"&amp;IF($E12="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="13" spans="1:20">
+      <c r="U12">
+        <f>IF($A12="",0,IFERROR(MATCH(TRIM($A12),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <f>IF($U12=0,0,IF(TRIM(INDEX(spisak_klub,$U12))=TRIM($B$4),$U12,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
+      <c r="B13" s="5">
+        <f>IF($V13=0,"",INDEX(spisak_ime,$V13)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C13" s="5">
+        <f>IF($V13=0,"",INDEX(spisak_prezime,$V13)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D13" s="5">
+        <f>IF($V13=0,"",INDEX(spisak_godiste,$V13))</f>
+        <v/>
+      </c>
+      <c r="E13" s="5">
+        <f>IF($V13=0,"",INDEX(spisak_pol,$V13)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="5">
+        <f>IF($V13=0,"",INDEX(spisak_pojas,$V13)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G13" s="7">
         <f>IF($D13="","",LOOKUP($D13,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1279,7 +1391,7 @@
       <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
       <c r="R13" s="8">
-        <f>IF(COUNTA($A13:$F13,I13:P13,Q13)=0,"",IF(AND($A13&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A13,4))="FSS-",MID($A13,LEN($A13)-2,1)="/",ISNUMBER(VALUE(RIGHT($A13,2))),VALUE(MID($A13,5,LEN($A13)-7))&gt;=1,VALUE(MID($A13,5,LEN($A13)-7))=INT(VALUE(MID($A13,5,LEN($A13)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B13="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B13&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C13="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C13&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D13="","Nedostaje godište",IF($G13="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E13="","Nedostaje pol",IF($F13="","Nedostaje pojas",IF(COUNTA(I13:P13)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I13:P13&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G13),I13:P13)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G13,IF(AND(COUNTIF(I13:P13,"Fudokan sport kumite")&gt;0,Q13=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I13:P13,"Fudokan sport kumite")=0,Q13&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A13:$F13))+SUMPRODUCT(LEN(I13:P13))+LEN(Q13)=0,"",IF(AND($A13&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A13,4))="FSS-",MID($A13,LEN($A13)-2,1)="/",ISNUMBER(VALUE(RIGHT($A13,2))),VALUE(MID($A13,5,LEN($A13)-7))&gt;=1,VALUE(MID($A13,5,LEN($A13)-7))=INT(VALUE(MID($A13,5,LEN($A13)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A13&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A13&lt;&gt;"",$U13=0,$B13=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U13&gt;0,$V13=0,$B13=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U13)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B13="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B13&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C13="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C13&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D13="","Nedostaje godište",IF($G13="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E13="","Nedostaje pol",IF($F13="","Nedostaje pojas",IF(COUNTA(I13:P13)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I13:P13&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G13),I13:P13)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G13,IF(AND(COUNTIF(I13:P13,"Fudokan sport kumite")&gt;0,Q13=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I13:P13,"Fudokan sport kumite")=0,Q13&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S13">
@@ -1290,14 +1402,37 @@
         <f>IF(OR($G13="",$E13=""),"sve_kilaze","kg_"&amp;$G13&amp;"_"&amp;IF($E13="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="14" spans="1:20">
+      <c r="U13">
+        <f>IF($A13="",0,IFERROR(MATCH(TRIM($A13),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <f>IF($U13=0,0,IF(TRIM(INDEX(spisak_klub,$U13))=TRIM($B$4),$U13,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="B14" s="5">
+        <f>IF($V14=0,"",INDEX(spisak_ime,$V14)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IF($V14=0,"",INDEX(spisak_prezime,$V14)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IF($V14=0,"",INDEX(spisak_godiste,$V14))</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IF($V14=0,"",INDEX(spisak_pol,$V14)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="5">
+        <f>IF($V14=0,"",INDEX(spisak_pojas,$V14)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G14" s="7">
         <f>IF($D14="","",LOOKUP($D14,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1316,7 +1451,7 @@
       <c r="P14" s="5"/>
       <c r="Q14" s="5"/>
       <c r="R14" s="8">
-        <f>IF(COUNTA($A14:$F14,I14:P14,Q14)=0,"",IF(AND($A14&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A14,4))="FSS-",MID($A14,LEN($A14)-2,1)="/",ISNUMBER(VALUE(RIGHT($A14,2))),VALUE(MID($A14,5,LEN($A14)-7))&gt;=1,VALUE(MID($A14,5,LEN($A14)-7))=INT(VALUE(MID($A14,5,LEN($A14)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B14="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B14&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C14="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C14&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D14="","Nedostaje godište",IF($G14="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E14="","Nedostaje pol",IF($F14="","Nedostaje pojas",IF(COUNTA(I14:P14)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I14:P14&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G14),I14:P14)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G14,IF(AND(COUNTIF(I14:P14,"Fudokan sport kumite")&gt;0,Q14=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I14:P14,"Fudokan sport kumite")=0,Q14&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A14:$F14))+SUMPRODUCT(LEN(I14:P14))+LEN(Q14)=0,"",IF(AND($A14&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A14,4))="FSS-",MID($A14,LEN($A14)-2,1)="/",ISNUMBER(VALUE(RIGHT($A14,2))),VALUE(MID($A14,5,LEN($A14)-7))&gt;=1,VALUE(MID($A14,5,LEN($A14)-7))=INT(VALUE(MID($A14,5,LEN($A14)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A14&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A14&lt;&gt;"",$U14=0,$B14=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U14&gt;0,$V14=0,$B14=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U14)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B14="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B14&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C14="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C14&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D14="","Nedostaje godište",IF($G14="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E14="","Nedostaje pol",IF($F14="","Nedostaje pojas",IF(COUNTA(I14:P14)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I14:P14&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G14),I14:P14)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G14,IF(AND(COUNTIF(I14:P14,"Fudokan sport kumite")&gt;0,Q14=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I14:P14,"Fudokan sport kumite")=0,Q14&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S14">
@@ -1327,14 +1462,37 @@
         <f>IF(OR($G14="",$E14=""),"sve_kilaze","kg_"&amp;$G14&amp;"_"&amp;IF($E14="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="15" spans="1:20">
+      <c r="U14">
+        <f>IF($A14="",0,IFERROR(MATCH(TRIM($A14),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <f>IF($U14=0,0,IF(TRIM(INDEX(spisak_klub,$U14))=TRIM($B$4),$U14,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="B15" s="5">
+        <f>IF($V15=0,"",INDEX(spisak_ime,$V15)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C15" s="5">
+        <f>IF($V15=0,"",INDEX(spisak_prezime,$V15)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D15" s="5">
+        <f>IF($V15=0,"",INDEX(spisak_godiste,$V15))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5">
+        <f>IF($V15=0,"",INDEX(spisak_pol,$V15)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="5">
+        <f>IF($V15=0,"",INDEX(spisak_pojas,$V15)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G15" s="7">
         <f>IF($D15="","",LOOKUP($D15,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1353,7 +1511,7 @@
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
       <c r="R15" s="8">
-        <f>IF(COUNTA($A15:$F15,I15:P15,Q15)=0,"",IF(AND($A15&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A15,4))="FSS-",MID($A15,LEN($A15)-2,1)="/",ISNUMBER(VALUE(RIGHT($A15,2))),VALUE(MID($A15,5,LEN($A15)-7))&gt;=1,VALUE(MID($A15,5,LEN($A15)-7))=INT(VALUE(MID($A15,5,LEN($A15)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B15="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B15&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C15="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C15&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D15="","Nedostaje godište",IF($G15="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E15="","Nedostaje pol",IF($F15="","Nedostaje pojas",IF(COUNTA(I15:P15)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I15:P15&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G15),I15:P15)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G15,IF(AND(COUNTIF(I15:P15,"Fudokan sport kumite")&gt;0,Q15=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I15:P15,"Fudokan sport kumite")=0,Q15&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A15:$F15))+SUMPRODUCT(LEN(I15:P15))+LEN(Q15)=0,"",IF(AND($A15&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A15,4))="FSS-",MID($A15,LEN($A15)-2,1)="/",ISNUMBER(VALUE(RIGHT($A15,2))),VALUE(MID($A15,5,LEN($A15)-7))&gt;=1,VALUE(MID($A15,5,LEN($A15)-7))=INT(VALUE(MID($A15,5,LEN($A15)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A15&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A15&lt;&gt;"",$U15=0,$B15=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U15&gt;0,$V15=0,$B15=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U15)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B15="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B15&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C15="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C15&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D15="","Nedostaje godište",IF($G15="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E15="","Nedostaje pol",IF($F15="","Nedostaje pojas",IF(COUNTA(I15:P15)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I15:P15&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G15),I15:P15)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G15,IF(AND(COUNTIF(I15:P15,"Fudokan sport kumite")&gt;0,Q15=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I15:P15,"Fudokan sport kumite")=0,Q15&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S15">
@@ -1364,14 +1522,37 @@
         <f>IF(OR($G15="",$E15=""),"sve_kilaze","kg_"&amp;$G15&amp;"_"&amp;IF($E15="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="16" spans="1:20">
+      <c r="U15">
+        <f>IF($A15="",0,IFERROR(MATCH(TRIM($A15),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <f>IF($U15=0,0,IF(TRIM(INDEX(spisak_klub,$U15))=TRIM($B$4),$U15,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
+      <c r="B16" s="5">
+        <f>IF($V16=0,"",INDEX(spisak_ime,$V16)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C16" s="5">
+        <f>IF($V16=0,"",INDEX(spisak_prezime,$V16)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="5">
+        <f>IF($V16=0,"",INDEX(spisak_godiste,$V16))</f>
+        <v/>
+      </c>
+      <c r="E16" s="5">
+        <f>IF($V16=0,"",INDEX(spisak_pol,$V16)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="5">
+        <f>IF($V16=0,"",INDEX(spisak_pojas,$V16)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G16" s="7">
         <f>IF($D16="","",LOOKUP($D16,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1390,7 +1571,7 @@
       <c r="P16" s="5"/>
       <c r="Q16" s="5"/>
       <c r="R16" s="8">
-        <f>IF(COUNTA($A16:$F16,I16:P16,Q16)=0,"",IF(AND($A16&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A16,4))="FSS-",MID($A16,LEN($A16)-2,1)="/",ISNUMBER(VALUE(RIGHT($A16,2))),VALUE(MID($A16,5,LEN($A16)-7))&gt;=1,VALUE(MID($A16,5,LEN($A16)-7))=INT(VALUE(MID($A16,5,LEN($A16)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B16="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B16&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C16="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C16&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D16="","Nedostaje godište",IF($G16="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E16="","Nedostaje pol",IF($F16="","Nedostaje pojas",IF(COUNTA(I16:P16)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I16:P16&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G16),I16:P16)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G16,IF(AND(COUNTIF(I16:P16,"Fudokan sport kumite")&gt;0,Q16=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I16:P16,"Fudokan sport kumite")=0,Q16&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A16:$F16))+SUMPRODUCT(LEN(I16:P16))+LEN(Q16)=0,"",IF(AND($A16&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A16,4))="FSS-",MID($A16,LEN($A16)-2,1)="/",ISNUMBER(VALUE(RIGHT($A16,2))),VALUE(MID($A16,5,LEN($A16)-7))&gt;=1,VALUE(MID($A16,5,LEN($A16)-7))=INT(VALUE(MID($A16,5,LEN($A16)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A16&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A16&lt;&gt;"",$U16=0,$B16=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U16&gt;0,$V16=0,$B16=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U16)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B16="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B16&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C16="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C16&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D16="","Nedostaje godište",IF($G16="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E16="","Nedostaje pol",IF($F16="","Nedostaje pojas",IF(COUNTA(I16:P16)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I16:P16&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G16),I16:P16)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G16,IF(AND(COUNTIF(I16:P16,"Fudokan sport kumite")&gt;0,Q16=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I16:P16,"Fudokan sport kumite")=0,Q16&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S16">
@@ -1401,14 +1582,37 @@
         <f>IF(OR($G16="",$E16=""),"sve_kilaze","kg_"&amp;$G16&amp;"_"&amp;IF($E16="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="17" spans="1:20">
+      <c r="U16">
+        <f>IF($A16="",0,IFERROR(MATCH(TRIM($A16),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <f>IF($U16=0,0,IF(TRIM(INDEX(spisak_klub,$U16))=TRIM($B$4),$U16,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22">
       <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
+      <c r="B17" s="5">
+        <f>IF($V17=0,"",INDEX(spisak_ime,$V17)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C17" s="5">
+        <f>IF($V17=0,"",INDEX(spisak_prezime,$V17)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D17" s="5">
+        <f>IF($V17=0,"",INDEX(spisak_godiste,$V17))</f>
+        <v/>
+      </c>
+      <c r="E17" s="5">
+        <f>IF($V17=0,"",INDEX(spisak_pol,$V17)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="5">
+        <f>IF($V17=0,"",INDEX(spisak_pojas,$V17)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G17" s="7">
         <f>IF($D17="","",LOOKUP($D17,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1427,7 +1631,7 @@
       <c r="P17" s="5"/>
       <c r="Q17" s="5"/>
       <c r="R17" s="8">
-        <f>IF(COUNTA($A17:$F17,I17:P17,Q17)=0,"",IF(AND($A17&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A17,4))="FSS-",MID($A17,LEN($A17)-2,1)="/",ISNUMBER(VALUE(RIGHT($A17,2))),VALUE(MID($A17,5,LEN($A17)-7))&gt;=1,VALUE(MID($A17,5,LEN($A17)-7))=INT(VALUE(MID($A17,5,LEN($A17)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B17="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B17&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C17="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C17&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D17="","Nedostaje godište",IF($G17="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E17="","Nedostaje pol",IF($F17="","Nedostaje pojas",IF(COUNTA(I17:P17)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I17:P17&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G17),I17:P17)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G17,IF(AND(COUNTIF(I17:P17,"Fudokan sport kumite")&gt;0,Q17=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I17:P17,"Fudokan sport kumite")=0,Q17&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A17:$F17))+SUMPRODUCT(LEN(I17:P17))+LEN(Q17)=0,"",IF(AND($A17&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A17,4))="FSS-",MID($A17,LEN($A17)-2,1)="/",ISNUMBER(VALUE(RIGHT($A17,2))),VALUE(MID($A17,5,LEN($A17)-7))&gt;=1,VALUE(MID($A17,5,LEN($A17)-7))=INT(VALUE(MID($A17,5,LEN($A17)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A17&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A17&lt;&gt;"",$U17=0,$B17=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U17&gt;0,$V17=0,$B17=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U17)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B17="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B17&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C17="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C17&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D17="","Nedostaje godište",IF($G17="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E17="","Nedostaje pol",IF($F17="","Nedostaje pojas",IF(COUNTA(I17:P17)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I17:P17&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G17),I17:P17)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G17,IF(AND(COUNTIF(I17:P17,"Fudokan sport kumite")&gt;0,Q17=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I17:P17,"Fudokan sport kumite")=0,Q17&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S17">
@@ -1438,14 +1642,37 @@
         <f>IF(OR($G17="",$E17=""),"sve_kilaze","kg_"&amp;$G17&amp;"_"&amp;IF($E17="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="18" spans="1:20">
+      <c r="U17">
+        <f>IF($A17="",0,IFERROR(MATCH(TRIM($A17),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <f>IF($U17=0,0,IF(TRIM(INDEX(spisak_klub,$U17))=TRIM($B$4),$U17,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22">
       <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="B18" s="5">
+        <f>IF($V18=0,"",INDEX(spisak_ime,$V18)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C18" s="5">
+        <f>IF($V18=0,"",INDEX(spisak_prezime,$V18)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D18" s="5">
+        <f>IF($V18=0,"",INDEX(spisak_godiste,$V18))</f>
+        <v/>
+      </c>
+      <c r="E18" s="5">
+        <f>IF($V18=0,"",INDEX(spisak_pol,$V18)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="5">
+        <f>IF($V18=0,"",INDEX(spisak_pojas,$V18)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G18" s="7">
         <f>IF($D18="","",LOOKUP($D18,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1464,7 +1691,7 @@
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
       <c r="R18" s="8">
-        <f>IF(COUNTA($A18:$F18,I18:P18,Q18)=0,"",IF(AND($A18&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A18,4))="FSS-",MID($A18,LEN($A18)-2,1)="/",ISNUMBER(VALUE(RIGHT($A18,2))),VALUE(MID($A18,5,LEN($A18)-7))&gt;=1,VALUE(MID($A18,5,LEN($A18)-7))=INT(VALUE(MID($A18,5,LEN($A18)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B18="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B18&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C18="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C18&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D18="","Nedostaje godište",IF($G18="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E18="","Nedostaje pol",IF($F18="","Nedostaje pojas",IF(COUNTA(I18:P18)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I18:P18&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G18),I18:P18)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G18,IF(AND(COUNTIF(I18:P18,"Fudokan sport kumite")&gt;0,Q18=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I18:P18,"Fudokan sport kumite")=0,Q18&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A18:$F18))+SUMPRODUCT(LEN(I18:P18))+LEN(Q18)=0,"",IF(AND($A18&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A18,4))="FSS-",MID($A18,LEN($A18)-2,1)="/",ISNUMBER(VALUE(RIGHT($A18,2))),VALUE(MID($A18,5,LEN($A18)-7))&gt;=1,VALUE(MID($A18,5,LEN($A18)-7))=INT(VALUE(MID($A18,5,LEN($A18)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A18&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A18&lt;&gt;"",$U18=0,$B18=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U18&gt;0,$V18=0,$B18=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U18)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B18="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B18&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C18="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C18&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D18="","Nedostaje godište",IF($G18="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E18="","Nedostaje pol",IF($F18="","Nedostaje pojas",IF(COUNTA(I18:P18)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I18:P18&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G18),I18:P18)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G18,IF(AND(COUNTIF(I18:P18,"Fudokan sport kumite")&gt;0,Q18=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I18:P18,"Fudokan sport kumite")=0,Q18&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S18">
@@ -1475,14 +1702,37 @@
         <f>IF(OR($G18="",$E18=""),"sve_kilaze","kg_"&amp;$G18&amp;"_"&amp;IF($E18="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="19" spans="1:20">
+      <c r="U18">
+        <f>IF($A18="",0,IFERROR(MATCH(TRIM($A18),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <f>IF($U18=0,0,IF(TRIM(INDEX(spisak_klub,$U18))=TRIM($B$4),$U18,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22">
       <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+      <c r="B19" s="5">
+        <f>IF($V19=0,"",INDEX(spisak_ime,$V19)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C19" s="5">
+        <f>IF($V19=0,"",INDEX(spisak_prezime,$V19)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D19" s="5">
+        <f>IF($V19=0,"",INDEX(spisak_godiste,$V19))</f>
+        <v/>
+      </c>
+      <c r="E19" s="5">
+        <f>IF($V19=0,"",INDEX(spisak_pol,$V19)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="5">
+        <f>IF($V19=0,"",INDEX(spisak_pojas,$V19)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G19" s="7">
         <f>IF($D19="","",LOOKUP($D19,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1501,7 +1751,7 @@
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
       <c r="R19" s="8">
-        <f>IF(COUNTA($A19:$F19,I19:P19,Q19)=0,"",IF(AND($A19&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A19,4))="FSS-",MID($A19,LEN($A19)-2,1)="/",ISNUMBER(VALUE(RIGHT($A19,2))),VALUE(MID($A19,5,LEN($A19)-7))&gt;=1,VALUE(MID($A19,5,LEN($A19)-7))=INT(VALUE(MID($A19,5,LEN($A19)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B19="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B19&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C19="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C19&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D19="","Nedostaje godište",IF($G19="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E19="","Nedostaje pol",IF($F19="","Nedostaje pojas",IF(COUNTA(I19:P19)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I19:P19&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G19),I19:P19)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G19,IF(AND(COUNTIF(I19:P19,"Fudokan sport kumite")&gt;0,Q19=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I19:P19,"Fudokan sport kumite")=0,Q19&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A19:$F19))+SUMPRODUCT(LEN(I19:P19))+LEN(Q19)=0,"",IF(AND($A19&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A19,4))="FSS-",MID($A19,LEN($A19)-2,1)="/",ISNUMBER(VALUE(RIGHT($A19,2))),VALUE(MID($A19,5,LEN($A19)-7))&gt;=1,VALUE(MID($A19,5,LEN($A19)-7))=INT(VALUE(MID($A19,5,LEN($A19)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A19&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A19&lt;&gt;"",$U19=0,$B19=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U19&gt;0,$V19=0,$B19=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U19)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B19="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B19&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C19="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C19&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D19="","Nedostaje godište",IF($G19="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E19="","Nedostaje pol",IF($F19="","Nedostaje pojas",IF(COUNTA(I19:P19)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I19:P19&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G19),I19:P19)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G19,IF(AND(COUNTIF(I19:P19,"Fudokan sport kumite")&gt;0,Q19=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I19:P19,"Fudokan sport kumite")=0,Q19&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S19">
@@ -1512,14 +1762,37 @@
         <f>IF(OR($G19="",$E19=""),"sve_kilaze","kg_"&amp;$G19&amp;"_"&amp;IF($E19="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="20" spans="1:20">
+      <c r="U19">
+        <f>IF($A19="",0,IFERROR(MATCH(TRIM($A19),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <f>IF($U19=0,0,IF(TRIM(INDEX(spisak_klub,$U19))=TRIM($B$4),$U19,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22">
       <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+      <c r="B20" s="5">
+        <f>IF($V20=0,"",INDEX(spisak_ime,$V20)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C20" s="5">
+        <f>IF($V20=0,"",INDEX(spisak_prezime,$V20)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D20" s="5">
+        <f>IF($V20=0,"",INDEX(spisak_godiste,$V20))</f>
+        <v/>
+      </c>
+      <c r="E20" s="5">
+        <f>IF($V20=0,"",INDEX(spisak_pol,$V20)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="5">
+        <f>IF($V20=0,"",INDEX(spisak_pojas,$V20)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G20" s="7">
         <f>IF($D20="","",LOOKUP($D20,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1538,7 +1811,7 @@
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
       <c r="R20" s="8">
-        <f>IF(COUNTA($A20:$F20,I20:P20,Q20)=0,"",IF(AND($A20&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A20,4))="FSS-",MID($A20,LEN($A20)-2,1)="/",ISNUMBER(VALUE(RIGHT($A20,2))),VALUE(MID($A20,5,LEN($A20)-7))&gt;=1,VALUE(MID($A20,5,LEN($A20)-7))=INT(VALUE(MID($A20,5,LEN($A20)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B20="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B20&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C20="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C20&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D20="","Nedostaje godište",IF($G20="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E20="","Nedostaje pol",IF($F20="","Nedostaje pojas",IF(COUNTA(I20:P20)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I20:P20&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G20),I20:P20)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G20,IF(AND(COUNTIF(I20:P20,"Fudokan sport kumite")&gt;0,Q20=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I20:P20,"Fudokan sport kumite")=0,Q20&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A20:$F20))+SUMPRODUCT(LEN(I20:P20))+LEN(Q20)=0,"",IF(AND($A20&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A20,4))="FSS-",MID($A20,LEN($A20)-2,1)="/",ISNUMBER(VALUE(RIGHT($A20,2))),VALUE(MID($A20,5,LEN($A20)-7))&gt;=1,VALUE(MID($A20,5,LEN($A20)-7))=INT(VALUE(MID($A20,5,LEN($A20)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A20&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A20&lt;&gt;"",$U20=0,$B20=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U20&gt;0,$V20=0,$B20=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U20)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B20="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B20&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C20="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C20&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D20="","Nedostaje godište",IF($G20="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E20="","Nedostaje pol",IF($F20="","Nedostaje pojas",IF(COUNTA(I20:P20)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I20:P20&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G20),I20:P20)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G20,IF(AND(COUNTIF(I20:P20,"Fudokan sport kumite")&gt;0,Q20=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I20:P20,"Fudokan sport kumite")=0,Q20&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S20">
@@ -1549,14 +1822,37 @@
         <f>IF(OR($G20="",$E20=""),"sve_kilaze","kg_"&amp;$G20&amp;"_"&amp;IF($E20="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="21" spans="1:20">
+      <c r="U20">
+        <f>IF($A20="",0,IFERROR(MATCH(TRIM($A20),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <f>IF($U20=0,0,IF(TRIM(INDEX(spisak_klub,$U20))=TRIM($B$4),$U20,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22">
       <c r="A21" s="5"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="B21" s="5">
+        <f>IF($V21=0,"",INDEX(spisak_ime,$V21)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C21" s="5">
+        <f>IF($V21=0,"",INDEX(spisak_prezime,$V21)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D21" s="5">
+        <f>IF($V21=0,"",INDEX(spisak_godiste,$V21))</f>
+        <v/>
+      </c>
+      <c r="E21" s="5">
+        <f>IF($V21=0,"",INDEX(spisak_pol,$V21)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="5">
+        <f>IF($V21=0,"",INDEX(spisak_pojas,$V21)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G21" s="7">
         <f>IF($D21="","",LOOKUP($D21,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1575,7 +1871,7 @@
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
       <c r="R21" s="8">
-        <f>IF(COUNTA($A21:$F21,I21:P21,Q21)=0,"",IF(AND($A21&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A21,4))="FSS-",MID($A21,LEN($A21)-2,1)="/",ISNUMBER(VALUE(RIGHT($A21,2))),VALUE(MID($A21,5,LEN($A21)-7))&gt;=1,VALUE(MID($A21,5,LEN($A21)-7))=INT(VALUE(MID($A21,5,LEN($A21)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B21="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B21&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C21="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C21&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D21="","Nedostaje godište",IF($G21="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E21="","Nedostaje pol",IF($F21="","Nedostaje pojas",IF(COUNTA(I21:P21)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I21:P21&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G21),I21:P21)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G21,IF(AND(COUNTIF(I21:P21,"Fudokan sport kumite")&gt;0,Q21=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I21:P21,"Fudokan sport kumite")=0,Q21&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A21:$F21))+SUMPRODUCT(LEN(I21:P21))+LEN(Q21)=0,"",IF(AND($A21&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A21,4))="FSS-",MID($A21,LEN($A21)-2,1)="/",ISNUMBER(VALUE(RIGHT($A21,2))),VALUE(MID($A21,5,LEN($A21)-7))&gt;=1,VALUE(MID($A21,5,LEN($A21)-7))=INT(VALUE(MID($A21,5,LEN($A21)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A21&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A21&lt;&gt;"",$U21=0,$B21=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U21&gt;0,$V21=0,$B21=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U21)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B21="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B21&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C21="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C21&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D21="","Nedostaje godište",IF($G21="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E21="","Nedostaje pol",IF($F21="","Nedostaje pojas",IF(COUNTA(I21:P21)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I21:P21&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G21),I21:P21)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G21,IF(AND(COUNTIF(I21:P21,"Fudokan sport kumite")&gt;0,Q21=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I21:P21,"Fudokan sport kumite")=0,Q21&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S21">
@@ -1586,14 +1882,37 @@
         <f>IF(OR($G21="",$E21=""),"sve_kilaze","kg_"&amp;$G21&amp;"_"&amp;IF($E21="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="22" spans="1:20">
+      <c r="U21">
+        <f>IF($A21="",0,IFERROR(MATCH(TRIM($A21),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <f>IF($U21=0,0,IF(TRIM(INDEX(spisak_klub,$U21))=TRIM($B$4),$U21,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22">
       <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
+      <c r="B22" s="5">
+        <f>IF($V22=0,"",INDEX(spisak_ime,$V22)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C22" s="5">
+        <f>IF($V22=0,"",INDEX(spisak_prezime,$V22)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D22" s="5">
+        <f>IF($V22=0,"",INDEX(spisak_godiste,$V22))</f>
+        <v/>
+      </c>
+      <c r="E22" s="5">
+        <f>IF($V22=0,"",INDEX(spisak_pol,$V22)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="5">
+        <f>IF($V22=0,"",INDEX(spisak_pojas,$V22)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G22" s="7">
         <f>IF($D22="","",LOOKUP($D22,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1612,7 +1931,7 @@
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
       <c r="R22" s="8">
-        <f>IF(COUNTA($A22:$F22,I22:P22,Q22)=0,"",IF(AND($A22&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A22,4))="FSS-",MID($A22,LEN($A22)-2,1)="/",ISNUMBER(VALUE(RIGHT($A22,2))),VALUE(MID($A22,5,LEN($A22)-7))&gt;=1,VALUE(MID($A22,5,LEN($A22)-7))=INT(VALUE(MID($A22,5,LEN($A22)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B22="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B22&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C22="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C22&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D22="","Nedostaje godište",IF($G22="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E22="","Nedostaje pol",IF($F22="","Nedostaje pojas",IF(COUNTA(I22:P22)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I22:P22&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G22),I22:P22)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G22,IF(AND(COUNTIF(I22:P22,"Fudokan sport kumite")&gt;0,Q22=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I22:P22,"Fudokan sport kumite")=0,Q22&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A22:$F22))+SUMPRODUCT(LEN(I22:P22))+LEN(Q22)=0,"",IF(AND($A22&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A22,4))="FSS-",MID($A22,LEN($A22)-2,1)="/",ISNUMBER(VALUE(RIGHT($A22,2))),VALUE(MID($A22,5,LEN($A22)-7))&gt;=1,VALUE(MID($A22,5,LEN($A22)-7))=INT(VALUE(MID($A22,5,LEN($A22)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A22&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A22&lt;&gt;"",$U22=0,$B22=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U22&gt;0,$V22=0,$B22=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U22)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B22="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B22&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C22="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C22&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D22="","Nedostaje godište",IF($G22="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E22="","Nedostaje pol",IF($F22="","Nedostaje pojas",IF(COUNTA(I22:P22)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I22:P22&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G22),I22:P22)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G22,IF(AND(COUNTIF(I22:P22,"Fudokan sport kumite")&gt;0,Q22=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I22:P22,"Fudokan sport kumite")=0,Q22&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S22">
@@ -1623,14 +1942,37 @@
         <f>IF(OR($G22="",$E22=""),"sve_kilaze","kg_"&amp;$G22&amp;"_"&amp;IF($E22="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="23" spans="1:20">
+      <c r="U22">
+        <f>IF($A22="",0,IFERROR(MATCH(TRIM($A22),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <f>IF($U22=0,0,IF(TRIM(INDEX(spisak_klub,$U22))=TRIM($B$4),$U22,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22">
       <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
+      <c r="B23" s="5">
+        <f>IF($V23=0,"",INDEX(spisak_ime,$V23)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C23" s="5">
+        <f>IF($V23=0,"",INDEX(spisak_prezime,$V23)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D23" s="5">
+        <f>IF($V23=0,"",INDEX(spisak_godiste,$V23))</f>
+        <v/>
+      </c>
+      <c r="E23" s="5">
+        <f>IF($V23=0,"",INDEX(spisak_pol,$V23)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="5">
+        <f>IF($V23=0,"",INDEX(spisak_pojas,$V23)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G23" s="7">
         <f>IF($D23="","",LOOKUP($D23,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1649,7 +1991,7 @@
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
       <c r="R23" s="8">
-        <f>IF(COUNTA($A23:$F23,I23:P23,Q23)=0,"",IF(AND($A23&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A23,4))="FSS-",MID($A23,LEN($A23)-2,1)="/",ISNUMBER(VALUE(RIGHT($A23,2))),VALUE(MID($A23,5,LEN($A23)-7))&gt;=1,VALUE(MID($A23,5,LEN($A23)-7))=INT(VALUE(MID($A23,5,LEN($A23)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B23="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B23&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C23="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C23&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D23="","Nedostaje godište",IF($G23="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E23="","Nedostaje pol",IF($F23="","Nedostaje pojas",IF(COUNTA(I23:P23)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I23:P23&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G23),I23:P23)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G23,IF(AND(COUNTIF(I23:P23,"Fudokan sport kumite")&gt;0,Q23=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I23:P23,"Fudokan sport kumite")=0,Q23&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A23:$F23))+SUMPRODUCT(LEN(I23:P23))+LEN(Q23)=0,"",IF(AND($A23&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A23,4))="FSS-",MID($A23,LEN($A23)-2,1)="/",ISNUMBER(VALUE(RIGHT($A23,2))),VALUE(MID($A23,5,LEN($A23)-7))&gt;=1,VALUE(MID($A23,5,LEN($A23)-7))=INT(VALUE(MID($A23,5,LEN($A23)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A23&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A23&lt;&gt;"",$U23=0,$B23=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U23&gt;0,$V23=0,$B23=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U23)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B23="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B23&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C23="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C23&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D23="","Nedostaje godište",IF($G23="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E23="","Nedostaje pol",IF($F23="","Nedostaje pojas",IF(COUNTA(I23:P23)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I23:P23&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G23),I23:P23)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G23,IF(AND(COUNTIF(I23:P23,"Fudokan sport kumite")&gt;0,Q23=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I23:P23,"Fudokan sport kumite")=0,Q23&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S23">
@@ -1660,14 +2002,37 @@
         <f>IF(OR($G23="",$E23=""),"sve_kilaze","kg_"&amp;$G23&amp;"_"&amp;IF($E23="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="24" spans="1:20">
+      <c r="U23">
+        <f>IF($A23="",0,IFERROR(MATCH(TRIM($A23),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <f>IF($U23=0,0,IF(TRIM(INDEX(spisak_klub,$U23))=TRIM($B$4),$U23,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
       <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
+      <c r="B24" s="5">
+        <f>IF($V24=0,"",INDEX(spisak_ime,$V24)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C24" s="5">
+        <f>IF($V24=0,"",INDEX(spisak_prezime,$V24)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D24" s="5">
+        <f>IF($V24=0,"",INDEX(spisak_godiste,$V24))</f>
+        <v/>
+      </c>
+      <c r="E24" s="5">
+        <f>IF($V24=0,"",INDEX(spisak_pol,$V24)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="5">
+        <f>IF($V24=0,"",INDEX(spisak_pojas,$V24)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G24" s="7">
         <f>IF($D24="","",LOOKUP($D24,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1686,7 +2051,7 @@
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
       <c r="R24" s="8">
-        <f>IF(COUNTA($A24:$F24,I24:P24,Q24)=0,"",IF(AND($A24&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A24,4))="FSS-",MID($A24,LEN($A24)-2,1)="/",ISNUMBER(VALUE(RIGHT($A24,2))),VALUE(MID($A24,5,LEN($A24)-7))&gt;=1,VALUE(MID($A24,5,LEN($A24)-7))=INT(VALUE(MID($A24,5,LEN($A24)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B24="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B24&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C24="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C24&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D24="","Nedostaje godište",IF($G24="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E24="","Nedostaje pol",IF($F24="","Nedostaje pojas",IF(COUNTA(I24:P24)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I24:P24&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G24),I24:P24)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G24,IF(AND(COUNTIF(I24:P24,"Fudokan sport kumite")&gt;0,Q24=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I24:P24,"Fudokan sport kumite")=0,Q24&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A24:$F24))+SUMPRODUCT(LEN(I24:P24))+LEN(Q24)=0,"",IF(AND($A24&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A24,4))="FSS-",MID($A24,LEN($A24)-2,1)="/",ISNUMBER(VALUE(RIGHT($A24,2))),VALUE(MID($A24,5,LEN($A24)-7))&gt;=1,VALUE(MID($A24,5,LEN($A24)-7))=INT(VALUE(MID($A24,5,LEN($A24)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A24&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A24&lt;&gt;"",$U24=0,$B24=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U24&gt;0,$V24=0,$B24=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U24)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B24="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B24&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C24="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C24&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D24="","Nedostaje godište",IF($G24="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E24="","Nedostaje pol",IF($F24="","Nedostaje pojas",IF(COUNTA(I24:P24)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I24:P24&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G24),I24:P24)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G24,IF(AND(COUNTIF(I24:P24,"Fudokan sport kumite")&gt;0,Q24=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I24:P24,"Fudokan sport kumite")=0,Q24&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S24">
@@ -1697,14 +2062,37 @@
         <f>IF(OR($G24="",$E24=""),"sve_kilaze","kg_"&amp;$G24&amp;"_"&amp;IF($E24="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="25" spans="1:20">
+      <c r="U24">
+        <f>IF($A24="",0,IFERROR(MATCH(TRIM($A24),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <f>IF($U24=0,0,IF(TRIM(INDEX(spisak_klub,$U24))=TRIM($B$4),$U24,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
       <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
+      <c r="B25" s="5">
+        <f>IF($V25=0,"",INDEX(spisak_ime,$V25)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C25" s="5">
+        <f>IF($V25=0,"",INDEX(spisak_prezime,$V25)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D25" s="5">
+        <f>IF($V25=0,"",INDEX(spisak_godiste,$V25))</f>
+        <v/>
+      </c>
+      <c r="E25" s="5">
+        <f>IF($V25=0,"",INDEX(spisak_pol,$V25)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="5">
+        <f>IF($V25=0,"",INDEX(spisak_pojas,$V25)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G25" s="7">
         <f>IF($D25="","",LOOKUP($D25,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1723,7 +2111,7 @@
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
       <c r="R25" s="8">
-        <f>IF(COUNTA($A25:$F25,I25:P25,Q25)=0,"",IF(AND($A25&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A25,4))="FSS-",MID($A25,LEN($A25)-2,1)="/",ISNUMBER(VALUE(RIGHT($A25,2))),VALUE(MID($A25,5,LEN($A25)-7))&gt;=1,VALUE(MID($A25,5,LEN($A25)-7))=INT(VALUE(MID($A25,5,LEN($A25)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B25="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B25&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C25="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C25&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D25="","Nedostaje godište",IF($G25="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E25="","Nedostaje pol",IF($F25="","Nedostaje pojas",IF(COUNTA(I25:P25)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I25:P25&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G25),I25:P25)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G25,IF(AND(COUNTIF(I25:P25,"Fudokan sport kumite")&gt;0,Q25=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I25:P25,"Fudokan sport kumite")=0,Q25&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A25:$F25))+SUMPRODUCT(LEN(I25:P25))+LEN(Q25)=0,"",IF(AND($A25&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A25,4))="FSS-",MID($A25,LEN($A25)-2,1)="/",ISNUMBER(VALUE(RIGHT($A25,2))),VALUE(MID($A25,5,LEN($A25)-7))&gt;=1,VALUE(MID($A25,5,LEN($A25)-7))=INT(VALUE(MID($A25,5,LEN($A25)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A25&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A25&lt;&gt;"",$U25=0,$B25=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U25&gt;0,$V25=0,$B25=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U25)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B25="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B25&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C25="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C25&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D25="","Nedostaje godište",IF($G25="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E25="","Nedostaje pol",IF($F25="","Nedostaje pojas",IF(COUNTA(I25:P25)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I25:P25&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G25),I25:P25)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G25,IF(AND(COUNTIF(I25:P25,"Fudokan sport kumite")&gt;0,Q25=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I25:P25,"Fudokan sport kumite")=0,Q25&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S25">
@@ -1734,14 +2122,37 @@
         <f>IF(OR($G25="",$E25=""),"sve_kilaze","kg_"&amp;$G25&amp;"_"&amp;IF($E25="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="26" spans="1:20">
+      <c r="U25">
+        <f>IF($A25="",0,IFERROR(MATCH(TRIM($A25),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <f>IF($U25=0,0,IF(TRIM(INDEX(spisak_klub,$U25))=TRIM($B$4),$U25,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22">
       <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
+      <c r="B26" s="5">
+        <f>IF($V26=0,"",INDEX(spisak_ime,$V26)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C26" s="5">
+        <f>IF($V26=0,"",INDEX(spisak_prezime,$V26)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D26" s="5">
+        <f>IF($V26=0,"",INDEX(spisak_godiste,$V26))</f>
+        <v/>
+      </c>
+      <c r="E26" s="5">
+        <f>IF($V26=0,"",INDEX(spisak_pol,$V26)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="5">
+        <f>IF($V26=0,"",INDEX(spisak_pojas,$V26)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G26" s="7">
         <f>IF($D26="","",LOOKUP($D26,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1760,7 +2171,7 @@
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
       <c r="R26" s="8">
-        <f>IF(COUNTA($A26:$F26,I26:P26,Q26)=0,"",IF(AND($A26&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A26,4))="FSS-",MID($A26,LEN($A26)-2,1)="/",ISNUMBER(VALUE(RIGHT($A26,2))),VALUE(MID($A26,5,LEN($A26)-7))&gt;=1,VALUE(MID($A26,5,LEN($A26)-7))=INT(VALUE(MID($A26,5,LEN($A26)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B26="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B26&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C26="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C26&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D26="","Nedostaje godište",IF($G26="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E26="","Nedostaje pol",IF($F26="","Nedostaje pojas",IF(COUNTA(I26:P26)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I26:P26&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G26),I26:P26)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G26,IF(AND(COUNTIF(I26:P26,"Fudokan sport kumite")&gt;0,Q26=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I26:P26,"Fudokan sport kumite")=0,Q26&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A26:$F26))+SUMPRODUCT(LEN(I26:P26))+LEN(Q26)=0,"",IF(AND($A26&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A26,4))="FSS-",MID($A26,LEN($A26)-2,1)="/",ISNUMBER(VALUE(RIGHT($A26,2))),VALUE(MID($A26,5,LEN($A26)-7))&gt;=1,VALUE(MID($A26,5,LEN($A26)-7))=INT(VALUE(MID($A26,5,LEN($A26)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A26&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A26&lt;&gt;"",$U26=0,$B26=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U26&gt;0,$V26=0,$B26=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U26)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B26="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B26&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C26="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C26&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D26="","Nedostaje godište",IF($G26="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E26="","Nedostaje pol",IF($F26="","Nedostaje pojas",IF(COUNTA(I26:P26)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I26:P26&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G26),I26:P26)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G26,IF(AND(COUNTIF(I26:P26,"Fudokan sport kumite")&gt;0,Q26=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I26:P26,"Fudokan sport kumite")=0,Q26&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S26">
@@ -1771,14 +2182,37 @@
         <f>IF(OR($G26="",$E26=""),"sve_kilaze","kg_"&amp;$G26&amp;"_"&amp;IF($E26="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="27" spans="1:20">
+      <c r="U26">
+        <f>IF($A26="",0,IFERROR(MATCH(TRIM($A26),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <f>IF($U26=0,0,IF(TRIM(INDEX(spisak_klub,$U26))=TRIM($B$4),$U26,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22">
       <c r="A27" s="5"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
+      <c r="B27" s="5">
+        <f>IF($V27=0,"",INDEX(spisak_ime,$V27)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C27" s="5">
+        <f>IF($V27=0,"",INDEX(spisak_prezime,$V27)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D27" s="5">
+        <f>IF($V27=0,"",INDEX(spisak_godiste,$V27))</f>
+        <v/>
+      </c>
+      <c r="E27" s="5">
+        <f>IF($V27=0,"",INDEX(spisak_pol,$V27)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="5">
+        <f>IF($V27=0,"",INDEX(spisak_pojas,$V27)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G27" s="7">
         <f>IF($D27="","",LOOKUP($D27,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1797,7 +2231,7 @@
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
       <c r="R27" s="8">
-        <f>IF(COUNTA($A27:$F27,I27:P27,Q27)=0,"",IF(AND($A27&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A27,4))="FSS-",MID($A27,LEN($A27)-2,1)="/",ISNUMBER(VALUE(RIGHT($A27,2))),VALUE(MID($A27,5,LEN($A27)-7))&gt;=1,VALUE(MID($A27,5,LEN($A27)-7))=INT(VALUE(MID($A27,5,LEN($A27)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B27="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B27&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C27="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C27&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D27="","Nedostaje godište",IF($G27="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E27="","Nedostaje pol",IF($F27="","Nedostaje pojas",IF(COUNTA(I27:P27)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I27:P27&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G27),I27:P27)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G27,IF(AND(COUNTIF(I27:P27,"Fudokan sport kumite")&gt;0,Q27=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I27:P27,"Fudokan sport kumite")=0,Q27&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A27:$F27))+SUMPRODUCT(LEN(I27:P27))+LEN(Q27)=0,"",IF(AND($A27&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A27,4))="FSS-",MID($A27,LEN($A27)-2,1)="/",ISNUMBER(VALUE(RIGHT($A27,2))),VALUE(MID($A27,5,LEN($A27)-7))&gt;=1,VALUE(MID($A27,5,LEN($A27)-7))=INT(VALUE(MID($A27,5,LEN($A27)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A27&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A27&lt;&gt;"",$U27=0,$B27=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U27&gt;0,$V27=0,$B27=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U27)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B27="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B27&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C27="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C27&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D27="","Nedostaje godište",IF($G27="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E27="","Nedostaje pol",IF($F27="","Nedostaje pojas",IF(COUNTA(I27:P27)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I27:P27&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G27),I27:P27)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G27,IF(AND(COUNTIF(I27:P27,"Fudokan sport kumite")&gt;0,Q27=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I27:P27,"Fudokan sport kumite")=0,Q27&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S27">
@@ -1808,14 +2242,37 @@
         <f>IF(OR($G27="",$E27=""),"sve_kilaze","kg_"&amp;$G27&amp;"_"&amp;IF($E27="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="28" spans="1:20">
+      <c r="U27">
+        <f>IF($A27="",0,IFERROR(MATCH(TRIM($A27),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <f>IF($U27=0,0,IF(TRIM(INDEX(spisak_klub,$U27))=TRIM($B$4),$U27,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22">
       <c r="A28" s="5"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
+      <c r="B28" s="5">
+        <f>IF($V28=0,"",INDEX(spisak_ime,$V28)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C28" s="5">
+        <f>IF($V28=0,"",INDEX(spisak_prezime,$V28)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D28" s="5">
+        <f>IF($V28=0,"",INDEX(spisak_godiste,$V28))</f>
+        <v/>
+      </c>
+      <c r="E28" s="5">
+        <f>IF($V28=0,"",INDEX(spisak_pol,$V28)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="5">
+        <f>IF($V28=0,"",INDEX(spisak_pojas,$V28)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G28" s="7">
         <f>IF($D28="","",LOOKUP($D28,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1834,7 +2291,7 @@
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
       <c r="R28" s="8">
-        <f>IF(COUNTA($A28:$F28,I28:P28,Q28)=0,"",IF(AND($A28&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A28,4))="FSS-",MID($A28,LEN($A28)-2,1)="/",ISNUMBER(VALUE(RIGHT($A28,2))),VALUE(MID($A28,5,LEN($A28)-7))&gt;=1,VALUE(MID($A28,5,LEN($A28)-7))=INT(VALUE(MID($A28,5,LEN($A28)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B28="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B28&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C28="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C28&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D28="","Nedostaje godište",IF($G28="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E28="","Nedostaje pol",IF($F28="","Nedostaje pojas",IF(COUNTA(I28:P28)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I28:P28&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G28),I28:P28)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G28,IF(AND(COUNTIF(I28:P28,"Fudokan sport kumite")&gt;0,Q28=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I28:P28,"Fudokan sport kumite")=0,Q28&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A28:$F28))+SUMPRODUCT(LEN(I28:P28))+LEN(Q28)=0,"",IF(AND($A28&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A28,4))="FSS-",MID($A28,LEN($A28)-2,1)="/",ISNUMBER(VALUE(RIGHT($A28,2))),VALUE(MID($A28,5,LEN($A28)-7))&gt;=1,VALUE(MID($A28,5,LEN($A28)-7))=INT(VALUE(MID($A28,5,LEN($A28)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A28&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A28&lt;&gt;"",$U28=0,$B28=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U28&gt;0,$V28=0,$B28=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U28)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B28="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B28&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C28="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C28&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D28="","Nedostaje godište",IF($G28="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E28="","Nedostaje pol",IF($F28="","Nedostaje pojas",IF(COUNTA(I28:P28)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I28:P28&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G28),I28:P28)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G28,IF(AND(COUNTIF(I28:P28,"Fudokan sport kumite")&gt;0,Q28=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I28:P28,"Fudokan sport kumite")=0,Q28&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S28">
@@ -1845,14 +2302,37 @@
         <f>IF(OR($G28="",$E28=""),"sve_kilaze","kg_"&amp;$G28&amp;"_"&amp;IF($E28="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="29" spans="1:20">
+      <c r="U28">
+        <f>IF($A28="",0,IFERROR(MATCH(TRIM($A28),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <f>IF($U28=0,0,IF(TRIM(INDEX(spisak_klub,$U28))=TRIM($B$4),$U28,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22">
       <c r="A29" s="5"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
+      <c r="B29" s="5">
+        <f>IF($V29=0,"",INDEX(spisak_ime,$V29)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C29" s="5">
+        <f>IF($V29=0,"",INDEX(spisak_prezime,$V29)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D29" s="5">
+        <f>IF($V29=0,"",INDEX(spisak_godiste,$V29))</f>
+        <v/>
+      </c>
+      <c r="E29" s="5">
+        <f>IF($V29=0,"",INDEX(spisak_pol,$V29)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="5">
+        <f>IF($V29=0,"",INDEX(spisak_pojas,$V29)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G29" s="7">
         <f>IF($D29="","",LOOKUP($D29,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1871,7 +2351,7 @@
       <c r="P29" s="5"/>
       <c r="Q29" s="5"/>
       <c r="R29" s="8">
-        <f>IF(COUNTA($A29:$F29,I29:P29,Q29)=0,"",IF(AND($A29&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A29,4))="FSS-",MID($A29,LEN($A29)-2,1)="/",ISNUMBER(VALUE(RIGHT($A29,2))),VALUE(MID($A29,5,LEN($A29)-7))&gt;=1,VALUE(MID($A29,5,LEN($A29)-7))=INT(VALUE(MID($A29,5,LEN($A29)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B29="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B29&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C29="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C29&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D29="","Nedostaje godište",IF($G29="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E29="","Nedostaje pol",IF($F29="","Nedostaje pojas",IF(COUNTA(I29:P29)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I29:P29&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G29),I29:P29)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G29,IF(AND(COUNTIF(I29:P29,"Fudokan sport kumite")&gt;0,Q29=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I29:P29,"Fudokan sport kumite")=0,Q29&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A29:$F29))+SUMPRODUCT(LEN(I29:P29))+LEN(Q29)=0,"",IF(AND($A29&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A29,4))="FSS-",MID($A29,LEN($A29)-2,1)="/",ISNUMBER(VALUE(RIGHT($A29,2))),VALUE(MID($A29,5,LEN($A29)-7))&gt;=1,VALUE(MID($A29,5,LEN($A29)-7))=INT(VALUE(MID($A29,5,LEN($A29)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A29&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A29&lt;&gt;"",$U29=0,$B29=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U29&gt;0,$V29=0,$B29=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U29)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B29="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B29&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C29="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C29&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D29="","Nedostaje godište",IF($G29="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E29="","Nedostaje pol",IF($F29="","Nedostaje pojas",IF(COUNTA(I29:P29)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I29:P29&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G29),I29:P29)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G29,IF(AND(COUNTIF(I29:P29,"Fudokan sport kumite")&gt;0,Q29=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I29:P29,"Fudokan sport kumite")=0,Q29&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S29">
@@ -1882,14 +2362,37 @@
         <f>IF(OR($G29="",$E29=""),"sve_kilaze","kg_"&amp;$G29&amp;"_"&amp;IF($E29="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="30" spans="1:20">
+      <c r="U29">
+        <f>IF($A29="",0,IFERROR(MATCH(TRIM($A29),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <f>IF($U29=0,0,IF(TRIM(INDEX(spisak_klub,$U29))=TRIM($B$4),$U29,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22">
       <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
+      <c r="B30" s="5">
+        <f>IF($V30=0,"",INDEX(spisak_ime,$V30)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C30" s="5">
+        <f>IF($V30=0,"",INDEX(spisak_prezime,$V30)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D30" s="5">
+        <f>IF($V30=0,"",INDEX(spisak_godiste,$V30))</f>
+        <v/>
+      </c>
+      <c r="E30" s="5">
+        <f>IF($V30=0,"",INDEX(spisak_pol,$V30)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="5">
+        <f>IF($V30=0,"",INDEX(spisak_pojas,$V30)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G30" s="7">
         <f>IF($D30="","",LOOKUP($D30,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1908,7 +2411,7 @@
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
       <c r="R30" s="8">
-        <f>IF(COUNTA($A30:$F30,I30:P30,Q30)=0,"",IF(AND($A30&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A30,4))="FSS-",MID($A30,LEN($A30)-2,1)="/",ISNUMBER(VALUE(RIGHT($A30,2))),VALUE(MID($A30,5,LEN($A30)-7))&gt;=1,VALUE(MID($A30,5,LEN($A30)-7))=INT(VALUE(MID($A30,5,LEN($A30)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B30="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B30&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C30="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C30&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D30="","Nedostaje godište",IF($G30="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E30="","Nedostaje pol",IF($F30="","Nedostaje pojas",IF(COUNTA(I30:P30)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I30:P30&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G30),I30:P30)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G30,IF(AND(COUNTIF(I30:P30,"Fudokan sport kumite")&gt;0,Q30=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I30:P30,"Fudokan sport kumite")=0,Q30&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A30:$F30))+SUMPRODUCT(LEN(I30:P30))+LEN(Q30)=0,"",IF(AND($A30&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A30,4))="FSS-",MID($A30,LEN($A30)-2,1)="/",ISNUMBER(VALUE(RIGHT($A30,2))),VALUE(MID($A30,5,LEN($A30)-7))&gt;=1,VALUE(MID($A30,5,LEN($A30)-7))=INT(VALUE(MID($A30,5,LEN($A30)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A30&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A30&lt;&gt;"",$U30=0,$B30=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U30&gt;0,$V30=0,$B30=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U30)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B30="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B30&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C30="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C30&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D30="","Nedostaje godište",IF($G30="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E30="","Nedostaje pol",IF($F30="","Nedostaje pojas",IF(COUNTA(I30:P30)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I30:P30&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G30),I30:P30)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G30,IF(AND(COUNTIF(I30:P30,"Fudokan sport kumite")&gt;0,Q30=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I30:P30,"Fudokan sport kumite")=0,Q30&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S30">
@@ -1919,14 +2422,37 @@
         <f>IF(OR($G30="",$E30=""),"sve_kilaze","kg_"&amp;$G30&amp;"_"&amp;IF($E30="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="31" spans="1:20">
+      <c r="U30">
+        <f>IF($A30="",0,IFERROR(MATCH(TRIM($A30),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <f>IF($U30=0,0,IF(TRIM(INDEX(spisak_klub,$U30))=TRIM($B$4),$U30,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22">
       <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
+      <c r="B31" s="5">
+        <f>IF($V31=0,"",INDEX(spisak_ime,$V31)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C31" s="5">
+        <f>IF($V31=0,"",INDEX(spisak_prezime,$V31)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D31" s="5">
+        <f>IF($V31=0,"",INDEX(spisak_godiste,$V31))</f>
+        <v/>
+      </c>
+      <c r="E31" s="5">
+        <f>IF($V31=0,"",INDEX(spisak_pol,$V31)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="5">
+        <f>IF($V31=0,"",INDEX(spisak_pojas,$V31)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G31" s="7">
         <f>IF($D31="","",LOOKUP($D31,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1945,7 +2471,7 @@
       <c r="P31" s="5"/>
       <c r="Q31" s="5"/>
       <c r="R31" s="8">
-        <f>IF(COUNTA($A31:$F31,I31:P31,Q31)=0,"",IF(AND($A31&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A31,4))="FSS-",MID($A31,LEN($A31)-2,1)="/",ISNUMBER(VALUE(RIGHT($A31,2))),VALUE(MID($A31,5,LEN($A31)-7))&gt;=1,VALUE(MID($A31,5,LEN($A31)-7))=INT(VALUE(MID($A31,5,LEN($A31)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B31="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B31&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C31="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C31&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D31="","Nedostaje godište",IF($G31="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E31="","Nedostaje pol",IF($F31="","Nedostaje pojas",IF(COUNTA(I31:P31)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I31:P31&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G31),I31:P31)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G31,IF(AND(COUNTIF(I31:P31,"Fudokan sport kumite")&gt;0,Q31=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I31:P31,"Fudokan sport kumite")=0,Q31&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A31:$F31))+SUMPRODUCT(LEN(I31:P31))+LEN(Q31)=0,"",IF(AND($A31&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A31,4))="FSS-",MID($A31,LEN($A31)-2,1)="/",ISNUMBER(VALUE(RIGHT($A31,2))),VALUE(MID($A31,5,LEN($A31)-7))&gt;=1,VALUE(MID($A31,5,LEN($A31)-7))=INT(VALUE(MID($A31,5,LEN($A31)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A31&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A31&lt;&gt;"",$U31=0,$B31=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U31&gt;0,$V31=0,$B31=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U31)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B31="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B31&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C31="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C31&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D31="","Nedostaje godište",IF($G31="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E31="","Nedostaje pol",IF($F31="","Nedostaje pojas",IF(COUNTA(I31:P31)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I31:P31&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G31),I31:P31)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G31,IF(AND(COUNTIF(I31:P31,"Fudokan sport kumite")&gt;0,Q31=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I31:P31,"Fudokan sport kumite")=0,Q31&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S31">
@@ -1956,14 +2482,37 @@
         <f>IF(OR($G31="",$E31=""),"sve_kilaze","kg_"&amp;$G31&amp;"_"&amp;IF($E31="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="32" spans="1:20">
+      <c r="U31">
+        <f>IF($A31="",0,IFERROR(MATCH(TRIM($A31),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <f>IF($U31=0,0,IF(TRIM(INDEX(spisak_klub,$U31))=TRIM($B$4),$U31,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22">
       <c r="A32" s="5"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
+      <c r="B32" s="5">
+        <f>IF($V32=0,"",INDEX(spisak_ime,$V32)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="5">
+        <f>IF($V32=0,"",INDEX(spisak_prezime,$V32)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="5">
+        <f>IF($V32=0,"",INDEX(spisak_godiste,$V32))</f>
+        <v/>
+      </c>
+      <c r="E32" s="5">
+        <f>IF($V32=0,"",INDEX(spisak_pol,$V32)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="5">
+        <f>IF($V32=0,"",INDEX(spisak_pojas,$V32)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G32" s="7">
         <f>IF($D32="","",LOOKUP($D32,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -1982,7 +2531,7 @@
       <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
       <c r="R32" s="8">
-        <f>IF(COUNTA($A32:$F32,I32:P32,Q32)=0,"",IF(AND($A32&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A32,4))="FSS-",MID($A32,LEN($A32)-2,1)="/",ISNUMBER(VALUE(RIGHT($A32,2))),VALUE(MID($A32,5,LEN($A32)-7))&gt;=1,VALUE(MID($A32,5,LEN($A32)-7))=INT(VALUE(MID($A32,5,LEN($A32)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B32="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B32&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C32="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C32&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D32="","Nedostaje godište",IF($G32="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E32="","Nedostaje pol",IF($F32="","Nedostaje pojas",IF(COUNTA(I32:P32)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I32:P32&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G32),I32:P32)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G32,IF(AND(COUNTIF(I32:P32,"Fudokan sport kumite")&gt;0,Q32=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I32:P32,"Fudokan sport kumite")=0,Q32&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A32:$F32))+SUMPRODUCT(LEN(I32:P32))+LEN(Q32)=0,"",IF(AND($A32&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A32,4))="FSS-",MID($A32,LEN($A32)-2,1)="/",ISNUMBER(VALUE(RIGHT($A32,2))),VALUE(MID($A32,5,LEN($A32)-7))&gt;=1,VALUE(MID($A32,5,LEN($A32)-7))=INT(VALUE(MID($A32,5,LEN($A32)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A32&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A32&lt;&gt;"",$U32=0,$B32=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U32&gt;0,$V32=0,$B32=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U32)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B32="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B32&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C32="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C32&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D32="","Nedostaje godište",IF($G32="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E32="","Nedostaje pol",IF($F32="","Nedostaje pojas",IF(COUNTA(I32:P32)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I32:P32&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G32),I32:P32)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G32,IF(AND(COUNTIF(I32:P32,"Fudokan sport kumite")&gt;0,Q32=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I32:P32,"Fudokan sport kumite")=0,Q32&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S32">
@@ -1993,14 +2542,37 @@
         <f>IF(OR($G32="",$E32=""),"sve_kilaze","kg_"&amp;$G32&amp;"_"&amp;IF($E32="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="33" spans="1:20">
+      <c r="U32">
+        <f>IF($A32="",0,IFERROR(MATCH(TRIM($A32),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <f>IF($U32=0,0,IF(TRIM(INDEX(spisak_klub,$U32))=TRIM($B$4),$U32,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22">
       <c r="A33" s="5"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
+      <c r="B33" s="5">
+        <f>IF($V33=0,"",INDEX(spisak_ime,$V33)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="5">
+        <f>IF($V33=0,"",INDEX(spisak_prezime,$V33)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="5">
+        <f>IF($V33=0,"",INDEX(spisak_godiste,$V33))</f>
+        <v/>
+      </c>
+      <c r="E33" s="5">
+        <f>IF($V33=0,"",INDEX(spisak_pol,$V33)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="5">
+        <f>IF($V33=0,"",INDEX(spisak_pojas,$V33)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G33" s="7">
         <f>IF($D33="","",LOOKUP($D33,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2019,7 +2591,7 @@
       <c r="P33" s="5"/>
       <c r="Q33" s="5"/>
       <c r="R33" s="8">
-        <f>IF(COUNTA($A33:$F33,I33:P33,Q33)=0,"",IF(AND($A33&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A33,4))="FSS-",MID($A33,LEN($A33)-2,1)="/",ISNUMBER(VALUE(RIGHT($A33,2))),VALUE(MID($A33,5,LEN($A33)-7))&gt;=1,VALUE(MID($A33,5,LEN($A33)-7))=INT(VALUE(MID($A33,5,LEN($A33)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B33="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B33&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C33="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C33&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D33="","Nedostaje godište",IF($G33="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E33="","Nedostaje pol",IF($F33="","Nedostaje pojas",IF(COUNTA(I33:P33)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I33:P33&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G33),I33:P33)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G33,IF(AND(COUNTIF(I33:P33,"Fudokan sport kumite")&gt;0,Q33=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I33:P33,"Fudokan sport kumite")=0,Q33&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A33:$F33))+SUMPRODUCT(LEN(I33:P33))+LEN(Q33)=0,"",IF(AND($A33&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A33,4))="FSS-",MID($A33,LEN($A33)-2,1)="/",ISNUMBER(VALUE(RIGHT($A33,2))),VALUE(MID($A33,5,LEN($A33)-7))&gt;=1,VALUE(MID($A33,5,LEN($A33)-7))=INT(VALUE(MID($A33,5,LEN($A33)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A33&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A33&lt;&gt;"",$U33=0,$B33=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U33&gt;0,$V33=0,$B33=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U33)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B33="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B33&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C33="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C33&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D33="","Nedostaje godište",IF($G33="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E33="","Nedostaje pol",IF($F33="","Nedostaje pojas",IF(COUNTA(I33:P33)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I33:P33&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G33),I33:P33)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G33,IF(AND(COUNTIF(I33:P33,"Fudokan sport kumite")&gt;0,Q33=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I33:P33,"Fudokan sport kumite")=0,Q33&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S33">
@@ -2030,14 +2602,37 @@
         <f>IF(OR($G33="",$E33=""),"sve_kilaze","kg_"&amp;$G33&amp;"_"&amp;IF($E33="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="34" spans="1:20">
+      <c r="U33">
+        <f>IF($A33="",0,IFERROR(MATCH(TRIM($A33),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <f>IF($U33=0,0,IF(TRIM(INDEX(spisak_klub,$U33))=TRIM($B$4),$U33,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22">
       <c r="A34" s="5"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
+      <c r="B34" s="5">
+        <f>IF($V34=0,"",INDEX(spisak_ime,$V34)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="5">
+        <f>IF($V34=0,"",INDEX(spisak_prezime,$V34)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="5">
+        <f>IF($V34=0,"",INDEX(spisak_godiste,$V34))</f>
+        <v/>
+      </c>
+      <c r="E34" s="5">
+        <f>IF($V34=0,"",INDEX(spisak_pol,$V34)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="5">
+        <f>IF($V34=0,"",INDEX(spisak_pojas,$V34)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G34" s="7">
         <f>IF($D34="","",LOOKUP($D34,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2056,7 +2651,7 @@
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
       <c r="R34" s="8">
-        <f>IF(COUNTA($A34:$F34,I34:P34,Q34)=0,"",IF(AND($A34&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A34,4))="FSS-",MID($A34,LEN($A34)-2,1)="/",ISNUMBER(VALUE(RIGHT($A34,2))),VALUE(MID($A34,5,LEN($A34)-7))&gt;=1,VALUE(MID($A34,5,LEN($A34)-7))=INT(VALUE(MID($A34,5,LEN($A34)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B34="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B34&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C34="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C34&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D34="","Nedostaje godište",IF($G34="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E34="","Nedostaje pol",IF($F34="","Nedostaje pojas",IF(COUNTA(I34:P34)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I34:P34&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G34),I34:P34)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G34,IF(AND(COUNTIF(I34:P34,"Fudokan sport kumite")&gt;0,Q34=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I34:P34,"Fudokan sport kumite")=0,Q34&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A34:$F34))+SUMPRODUCT(LEN(I34:P34))+LEN(Q34)=0,"",IF(AND($A34&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A34,4))="FSS-",MID($A34,LEN($A34)-2,1)="/",ISNUMBER(VALUE(RIGHT($A34,2))),VALUE(MID($A34,5,LEN($A34)-7))&gt;=1,VALUE(MID($A34,5,LEN($A34)-7))=INT(VALUE(MID($A34,5,LEN($A34)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A34&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A34&lt;&gt;"",$U34=0,$B34=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U34&gt;0,$V34=0,$B34=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U34)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B34="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B34&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C34="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C34&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D34="","Nedostaje godište",IF($G34="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E34="","Nedostaje pol",IF($F34="","Nedostaje pojas",IF(COUNTA(I34:P34)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I34:P34&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G34),I34:P34)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G34,IF(AND(COUNTIF(I34:P34,"Fudokan sport kumite")&gt;0,Q34=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I34:P34,"Fudokan sport kumite")=0,Q34&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S34">
@@ -2067,14 +2662,37 @@
         <f>IF(OR($G34="",$E34=""),"sve_kilaze","kg_"&amp;$G34&amp;"_"&amp;IF($E34="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="35" spans="1:20">
+      <c r="U34">
+        <f>IF($A34="",0,IFERROR(MATCH(TRIM($A34),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <f>IF($U34=0,0,IF(TRIM(INDEX(spisak_klub,$U34))=TRIM($B$4),$U34,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22">
       <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
+      <c r="B35" s="5">
+        <f>IF($V35=0,"",INDEX(spisak_ime,$V35)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="5">
+        <f>IF($V35=0,"",INDEX(spisak_prezime,$V35)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="5">
+        <f>IF($V35=0,"",INDEX(spisak_godiste,$V35))</f>
+        <v/>
+      </c>
+      <c r="E35" s="5">
+        <f>IF($V35=0,"",INDEX(spisak_pol,$V35)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="5">
+        <f>IF($V35=0,"",INDEX(spisak_pojas,$V35)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G35" s="7">
         <f>IF($D35="","",LOOKUP($D35,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2093,7 +2711,7 @@
       <c r="P35" s="5"/>
       <c r="Q35" s="5"/>
       <c r="R35" s="8">
-        <f>IF(COUNTA($A35:$F35,I35:P35,Q35)=0,"",IF(AND($A35&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A35,4))="FSS-",MID($A35,LEN($A35)-2,1)="/",ISNUMBER(VALUE(RIGHT($A35,2))),VALUE(MID($A35,5,LEN($A35)-7))&gt;=1,VALUE(MID($A35,5,LEN($A35)-7))=INT(VALUE(MID($A35,5,LEN($A35)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B35="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B35&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C35="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C35&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D35="","Nedostaje godište",IF($G35="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E35="","Nedostaje pol",IF($F35="","Nedostaje pojas",IF(COUNTA(I35:P35)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I35:P35&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G35),I35:P35)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G35,IF(AND(COUNTIF(I35:P35,"Fudokan sport kumite")&gt;0,Q35=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I35:P35,"Fudokan sport kumite")=0,Q35&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A35:$F35))+SUMPRODUCT(LEN(I35:P35))+LEN(Q35)=0,"",IF(AND($A35&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A35,4))="FSS-",MID($A35,LEN($A35)-2,1)="/",ISNUMBER(VALUE(RIGHT($A35,2))),VALUE(MID($A35,5,LEN($A35)-7))&gt;=1,VALUE(MID($A35,5,LEN($A35)-7))=INT(VALUE(MID($A35,5,LEN($A35)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A35&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A35&lt;&gt;"",$U35=0,$B35=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U35&gt;0,$V35=0,$B35=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U35)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B35="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B35&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C35="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C35&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D35="","Nedostaje godište",IF($G35="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E35="","Nedostaje pol",IF($F35="","Nedostaje pojas",IF(COUNTA(I35:P35)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I35:P35&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G35),I35:P35)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G35,IF(AND(COUNTIF(I35:P35,"Fudokan sport kumite")&gt;0,Q35=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I35:P35,"Fudokan sport kumite")=0,Q35&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S35">
@@ -2104,14 +2722,37 @@
         <f>IF(OR($G35="",$E35=""),"sve_kilaze","kg_"&amp;$G35&amp;"_"&amp;IF($E35="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="36" spans="1:20">
+      <c r="U35">
+        <f>IF($A35="",0,IFERROR(MATCH(TRIM($A35),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <f>IF($U35=0,0,IF(TRIM(INDEX(spisak_klub,$U35))=TRIM($B$4),$U35,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22">
       <c r="A36" s="5"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
+      <c r="B36" s="5">
+        <f>IF($V36=0,"",INDEX(spisak_ime,$V36)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="5">
+        <f>IF($V36=0,"",INDEX(spisak_prezime,$V36)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="5">
+        <f>IF($V36=0,"",INDEX(spisak_godiste,$V36))</f>
+        <v/>
+      </c>
+      <c r="E36" s="5">
+        <f>IF($V36=0,"",INDEX(spisak_pol,$V36)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="5">
+        <f>IF($V36=0,"",INDEX(spisak_pojas,$V36)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G36" s="7">
         <f>IF($D36="","",LOOKUP($D36,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2130,7 +2771,7 @@
       <c r="P36" s="5"/>
       <c r="Q36" s="5"/>
       <c r="R36" s="8">
-        <f>IF(COUNTA($A36:$F36,I36:P36,Q36)=0,"",IF(AND($A36&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A36,4))="FSS-",MID($A36,LEN($A36)-2,1)="/",ISNUMBER(VALUE(RIGHT($A36,2))),VALUE(MID($A36,5,LEN($A36)-7))&gt;=1,VALUE(MID($A36,5,LEN($A36)-7))=INT(VALUE(MID($A36,5,LEN($A36)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B36="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B36&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C36="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C36&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D36="","Nedostaje godište",IF($G36="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E36="","Nedostaje pol",IF($F36="","Nedostaje pojas",IF(COUNTA(I36:P36)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I36:P36&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G36),I36:P36)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G36,IF(AND(COUNTIF(I36:P36,"Fudokan sport kumite")&gt;0,Q36=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I36:P36,"Fudokan sport kumite")=0,Q36&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A36:$F36))+SUMPRODUCT(LEN(I36:P36))+LEN(Q36)=0,"",IF(AND($A36&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A36,4))="FSS-",MID($A36,LEN($A36)-2,1)="/",ISNUMBER(VALUE(RIGHT($A36,2))),VALUE(MID($A36,5,LEN($A36)-7))&gt;=1,VALUE(MID($A36,5,LEN($A36)-7))=INT(VALUE(MID($A36,5,LEN($A36)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A36&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A36&lt;&gt;"",$U36=0,$B36=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U36&gt;0,$V36=0,$B36=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U36)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B36="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B36&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C36="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C36&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D36="","Nedostaje godište",IF($G36="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E36="","Nedostaje pol",IF($F36="","Nedostaje pojas",IF(COUNTA(I36:P36)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I36:P36&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G36),I36:P36)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G36,IF(AND(COUNTIF(I36:P36,"Fudokan sport kumite")&gt;0,Q36=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I36:P36,"Fudokan sport kumite")=0,Q36&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S36">
@@ -2141,14 +2782,37 @@
         <f>IF(OR($G36="",$E36=""),"sve_kilaze","kg_"&amp;$G36&amp;"_"&amp;IF($E36="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="37" spans="1:20">
+      <c r="U36">
+        <f>IF($A36="",0,IFERROR(MATCH(TRIM($A36),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <f>IF($U36=0,0,IF(TRIM(INDEX(spisak_klub,$U36))=TRIM($B$4),$U36,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22">
       <c r="A37" s="5"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
+      <c r="B37" s="5">
+        <f>IF($V37=0,"",INDEX(spisak_ime,$V37)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="5">
+        <f>IF($V37=0,"",INDEX(spisak_prezime,$V37)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="5">
+        <f>IF($V37=0,"",INDEX(spisak_godiste,$V37))</f>
+        <v/>
+      </c>
+      <c r="E37" s="5">
+        <f>IF($V37=0,"",INDEX(spisak_pol,$V37)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="5">
+        <f>IF($V37=0,"",INDEX(spisak_pojas,$V37)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G37" s="7">
         <f>IF($D37="","",LOOKUP($D37,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2167,7 +2831,7 @@
       <c r="P37" s="5"/>
       <c r="Q37" s="5"/>
       <c r="R37" s="8">
-        <f>IF(COUNTA($A37:$F37,I37:P37,Q37)=0,"",IF(AND($A37&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A37,4))="FSS-",MID($A37,LEN($A37)-2,1)="/",ISNUMBER(VALUE(RIGHT($A37,2))),VALUE(MID($A37,5,LEN($A37)-7))&gt;=1,VALUE(MID($A37,5,LEN($A37)-7))=INT(VALUE(MID($A37,5,LEN($A37)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B37="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B37&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C37="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C37&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D37="","Nedostaje godište",IF($G37="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E37="","Nedostaje pol",IF($F37="","Nedostaje pojas",IF(COUNTA(I37:P37)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I37:P37&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G37),I37:P37)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G37,IF(AND(COUNTIF(I37:P37,"Fudokan sport kumite")&gt;0,Q37=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I37:P37,"Fudokan sport kumite")=0,Q37&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A37:$F37))+SUMPRODUCT(LEN(I37:P37))+LEN(Q37)=0,"",IF(AND($A37&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A37,4))="FSS-",MID($A37,LEN($A37)-2,1)="/",ISNUMBER(VALUE(RIGHT($A37,2))),VALUE(MID($A37,5,LEN($A37)-7))&gt;=1,VALUE(MID($A37,5,LEN($A37)-7))=INT(VALUE(MID($A37,5,LEN($A37)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A37&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A37&lt;&gt;"",$U37=0,$B37=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U37&gt;0,$V37=0,$B37=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U37)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B37="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B37&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C37="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C37&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D37="","Nedostaje godište",IF($G37="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E37="","Nedostaje pol",IF($F37="","Nedostaje pojas",IF(COUNTA(I37:P37)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I37:P37&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G37),I37:P37)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G37,IF(AND(COUNTIF(I37:P37,"Fudokan sport kumite")&gt;0,Q37=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I37:P37,"Fudokan sport kumite")=0,Q37&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S37">
@@ -2178,14 +2842,37 @@
         <f>IF(OR($G37="",$E37=""),"sve_kilaze","kg_"&amp;$G37&amp;"_"&amp;IF($E37="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="38" spans="1:20">
+      <c r="U37">
+        <f>IF($A37="",0,IFERROR(MATCH(TRIM($A37),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <f>IF($U37=0,0,IF(TRIM(INDEX(spisak_klub,$U37))=TRIM($B$4),$U37,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22">
       <c r="A38" s="5"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
+      <c r="B38" s="5">
+        <f>IF($V38=0,"",INDEX(spisak_ime,$V38)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="5">
+        <f>IF($V38=0,"",INDEX(spisak_prezime,$V38)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="5">
+        <f>IF($V38=0,"",INDEX(spisak_godiste,$V38))</f>
+        <v/>
+      </c>
+      <c r="E38" s="5">
+        <f>IF($V38=0,"",INDEX(spisak_pol,$V38)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="5">
+        <f>IF($V38=0,"",INDEX(spisak_pojas,$V38)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G38" s="7">
         <f>IF($D38="","",LOOKUP($D38,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2204,7 +2891,7 @@
       <c r="P38" s="5"/>
       <c r="Q38" s="5"/>
       <c r="R38" s="8">
-        <f>IF(COUNTA($A38:$F38,I38:P38,Q38)=0,"",IF(AND($A38&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A38,4))="FSS-",MID($A38,LEN($A38)-2,1)="/",ISNUMBER(VALUE(RIGHT($A38,2))),VALUE(MID($A38,5,LEN($A38)-7))&gt;=1,VALUE(MID($A38,5,LEN($A38)-7))=INT(VALUE(MID($A38,5,LEN($A38)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B38="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B38&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C38="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C38&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D38="","Nedostaje godište",IF($G38="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E38="","Nedostaje pol",IF($F38="","Nedostaje pojas",IF(COUNTA(I38:P38)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I38:P38&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G38),I38:P38)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G38,IF(AND(COUNTIF(I38:P38,"Fudokan sport kumite")&gt;0,Q38=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I38:P38,"Fudokan sport kumite")=0,Q38&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A38:$F38))+SUMPRODUCT(LEN(I38:P38))+LEN(Q38)=0,"",IF(AND($A38&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A38,4))="FSS-",MID($A38,LEN($A38)-2,1)="/",ISNUMBER(VALUE(RIGHT($A38,2))),VALUE(MID($A38,5,LEN($A38)-7))&gt;=1,VALUE(MID($A38,5,LEN($A38)-7))=INT(VALUE(MID($A38,5,LEN($A38)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A38&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A38&lt;&gt;"",$U38=0,$B38=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U38&gt;0,$V38=0,$B38=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U38)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B38="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B38&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C38="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C38&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D38="","Nedostaje godište",IF($G38="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E38="","Nedostaje pol",IF($F38="","Nedostaje pojas",IF(COUNTA(I38:P38)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I38:P38&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G38),I38:P38)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G38,IF(AND(COUNTIF(I38:P38,"Fudokan sport kumite")&gt;0,Q38=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I38:P38,"Fudokan sport kumite")=0,Q38&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S38">
@@ -2215,14 +2902,37 @@
         <f>IF(OR($G38="",$E38=""),"sve_kilaze","kg_"&amp;$G38&amp;"_"&amp;IF($E38="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="39" spans="1:20">
+      <c r="U38">
+        <f>IF($A38="",0,IFERROR(MATCH(TRIM($A38),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <f>IF($U38=0,0,IF(TRIM(INDEX(spisak_klub,$U38))=TRIM($B$4),$U38,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22">
       <c r="A39" s="5"/>
-      <c r="B39" s="5"/>
-      <c r="C39" s="5"/>
-      <c r="D39" s="5"/>
-      <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
+      <c r="B39" s="5">
+        <f>IF($V39=0,"",INDEX(spisak_ime,$V39)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C39" s="5">
+        <f>IF($V39=0,"",INDEX(spisak_prezime,$V39)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="5">
+        <f>IF($V39=0,"",INDEX(spisak_godiste,$V39))</f>
+        <v/>
+      </c>
+      <c r="E39" s="5">
+        <f>IF($V39=0,"",INDEX(spisak_pol,$V39)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="5">
+        <f>IF($V39=0,"",INDEX(spisak_pojas,$V39)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G39" s="7">
         <f>IF($D39="","",LOOKUP($D39,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2241,7 +2951,7 @@
       <c r="P39" s="5"/>
       <c r="Q39" s="5"/>
       <c r="R39" s="8">
-        <f>IF(COUNTA($A39:$F39,I39:P39,Q39)=0,"",IF(AND($A39&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A39,4))="FSS-",MID($A39,LEN($A39)-2,1)="/",ISNUMBER(VALUE(RIGHT($A39,2))),VALUE(MID($A39,5,LEN($A39)-7))&gt;=1,VALUE(MID($A39,5,LEN($A39)-7))=INT(VALUE(MID($A39,5,LEN($A39)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B39="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B39&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C39="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C39&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D39="","Nedostaje godište",IF($G39="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E39="","Nedostaje pol",IF($F39="","Nedostaje pojas",IF(COUNTA(I39:P39)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I39:P39&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G39),I39:P39)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G39,IF(AND(COUNTIF(I39:P39,"Fudokan sport kumite")&gt;0,Q39=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I39:P39,"Fudokan sport kumite")=0,Q39&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A39:$F39))+SUMPRODUCT(LEN(I39:P39))+LEN(Q39)=0,"",IF(AND($A39&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A39,4))="FSS-",MID($A39,LEN($A39)-2,1)="/",ISNUMBER(VALUE(RIGHT($A39,2))),VALUE(MID($A39,5,LEN($A39)-7))&gt;=1,VALUE(MID($A39,5,LEN($A39)-7))=INT(VALUE(MID($A39,5,LEN($A39)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A39&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A39&lt;&gt;"",$U39=0,$B39=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U39&gt;0,$V39=0,$B39=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U39)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B39="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B39&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C39="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C39&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D39="","Nedostaje godište",IF($G39="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E39="","Nedostaje pol",IF($F39="","Nedostaje pojas",IF(COUNTA(I39:P39)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I39:P39&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G39),I39:P39)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G39,IF(AND(COUNTIF(I39:P39,"Fudokan sport kumite")&gt;0,Q39=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I39:P39,"Fudokan sport kumite")=0,Q39&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S39">
@@ -2252,14 +2962,37 @@
         <f>IF(OR($G39="",$E39=""),"sve_kilaze","kg_"&amp;$G39&amp;"_"&amp;IF($E39="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="40" spans="1:20">
+      <c r="U39">
+        <f>IF($A39="",0,IFERROR(MATCH(TRIM($A39),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <f>IF($U39=0,0,IF(TRIM(INDEX(spisak_klub,$U39))=TRIM($B$4),$U39,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22">
       <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
+      <c r="B40" s="5">
+        <f>IF($V40=0,"",INDEX(spisak_ime,$V40)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C40" s="5">
+        <f>IF($V40=0,"",INDEX(spisak_prezime,$V40)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D40" s="5">
+        <f>IF($V40=0,"",INDEX(spisak_godiste,$V40))</f>
+        <v/>
+      </c>
+      <c r="E40" s="5">
+        <f>IF($V40=0,"",INDEX(spisak_pol,$V40)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="5">
+        <f>IF($V40=0,"",INDEX(spisak_pojas,$V40)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G40" s="7">
         <f>IF($D40="","",LOOKUP($D40,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2278,7 +3011,7 @@
       <c r="P40" s="5"/>
       <c r="Q40" s="5"/>
       <c r="R40" s="8">
-        <f>IF(COUNTA($A40:$F40,I40:P40,Q40)=0,"",IF(AND($A40&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A40,4))="FSS-",MID($A40,LEN($A40)-2,1)="/",ISNUMBER(VALUE(RIGHT($A40,2))),VALUE(MID($A40,5,LEN($A40)-7))&gt;=1,VALUE(MID($A40,5,LEN($A40)-7))=INT(VALUE(MID($A40,5,LEN($A40)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B40="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B40&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C40="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C40&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D40="","Nedostaje godište",IF($G40="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E40="","Nedostaje pol",IF($F40="","Nedostaje pojas",IF(COUNTA(I40:P40)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I40:P40&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G40),I40:P40)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G40,IF(AND(COUNTIF(I40:P40,"Fudokan sport kumite")&gt;0,Q40=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I40:P40,"Fudokan sport kumite")=0,Q40&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A40:$F40))+SUMPRODUCT(LEN(I40:P40))+LEN(Q40)=0,"",IF(AND($A40&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A40,4))="FSS-",MID($A40,LEN($A40)-2,1)="/",ISNUMBER(VALUE(RIGHT($A40,2))),VALUE(MID($A40,5,LEN($A40)-7))&gt;=1,VALUE(MID($A40,5,LEN($A40)-7))=INT(VALUE(MID($A40,5,LEN($A40)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A40&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A40&lt;&gt;"",$U40=0,$B40=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U40&gt;0,$V40=0,$B40=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U40)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B40="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B40&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C40="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C40&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D40="","Nedostaje godište",IF($G40="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E40="","Nedostaje pol",IF($F40="","Nedostaje pojas",IF(COUNTA(I40:P40)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I40:P40&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G40),I40:P40)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G40,IF(AND(COUNTIF(I40:P40,"Fudokan sport kumite")&gt;0,Q40=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I40:P40,"Fudokan sport kumite")=0,Q40&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S40">
@@ -2289,14 +3022,37 @@
         <f>IF(OR($G40="",$E40=""),"sve_kilaze","kg_"&amp;$G40&amp;"_"&amp;IF($E40="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="41" spans="1:20">
+      <c r="U40">
+        <f>IF($A40="",0,IFERROR(MATCH(TRIM($A40),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <f>IF($U40=0,0,IF(TRIM(INDEX(spisak_klub,$U40))=TRIM($B$4),$U40,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22">
       <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
+      <c r="B41" s="5">
+        <f>IF($V41=0,"",INDEX(spisak_ime,$V41)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="5">
+        <f>IF($V41=0,"",INDEX(spisak_prezime,$V41)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="5">
+        <f>IF($V41=0,"",INDEX(spisak_godiste,$V41))</f>
+        <v/>
+      </c>
+      <c r="E41" s="5">
+        <f>IF($V41=0,"",INDEX(spisak_pol,$V41)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="5">
+        <f>IF($V41=0,"",INDEX(spisak_pojas,$V41)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G41" s="7">
         <f>IF($D41="","",LOOKUP($D41,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2315,7 +3071,7 @@
       <c r="P41" s="5"/>
       <c r="Q41" s="5"/>
       <c r="R41" s="8">
-        <f>IF(COUNTA($A41:$F41,I41:P41,Q41)=0,"",IF(AND($A41&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A41,4))="FSS-",MID($A41,LEN($A41)-2,1)="/",ISNUMBER(VALUE(RIGHT($A41,2))),VALUE(MID($A41,5,LEN($A41)-7))&gt;=1,VALUE(MID($A41,5,LEN($A41)-7))=INT(VALUE(MID($A41,5,LEN($A41)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B41="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B41&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C41="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C41&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D41="","Nedostaje godište",IF($G41="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E41="","Nedostaje pol",IF($F41="","Nedostaje pojas",IF(COUNTA(I41:P41)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I41:P41&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G41),I41:P41)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G41,IF(AND(COUNTIF(I41:P41,"Fudokan sport kumite")&gt;0,Q41=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I41:P41,"Fudokan sport kumite")=0,Q41&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A41:$F41))+SUMPRODUCT(LEN(I41:P41))+LEN(Q41)=0,"",IF(AND($A41&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A41,4))="FSS-",MID($A41,LEN($A41)-2,1)="/",ISNUMBER(VALUE(RIGHT($A41,2))),VALUE(MID($A41,5,LEN($A41)-7))&gt;=1,VALUE(MID($A41,5,LEN($A41)-7))=INT(VALUE(MID($A41,5,LEN($A41)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A41&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A41&lt;&gt;"",$U41=0,$B41=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U41&gt;0,$V41=0,$B41=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U41)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B41="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B41&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C41="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C41&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D41="","Nedostaje godište",IF($G41="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E41="","Nedostaje pol",IF($F41="","Nedostaje pojas",IF(COUNTA(I41:P41)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I41:P41&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G41),I41:P41)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G41,IF(AND(COUNTIF(I41:P41,"Fudokan sport kumite")&gt;0,Q41=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I41:P41,"Fudokan sport kumite")=0,Q41&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S41">
@@ -2326,14 +3082,37 @@
         <f>IF(OR($G41="",$E41=""),"sve_kilaze","kg_"&amp;$G41&amp;"_"&amp;IF($E41="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="42" spans="1:20">
+      <c r="U41">
+        <f>IF($A41="",0,IFERROR(MATCH(TRIM($A41),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <f>IF($U41=0,0,IF(TRIM(INDEX(spisak_klub,$U41))=TRIM($B$4),$U41,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22">
       <c r="A42" s="5"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
+      <c r="B42" s="5">
+        <f>IF($V42=0,"",INDEX(spisak_ime,$V42)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C42" s="5">
+        <f>IF($V42=0,"",INDEX(spisak_prezime,$V42)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D42" s="5">
+        <f>IF($V42=0,"",INDEX(spisak_godiste,$V42))</f>
+        <v/>
+      </c>
+      <c r="E42" s="5">
+        <f>IF($V42=0,"",INDEX(spisak_pol,$V42)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="5">
+        <f>IF($V42=0,"",INDEX(spisak_pojas,$V42)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G42" s="7">
         <f>IF($D42="","",LOOKUP($D42,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2352,7 +3131,7 @@
       <c r="P42" s="5"/>
       <c r="Q42" s="5"/>
       <c r="R42" s="8">
-        <f>IF(COUNTA($A42:$F42,I42:P42,Q42)=0,"",IF(AND($A42&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A42,4))="FSS-",MID($A42,LEN($A42)-2,1)="/",ISNUMBER(VALUE(RIGHT($A42,2))),VALUE(MID($A42,5,LEN($A42)-7))&gt;=1,VALUE(MID($A42,5,LEN($A42)-7))=INT(VALUE(MID($A42,5,LEN($A42)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B42="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B42&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C42="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C42&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D42="","Nedostaje godište",IF($G42="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E42="","Nedostaje pol",IF($F42="","Nedostaje pojas",IF(COUNTA(I42:P42)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I42:P42&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G42),I42:P42)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G42,IF(AND(COUNTIF(I42:P42,"Fudokan sport kumite")&gt;0,Q42=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I42:P42,"Fudokan sport kumite")=0,Q42&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A42:$F42))+SUMPRODUCT(LEN(I42:P42))+LEN(Q42)=0,"",IF(AND($A42&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A42,4))="FSS-",MID($A42,LEN($A42)-2,1)="/",ISNUMBER(VALUE(RIGHT($A42,2))),VALUE(MID($A42,5,LEN($A42)-7))&gt;=1,VALUE(MID($A42,5,LEN($A42)-7))=INT(VALUE(MID($A42,5,LEN($A42)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A42&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A42&lt;&gt;"",$U42=0,$B42=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U42&gt;0,$V42=0,$B42=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U42)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B42="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B42&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C42="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C42&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D42="","Nedostaje godište",IF($G42="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E42="","Nedostaje pol",IF($F42="","Nedostaje pojas",IF(COUNTA(I42:P42)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I42:P42&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G42),I42:P42)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G42,IF(AND(COUNTIF(I42:P42,"Fudokan sport kumite")&gt;0,Q42=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I42:P42,"Fudokan sport kumite")=0,Q42&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S42">
@@ -2363,14 +3142,37 @@
         <f>IF(OR($G42="",$E42=""),"sve_kilaze","kg_"&amp;$G42&amp;"_"&amp;IF($E42="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="43" spans="1:20">
+      <c r="U42">
+        <f>IF($A42="",0,IFERROR(MATCH(TRIM($A42),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <f>IF($U42=0,0,IF(TRIM(INDEX(spisak_klub,$U42))=TRIM($B$4),$U42,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22">
       <c r="A43" s="5"/>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
+      <c r="B43" s="5">
+        <f>IF($V43=0,"",INDEX(spisak_ime,$V43)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="5">
+        <f>IF($V43=0,"",INDEX(spisak_prezime,$V43)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="5">
+        <f>IF($V43=0,"",INDEX(spisak_godiste,$V43))</f>
+        <v/>
+      </c>
+      <c r="E43" s="5">
+        <f>IF($V43=0,"",INDEX(spisak_pol,$V43)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="5">
+        <f>IF($V43=0,"",INDEX(spisak_pojas,$V43)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G43" s="7">
         <f>IF($D43="","",LOOKUP($D43,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2389,7 +3191,7 @@
       <c r="P43" s="5"/>
       <c r="Q43" s="5"/>
       <c r="R43" s="8">
-        <f>IF(COUNTA($A43:$F43,I43:P43,Q43)=0,"",IF(AND($A43&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A43,4))="FSS-",MID($A43,LEN($A43)-2,1)="/",ISNUMBER(VALUE(RIGHT($A43,2))),VALUE(MID($A43,5,LEN($A43)-7))&gt;=1,VALUE(MID($A43,5,LEN($A43)-7))=INT(VALUE(MID($A43,5,LEN($A43)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B43="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B43&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C43="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C43&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D43="","Nedostaje godište",IF($G43="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E43="","Nedostaje pol",IF($F43="","Nedostaje pojas",IF(COUNTA(I43:P43)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I43:P43&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G43),I43:P43)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G43,IF(AND(COUNTIF(I43:P43,"Fudokan sport kumite")&gt;0,Q43=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I43:P43,"Fudokan sport kumite")=0,Q43&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A43:$F43))+SUMPRODUCT(LEN(I43:P43))+LEN(Q43)=0,"",IF(AND($A43&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A43,4))="FSS-",MID($A43,LEN($A43)-2,1)="/",ISNUMBER(VALUE(RIGHT($A43,2))),VALUE(MID($A43,5,LEN($A43)-7))&gt;=1,VALUE(MID($A43,5,LEN($A43)-7))=INT(VALUE(MID($A43,5,LEN($A43)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A43&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A43&lt;&gt;"",$U43=0,$B43=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U43&gt;0,$V43=0,$B43=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U43)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B43="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B43&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C43="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C43&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D43="","Nedostaje godište",IF($G43="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E43="","Nedostaje pol",IF($F43="","Nedostaje pojas",IF(COUNTA(I43:P43)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I43:P43&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G43),I43:P43)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G43,IF(AND(COUNTIF(I43:P43,"Fudokan sport kumite")&gt;0,Q43=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I43:P43,"Fudokan sport kumite")=0,Q43&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S43">
@@ -2400,14 +3202,37 @@
         <f>IF(OR($G43="",$E43=""),"sve_kilaze","kg_"&amp;$G43&amp;"_"&amp;IF($E43="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="44" spans="1:20">
+      <c r="U43">
+        <f>IF($A43="",0,IFERROR(MATCH(TRIM($A43),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <f>IF($U43=0,0,IF(TRIM(INDEX(spisak_klub,$U43))=TRIM($B$4),$U43,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22">
       <c r="A44" s="5"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
+      <c r="B44" s="5">
+        <f>IF($V44=0,"",INDEX(spisak_ime,$V44)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="5">
+        <f>IF($V44=0,"",INDEX(spisak_prezime,$V44)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="5">
+        <f>IF($V44=0,"",INDEX(spisak_godiste,$V44))</f>
+        <v/>
+      </c>
+      <c r="E44" s="5">
+        <f>IF($V44=0,"",INDEX(spisak_pol,$V44)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="5">
+        <f>IF($V44=0,"",INDEX(spisak_pojas,$V44)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G44" s="7">
         <f>IF($D44="","",LOOKUP($D44,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2426,7 +3251,7 @@
       <c r="P44" s="5"/>
       <c r="Q44" s="5"/>
       <c r="R44" s="8">
-        <f>IF(COUNTA($A44:$F44,I44:P44,Q44)=0,"",IF(AND($A44&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A44,4))="FSS-",MID($A44,LEN($A44)-2,1)="/",ISNUMBER(VALUE(RIGHT($A44,2))),VALUE(MID($A44,5,LEN($A44)-7))&gt;=1,VALUE(MID($A44,5,LEN($A44)-7))=INT(VALUE(MID($A44,5,LEN($A44)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B44="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B44&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C44="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C44&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D44="","Nedostaje godište",IF($G44="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E44="","Nedostaje pol",IF($F44="","Nedostaje pojas",IF(COUNTA(I44:P44)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I44:P44&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G44),I44:P44)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G44,IF(AND(COUNTIF(I44:P44,"Fudokan sport kumite")&gt;0,Q44=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I44:P44,"Fudokan sport kumite")=0,Q44&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A44:$F44))+SUMPRODUCT(LEN(I44:P44))+LEN(Q44)=0,"",IF(AND($A44&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A44,4))="FSS-",MID($A44,LEN($A44)-2,1)="/",ISNUMBER(VALUE(RIGHT($A44,2))),VALUE(MID($A44,5,LEN($A44)-7))&gt;=1,VALUE(MID($A44,5,LEN($A44)-7))=INT(VALUE(MID($A44,5,LEN($A44)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A44&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A44&lt;&gt;"",$U44=0,$B44=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U44&gt;0,$V44=0,$B44=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U44)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B44="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B44&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C44="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C44&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D44="","Nedostaje godište",IF($G44="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E44="","Nedostaje pol",IF($F44="","Nedostaje pojas",IF(COUNTA(I44:P44)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I44:P44&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G44),I44:P44)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G44,IF(AND(COUNTIF(I44:P44,"Fudokan sport kumite")&gt;0,Q44=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I44:P44,"Fudokan sport kumite")=0,Q44&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S44">
@@ -2437,14 +3262,37 @@
         <f>IF(OR($G44="",$E44=""),"sve_kilaze","kg_"&amp;$G44&amp;"_"&amp;IF($E44="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="45" spans="1:20">
+      <c r="U44">
+        <f>IF($A44="",0,IFERROR(MATCH(TRIM($A44),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <f>IF($U44=0,0,IF(TRIM(INDEX(spisak_klub,$U44))=TRIM($B$4),$U44,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22">
       <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
+      <c r="B45" s="5">
+        <f>IF($V45=0,"",INDEX(spisak_ime,$V45)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="5">
+        <f>IF($V45=0,"",INDEX(spisak_prezime,$V45)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D45" s="5">
+        <f>IF($V45=0,"",INDEX(spisak_godiste,$V45))</f>
+        <v/>
+      </c>
+      <c r="E45" s="5">
+        <f>IF($V45=0,"",INDEX(spisak_pol,$V45)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="5">
+        <f>IF($V45=0,"",INDEX(spisak_pojas,$V45)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G45" s="7">
         <f>IF($D45="","",LOOKUP($D45,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2463,7 +3311,7 @@
       <c r="P45" s="5"/>
       <c r="Q45" s="5"/>
       <c r="R45" s="8">
-        <f>IF(COUNTA($A45:$F45,I45:P45,Q45)=0,"",IF(AND($A45&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A45,4))="FSS-",MID($A45,LEN($A45)-2,1)="/",ISNUMBER(VALUE(RIGHT($A45,2))),VALUE(MID($A45,5,LEN($A45)-7))&gt;=1,VALUE(MID($A45,5,LEN($A45)-7))=INT(VALUE(MID($A45,5,LEN($A45)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B45="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B45&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C45="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C45&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D45="","Nedostaje godište",IF($G45="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E45="","Nedostaje pol",IF($F45="","Nedostaje pojas",IF(COUNTA(I45:P45)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I45:P45&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G45),I45:P45)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G45,IF(AND(COUNTIF(I45:P45,"Fudokan sport kumite")&gt;0,Q45=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I45:P45,"Fudokan sport kumite")=0,Q45&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A45:$F45))+SUMPRODUCT(LEN(I45:P45))+LEN(Q45)=0,"",IF(AND($A45&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A45,4))="FSS-",MID($A45,LEN($A45)-2,1)="/",ISNUMBER(VALUE(RIGHT($A45,2))),VALUE(MID($A45,5,LEN($A45)-7))&gt;=1,VALUE(MID($A45,5,LEN($A45)-7))=INT(VALUE(MID($A45,5,LEN($A45)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A45&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A45&lt;&gt;"",$U45=0,$B45=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U45&gt;0,$V45=0,$B45=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U45)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B45="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B45&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C45="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C45&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D45="","Nedostaje godište",IF($G45="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E45="","Nedostaje pol",IF($F45="","Nedostaje pojas",IF(COUNTA(I45:P45)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I45:P45&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G45),I45:P45)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G45,IF(AND(COUNTIF(I45:P45,"Fudokan sport kumite")&gt;0,Q45=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I45:P45,"Fudokan sport kumite")=0,Q45&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S45">
@@ -2474,14 +3322,37 @@
         <f>IF(OR($G45="",$E45=""),"sve_kilaze","kg_"&amp;$G45&amp;"_"&amp;IF($E45="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="46" spans="1:20">
+      <c r="U45">
+        <f>IF($A45="",0,IFERROR(MATCH(TRIM($A45),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <f>IF($U45=0,0,IF(TRIM(INDEX(spisak_klub,$U45))=TRIM($B$4),$U45,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22">
       <c r="A46" s="5"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
+      <c r="B46" s="5">
+        <f>IF($V46=0,"",INDEX(spisak_ime,$V46)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C46" s="5">
+        <f>IF($V46=0,"",INDEX(spisak_prezime,$V46)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="5">
+        <f>IF($V46=0,"",INDEX(spisak_godiste,$V46))</f>
+        <v/>
+      </c>
+      <c r="E46" s="5">
+        <f>IF($V46=0,"",INDEX(spisak_pol,$V46)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="5">
+        <f>IF($V46=0,"",INDEX(spisak_pojas,$V46)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G46" s="7">
         <f>IF($D46="","",LOOKUP($D46,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2500,7 +3371,7 @@
       <c r="P46" s="5"/>
       <c r="Q46" s="5"/>
       <c r="R46" s="8">
-        <f>IF(COUNTA($A46:$F46,I46:P46,Q46)=0,"",IF(AND($A46&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A46,4))="FSS-",MID($A46,LEN($A46)-2,1)="/",ISNUMBER(VALUE(RIGHT($A46,2))),VALUE(MID($A46,5,LEN($A46)-7))&gt;=1,VALUE(MID($A46,5,LEN($A46)-7))=INT(VALUE(MID($A46,5,LEN($A46)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B46="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B46&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C46="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C46&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D46="","Nedostaje godište",IF($G46="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E46="","Nedostaje pol",IF($F46="","Nedostaje pojas",IF(COUNTA(I46:P46)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I46:P46&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G46),I46:P46)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G46,IF(AND(COUNTIF(I46:P46,"Fudokan sport kumite")&gt;0,Q46=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I46:P46,"Fudokan sport kumite")=0,Q46&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A46:$F46))+SUMPRODUCT(LEN(I46:P46))+LEN(Q46)=0,"",IF(AND($A46&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A46,4))="FSS-",MID($A46,LEN($A46)-2,1)="/",ISNUMBER(VALUE(RIGHT($A46,2))),VALUE(MID($A46,5,LEN($A46)-7))&gt;=1,VALUE(MID($A46,5,LEN($A46)-7))=INT(VALUE(MID($A46,5,LEN($A46)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A46&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A46&lt;&gt;"",$U46=0,$B46=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U46&gt;0,$V46=0,$B46=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U46)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B46="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B46&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C46="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C46&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D46="","Nedostaje godište",IF($G46="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E46="","Nedostaje pol",IF($F46="","Nedostaje pojas",IF(COUNTA(I46:P46)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I46:P46&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G46),I46:P46)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G46,IF(AND(COUNTIF(I46:P46,"Fudokan sport kumite")&gt;0,Q46=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I46:P46,"Fudokan sport kumite")=0,Q46&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S46">
@@ -2511,14 +3382,37 @@
         <f>IF(OR($G46="",$E46=""),"sve_kilaze","kg_"&amp;$G46&amp;"_"&amp;IF($E46="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="47" spans="1:20">
+      <c r="U46">
+        <f>IF($A46="",0,IFERROR(MATCH(TRIM($A46),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <f>IF($U46=0,0,IF(TRIM(INDEX(spisak_klub,$U46))=TRIM($B$4),$U46,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22">
       <c r="A47" s="5"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
+      <c r="B47" s="5">
+        <f>IF($V47=0,"",INDEX(spisak_ime,$V47)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C47" s="5">
+        <f>IF($V47=0,"",INDEX(spisak_prezime,$V47)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D47" s="5">
+        <f>IF($V47=0,"",INDEX(spisak_godiste,$V47))</f>
+        <v/>
+      </c>
+      <c r="E47" s="5">
+        <f>IF($V47=0,"",INDEX(spisak_pol,$V47)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="5">
+        <f>IF($V47=0,"",INDEX(spisak_pojas,$V47)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G47" s="7">
         <f>IF($D47="","",LOOKUP($D47,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2537,7 +3431,7 @@
       <c r="P47" s="5"/>
       <c r="Q47" s="5"/>
       <c r="R47" s="8">
-        <f>IF(COUNTA($A47:$F47,I47:P47,Q47)=0,"",IF(AND($A47&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A47,4))="FSS-",MID($A47,LEN($A47)-2,1)="/",ISNUMBER(VALUE(RIGHT($A47,2))),VALUE(MID($A47,5,LEN($A47)-7))&gt;=1,VALUE(MID($A47,5,LEN($A47)-7))=INT(VALUE(MID($A47,5,LEN($A47)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B47="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B47&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C47="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C47&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D47="","Nedostaje godište",IF($G47="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E47="","Nedostaje pol",IF($F47="","Nedostaje pojas",IF(COUNTA(I47:P47)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I47:P47&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G47),I47:P47)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G47,IF(AND(COUNTIF(I47:P47,"Fudokan sport kumite")&gt;0,Q47=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I47:P47,"Fudokan sport kumite")=0,Q47&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A47:$F47))+SUMPRODUCT(LEN(I47:P47))+LEN(Q47)=0,"",IF(AND($A47&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A47,4))="FSS-",MID($A47,LEN($A47)-2,1)="/",ISNUMBER(VALUE(RIGHT($A47,2))),VALUE(MID($A47,5,LEN($A47)-7))&gt;=1,VALUE(MID($A47,5,LEN($A47)-7))=INT(VALUE(MID($A47,5,LEN($A47)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A47&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A47&lt;&gt;"",$U47=0,$B47=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U47&gt;0,$V47=0,$B47=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U47)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B47="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B47&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C47="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C47&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D47="","Nedostaje godište",IF($G47="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E47="","Nedostaje pol",IF($F47="","Nedostaje pojas",IF(COUNTA(I47:P47)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I47:P47&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G47),I47:P47)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G47,IF(AND(COUNTIF(I47:P47,"Fudokan sport kumite")&gt;0,Q47=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I47:P47,"Fudokan sport kumite")=0,Q47&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S47">
@@ -2548,14 +3442,37 @@
         <f>IF(OR($G47="",$E47=""),"sve_kilaze","kg_"&amp;$G47&amp;"_"&amp;IF($E47="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="48" spans="1:20">
+      <c r="U47">
+        <f>IF($A47="",0,IFERROR(MATCH(TRIM($A47),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <f>IF($U47=0,0,IF(TRIM(INDEX(spisak_klub,$U47))=TRIM($B$4),$U47,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22">
       <c r="A48" s="5"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
+      <c r="B48" s="5">
+        <f>IF($V48=0,"",INDEX(spisak_ime,$V48)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C48" s="5">
+        <f>IF($V48=0,"",INDEX(spisak_prezime,$V48)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D48" s="5">
+        <f>IF($V48=0,"",INDEX(spisak_godiste,$V48))</f>
+        <v/>
+      </c>
+      <c r="E48" s="5">
+        <f>IF($V48=0,"",INDEX(spisak_pol,$V48)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F48" s="5">
+        <f>IF($V48=0,"",INDEX(spisak_pojas,$V48)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G48" s="7">
         <f>IF($D48="","",LOOKUP($D48,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2574,7 +3491,7 @@
       <c r="P48" s="5"/>
       <c r="Q48" s="5"/>
       <c r="R48" s="8">
-        <f>IF(COUNTA($A48:$F48,I48:P48,Q48)=0,"",IF(AND($A48&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A48,4))="FSS-",MID($A48,LEN($A48)-2,1)="/",ISNUMBER(VALUE(RIGHT($A48,2))),VALUE(MID($A48,5,LEN($A48)-7))&gt;=1,VALUE(MID($A48,5,LEN($A48)-7))=INT(VALUE(MID($A48,5,LEN($A48)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B48="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B48&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C48="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C48&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D48="","Nedostaje godište",IF($G48="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E48="","Nedostaje pol",IF($F48="","Nedostaje pojas",IF(COUNTA(I48:P48)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I48:P48&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G48),I48:P48)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G48,IF(AND(COUNTIF(I48:P48,"Fudokan sport kumite")&gt;0,Q48=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I48:P48,"Fudokan sport kumite")=0,Q48&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A48:$F48))+SUMPRODUCT(LEN(I48:P48))+LEN(Q48)=0,"",IF(AND($A48&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A48,4))="FSS-",MID($A48,LEN($A48)-2,1)="/",ISNUMBER(VALUE(RIGHT($A48,2))),VALUE(MID($A48,5,LEN($A48)-7))&gt;=1,VALUE(MID($A48,5,LEN($A48)-7))=INT(VALUE(MID($A48,5,LEN($A48)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A48&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A48&lt;&gt;"",$U48=0,$B48=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U48&gt;0,$V48=0,$B48=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U48)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B48="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B48&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C48="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C48&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D48="","Nedostaje godište",IF($G48="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E48="","Nedostaje pol",IF($F48="","Nedostaje pojas",IF(COUNTA(I48:P48)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I48:P48&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G48),I48:P48)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G48,IF(AND(COUNTIF(I48:P48,"Fudokan sport kumite")&gt;0,Q48=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I48:P48,"Fudokan sport kumite")=0,Q48&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S48">
@@ -2585,14 +3502,37 @@
         <f>IF(OR($G48="",$E48=""),"sve_kilaze","kg_"&amp;$G48&amp;"_"&amp;IF($E48="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="49" spans="1:20">
+      <c r="U48">
+        <f>IF($A48="",0,IFERROR(MATCH(TRIM($A48),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <f>IF($U48=0,0,IF(TRIM(INDEX(spisak_klub,$U48))=TRIM($B$4),$U48,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22">
       <c r="A49" s="5"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
+      <c r="B49" s="5">
+        <f>IF($V49=0,"",INDEX(spisak_ime,$V49)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C49" s="5">
+        <f>IF($V49=0,"",INDEX(spisak_prezime,$V49)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D49" s="5">
+        <f>IF($V49=0,"",INDEX(spisak_godiste,$V49))</f>
+        <v/>
+      </c>
+      <c r="E49" s="5">
+        <f>IF($V49=0,"",INDEX(spisak_pol,$V49)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="5">
+        <f>IF($V49=0,"",INDEX(spisak_pojas,$V49)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G49" s="7">
         <f>IF($D49="","",LOOKUP($D49,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2611,7 +3551,7 @@
       <c r="P49" s="5"/>
       <c r="Q49" s="5"/>
       <c r="R49" s="8">
-        <f>IF(COUNTA($A49:$F49,I49:P49,Q49)=0,"",IF(AND($A49&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A49,4))="FSS-",MID($A49,LEN($A49)-2,1)="/",ISNUMBER(VALUE(RIGHT($A49,2))),VALUE(MID($A49,5,LEN($A49)-7))&gt;=1,VALUE(MID($A49,5,LEN($A49)-7))=INT(VALUE(MID($A49,5,LEN($A49)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B49="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B49&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C49="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C49&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D49="","Nedostaje godište",IF($G49="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E49="","Nedostaje pol",IF($F49="","Nedostaje pojas",IF(COUNTA(I49:P49)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I49:P49&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G49),I49:P49)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G49,IF(AND(COUNTIF(I49:P49,"Fudokan sport kumite")&gt;0,Q49=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I49:P49,"Fudokan sport kumite")=0,Q49&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A49:$F49))+SUMPRODUCT(LEN(I49:P49))+LEN(Q49)=0,"",IF(AND($A49&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A49,4))="FSS-",MID($A49,LEN($A49)-2,1)="/",ISNUMBER(VALUE(RIGHT($A49,2))),VALUE(MID($A49,5,LEN($A49)-7))&gt;=1,VALUE(MID($A49,5,LEN($A49)-7))=INT(VALUE(MID($A49,5,LEN($A49)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A49&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A49&lt;&gt;"",$U49=0,$B49=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U49&gt;0,$V49=0,$B49=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U49)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B49="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B49&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C49="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C49&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D49="","Nedostaje godište",IF($G49="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E49="","Nedostaje pol",IF($F49="","Nedostaje pojas",IF(COUNTA(I49:P49)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I49:P49&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G49),I49:P49)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G49,IF(AND(COUNTIF(I49:P49,"Fudokan sport kumite")&gt;0,Q49=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I49:P49,"Fudokan sport kumite")=0,Q49&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S49">
@@ -2622,14 +3562,37 @@
         <f>IF(OR($G49="",$E49=""),"sve_kilaze","kg_"&amp;$G49&amp;"_"&amp;IF($E49="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="50" spans="1:20">
+      <c r="U49">
+        <f>IF($A49="",0,IFERROR(MATCH(TRIM($A49),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <f>IF($U49=0,0,IF(TRIM(INDEX(spisak_klub,$U49))=TRIM($B$4),$U49,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22">
       <c r="A50" s="5"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
+      <c r="B50" s="5">
+        <f>IF($V50=0,"",INDEX(spisak_ime,$V50)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C50" s="5">
+        <f>IF($V50=0,"",INDEX(spisak_prezime,$V50)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D50" s="5">
+        <f>IF($V50=0,"",INDEX(spisak_godiste,$V50))</f>
+        <v/>
+      </c>
+      <c r="E50" s="5">
+        <f>IF($V50=0,"",INDEX(spisak_pol,$V50)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F50" s="5">
+        <f>IF($V50=0,"",INDEX(spisak_pojas,$V50)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G50" s="7">
         <f>IF($D50="","",LOOKUP($D50,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2648,7 +3611,7 @@
       <c r="P50" s="5"/>
       <c r="Q50" s="5"/>
       <c r="R50" s="8">
-        <f>IF(COUNTA($A50:$F50,I50:P50,Q50)=0,"",IF(AND($A50&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A50,4))="FSS-",MID($A50,LEN($A50)-2,1)="/",ISNUMBER(VALUE(RIGHT($A50,2))),VALUE(MID($A50,5,LEN($A50)-7))&gt;=1,VALUE(MID($A50,5,LEN($A50)-7))=INT(VALUE(MID($A50,5,LEN($A50)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B50="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B50&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C50="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C50&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D50="","Nedostaje godište",IF($G50="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E50="","Nedostaje pol",IF($F50="","Nedostaje pojas",IF(COUNTA(I50:P50)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I50:P50&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G50),I50:P50)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G50,IF(AND(COUNTIF(I50:P50,"Fudokan sport kumite")&gt;0,Q50=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I50:P50,"Fudokan sport kumite")=0,Q50&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A50:$F50))+SUMPRODUCT(LEN(I50:P50))+LEN(Q50)=0,"",IF(AND($A50&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A50,4))="FSS-",MID($A50,LEN($A50)-2,1)="/",ISNUMBER(VALUE(RIGHT($A50,2))),VALUE(MID($A50,5,LEN($A50)-7))&gt;=1,VALUE(MID($A50,5,LEN($A50)-7))=INT(VALUE(MID($A50,5,LEN($A50)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A50&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A50&lt;&gt;"",$U50=0,$B50=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U50&gt;0,$V50=0,$B50=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U50)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B50="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B50&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C50="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C50&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D50="","Nedostaje godište",IF($G50="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E50="","Nedostaje pol",IF($F50="","Nedostaje pojas",IF(COUNTA(I50:P50)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I50:P50&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G50),I50:P50)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G50,IF(AND(COUNTIF(I50:P50,"Fudokan sport kumite")&gt;0,Q50=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I50:P50,"Fudokan sport kumite")=0,Q50&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S50">
@@ -2659,14 +3622,37 @@
         <f>IF(OR($G50="",$E50=""),"sve_kilaze","kg_"&amp;$G50&amp;"_"&amp;IF($E50="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="51" spans="1:20">
+      <c r="U50">
+        <f>IF($A50="",0,IFERROR(MATCH(TRIM($A50),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <f>IF($U50=0,0,IF(TRIM(INDEX(spisak_klub,$U50))=TRIM($B$4),$U50,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22">
       <c r="A51" s="5"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="5"/>
-      <c r="E51" s="5"/>
-      <c r="F51" s="5"/>
+      <c r="B51" s="5">
+        <f>IF($V51=0,"",INDEX(spisak_ime,$V51)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C51" s="5">
+        <f>IF($V51=0,"",INDEX(spisak_prezime,$V51)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D51" s="5">
+        <f>IF($V51=0,"",INDEX(spisak_godiste,$V51))</f>
+        <v/>
+      </c>
+      <c r="E51" s="5">
+        <f>IF($V51=0,"",INDEX(spisak_pol,$V51)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="5">
+        <f>IF($V51=0,"",INDEX(spisak_pojas,$V51)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G51" s="7">
         <f>IF($D51="","",LOOKUP($D51,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2685,7 +3671,7 @@
       <c r="P51" s="5"/>
       <c r="Q51" s="5"/>
       <c r="R51" s="8">
-        <f>IF(COUNTA($A51:$F51,I51:P51,Q51)=0,"",IF(AND($A51&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A51,4))="FSS-",MID($A51,LEN($A51)-2,1)="/",ISNUMBER(VALUE(RIGHT($A51,2))),VALUE(MID($A51,5,LEN($A51)-7))&gt;=1,VALUE(MID($A51,5,LEN($A51)-7))=INT(VALUE(MID($A51,5,LEN($A51)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B51="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B51&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C51="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C51&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D51="","Nedostaje godište",IF($G51="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E51="","Nedostaje pol",IF($F51="","Nedostaje pojas",IF(COUNTA(I51:P51)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I51:P51&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G51),I51:P51)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G51,IF(AND(COUNTIF(I51:P51,"Fudokan sport kumite")&gt;0,Q51=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I51:P51,"Fudokan sport kumite")=0,Q51&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A51:$F51))+SUMPRODUCT(LEN(I51:P51))+LEN(Q51)=0,"",IF(AND($A51&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A51,4))="FSS-",MID($A51,LEN($A51)-2,1)="/",ISNUMBER(VALUE(RIGHT($A51,2))),VALUE(MID($A51,5,LEN($A51)-7))&gt;=1,VALUE(MID($A51,5,LEN($A51)-7))=INT(VALUE(MID($A51,5,LEN($A51)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A51&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A51&lt;&gt;"",$U51=0,$B51=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U51&gt;0,$V51=0,$B51=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U51)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B51="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B51&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C51="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C51&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D51="","Nedostaje godište",IF($G51="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E51="","Nedostaje pol",IF($F51="","Nedostaje pojas",IF(COUNTA(I51:P51)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I51:P51&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G51),I51:P51)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G51,IF(AND(COUNTIF(I51:P51,"Fudokan sport kumite")&gt;0,Q51=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I51:P51,"Fudokan sport kumite")=0,Q51&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S51">
@@ -2696,14 +3682,37 @@
         <f>IF(OR($G51="",$E51=""),"sve_kilaze","kg_"&amp;$G51&amp;"_"&amp;IF($E51="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="52" spans="1:20">
+      <c r="U51">
+        <f>IF($A51="",0,IFERROR(MATCH(TRIM($A51),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <f>IF($U51=0,0,IF(TRIM(INDEX(spisak_klub,$U51))=TRIM($B$4),$U51,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22">
       <c r="A52" s="5"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
+      <c r="B52" s="5">
+        <f>IF($V52=0,"",INDEX(spisak_ime,$V52)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C52" s="5">
+        <f>IF($V52=0,"",INDEX(spisak_prezime,$V52)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D52" s="5">
+        <f>IF($V52=0,"",INDEX(spisak_godiste,$V52))</f>
+        <v/>
+      </c>
+      <c r="E52" s="5">
+        <f>IF($V52=0,"",INDEX(spisak_pol,$V52)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F52" s="5">
+        <f>IF($V52=0,"",INDEX(spisak_pojas,$V52)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G52" s="7">
         <f>IF($D52="","",LOOKUP($D52,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2722,7 +3731,7 @@
       <c r="P52" s="5"/>
       <c r="Q52" s="5"/>
       <c r="R52" s="8">
-        <f>IF(COUNTA($A52:$F52,I52:P52,Q52)=0,"",IF(AND($A52&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A52,4))="FSS-",MID($A52,LEN($A52)-2,1)="/",ISNUMBER(VALUE(RIGHT($A52,2))),VALUE(MID($A52,5,LEN($A52)-7))&gt;=1,VALUE(MID($A52,5,LEN($A52)-7))=INT(VALUE(MID($A52,5,LEN($A52)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B52="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B52&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C52="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C52&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D52="","Nedostaje godište",IF($G52="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E52="","Nedostaje pol",IF($F52="","Nedostaje pojas",IF(COUNTA(I52:P52)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I52:P52&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G52),I52:P52)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G52,IF(AND(COUNTIF(I52:P52,"Fudokan sport kumite")&gt;0,Q52=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I52:P52,"Fudokan sport kumite")=0,Q52&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A52:$F52))+SUMPRODUCT(LEN(I52:P52))+LEN(Q52)=0,"",IF(AND($A52&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A52,4))="FSS-",MID($A52,LEN($A52)-2,1)="/",ISNUMBER(VALUE(RIGHT($A52,2))),VALUE(MID($A52,5,LEN($A52)-7))&gt;=1,VALUE(MID($A52,5,LEN($A52)-7))=INT(VALUE(MID($A52,5,LEN($A52)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A52&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A52&lt;&gt;"",$U52=0,$B52=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U52&gt;0,$V52=0,$B52=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U52)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B52="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B52&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C52="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C52&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D52="","Nedostaje godište",IF($G52="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E52="","Nedostaje pol",IF($F52="","Nedostaje pojas",IF(COUNTA(I52:P52)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I52:P52&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G52),I52:P52)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G52,IF(AND(COUNTIF(I52:P52,"Fudokan sport kumite")&gt;0,Q52=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I52:P52,"Fudokan sport kumite")=0,Q52&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S52">
@@ -2733,14 +3742,37 @@
         <f>IF(OR($G52="",$E52=""),"sve_kilaze","kg_"&amp;$G52&amp;"_"&amp;IF($E52="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="53" spans="1:20">
+      <c r="U52">
+        <f>IF($A52="",0,IFERROR(MATCH(TRIM($A52),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <f>IF($U52=0,0,IF(TRIM(INDEX(spisak_klub,$U52))=TRIM($B$4),$U52,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22">
       <c r="A53" s="5"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
+      <c r="B53" s="5">
+        <f>IF($V53=0,"",INDEX(spisak_ime,$V53)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C53" s="5">
+        <f>IF($V53=0,"",INDEX(spisak_prezime,$V53)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D53" s="5">
+        <f>IF($V53=0,"",INDEX(spisak_godiste,$V53))</f>
+        <v/>
+      </c>
+      <c r="E53" s="5">
+        <f>IF($V53=0,"",INDEX(spisak_pol,$V53)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F53" s="5">
+        <f>IF($V53=0,"",INDEX(spisak_pojas,$V53)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G53" s="7">
         <f>IF($D53="","",LOOKUP($D53,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2759,7 +3791,7 @@
       <c r="P53" s="5"/>
       <c r="Q53" s="5"/>
       <c r="R53" s="8">
-        <f>IF(COUNTA($A53:$F53,I53:P53,Q53)=0,"",IF(AND($A53&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A53,4))="FSS-",MID($A53,LEN($A53)-2,1)="/",ISNUMBER(VALUE(RIGHT($A53,2))),VALUE(MID($A53,5,LEN($A53)-7))&gt;=1,VALUE(MID($A53,5,LEN($A53)-7))=INT(VALUE(MID($A53,5,LEN($A53)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B53="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B53&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C53="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C53&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D53="","Nedostaje godište",IF($G53="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E53="","Nedostaje pol",IF($F53="","Nedostaje pojas",IF(COUNTA(I53:P53)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I53:P53&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G53),I53:P53)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G53,IF(AND(COUNTIF(I53:P53,"Fudokan sport kumite")&gt;0,Q53=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I53:P53,"Fudokan sport kumite")=0,Q53&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A53:$F53))+SUMPRODUCT(LEN(I53:P53))+LEN(Q53)=0,"",IF(AND($A53&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A53,4))="FSS-",MID($A53,LEN($A53)-2,1)="/",ISNUMBER(VALUE(RIGHT($A53,2))),VALUE(MID($A53,5,LEN($A53)-7))&gt;=1,VALUE(MID($A53,5,LEN($A53)-7))=INT(VALUE(MID($A53,5,LEN($A53)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A53&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A53&lt;&gt;"",$U53=0,$B53=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U53&gt;0,$V53=0,$B53=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U53)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B53="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B53&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C53="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C53&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D53="","Nedostaje godište",IF($G53="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E53="","Nedostaje pol",IF($F53="","Nedostaje pojas",IF(COUNTA(I53:P53)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I53:P53&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G53),I53:P53)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G53,IF(AND(COUNTIF(I53:P53,"Fudokan sport kumite")&gt;0,Q53=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I53:P53,"Fudokan sport kumite")=0,Q53&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S53">
@@ -2770,14 +3802,37 @@
         <f>IF(OR($G53="",$E53=""),"sve_kilaze","kg_"&amp;$G53&amp;"_"&amp;IF($E53="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="54" spans="1:20">
+      <c r="U53">
+        <f>IF($A53="",0,IFERROR(MATCH(TRIM($A53),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <f>IF($U53=0,0,IF(TRIM(INDEX(spisak_klub,$U53))=TRIM($B$4),$U53,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22">
       <c r="A54" s="5"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
+      <c r="B54" s="5">
+        <f>IF($V54=0,"",INDEX(spisak_ime,$V54)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C54" s="5">
+        <f>IF($V54=0,"",INDEX(spisak_prezime,$V54)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D54" s="5">
+        <f>IF($V54=0,"",INDEX(spisak_godiste,$V54))</f>
+        <v/>
+      </c>
+      <c r="E54" s="5">
+        <f>IF($V54=0,"",INDEX(spisak_pol,$V54)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F54" s="5">
+        <f>IF($V54=0,"",INDEX(spisak_pojas,$V54)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G54" s="7">
         <f>IF($D54="","",LOOKUP($D54,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2796,7 +3851,7 @@
       <c r="P54" s="5"/>
       <c r="Q54" s="5"/>
       <c r="R54" s="8">
-        <f>IF(COUNTA($A54:$F54,I54:P54,Q54)=0,"",IF(AND($A54&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A54,4))="FSS-",MID($A54,LEN($A54)-2,1)="/",ISNUMBER(VALUE(RIGHT($A54,2))),VALUE(MID($A54,5,LEN($A54)-7))&gt;=1,VALUE(MID($A54,5,LEN($A54)-7))=INT(VALUE(MID($A54,5,LEN($A54)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B54="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B54&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C54="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C54&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D54="","Nedostaje godište",IF($G54="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E54="","Nedostaje pol",IF($F54="","Nedostaje pojas",IF(COUNTA(I54:P54)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I54:P54&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G54),I54:P54)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G54,IF(AND(COUNTIF(I54:P54,"Fudokan sport kumite")&gt;0,Q54=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I54:P54,"Fudokan sport kumite")=0,Q54&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A54:$F54))+SUMPRODUCT(LEN(I54:P54))+LEN(Q54)=0,"",IF(AND($A54&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A54,4))="FSS-",MID($A54,LEN($A54)-2,1)="/",ISNUMBER(VALUE(RIGHT($A54,2))),VALUE(MID($A54,5,LEN($A54)-7))&gt;=1,VALUE(MID($A54,5,LEN($A54)-7))=INT(VALUE(MID($A54,5,LEN($A54)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A54&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A54&lt;&gt;"",$U54=0,$B54=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U54&gt;0,$V54=0,$B54=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U54)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B54="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B54&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C54="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C54&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D54="","Nedostaje godište",IF($G54="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E54="","Nedostaje pol",IF($F54="","Nedostaje pojas",IF(COUNTA(I54:P54)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I54:P54&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G54),I54:P54)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G54,IF(AND(COUNTIF(I54:P54,"Fudokan sport kumite")&gt;0,Q54=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I54:P54,"Fudokan sport kumite")=0,Q54&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S54">
@@ -2807,14 +3862,37 @@
         <f>IF(OR($G54="",$E54=""),"sve_kilaze","kg_"&amp;$G54&amp;"_"&amp;IF($E54="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="55" spans="1:20">
+      <c r="U54">
+        <f>IF($A54="",0,IFERROR(MATCH(TRIM($A54),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <f>IF($U54=0,0,IF(TRIM(INDEX(spisak_klub,$U54))=TRIM($B$4),$U54,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22">
       <c r="A55" s="5"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
+      <c r="B55" s="5">
+        <f>IF($V55=0,"",INDEX(spisak_ime,$V55)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C55" s="5">
+        <f>IF($V55=0,"",INDEX(spisak_prezime,$V55)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D55" s="5">
+        <f>IF($V55=0,"",INDEX(spisak_godiste,$V55))</f>
+        <v/>
+      </c>
+      <c r="E55" s="5">
+        <f>IF($V55=0,"",INDEX(spisak_pol,$V55)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F55" s="5">
+        <f>IF($V55=0,"",INDEX(spisak_pojas,$V55)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G55" s="7">
         <f>IF($D55="","",LOOKUP($D55,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2833,7 +3911,7 @@
       <c r="P55" s="5"/>
       <c r="Q55" s="5"/>
       <c r="R55" s="8">
-        <f>IF(COUNTA($A55:$F55,I55:P55,Q55)=0,"",IF(AND($A55&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A55,4))="FSS-",MID($A55,LEN($A55)-2,1)="/",ISNUMBER(VALUE(RIGHT($A55,2))),VALUE(MID($A55,5,LEN($A55)-7))&gt;=1,VALUE(MID($A55,5,LEN($A55)-7))=INT(VALUE(MID($A55,5,LEN($A55)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B55="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B55&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C55="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C55&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D55="","Nedostaje godište",IF($G55="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E55="","Nedostaje pol",IF($F55="","Nedostaje pojas",IF(COUNTA(I55:P55)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I55:P55&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G55),I55:P55)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G55,IF(AND(COUNTIF(I55:P55,"Fudokan sport kumite")&gt;0,Q55=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I55:P55,"Fudokan sport kumite")=0,Q55&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A55:$F55))+SUMPRODUCT(LEN(I55:P55))+LEN(Q55)=0,"",IF(AND($A55&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A55,4))="FSS-",MID($A55,LEN($A55)-2,1)="/",ISNUMBER(VALUE(RIGHT($A55,2))),VALUE(MID($A55,5,LEN($A55)-7))&gt;=1,VALUE(MID($A55,5,LEN($A55)-7))=INT(VALUE(MID($A55,5,LEN($A55)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A55&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A55&lt;&gt;"",$U55=0,$B55=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U55&gt;0,$V55=0,$B55=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U55)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B55="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B55&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C55="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C55&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D55="","Nedostaje godište",IF($G55="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E55="","Nedostaje pol",IF($F55="","Nedostaje pojas",IF(COUNTA(I55:P55)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I55:P55&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G55),I55:P55)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G55,IF(AND(COUNTIF(I55:P55,"Fudokan sport kumite")&gt;0,Q55=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I55:P55,"Fudokan sport kumite")=0,Q55&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S55">
@@ -2844,14 +3922,37 @@
         <f>IF(OR($G55="",$E55=""),"sve_kilaze","kg_"&amp;$G55&amp;"_"&amp;IF($E55="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="56" spans="1:20">
+      <c r="U55">
+        <f>IF($A55="",0,IFERROR(MATCH(TRIM($A55),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <f>IF($U55=0,0,IF(TRIM(INDEX(spisak_klub,$U55))=TRIM($B$4),$U55,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22">
       <c r="A56" s="5"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
+      <c r="B56" s="5">
+        <f>IF($V56=0,"",INDEX(spisak_ime,$V56)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C56" s="5">
+        <f>IF($V56=0,"",INDEX(spisak_prezime,$V56)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D56" s="5">
+        <f>IF($V56=0,"",INDEX(spisak_godiste,$V56))</f>
+        <v/>
+      </c>
+      <c r="E56" s="5">
+        <f>IF($V56=0,"",INDEX(spisak_pol,$V56)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F56" s="5">
+        <f>IF($V56=0,"",INDEX(spisak_pojas,$V56)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G56" s="7">
         <f>IF($D56="","",LOOKUP($D56,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2870,7 +3971,7 @@
       <c r="P56" s="5"/>
       <c r="Q56" s="5"/>
       <c r="R56" s="8">
-        <f>IF(COUNTA($A56:$F56,I56:P56,Q56)=0,"",IF(AND($A56&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A56,4))="FSS-",MID($A56,LEN($A56)-2,1)="/",ISNUMBER(VALUE(RIGHT($A56,2))),VALUE(MID($A56,5,LEN($A56)-7))&gt;=1,VALUE(MID($A56,5,LEN($A56)-7))=INT(VALUE(MID($A56,5,LEN($A56)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B56="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B56&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C56="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C56&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D56="","Nedostaje godište",IF($G56="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E56="","Nedostaje pol",IF($F56="","Nedostaje pojas",IF(COUNTA(I56:P56)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I56:P56&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G56),I56:P56)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G56,IF(AND(COUNTIF(I56:P56,"Fudokan sport kumite")&gt;0,Q56=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I56:P56,"Fudokan sport kumite")=0,Q56&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A56:$F56))+SUMPRODUCT(LEN(I56:P56))+LEN(Q56)=0,"",IF(AND($A56&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A56,4))="FSS-",MID($A56,LEN($A56)-2,1)="/",ISNUMBER(VALUE(RIGHT($A56,2))),VALUE(MID($A56,5,LEN($A56)-7))&gt;=1,VALUE(MID($A56,5,LEN($A56)-7))=INT(VALUE(MID($A56,5,LEN($A56)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A56&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A56&lt;&gt;"",$U56=0,$B56=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U56&gt;0,$V56=0,$B56=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U56)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B56="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B56&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C56="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C56&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D56="","Nedostaje godište",IF($G56="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E56="","Nedostaje pol",IF($F56="","Nedostaje pojas",IF(COUNTA(I56:P56)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I56:P56&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G56),I56:P56)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G56,IF(AND(COUNTIF(I56:P56,"Fudokan sport kumite")&gt;0,Q56=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I56:P56,"Fudokan sport kumite")=0,Q56&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S56">
@@ -2881,14 +3982,37 @@
         <f>IF(OR($G56="",$E56=""),"sve_kilaze","kg_"&amp;$G56&amp;"_"&amp;IF($E56="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="57" spans="1:20">
+      <c r="U56">
+        <f>IF($A56="",0,IFERROR(MATCH(TRIM($A56),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V56">
+        <f>IF($U56=0,0,IF(TRIM(INDEX(spisak_klub,$U56))=TRIM($B$4),$U56,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22">
       <c r="A57" s="5"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="5"/>
-      <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
+      <c r="B57" s="5">
+        <f>IF($V57=0,"",INDEX(spisak_ime,$V57)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C57" s="5">
+        <f>IF($V57=0,"",INDEX(spisak_prezime,$V57)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D57" s="5">
+        <f>IF($V57=0,"",INDEX(spisak_godiste,$V57))</f>
+        <v/>
+      </c>
+      <c r="E57" s="5">
+        <f>IF($V57=0,"",INDEX(spisak_pol,$V57)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F57" s="5">
+        <f>IF($V57=0,"",INDEX(spisak_pojas,$V57)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G57" s="7">
         <f>IF($D57="","",LOOKUP($D57,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2907,7 +4031,7 @@
       <c r="P57" s="5"/>
       <c r="Q57" s="5"/>
       <c r="R57" s="8">
-        <f>IF(COUNTA($A57:$F57,I57:P57,Q57)=0,"",IF(AND($A57&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A57,4))="FSS-",MID($A57,LEN($A57)-2,1)="/",ISNUMBER(VALUE(RIGHT($A57,2))),VALUE(MID($A57,5,LEN($A57)-7))&gt;=1,VALUE(MID($A57,5,LEN($A57)-7))=INT(VALUE(MID($A57,5,LEN($A57)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B57="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B57&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C57="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C57&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D57="","Nedostaje godište",IF($G57="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E57="","Nedostaje pol",IF($F57="","Nedostaje pojas",IF(COUNTA(I57:P57)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I57:P57&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G57),I57:P57)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G57,IF(AND(COUNTIF(I57:P57,"Fudokan sport kumite")&gt;0,Q57=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I57:P57,"Fudokan sport kumite")=0,Q57&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A57:$F57))+SUMPRODUCT(LEN(I57:P57))+LEN(Q57)=0,"",IF(AND($A57&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A57,4))="FSS-",MID($A57,LEN($A57)-2,1)="/",ISNUMBER(VALUE(RIGHT($A57,2))),VALUE(MID($A57,5,LEN($A57)-7))&gt;=1,VALUE(MID($A57,5,LEN($A57)-7))=INT(VALUE(MID($A57,5,LEN($A57)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A57&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A57&lt;&gt;"",$U57=0,$B57=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U57&gt;0,$V57=0,$B57=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U57)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B57="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B57&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C57="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C57&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D57="","Nedostaje godište",IF($G57="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E57="","Nedostaje pol",IF($F57="","Nedostaje pojas",IF(COUNTA(I57:P57)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I57:P57&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G57),I57:P57)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G57,IF(AND(COUNTIF(I57:P57,"Fudokan sport kumite")&gt;0,Q57=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I57:P57,"Fudokan sport kumite")=0,Q57&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S57">
@@ -2918,14 +4042,37 @@
         <f>IF(OR($G57="",$E57=""),"sve_kilaze","kg_"&amp;$G57&amp;"_"&amp;IF($E57="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="58" spans="1:20">
+      <c r="U57">
+        <f>IF($A57="",0,IFERROR(MATCH(TRIM($A57),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V57">
+        <f>IF($U57=0,0,IF(TRIM(INDEX(spisak_klub,$U57))=TRIM($B$4),$U57,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22">
       <c r="A58" s="5"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
+      <c r="B58" s="5">
+        <f>IF($V58=0,"",INDEX(spisak_ime,$V58)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C58" s="5">
+        <f>IF($V58=0,"",INDEX(spisak_prezime,$V58)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D58" s="5">
+        <f>IF($V58=0,"",INDEX(spisak_godiste,$V58))</f>
+        <v/>
+      </c>
+      <c r="E58" s="5">
+        <f>IF($V58=0,"",INDEX(spisak_pol,$V58)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F58" s="5">
+        <f>IF($V58=0,"",INDEX(spisak_pojas,$V58)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G58" s="7">
         <f>IF($D58="","",LOOKUP($D58,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2944,7 +4091,7 @@
       <c r="P58" s="5"/>
       <c r="Q58" s="5"/>
       <c r="R58" s="8">
-        <f>IF(COUNTA($A58:$F58,I58:P58,Q58)=0,"",IF(AND($A58&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A58,4))="FSS-",MID($A58,LEN($A58)-2,1)="/",ISNUMBER(VALUE(RIGHT($A58,2))),VALUE(MID($A58,5,LEN($A58)-7))&gt;=1,VALUE(MID($A58,5,LEN($A58)-7))=INT(VALUE(MID($A58,5,LEN($A58)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B58="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B58&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C58="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C58&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D58="","Nedostaje godište",IF($G58="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E58="","Nedostaje pol",IF($F58="","Nedostaje pojas",IF(COUNTA(I58:P58)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I58:P58&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G58),I58:P58)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G58,IF(AND(COUNTIF(I58:P58,"Fudokan sport kumite")&gt;0,Q58=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I58:P58,"Fudokan sport kumite")=0,Q58&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A58:$F58))+SUMPRODUCT(LEN(I58:P58))+LEN(Q58)=0,"",IF(AND($A58&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A58,4))="FSS-",MID($A58,LEN($A58)-2,1)="/",ISNUMBER(VALUE(RIGHT($A58,2))),VALUE(MID($A58,5,LEN($A58)-7))&gt;=1,VALUE(MID($A58,5,LEN($A58)-7))=INT(VALUE(MID($A58,5,LEN($A58)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A58&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A58&lt;&gt;"",$U58=0,$B58=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U58&gt;0,$V58=0,$B58=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U58)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B58="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B58&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C58="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C58&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D58="","Nedostaje godište",IF($G58="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E58="","Nedostaje pol",IF($F58="","Nedostaje pojas",IF(COUNTA(I58:P58)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I58:P58&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G58),I58:P58)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G58,IF(AND(COUNTIF(I58:P58,"Fudokan sport kumite")&gt;0,Q58=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I58:P58,"Fudokan sport kumite")=0,Q58&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S58">
@@ -2955,14 +4102,37 @@
         <f>IF(OR($G58="",$E58=""),"sve_kilaze","kg_"&amp;$G58&amp;"_"&amp;IF($E58="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="59" spans="1:20">
+      <c r="U58">
+        <f>IF($A58="",0,IFERROR(MATCH(TRIM($A58),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <f>IF($U58=0,0,IF(TRIM(INDEX(spisak_klub,$U58))=TRIM($B$4),$U58,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22">
       <c r="A59" s="5"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5"/>
-      <c r="E59" s="5"/>
-      <c r="F59" s="5"/>
+      <c r="B59" s="5">
+        <f>IF($V59=0,"",INDEX(spisak_ime,$V59)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C59" s="5">
+        <f>IF($V59=0,"",INDEX(spisak_prezime,$V59)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D59" s="5">
+        <f>IF($V59=0,"",INDEX(spisak_godiste,$V59))</f>
+        <v/>
+      </c>
+      <c r="E59" s="5">
+        <f>IF($V59=0,"",INDEX(spisak_pol,$V59)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F59" s="5">
+        <f>IF($V59=0,"",INDEX(spisak_pojas,$V59)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G59" s="7">
         <f>IF($D59="","",LOOKUP($D59,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -2981,7 +4151,7 @@
       <c r="P59" s="5"/>
       <c r="Q59" s="5"/>
       <c r="R59" s="8">
-        <f>IF(COUNTA($A59:$F59,I59:P59,Q59)=0,"",IF(AND($A59&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A59,4))="FSS-",MID($A59,LEN($A59)-2,1)="/",ISNUMBER(VALUE(RIGHT($A59,2))),VALUE(MID($A59,5,LEN($A59)-7))&gt;=1,VALUE(MID($A59,5,LEN($A59)-7))=INT(VALUE(MID($A59,5,LEN($A59)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B59="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B59&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C59="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C59&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D59="","Nedostaje godište",IF($G59="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E59="","Nedostaje pol",IF($F59="","Nedostaje pojas",IF(COUNTA(I59:P59)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I59:P59&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G59),I59:P59)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G59,IF(AND(COUNTIF(I59:P59,"Fudokan sport kumite")&gt;0,Q59=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I59:P59,"Fudokan sport kumite")=0,Q59&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A59:$F59))+SUMPRODUCT(LEN(I59:P59))+LEN(Q59)=0,"",IF(AND($A59&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A59,4))="FSS-",MID($A59,LEN($A59)-2,1)="/",ISNUMBER(VALUE(RIGHT($A59,2))),VALUE(MID($A59,5,LEN($A59)-7))&gt;=1,VALUE(MID($A59,5,LEN($A59)-7))=INT(VALUE(MID($A59,5,LEN($A59)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A59&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A59&lt;&gt;"",$U59=0,$B59=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U59&gt;0,$V59=0,$B59=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U59)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B59="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B59&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C59="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C59&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D59="","Nedostaje godište",IF($G59="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E59="","Nedostaje pol",IF($F59="","Nedostaje pojas",IF(COUNTA(I59:P59)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I59:P59&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G59),I59:P59)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G59,IF(AND(COUNTIF(I59:P59,"Fudokan sport kumite")&gt;0,Q59=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I59:P59,"Fudokan sport kumite")=0,Q59&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S59">
@@ -2992,14 +4162,37 @@
         <f>IF(OR($G59="",$E59=""),"sve_kilaze","kg_"&amp;$G59&amp;"_"&amp;IF($E59="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="60" spans="1:20">
+      <c r="U59">
+        <f>IF($A59="",0,IFERROR(MATCH(TRIM($A59),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <f>IF($U59=0,0,IF(TRIM(INDEX(spisak_klub,$U59))=TRIM($B$4),$U59,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22">
       <c r="A60" s="5"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
+      <c r="B60" s="5">
+        <f>IF($V60=0,"",INDEX(spisak_ime,$V60)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C60" s="5">
+        <f>IF($V60=0,"",INDEX(spisak_prezime,$V60)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D60" s="5">
+        <f>IF($V60=0,"",INDEX(spisak_godiste,$V60))</f>
+        <v/>
+      </c>
+      <c r="E60" s="5">
+        <f>IF($V60=0,"",INDEX(spisak_pol,$V60)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F60" s="5">
+        <f>IF($V60=0,"",INDEX(spisak_pojas,$V60)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G60" s="7">
         <f>IF($D60="","",LOOKUP($D60,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3018,7 +4211,7 @@
       <c r="P60" s="5"/>
       <c r="Q60" s="5"/>
       <c r="R60" s="8">
-        <f>IF(COUNTA($A60:$F60,I60:P60,Q60)=0,"",IF(AND($A60&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A60,4))="FSS-",MID($A60,LEN($A60)-2,1)="/",ISNUMBER(VALUE(RIGHT($A60,2))),VALUE(MID($A60,5,LEN($A60)-7))&gt;=1,VALUE(MID($A60,5,LEN($A60)-7))=INT(VALUE(MID($A60,5,LEN($A60)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B60="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B60&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C60="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C60&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D60="","Nedostaje godište",IF($G60="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E60="","Nedostaje pol",IF($F60="","Nedostaje pojas",IF(COUNTA(I60:P60)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I60:P60&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G60),I60:P60)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G60,IF(AND(COUNTIF(I60:P60,"Fudokan sport kumite")&gt;0,Q60=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I60:P60,"Fudokan sport kumite")=0,Q60&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A60:$F60))+SUMPRODUCT(LEN(I60:P60))+LEN(Q60)=0,"",IF(AND($A60&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A60,4))="FSS-",MID($A60,LEN($A60)-2,1)="/",ISNUMBER(VALUE(RIGHT($A60,2))),VALUE(MID($A60,5,LEN($A60)-7))&gt;=1,VALUE(MID($A60,5,LEN($A60)-7))=INT(VALUE(MID($A60,5,LEN($A60)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A60&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A60&lt;&gt;"",$U60=0,$B60=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U60&gt;0,$V60=0,$B60=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U60)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B60="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B60&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C60="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C60&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D60="","Nedostaje godište",IF($G60="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E60="","Nedostaje pol",IF($F60="","Nedostaje pojas",IF(COUNTA(I60:P60)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I60:P60&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G60),I60:P60)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G60,IF(AND(COUNTIF(I60:P60,"Fudokan sport kumite")&gt;0,Q60=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I60:P60,"Fudokan sport kumite")=0,Q60&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S60">
@@ -3029,14 +4222,37 @@
         <f>IF(OR($G60="",$E60=""),"sve_kilaze","kg_"&amp;$G60&amp;"_"&amp;IF($E60="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="61" spans="1:20">
+      <c r="U60">
+        <f>IF($A60="",0,IFERROR(MATCH(TRIM($A60),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V60">
+        <f>IF($U60=0,0,IF(TRIM(INDEX(spisak_klub,$U60))=TRIM($B$4),$U60,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22">
       <c r="A61" s="5"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
+      <c r="B61" s="5">
+        <f>IF($V61=0,"",INDEX(spisak_ime,$V61)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C61" s="5">
+        <f>IF($V61=0,"",INDEX(spisak_prezime,$V61)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D61" s="5">
+        <f>IF($V61=0,"",INDEX(spisak_godiste,$V61))</f>
+        <v/>
+      </c>
+      <c r="E61" s="5">
+        <f>IF($V61=0,"",INDEX(spisak_pol,$V61)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F61" s="5">
+        <f>IF($V61=0,"",INDEX(spisak_pojas,$V61)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G61" s="7">
         <f>IF($D61="","",LOOKUP($D61,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3055,7 +4271,7 @@
       <c r="P61" s="5"/>
       <c r="Q61" s="5"/>
       <c r="R61" s="8">
-        <f>IF(COUNTA($A61:$F61,I61:P61,Q61)=0,"",IF(AND($A61&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A61,4))="FSS-",MID($A61,LEN($A61)-2,1)="/",ISNUMBER(VALUE(RIGHT($A61,2))),VALUE(MID($A61,5,LEN($A61)-7))&gt;=1,VALUE(MID($A61,5,LEN($A61)-7))=INT(VALUE(MID($A61,5,LEN($A61)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B61="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B61&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C61="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C61&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D61="","Nedostaje godište",IF($G61="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E61="","Nedostaje pol",IF($F61="","Nedostaje pojas",IF(COUNTA(I61:P61)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I61:P61&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G61),I61:P61)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G61,IF(AND(COUNTIF(I61:P61,"Fudokan sport kumite")&gt;0,Q61=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I61:P61,"Fudokan sport kumite")=0,Q61&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A61:$F61))+SUMPRODUCT(LEN(I61:P61))+LEN(Q61)=0,"",IF(AND($A61&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A61,4))="FSS-",MID($A61,LEN($A61)-2,1)="/",ISNUMBER(VALUE(RIGHT($A61,2))),VALUE(MID($A61,5,LEN($A61)-7))&gt;=1,VALUE(MID($A61,5,LEN($A61)-7))=INT(VALUE(MID($A61,5,LEN($A61)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A61&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A61&lt;&gt;"",$U61=0,$B61=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U61&gt;0,$V61=0,$B61=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U61)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B61="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B61&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C61="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C61&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D61="","Nedostaje godište",IF($G61="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E61="","Nedostaje pol",IF($F61="","Nedostaje pojas",IF(COUNTA(I61:P61)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I61:P61&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G61),I61:P61)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G61,IF(AND(COUNTIF(I61:P61,"Fudokan sport kumite")&gt;0,Q61=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I61:P61,"Fudokan sport kumite")=0,Q61&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S61">
@@ -3066,14 +4282,37 @@
         <f>IF(OR($G61="",$E61=""),"sve_kilaze","kg_"&amp;$G61&amp;"_"&amp;IF($E61="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="62" spans="1:20">
+      <c r="U61">
+        <f>IF($A61="",0,IFERROR(MATCH(TRIM($A61),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V61">
+        <f>IF($U61=0,0,IF(TRIM(INDEX(spisak_klub,$U61))=TRIM($B$4),$U61,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22">
       <c r="A62" s="5"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
+      <c r="B62" s="5">
+        <f>IF($V62=0,"",INDEX(spisak_ime,$V62)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C62" s="5">
+        <f>IF($V62=0,"",INDEX(spisak_prezime,$V62)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D62" s="5">
+        <f>IF($V62=0,"",INDEX(spisak_godiste,$V62))</f>
+        <v/>
+      </c>
+      <c r="E62" s="5">
+        <f>IF($V62=0,"",INDEX(spisak_pol,$V62)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F62" s="5">
+        <f>IF($V62=0,"",INDEX(spisak_pojas,$V62)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G62" s="7">
         <f>IF($D62="","",LOOKUP($D62,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3092,7 +4331,7 @@
       <c r="P62" s="5"/>
       <c r="Q62" s="5"/>
       <c r="R62" s="8">
-        <f>IF(COUNTA($A62:$F62,I62:P62,Q62)=0,"",IF(AND($A62&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A62,4))="FSS-",MID($A62,LEN($A62)-2,1)="/",ISNUMBER(VALUE(RIGHT($A62,2))),VALUE(MID($A62,5,LEN($A62)-7))&gt;=1,VALUE(MID($A62,5,LEN($A62)-7))=INT(VALUE(MID($A62,5,LEN($A62)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B62="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B62&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C62="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C62&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D62="","Nedostaje godište",IF($G62="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E62="","Nedostaje pol",IF($F62="","Nedostaje pojas",IF(COUNTA(I62:P62)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I62:P62&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G62),I62:P62)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G62,IF(AND(COUNTIF(I62:P62,"Fudokan sport kumite")&gt;0,Q62=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I62:P62,"Fudokan sport kumite")=0,Q62&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A62:$F62))+SUMPRODUCT(LEN(I62:P62))+LEN(Q62)=0,"",IF(AND($A62&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A62,4))="FSS-",MID($A62,LEN($A62)-2,1)="/",ISNUMBER(VALUE(RIGHT($A62,2))),VALUE(MID($A62,5,LEN($A62)-7))&gt;=1,VALUE(MID($A62,5,LEN($A62)-7))=INT(VALUE(MID($A62,5,LEN($A62)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A62&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A62&lt;&gt;"",$U62=0,$B62=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U62&gt;0,$V62=0,$B62=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U62)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B62="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B62&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C62="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C62&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D62="","Nedostaje godište",IF($G62="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E62="","Nedostaje pol",IF($F62="","Nedostaje pojas",IF(COUNTA(I62:P62)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I62:P62&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G62),I62:P62)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G62,IF(AND(COUNTIF(I62:P62,"Fudokan sport kumite")&gt;0,Q62=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I62:P62,"Fudokan sport kumite")=0,Q62&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S62">
@@ -3103,14 +4342,37 @@
         <f>IF(OR($G62="",$E62=""),"sve_kilaze","kg_"&amp;$G62&amp;"_"&amp;IF($E62="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="63" spans="1:20">
+      <c r="U62">
+        <f>IF($A62="",0,IFERROR(MATCH(TRIM($A62),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V62">
+        <f>IF($U62=0,0,IF(TRIM(INDEX(spisak_klub,$U62))=TRIM($B$4),$U62,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22">
       <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="5"/>
-      <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
+      <c r="B63" s="5">
+        <f>IF($V63=0,"",INDEX(spisak_ime,$V63)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C63" s="5">
+        <f>IF($V63=0,"",INDEX(spisak_prezime,$V63)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D63" s="5">
+        <f>IF($V63=0,"",INDEX(spisak_godiste,$V63))</f>
+        <v/>
+      </c>
+      <c r="E63" s="5">
+        <f>IF($V63=0,"",INDEX(spisak_pol,$V63)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F63" s="5">
+        <f>IF($V63=0,"",INDEX(spisak_pojas,$V63)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G63" s="7">
         <f>IF($D63="","",LOOKUP($D63,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3129,7 +4391,7 @@
       <c r="P63" s="5"/>
       <c r="Q63" s="5"/>
       <c r="R63" s="8">
-        <f>IF(COUNTA($A63:$F63,I63:P63,Q63)=0,"",IF(AND($A63&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A63,4))="FSS-",MID($A63,LEN($A63)-2,1)="/",ISNUMBER(VALUE(RIGHT($A63,2))),VALUE(MID($A63,5,LEN($A63)-7))&gt;=1,VALUE(MID($A63,5,LEN($A63)-7))=INT(VALUE(MID($A63,5,LEN($A63)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B63="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B63&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C63="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C63&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D63="","Nedostaje godište",IF($G63="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E63="","Nedostaje pol",IF($F63="","Nedostaje pojas",IF(COUNTA(I63:P63)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I63:P63&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G63),I63:P63)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G63,IF(AND(COUNTIF(I63:P63,"Fudokan sport kumite")&gt;0,Q63=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I63:P63,"Fudokan sport kumite")=0,Q63&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A63:$F63))+SUMPRODUCT(LEN(I63:P63))+LEN(Q63)=0,"",IF(AND($A63&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A63,4))="FSS-",MID($A63,LEN($A63)-2,1)="/",ISNUMBER(VALUE(RIGHT($A63,2))),VALUE(MID($A63,5,LEN($A63)-7))&gt;=1,VALUE(MID($A63,5,LEN($A63)-7))=INT(VALUE(MID($A63,5,LEN($A63)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A63&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A63&lt;&gt;"",$U63=0,$B63=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U63&gt;0,$V63=0,$B63=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U63)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B63="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B63&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C63="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C63&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D63="","Nedostaje godište",IF($G63="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E63="","Nedostaje pol",IF($F63="","Nedostaje pojas",IF(COUNTA(I63:P63)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I63:P63&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G63),I63:P63)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G63,IF(AND(COUNTIF(I63:P63,"Fudokan sport kumite")&gt;0,Q63=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I63:P63,"Fudokan sport kumite")=0,Q63&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S63">
@@ -3140,14 +4402,37 @@
         <f>IF(OR($G63="",$E63=""),"sve_kilaze","kg_"&amp;$G63&amp;"_"&amp;IF($E63="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="64" spans="1:20">
+      <c r="U63">
+        <f>IF($A63="",0,IFERROR(MATCH(TRIM($A63),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V63">
+        <f>IF($U63=0,0,IF(TRIM(INDEX(spisak_klub,$U63))=TRIM($B$4),$U63,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22">
       <c r="A64" s="5"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
+      <c r="B64" s="5">
+        <f>IF($V64=0,"",INDEX(spisak_ime,$V64)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C64" s="5">
+        <f>IF($V64=0,"",INDEX(spisak_prezime,$V64)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D64" s="5">
+        <f>IF($V64=0,"",INDEX(spisak_godiste,$V64))</f>
+        <v/>
+      </c>
+      <c r="E64" s="5">
+        <f>IF($V64=0,"",INDEX(spisak_pol,$V64)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F64" s="5">
+        <f>IF($V64=0,"",INDEX(spisak_pojas,$V64)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G64" s="7">
         <f>IF($D64="","",LOOKUP($D64,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3166,7 +4451,7 @@
       <c r="P64" s="5"/>
       <c r="Q64" s="5"/>
       <c r="R64" s="8">
-        <f>IF(COUNTA($A64:$F64,I64:P64,Q64)=0,"",IF(AND($A64&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A64,4))="FSS-",MID($A64,LEN($A64)-2,1)="/",ISNUMBER(VALUE(RIGHT($A64,2))),VALUE(MID($A64,5,LEN($A64)-7))&gt;=1,VALUE(MID($A64,5,LEN($A64)-7))=INT(VALUE(MID($A64,5,LEN($A64)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B64="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B64&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C64="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C64&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D64="","Nedostaje godište",IF($G64="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E64="","Nedostaje pol",IF($F64="","Nedostaje pojas",IF(COUNTA(I64:P64)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I64:P64&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G64),I64:P64)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G64,IF(AND(COUNTIF(I64:P64,"Fudokan sport kumite")&gt;0,Q64=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I64:P64,"Fudokan sport kumite")=0,Q64&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A64:$F64))+SUMPRODUCT(LEN(I64:P64))+LEN(Q64)=0,"",IF(AND($A64&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A64,4))="FSS-",MID($A64,LEN($A64)-2,1)="/",ISNUMBER(VALUE(RIGHT($A64,2))),VALUE(MID($A64,5,LEN($A64)-7))&gt;=1,VALUE(MID($A64,5,LEN($A64)-7))=INT(VALUE(MID($A64,5,LEN($A64)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A64&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A64&lt;&gt;"",$U64=0,$B64=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U64&gt;0,$V64=0,$B64=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U64)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B64="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B64&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C64="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C64&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D64="","Nedostaje godište",IF($G64="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E64="","Nedostaje pol",IF($F64="","Nedostaje pojas",IF(COUNTA(I64:P64)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I64:P64&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G64),I64:P64)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G64,IF(AND(COUNTIF(I64:P64,"Fudokan sport kumite")&gt;0,Q64=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I64:P64,"Fudokan sport kumite")=0,Q64&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S64">
@@ -3177,14 +4462,37 @@
         <f>IF(OR($G64="",$E64=""),"sve_kilaze","kg_"&amp;$G64&amp;"_"&amp;IF($E64="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="65" spans="1:20">
+      <c r="U64">
+        <f>IF($A64="",0,IFERROR(MATCH(TRIM($A64),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <f>IF($U64=0,0,IF(TRIM(INDEX(spisak_klub,$U64))=TRIM($B$4),$U64,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22">
       <c r="A65" s="5"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
+      <c r="B65" s="5">
+        <f>IF($V65=0,"",INDEX(spisak_ime,$V65)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C65" s="5">
+        <f>IF($V65=0,"",INDEX(spisak_prezime,$V65)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D65" s="5">
+        <f>IF($V65=0,"",INDEX(spisak_godiste,$V65))</f>
+        <v/>
+      </c>
+      <c r="E65" s="5">
+        <f>IF($V65=0,"",INDEX(spisak_pol,$V65)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F65" s="5">
+        <f>IF($V65=0,"",INDEX(spisak_pojas,$V65)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G65" s="7">
         <f>IF($D65="","",LOOKUP($D65,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3203,7 +4511,7 @@
       <c r="P65" s="5"/>
       <c r="Q65" s="5"/>
       <c r="R65" s="8">
-        <f>IF(COUNTA($A65:$F65,I65:P65,Q65)=0,"",IF(AND($A65&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A65,4))="FSS-",MID($A65,LEN($A65)-2,1)="/",ISNUMBER(VALUE(RIGHT($A65,2))),VALUE(MID($A65,5,LEN($A65)-7))&gt;=1,VALUE(MID($A65,5,LEN($A65)-7))=INT(VALUE(MID($A65,5,LEN($A65)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B65="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B65&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C65="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C65&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D65="","Nedostaje godište",IF($G65="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E65="","Nedostaje pol",IF($F65="","Nedostaje pojas",IF(COUNTA(I65:P65)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I65:P65&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G65),I65:P65)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G65,IF(AND(COUNTIF(I65:P65,"Fudokan sport kumite")&gt;0,Q65=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I65:P65,"Fudokan sport kumite")=0,Q65&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A65:$F65))+SUMPRODUCT(LEN(I65:P65))+LEN(Q65)=0,"",IF(AND($A65&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A65,4))="FSS-",MID($A65,LEN($A65)-2,1)="/",ISNUMBER(VALUE(RIGHT($A65,2))),VALUE(MID($A65,5,LEN($A65)-7))&gt;=1,VALUE(MID($A65,5,LEN($A65)-7))=INT(VALUE(MID($A65,5,LEN($A65)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A65&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A65&lt;&gt;"",$U65=0,$B65=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U65&gt;0,$V65=0,$B65=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U65)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B65="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B65&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C65="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C65&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D65="","Nedostaje godište",IF($G65="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E65="","Nedostaje pol",IF($F65="","Nedostaje pojas",IF(COUNTA(I65:P65)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I65:P65&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G65),I65:P65)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G65,IF(AND(COUNTIF(I65:P65,"Fudokan sport kumite")&gt;0,Q65=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I65:P65,"Fudokan sport kumite")=0,Q65&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S65">
@@ -3214,14 +4522,37 @@
         <f>IF(OR($G65="",$E65=""),"sve_kilaze","kg_"&amp;$G65&amp;"_"&amp;IF($E65="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="66" spans="1:20">
+      <c r="U65">
+        <f>IF($A65="",0,IFERROR(MATCH(TRIM($A65),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <f>IF($U65=0,0,IF(TRIM(INDEX(spisak_klub,$U65))=TRIM($B$4),$U65,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22">
       <c r="A66" s="5"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
+      <c r="B66" s="5">
+        <f>IF($V66=0,"",INDEX(spisak_ime,$V66)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C66" s="5">
+        <f>IF($V66=0,"",INDEX(spisak_prezime,$V66)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D66" s="5">
+        <f>IF($V66=0,"",INDEX(spisak_godiste,$V66))</f>
+        <v/>
+      </c>
+      <c r="E66" s="5">
+        <f>IF($V66=0,"",INDEX(spisak_pol,$V66)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F66" s="5">
+        <f>IF($V66=0,"",INDEX(spisak_pojas,$V66)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G66" s="7">
         <f>IF($D66="","",LOOKUP($D66,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3240,7 +4571,7 @@
       <c r="P66" s="5"/>
       <c r="Q66" s="5"/>
       <c r="R66" s="8">
-        <f>IF(COUNTA($A66:$F66,I66:P66,Q66)=0,"",IF(AND($A66&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A66,4))="FSS-",MID($A66,LEN($A66)-2,1)="/",ISNUMBER(VALUE(RIGHT($A66,2))),VALUE(MID($A66,5,LEN($A66)-7))&gt;=1,VALUE(MID($A66,5,LEN($A66)-7))=INT(VALUE(MID($A66,5,LEN($A66)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B66="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B66&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C66="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C66&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D66="","Nedostaje godište",IF($G66="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E66="","Nedostaje pol",IF($F66="","Nedostaje pojas",IF(COUNTA(I66:P66)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I66:P66&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G66),I66:P66)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G66,IF(AND(COUNTIF(I66:P66,"Fudokan sport kumite")&gt;0,Q66=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I66:P66,"Fudokan sport kumite")=0,Q66&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A66:$F66))+SUMPRODUCT(LEN(I66:P66))+LEN(Q66)=0,"",IF(AND($A66&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A66,4))="FSS-",MID($A66,LEN($A66)-2,1)="/",ISNUMBER(VALUE(RIGHT($A66,2))),VALUE(MID($A66,5,LEN($A66)-7))&gt;=1,VALUE(MID($A66,5,LEN($A66)-7))=INT(VALUE(MID($A66,5,LEN($A66)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A66&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A66&lt;&gt;"",$U66=0,$B66=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U66&gt;0,$V66=0,$B66=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U66)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B66="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B66&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C66="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C66&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D66="","Nedostaje godište",IF($G66="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E66="","Nedostaje pol",IF($F66="","Nedostaje pojas",IF(COUNTA(I66:P66)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I66:P66&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G66),I66:P66)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G66,IF(AND(COUNTIF(I66:P66,"Fudokan sport kumite")&gt;0,Q66=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I66:P66,"Fudokan sport kumite")=0,Q66&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S66">
@@ -3251,14 +4582,37 @@
         <f>IF(OR($G66="",$E66=""),"sve_kilaze","kg_"&amp;$G66&amp;"_"&amp;IF($E66="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="67" spans="1:20">
+      <c r="U66">
+        <f>IF($A66="",0,IFERROR(MATCH(TRIM($A66),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V66">
+        <f>IF($U66=0,0,IF(TRIM(INDEX(spisak_klub,$U66))=TRIM($B$4),$U66,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22">
       <c r="A67" s="5"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="5"/>
-      <c r="D67" s="5"/>
-      <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
+      <c r="B67" s="5">
+        <f>IF($V67=0,"",INDEX(spisak_ime,$V67)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C67" s="5">
+        <f>IF($V67=0,"",INDEX(spisak_prezime,$V67)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D67" s="5">
+        <f>IF($V67=0,"",INDEX(spisak_godiste,$V67))</f>
+        <v/>
+      </c>
+      <c r="E67" s="5">
+        <f>IF($V67=0,"",INDEX(spisak_pol,$V67)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F67" s="5">
+        <f>IF($V67=0,"",INDEX(spisak_pojas,$V67)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G67" s="7">
         <f>IF($D67="","",LOOKUP($D67,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3277,7 +4631,7 @@
       <c r="P67" s="5"/>
       <c r="Q67" s="5"/>
       <c r="R67" s="8">
-        <f>IF(COUNTA($A67:$F67,I67:P67,Q67)=0,"",IF(AND($A67&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A67,4))="FSS-",MID($A67,LEN($A67)-2,1)="/",ISNUMBER(VALUE(RIGHT($A67,2))),VALUE(MID($A67,5,LEN($A67)-7))&gt;=1,VALUE(MID($A67,5,LEN($A67)-7))=INT(VALUE(MID($A67,5,LEN($A67)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B67="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B67&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C67="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C67&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D67="","Nedostaje godište",IF($G67="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E67="","Nedostaje pol",IF($F67="","Nedostaje pojas",IF(COUNTA(I67:P67)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I67:P67&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G67),I67:P67)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G67,IF(AND(COUNTIF(I67:P67,"Fudokan sport kumite")&gt;0,Q67=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I67:P67,"Fudokan sport kumite")=0,Q67&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A67:$F67))+SUMPRODUCT(LEN(I67:P67))+LEN(Q67)=0,"",IF(AND($A67&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A67,4))="FSS-",MID($A67,LEN($A67)-2,1)="/",ISNUMBER(VALUE(RIGHT($A67,2))),VALUE(MID($A67,5,LEN($A67)-7))&gt;=1,VALUE(MID($A67,5,LEN($A67)-7))=INT(VALUE(MID($A67,5,LEN($A67)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A67&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A67&lt;&gt;"",$U67=0,$B67=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U67&gt;0,$V67=0,$B67=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U67)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B67="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B67&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C67="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C67&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D67="","Nedostaje godište",IF($G67="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E67="","Nedostaje pol",IF($F67="","Nedostaje pojas",IF(COUNTA(I67:P67)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I67:P67&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G67),I67:P67)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G67,IF(AND(COUNTIF(I67:P67,"Fudokan sport kumite")&gt;0,Q67=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I67:P67,"Fudokan sport kumite")=0,Q67&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S67">
@@ -3288,14 +4642,37 @@
         <f>IF(OR($G67="",$E67=""),"sve_kilaze","kg_"&amp;$G67&amp;"_"&amp;IF($E67="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="68" spans="1:20">
+      <c r="U67">
+        <f>IF($A67="",0,IFERROR(MATCH(TRIM($A67),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V67">
+        <f>IF($U67=0,0,IF(TRIM(INDEX(spisak_klub,$U67))=TRIM($B$4),$U67,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22">
       <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
+      <c r="B68" s="5">
+        <f>IF($V68=0,"",INDEX(spisak_ime,$V68)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C68" s="5">
+        <f>IF($V68=0,"",INDEX(spisak_prezime,$V68)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D68" s="5">
+        <f>IF($V68=0,"",INDEX(spisak_godiste,$V68))</f>
+        <v/>
+      </c>
+      <c r="E68" s="5">
+        <f>IF($V68=0,"",INDEX(spisak_pol,$V68)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F68" s="5">
+        <f>IF($V68=0,"",INDEX(spisak_pojas,$V68)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G68" s="7">
         <f>IF($D68="","",LOOKUP($D68,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3314,7 +4691,7 @@
       <c r="P68" s="5"/>
       <c r="Q68" s="5"/>
       <c r="R68" s="8">
-        <f>IF(COUNTA($A68:$F68,I68:P68,Q68)=0,"",IF(AND($A68&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A68,4))="FSS-",MID($A68,LEN($A68)-2,1)="/",ISNUMBER(VALUE(RIGHT($A68,2))),VALUE(MID($A68,5,LEN($A68)-7))&gt;=1,VALUE(MID($A68,5,LEN($A68)-7))=INT(VALUE(MID($A68,5,LEN($A68)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B68="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B68&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C68="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C68&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D68="","Nedostaje godište",IF($G68="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E68="","Nedostaje pol",IF($F68="","Nedostaje pojas",IF(COUNTA(I68:P68)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I68:P68&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G68),I68:P68)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G68,IF(AND(COUNTIF(I68:P68,"Fudokan sport kumite")&gt;0,Q68=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I68:P68,"Fudokan sport kumite")=0,Q68&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A68:$F68))+SUMPRODUCT(LEN(I68:P68))+LEN(Q68)=0,"",IF(AND($A68&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A68,4))="FSS-",MID($A68,LEN($A68)-2,1)="/",ISNUMBER(VALUE(RIGHT($A68,2))),VALUE(MID($A68,5,LEN($A68)-7))&gt;=1,VALUE(MID($A68,5,LEN($A68)-7))=INT(VALUE(MID($A68,5,LEN($A68)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A68&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A68&lt;&gt;"",$U68=0,$B68=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U68&gt;0,$V68=0,$B68=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U68)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B68="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B68&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C68="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C68&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D68="","Nedostaje godište",IF($G68="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E68="","Nedostaje pol",IF($F68="","Nedostaje pojas",IF(COUNTA(I68:P68)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I68:P68&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G68),I68:P68)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G68,IF(AND(COUNTIF(I68:P68,"Fudokan sport kumite")&gt;0,Q68=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I68:P68,"Fudokan sport kumite")=0,Q68&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S68">
@@ -3325,14 +4702,37 @@
         <f>IF(OR($G68="",$E68=""),"sve_kilaze","kg_"&amp;$G68&amp;"_"&amp;IF($E68="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="69" spans="1:20">
+      <c r="U68">
+        <f>IF($A68="",0,IFERROR(MATCH(TRIM($A68),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V68">
+        <f>IF($U68=0,0,IF(TRIM(INDEX(spisak_klub,$U68))=TRIM($B$4),$U68,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22">
       <c r="A69" s="5"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="5"/>
-      <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
+      <c r="B69" s="5">
+        <f>IF($V69=0,"",INDEX(spisak_ime,$V69)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C69" s="5">
+        <f>IF($V69=0,"",INDEX(spisak_prezime,$V69)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D69" s="5">
+        <f>IF($V69=0,"",INDEX(spisak_godiste,$V69))</f>
+        <v/>
+      </c>
+      <c r="E69" s="5">
+        <f>IF($V69=0,"",INDEX(spisak_pol,$V69)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F69" s="5">
+        <f>IF($V69=0,"",INDEX(spisak_pojas,$V69)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G69" s="7">
         <f>IF($D69="","",LOOKUP($D69,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3351,7 +4751,7 @@
       <c r="P69" s="5"/>
       <c r="Q69" s="5"/>
       <c r="R69" s="8">
-        <f>IF(COUNTA($A69:$F69,I69:P69,Q69)=0,"",IF(AND($A69&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A69,4))="FSS-",MID($A69,LEN($A69)-2,1)="/",ISNUMBER(VALUE(RIGHT($A69,2))),VALUE(MID($A69,5,LEN($A69)-7))&gt;=1,VALUE(MID($A69,5,LEN($A69)-7))=INT(VALUE(MID($A69,5,LEN($A69)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B69="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B69&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C69="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C69&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D69="","Nedostaje godište",IF($G69="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E69="","Nedostaje pol",IF($F69="","Nedostaje pojas",IF(COUNTA(I69:P69)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I69:P69&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G69),I69:P69)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G69,IF(AND(COUNTIF(I69:P69,"Fudokan sport kumite")&gt;0,Q69=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I69:P69,"Fudokan sport kumite")=0,Q69&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A69:$F69))+SUMPRODUCT(LEN(I69:P69))+LEN(Q69)=0,"",IF(AND($A69&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A69,4))="FSS-",MID($A69,LEN($A69)-2,1)="/",ISNUMBER(VALUE(RIGHT($A69,2))),VALUE(MID($A69,5,LEN($A69)-7))&gt;=1,VALUE(MID($A69,5,LEN($A69)-7))=INT(VALUE(MID($A69,5,LEN($A69)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A69&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A69&lt;&gt;"",$U69=0,$B69=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U69&gt;0,$V69=0,$B69=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U69)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B69="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B69&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C69="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C69&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D69="","Nedostaje godište",IF($G69="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E69="","Nedostaje pol",IF($F69="","Nedostaje pojas",IF(COUNTA(I69:P69)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I69:P69&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G69),I69:P69)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G69,IF(AND(COUNTIF(I69:P69,"Fudokan sport kumite")&gt;0,Q69=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I69:P69,"Fudokan sport kumite")=0,Q69&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S69">
@@ -3362,14 +4762,37 @@
         <f>IF(OR($G69="",$E69=""),"sve_kilaze","kg_"&amp;$G69&amp;"_"&amp;IF($E69="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="70" spans="1:20">
+      <c r="U69">
+        <f>IF($A69="",0,IFERROR(MATCH(TRIM($A69),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V69">
+        <f>IF($U69=0,0,IF(TRIM(INDEX(spisak_klub,$U69))=TRIM($B$4),$U69,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22">
       <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
+      <c r="B70" s="5">
+        <f>IF($V70=0,"",INDEX(spisak_ime,$V70)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C70" s="5">
+        <f>IF($V70=0,"",INDEX(spisak_prezime,$V70)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D70" s="5">
+        <f>IF($V70=0,"",INDEX(spisak_godiste,$V70))</f>
+        <v/>
+      </c>
+      <c r="E70" s="5">
+        <f>IF($V70=0,"",INDEX(spisak_pol,$V70)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F70" s="5">
+        <f>IF($V70=0,"",INDEX(spisak_pojas,$V70)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G70" s="7">
         <f>IF($D70="","",LOOKUP($D70,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3388,7 +4811,7 @@
       <c r="P70" s="5"/>
       <c r="Q70" s="5"/>
       <c r="R70" s="8">
-        <f>IF(COUNTA($A70:$F70,I70:P70,Q70)=0,"",IF(AND($A70&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A70,4))="FSS-",MID($A70,LEN($A70)-2,1)="/",ISNUMBER(VALUE(RIGHT($A70,2))),VALUE(MID($A70,5,LEN($A70)-7))&gt;=1,VALUE(MID($A70,5,LEN($A70)-7))=INT(VALUE(MID($A70,5,LEN($A70)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B70="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B70&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C70="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C70&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D70="","Nedostaje godište",IF($G70="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E70="","Nedostaje pol",IF($F70="","Nedostaje pojas",IF(COUNTA(I70:P70)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I70:P70&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G70),I70:P70)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G70,IF(AND(COUNTIF(I70:P70,"Fudokan sport kumite")&gt;0,Q70=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I70:P70,"Fudokan sport kumite")=0,Q70&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A70:$F70))+SUMPRODUCT(LEN(I70:P70))+LEN(Q70)=0,"",IF(AND($A70&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A70,4))="FSS-",MID($A70,LEN($A70)-2,1)="/",ISNUMBER(VALUE(RIGHT($A70,2))),VALUE(MID($A70,5,LEN($A70)-7))&gt;=1,VALUE(MID($A70,5,LEN($A70)-7))=INT(VALUE(MID($A70,5,LEN($A70)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A70&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A70&lt;&gt;"",$U70=0,$B70=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U70&gt;0,$V70=0,$B70=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U70)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B70="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B70&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C70="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C70&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D70="","Nedostaje godište",IF($G70="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E70="","Nedostaje pol",IF($F70="","Nedostaje pojas",IF(COUNTA(I70:P70)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I70:P70&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G70),I70:P70)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G70,IF(AND(COUNTIF(I70:P70,"Fudokan sport kumite")&gt;0,Q70=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I70:P70,"Fudokan sport kumite")=0,Q70&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S70">
@@ -3399,14 +4822,37 @@
         <f>IF(OR($G70="",$E70=""),"sve_kilaze","kg_"&amp;$G70&amp;"_"&amp;IF($E70="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="71" spans="1:20">
+      <c r="U70">
+        <f>IF($A70="",0,IFERROR(MATCH(TRIM($A70),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V70">
+        <f>IF($U70=0,0,IF(TRIM(INDEX(spisak_klub,$U70))=TRIM($B$4),$U70,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22">
       <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
+      <c r="B71" s="5">
+        <f>IF($V71=0,"",INDEX(spisak_ime,$V71)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C71" s="5">
+        <f>IF($V71=0,"",INDEX(spisak_prezime,$V71)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D71" s="5">
+        <f>IF($V71=0,"",INDEX(spisak_godiste,$V71))</f>
+        <v/>
+      </c>
+      <c r="E71" s="5">
+        <f>IF($V71=0,"",INDEX(spisak_pol,$V71)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F71" s="5">
+        <f>IF($V71=0,"",INDEX(spisak_pojas,$V71)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G71" s="7">
         <f>IF($D71="","",LOOKUP($D71,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3425,7 +4871,7 @@
       <c r="P71" s="5"/>
       <c r="Q71" s="5"/>
       <c r="R71" s="8">
-        <f>IF(COUNTA($A71:$F71,I71:P71,Q71)=0,"",IF(AND($A71&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A71,4))="FSS-",MID($A71,LEN($A71)-2,1)="/",ISNUMBER(VALUE(RIGHT($A71,2))),VALUE(MID($A71,5,LEN($A71)-7))&gt;=1,VALUE(MID($A71,5,LEN($A71)-7))=INT(VALUE(MID($A71,5,LEN($A71)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B71="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B71&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C71="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C71&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D71="","Nedostaje godište",IF($G71="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E71="","Nedostaje pol",IF($F71="","Nedostaje pojas",IF(COUNTA(I71:P71)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I71:P71&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G71),I71:P71)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G71,IF(AND(COUNTIF(I71:P71,"Fudokan sport kumite")&gt;0,Q71=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I71:P71,"Fudokan sport kumite")=0,Q71&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A71:$F71))+SUMPRODUCT(LEN(I71:P71))+LEN(Q71)=0,"",IF(AND($A71&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A71,4))="FSS-",MID($A71,LEN($A71)-2,1)="/",ISNUMBER(VALUE(RIGHT($A71,2))),VALUE(MID($A71,5,LEN($A71)-7))&gt;=1,VALUE(MID($A71,5,LEN($A71)-7))=INT(VALUE(MID($A71,5,LEN($A71)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A71&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A71&lt;&gt;"",$U71=0,$B71=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U71&gt;0,$V71=0,$B71=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U71)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B71="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B71&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C71="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C71&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D71="","Nedostaje godište",IF($G71="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E71="","Nedostaje pol",IF($F71="","Nedostaje pojas",IF(COUNTA(I71:P71)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I71:P71&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G71),I71:P71)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G71,IF(AND(COUNTIF(I71:P71,"Fudokan sport kumite")&gt;0,Q71=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I71:P71,"Fudokan sport kumite")=0,Q71&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S71">
@@ -3436,14 +4882,37 @@
         <f>IF(OR($G71="",$E71=""),"sve_kilaze","kg_"&amp;$G71&amp;"_"&amp;IF($E71="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="72" spans="1:20">
+      <c r="U71">
+        <f>IF($A71="",0,IFERROR(MATCH(TRIM($A71),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V71">
+        <f>IF($U71=0,0,IF(TRIM(INDEX(spisak_klub,$U71))=TRIM($B$4),$U71,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22">
       <c r="A72" s="5"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
+      <c r="B72" s="5">
+        <f>IF($V72=0,"",INDEX(spisak_ime,$V72)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C72" s="5">
+        <f>IF($V72=0,"",INDEX(spisak_prezime,$V72)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D72" s="5">
+        <f>IF($V72=0,"",INDEX(spisak_godiste,$V72))</f>
+        <v/>
+      </c>
+      <c r="E72" s="5">
+        <f>IF($V72=0,"",INDEX(spisak_pol,$V72)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F72" s="5">
+        <f>IF($V72=0,"",INDEX(spisak_pojas,$V72)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G72" s="7">
         <f>IF($D72="","",LOOKUP($D72,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3462,7 +4931,7 @@
       <c r="P72" s="5"/>
       <c r="Q72" s="5"/>
       <c r="R72" s="8">
-        <f>IF(COUNTA($A72:$F72,I72:P72,Q72)=0,"",IF(AND($A72&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A72,4))="FSS-",MID($A72,LEN($A72)-2,1)="/",ISNUMBER(VALUE(RIGHT($A72,2))),VALUE(MID($A72,5,LEN($A72)-7))&gt;=1,VALUE(MID($A72,5,LEN($A72)-7))=INT(VALUE(MID($A72,5,LEN($A72)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B72="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B72&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C72="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C72&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D72="","Nedostaje godište",IF($G72="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E72="","Nedostaje pol",IF($F72="","Nedostaje pojas",IF(COUNTA(I72:P72)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I72:P72&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G72),I72:P72)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G72,IF(AND(COUNTIF(I72:P72,"Fudokan sport kumite")&gt;0,Q72=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I72:P72,"Fudokan sport kumite")=0,Q72&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A72:$F72))+SUMPRODUCT(LEN(I72:P72))+LEN(Q72)=0,"",IF(AND($A72&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A72,4))="FSS-",MID($A72,LEN($A72)-2,1)="/",ISNUMBER(VALUE(RIGHT($A72,2))),VALUE(MID($A72,5,LEN($A72)-7))&gt;=1,VALUE(MID($A72,5,LEN($A72)-7))=INT(VALUE(MID($A72,5,LEN($A72)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A72&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A72&lt;&gt;"",$U72=0,$B72=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U72&gt;0,$V72=0,$B72=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U72)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B72="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B72&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C72="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C72&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D72="","Nedostaje godište",IF($G72="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E72="","Nedostaje pol",IF($F72="","Nedostaje pojas",IF(COUNTA(I72:P72)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I72:P72&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G72),I72:P72)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G72,IF(AND(COUNTIF(I72:P72,"Fudokan sport kumite")&gt;0,Q72=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I72:P72,"Fudokan sport kumite")=0,Q72&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S72">
@@ -3473,14 +4942,37 @@
         <f>IF(OR($G72="",$E72=""),"sve_kilaze","kg_"&amp;$G72&amp;"_"&amp;IF($E72="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="73" spans="1:20">
+      <c r="U72">
+        <f>IF($A72="",0,IFERROR(MATCH(TRIM($A72),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V72">
+        <f>IF($U72=0,0,IF(TRIM(INDEX(spisak_klub,$U72))=TRIM($B$4),$U72,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22">
       <c r="A73" s="5"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5"/>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
+      <c r="B73" s="5">
+        <f>IF($V73=0,"",INDEX(spisak_ime,$V73)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C73" s="5">
+        <f>IF($V73=0,"",INDEX(spisak_prezime,$V73)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D73" s="5">
+        <f>IF($V73=0,"",INDEX(spisak_godiste,$V73))</f>
+        <v/>
+      </c>
+      <c r="E73" s="5">
+        <f>IF($V73=0,"",INDEX(spisak_pol,$V73)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F73" s="5">
+        <f>IF($V73=0,"",INDEX(spisak_pojas,$V73)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G73" s="7">
         <f>IF($D73="","",LOOKUP($D73,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3499,7 +4991,7 @@
       <c r="P73" s="5"/>
       <c r="Q73" s="5"/>
       <c r="R73" s="8">
-        <f>IF(COUNTA($A73:$F73,I73:P73,Q73)=0,"",IF(AND($A73&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A73,4))="FSS-",MID($A73,LEN($A73)-2,1)="/",ISNUMBER(VALUE(RIGHT($A73,2))),VALUE(MID($A73,5,LEN($A73)-7))&gt;=1,VALUE(MID($A73,5,LEN($A73)-7))=INT(VALUE(MID($A73,5,LEN($A73)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B73="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B73&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C73="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C73&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D73="","Nedostaje godište",IF($G73="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E73="","Nedostaje pol",IF($F73="","Nedostaje pojas",IF(COUNTA(I73:P73)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I73:P73&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G73),I73:P73)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G73,IF(AND(COUNTIF(I73:P73,"Fudokan sport kumite")&gt;0,Q73=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I73:P73,"Fudokan sport kumite")=0,Q73&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A73:$F73))+SUMPRODUCT(LEN(I73:P73))+LEN(Q73)=0,"",IF(AND($A73&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A73,4))="FSS-",MID($A73,LEN($A73)-2,1)="/",ISNUMBER(VALUE(RIGHT($A73,2))),VALUE(MID($A73,5,LEN($A73)-7))&gt;=1,VALUE(MID($A73,5,LEN($A73)-7))=INT(VALUE(MID($A73,5,LEN($A73)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A73&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A73&lt;&gt;"",$U73=0,$B73=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U73&gt;0,$V73=0,$B73=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U73)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B73="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B73&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C73="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C73&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D73="","Nedostaje godište",IF($G73="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E73="","Nedostaje pol",IF($F73="","Nedostaje pojas",IF(COUNTA(I73:P73)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I73:P73&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G73),I73:P73)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G73,IF(AND(COUNTIF(I73:P73,"Fudokan sport kumite")&gt;0,Q73=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I73:P73,"Fudokan sport kumite")=0,Q73&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S73">
@@ -3510,14 +5002,37 @@
         <f>IF(OR($G73="",$E73=""),"sve_kilaze","kg_"&amp;$G73&amp;"_"&amp;IF($E73="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="74" spans="1:20">
+      <c r="U73">
+        <f>IF($A73="",0,IFERROR(MATCH(TRIM($A73),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V73">
+        <f>IF($U73=0,0,IF(TRIM(INDEX(spisak_klub,$U73))=TRIM($B$4),$U73,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22">
       <c r="A74" s="5"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="5"/>
-      <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
+      <c r="B74" s="5">
+        <f>IF($V74=0,"",INDEX(spisak_ime,$V74)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C74" s="5">
+        <f>IF($V74=0,"",INDEX(spisak_prezime,$V74)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D74" s="5">
+        <f>IF($V74=0,"",INDEX(spisak_godiste,$V74))</f>
+        <v/>
+      </c>
+      <c r="E74" s="5">
+        <f>IF($V74=0,"",INDEX(spisak_pol,$V74)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F74" s="5">
+        <f>IF($V74=0,"",INDEX(spisak_pojas,$V74)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G74" s="7">
         <f>IF($D74="","",LOOKUP($D74,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3536,7 +5051,7 @@
       <c r="P74" s="5"/>
       <c r="Q74" s="5"/>
       <c r="R74" s="8">
-        <f>IF(COUNTA($A74:$F74,I74:P74,Q74)=0,"",IF(AND($A74&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A74,4))="FSS-",MID($A74,LEN($A74)-2,1)="/",ISNUMBER(VALUE(RIGHT($A74,2))),VALUE(MID($A74,5,LEN($A74)-7))&gt;=1,VALUE(MID($A74,5,LEN($A74)-7))=INT(VALUE(MID($A74,5,LEN($A74)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B74="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B74&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C74="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C74&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D74="","Nedostaje godište",IF($G74="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E74="","Nedostaje pol",IF($F74="","Nedostaje pojas",IF(COUNTA(I74:P74)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I74:P74&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G74),I74:P74)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G74,IF(AND(COUNTIF(I74:P74,"Fudokan sport kumite")&gt;0,Q74=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I74:P74,"Fudokan sport kumite")=0,Q74&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A74:$F74))+SUMPRODUCT(LEN(I74:P74))+LEN(Q74)=0,"",IF(AND($A74&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A74,4))="FSS-",MID($A74,LEN($A74)-2,1)="/",ISNUMBER(VALUE(RIGHT($A74,2))),VALUE(MID($A74,5,LEN($A74)-7))&gt;=1,VALUE(MID($A74,5,LEN($A74)-7))=INT(VALUE(MID($A74,5,LEN($A74)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A74&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A74&lt;&gt;"",$U74=0,$B74=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U74&gt;0,$V74=0,$B74=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U74)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B74="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B74&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C74="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C74&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D74="","Nedostaje godište",IF($G74="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E74="","Nedostaje pol",IF($F74="","Nedostaje pojas",IF(COUNTA(I74:P74)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I74:P74&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G74),I74:P74)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G74,IF(AND(COUNTIF(I74:P74,"Fudokan sport kumite")&gt;0,Q74=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I74:P74,"Fudokan sport kumite")=0,Q74&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S74">
@@ -3547,14 +5062,37 @@
         <f>IF(OR($G74="",$E74=""),"sve_kilaze","kg_"&amp;$G74&amp;"_"&amp;IF($E74="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="75" spans="1:20">
+      <c r="U74">
+        <f>IF($A74="",0,IFERROR(MATCH(TRIM($A74),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V74">
+        <f>IF($U74=0,0,IF(TRIM(INDEX(spisak_klub,$U74))=TRIM($B$4),$U74,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22">
       <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
+      <c r="B75" s="5">
+        <f>IF($V75=0,"",INDEX(spisak_ime,$V75)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C75" s="5">
+        <f>IF($V75=0,"",INDEX(spisak_prezime,$V75)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D75" s="5">
+        <f>IF($V75=0,"",INDEX(spisak_godiste,$V75))</f>
+        <v/>
+      </c>
+      <c r="E75" s="5">
+        <f>IF($V75=0,"",INDEX(spisak_pol,$V75)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F75" s="5">
+        <f>IF($V75=0,"",INDEX(spisak_pojas,$V75)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G75" s="7">
         <f>IF($D75="","",LOOKUP($D75,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3573,7 +5111,7 @@
       <c r="P75" s="5"/>
       <c r="Q75" s="5"/>
       <c r="R75" s="8">
-        <f>IF(COUNTA($A75:$F75,I75:P75,Q75)=0,"",IF(AND($A75&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A75,4))="FSS-",MID($A75,LEN($A75)-2,1)="/",ISNUMBER(VALUE(RIGHT($A75,2))),VALUE(MID($A75,5,LEN($A75)-7))&gt;=1,VALUE(MID($A75,5,LEN($A75)-7))=INT(VALUE(MID($A75,5,LEN($A75)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B75="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B75&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C75="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C75&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D75="","Nedostaje godište",IF($G75="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E75="","Nedostaje pol",IF($F75="","Nedostaje pojas",IF(COUNTA(I75:P75)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I75:P75&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G75),I75:P75)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G75,IF(AND(COUNTIF(I75:P75,"Fudokan sport kumite")&gt;0,Q75=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I75:P75,"Fudokan sport kumite")=0,Q75&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A75:$F75))+SUMPRODUCT(LEN(I75:P75))+LEN(Q75)=0,"",IF(AND($A75&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A75,4))="FSS-",MID($A75,LEN($A75)-2,1)="/",ISNUMBER(VALUE(RIGHT($A75,2))),VALUE(MID($A75,5,LEN($A75)-7))&gt;=1,VALUE(MID($A75,5,LEN($A75)-7))=INT(VALUE(MID($A75,5,LEN($A75)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A75&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A75&lt;&gt;"",$U75=0,$B75=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U75&gt;0,$V75=0,$B75=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U75)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B75="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B75&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C75="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C75&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D75="","Nedostaje godište",IF($G75="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E75="","Nedostaje pol",IF($F75="","Nedostaje pojas",IF(COUNTA(I75:P75)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I75:P75&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G75),I75:P75)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G75,IF(AND(COUNTIF(I75:P75,"Fudokan sport kumite")&gt;0,Q75=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I75:P75,"Fudokan sport kumite")=0,Q75&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S75">
@@ -3584,14 +5122,37 @@
         <f>IF(OR($G75="",$E75=""),"sve_kilaze","kg_"&amp;$G75&amp;"_"&amp;IF($E75="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="76" spans="1:20">
+      <c r="U75">
+        <f>IF($A75="",0,IFERROR(MATCH(TRIM($A75),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V75">
+        <f>IF($U75=0,0,IF(TRIM(INDEX(spisak_klub,$U75))=TRIM($B$4),$U75,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22">
       <c r="A76" s="5"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
+      <c r="B76" s="5">
+        <f>IF($V76=0,"",INDEX(spisak_ime,$V76)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C76" s="5">
+        <f>IF($V76=0,"",INDEX(spisak_prezime,$V76)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D76" s="5">
+        <f>IF($V76=0,"",INDEX(spisak_godiste,$V76))</f>
+        <v/>
+      </c>
+      <c r="E76" s="5">
+        <f>IF($V76=0,"",INDEX(spisak_pol,$V76)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F76" s="5">
+        <f>IF($V76=0,"",INDEX(spisak_pojas,$V76)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G76" s="7">
         <f>IF($D76="","",LOOKUP($D76,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3610,7 +5171,7 @@
       <c r="P76" s="5"/>
       <c r="Q76" s="5"/>
       <c r="R76" s="8">
-        <f>IF(COUNTA($A76:$F76,I76:P76,Q76)=0,"",IF(AND($A76&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A76,4))="FSS-",MID($A76,LEN($A76)-2,1)="/",ISNUMBER(VALUE(RIGHT($A76,2))),VALUE(MID($A76,5,LEN($A76)-7))&gt;=1,VALUE(MID($A76,5,LEN($A76)-7))=INT(VALUE(MID($A76,5,LEN($A76)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B76="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B76&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C76="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C76&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D76="","Nedostaje godište",IF($G76="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E76="","Nedostaje pol",IF($F76="","Nedostaje pojas",IF(COUNTA(I76:P76)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I76:P76&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G76),I76:P76)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G76,IF(AND(COUNTIF(I76:P76,"Fudokan sport kumite")&gt;0,Q76=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I76:P76,"Fudokan sport kumite")=0,Q76&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A76:$F76))+SUMPRODUCT(LEN(I76:P76))+LEN(Q76)=0,"",IF(AND($A76&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A76,4))="FSS-",MID($A76,LEN($A76)-2,1)="/",ISNUMBER(VALUE(RIGHT($A76,2))),VALUE(MID($A76,5,LEN($A76)-7))&gt;=1,VALUE(MID($A76,5,LEN($A76)-7))=INT(VALUE(MID($A76,5,LEN($A76)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A76&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A76&lt;&gt;"",$U76=0,$B76=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U76&gt;0,$V76=0,$B76=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U76)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B76="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B76&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C76="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C76&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D76="","Nedostaje godište",IF($G76="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E76="","Nedostaje pol",IF($F76="","Nedostaje pojas",IF(COUNTA(I76:P76)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I76:P76&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G76),I76:P76)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G76,IF(AND(COUNTIF(I76:P76,"Fudokan sport kumite")&gt;0,Q76=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I76:P76,"Fudokan sport kumite")=0,Q76&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S76">
@@ -3621,14 +5182,37 @@
         <f>IF(OR($G76="",$E76=""),"sve_kilaze","kg_"&amp;$G76&amp;"_"&amp;IF($E76="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="77" spans="1:20">
+      <c r="U76">
+        <f>IF($A76="",0,IFERROR(MATCH(TRIM($A76),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V76">
+        <f>IF($U76=0,0,IF(TRIM(INDEX(spisak_klub,$U76))=TRIM($B$4),$U76,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22">
       <c r="A77" s="5"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="5"/>
-      <c r="D77" s="5"/>
-      <c r="E77" s="5"/>
-      <c r="F77" s="5"/>
+      <c r="B77" s="5">
+        <f>IF($V77=0,"",INDEX(spisak_ime,$V77)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C77" s="5">
+        <f>IF($V77=0,"",INDEX(spisak_prezime,$V77)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D77" s="5">
+        <f>IF($V77=0,"",INDEX(spisak_godiste,$V77))</f>
+        <v/>
+      </c>
+      <c r="E77" s="5">
+        <f>IF($V77=0,"",INDEX(spisak_pol,$V77)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F77" s="5">
+        <f>IF($V77=0,"",INDEX(spisak_pojas,$V77)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G77" s="7">
         <f>IF($D77="","",LOOKUP($D77,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3647,7 +5231,7 @@
       <c r="P77" s="5"/>
       <c r="Q77" s="5"/>
       <c r="R77" s="8">
-        <f>IF(COUNTA($A77:$F77,I77:P77,Q77)=0,"",IF(AND($A77&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A77,4))="FSS-",MID($A77,LEN($A77)-2,1)="/",ISNUMBER(VALUE(RIGHT($A77,2))),VALUE(MID($A77,5,LEN($A77)-7))&gt;=1,VALUE(MID($A77,5,LEN($A77)-7))=INT(VALUE(MID($A77,5,LEN($A77)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B77="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B77&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C77="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C77&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D77="","Nedostaje godište",IF($G77="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E77="","Nedostaje pol",IF($F77="","Nedostaje pojas",IF(COUNTA(I77:P77)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I77:P77&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G77),I77:P77)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G77,IF(AND(COUNTIF(I77:P77,"Fudokan sport kumite")&gt;0,Q77=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I77:P77,"Fudokan sport kumite")=0,Q77&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A77:$F77))+SUMPRODUCT(LEN(I77:P77))+LEN(Q77)=0,"",IF(AND($A77&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A77,4))="FSS-",MID($A77,LEN($A77)-2,1)="/",ISNUMBER(VALUE(RIGHT($A77,2))),VALUE(MID($A77,5,LEN($A77)-7))&gt;=1,VALUE(MID($A77,5,LEN($A77)-7))=INT(VALUE(MID($A77,5,LEN($A77)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A77&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A77&lt;&gt;"",$U77=0,$B77=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U77&gt;0,$V77=0,$B77=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U77)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B77="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B77&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C77="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C77&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D77="","Nedostaje godište",IF($G77="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E77="","Nedostaje pol",IF($F77="","Nedostaje pojas",IF(COUNTA(I77:P77)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I77:P77&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G77),I77:P77)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G77,IF(AND(COUNTIF(I77:P77,"Fudokan sport kumite")&gt;0,Q77=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I77:P77,"Fudokan sport kumite")=0,Q77&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S77">
@@ -3658,14 +5242,37 @@
         <f>IF(OR($G77="",$E77=""),"sve_kilaze","kg_"&amp;$G77&amp;"_"&amp;IF($E77="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="78" spans="1:20">
+      <c r="U77">
+        <f>IF($A77="",0,IFERROR(MATCH(TRIM($A77),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V77">
+        <f>IF($U77=0,0,IF(TRIM(INDEX(spisak_klub,$U77))=TRIM($B$4),$U77,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22">
       <c r="A78" s="5"/>
-      <c r="B78" s="5"/>
-      <c r="C78" s="5"/>
-      <c r="D78" s="5"/>
-      <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
+      <c r="B78" s="5">
+        <f>IF($V78=0,"",INDEX(spisak_ime,$V78)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C78" s="5">
+        <f>IF($V78=0,"",INDEX(spisak_prezime,$V78)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D78" s="5">
+        <f>IF($V78=0,"",INDEX(spisak_godiste,$V78))</f>
+        <v/>
+      </c>
+      <c r="E78" s="5">
+        <f>IF($V78=0,"",INDEX(spisak_pol,$V78)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F78" s="5">
+        <f>IF($V78=0,"",INDEX(spisak_pojas,$V78)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G78" s="7">
         <f>IF($D78="","",LOOKUP($D78,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3684,7 +5291,7 @@
       <c r="P78" s="5"/>
       <c r="Q78" s="5"/>
       <c r="R78" s="8">
-        <f>IF(COUNTA($A78:$F78,I78:P78,Q78)=0,"",IF(AND($A78&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A78,4))="FSS-",MID($A78,LEN($A78)-2,1)="/",ISNUMBER(VALUE(RIGHT($A78,2))),VALUE(MID($A78,5,LEN($A78)-7))&gt;=1,VALUE(MID($A78,5,LEN($A78)-7))=INT(VALUE(MID($A78,5,LEN($A78)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B78="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B78&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C78="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C78&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D78="","Nedostaje godište",IF($G78="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E78="","Nedostaje pol",IF($F78="","Nedostaje pojas",IF(COUNTA(I78:P78)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I78:P78&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G78),I78:P78)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G78,IF(AND(COUNTIF(I78:P78,"Fudokan sport kumite")&gt;0,Q78=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I78:P78,"Fudokan sport kumite")=0,Q78&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A78:$F78))+SUMPRODUCT(LEN(I78:P78))+LEN(Q78)=0,"",IF(AND($A78&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A78,4))="FSS-",MID($A78,LEN($A78)-2,1)="/",ISNUMBER(VALUE(RIGHT($A78,2))),VALUE(MID($A78,5,LEN($A78)-7))&gt;=1,VALUE(MID($A78,5,LEN($A78)-7))=INT(VALUE(MID($A78,5,LEN($A78)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A78&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A78&lt;&gt;"",$U78=0,$B78=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U78&gt;0,$V78=0,$B78=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U78)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B78="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B78&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C78="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C78&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D78="","Nedostaje godište",IF($G78="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E78="","Nedostaje pol",IF($F78="","Nedostaje pojas",IF(COUNTA(I78:P78)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I78:P78&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G78),I78:P78)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G78,IF(AND(COUNTIF(I78:P78,"Fudokan sport kumite")&gt;0,Q78=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I78:P78,"Fudokan sport kumite")=0,Q78&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S78">
@@ -3695,14 +5302,37 @@
         <f>IF(OR($G78="",$E78=""),"sve_kilaze","kg_"&amp;$G78&amp;"_"&amp;IF($E78="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="79" spans="1:20">
+      <c r="U78">
+        <f>IF($A78="",0,IFERROR(MATCH(TRIM($A78),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V78">
+        <f>IF($U78=0,0,IF(TRIM(INDEX(spisak_klub,$U78))=TRIM($B$4),$U78,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22">
       <c r="A79" s="5"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
-      <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
+      <c r="B79" s="5">
+        <f>IF($V79=0,"",INDEX(spisak_ime,$V79)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C79" s="5">
+        <f>IF($V79=0,"",INDEX(spisak_prezime,$V79)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D79" s="5">
+        <f>IF($V79=0,"",INDEX(spisak_godiste,$V79))</f>
+        <v/>
+      </c>
+      <c r="E79" s="5">
+        <f>IF($V79=0,"",INDEX(spisak_pol,$V79)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F79" s="5">
+        <f>IF($V79=0,"",INDEX(spisak_pojas,$V79)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G79" s="7">
         <f>IF($D79="","",LOOKUP($D79,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3721,7 +5351,7 @@
       <c r="P79" s="5"/>
       <c r="Q79" s="5"/>
       <c r="R79" s="8">
-        <f>IF(COUNTA($A79:$F79,I79:P79,Q79)=0,"",IF(AND($A79&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A79,4))="FSS-",MID($A79,LEN($A79)-2,1)="/",ISNUMBER(VALUE(RIGHT($A79,2))),VALUE(MID($A79,5,LEN($A79)-7))&gt;=1,VALUE(MID($A79,5,LEN($A79)-7))=INT(VALUE(MID($A79,5,LEN($A79)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B79="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B79&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C79="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C79&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D79="","Nedostaje godište",IF($G79="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E79="","Nedostaje pol",IF($F79="","Nedostaje pojas",IF(COUNTA(I79:P79)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I79:P79&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G79),I79:P79)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G79,IF(AND(COUNTIF(I79:P79,"Fudokan sport kumite")&gt;0,Q79=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I79:P79,"Fudokan sport kumite")=0,Q79&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A79:$F79))+SUMPRODUCT(LEN(I79:P79))+LEN(Q79)=0,"",IF(AND($A79&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A79,4))="FSS-",MID($A79,LEN($A79)-2,1)="/",ISNUMBER(VALUE(RIGHT($A79,2))),VALUE(MID($A79,5,LEN($A79)-7))&gt;=1,VALUE(MID($A79,5,LEN($A79)-7))=INT(VALUE(MID($A79,5,LEN($A79)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A79&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A79&lt;&gt;"",$U79=0,$B79=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U79&gt;0,$V79=0,$B79=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U79)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B79="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B79&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C79="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C79&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D79="","Nedostaje godište",IF($G79="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E79="","Nedostaje pol",IF($F79="","Nedostaje pojas",IF(COUNTA(I79:P79)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I79:P79&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G79),I79:P79)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G79,IF(AND(COUNTIF(I79:P79,"Fudokan sport kumite")&gt;0,Q79=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I79:P79,"Fudokan sport kumite")=0,Q79&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S79">
@@ -3732,14 +5362,37 @@
         <f>IF(OR($G79="",$E79=""),"sve_kilaze","kg_"&amp;$G79&amp;"_"&amp;IF($E79="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="80" spans="1:20">
+      <c r="U79">
+        <f>IF($A79="",0,IFERROR(MATCH(TRIM($A79),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V79">
+        <f>IF($U79=0,0,IF(TRIM(INDEX(spisak_klub,$U79))=TRIM($B$4),$U79,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22">
       <c r="A80" s="5"/>
-      <c r="B80" s="5"/>
-      <c r="C80" s="5"/>
-      <c r="D80" s="5"/>
-      <c r="E80" s="5"/>
-      <c r="F80" s="5"/>
+      <c r="B80" s="5">
+        <f>IF($V80=0,"",INDEX(spisak_ime,$V80)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C80" s="5">
+        <f>IF($V80=0,"",INDEX(spisak_prezime,$V80)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D80" s="5">
+        <f>IF($V80=0,"",INDEX(spisak_godiste,$V80))</f>
+        <v/>
+      </c>
+      <c r="E80" s="5">
+        <f>IF($V80=0,"",INDEX(spisak_pol,$V80)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F80" s="5">
+        <f>IF($V80=0,"",INDEX(spisak_pojas,$V80)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G80" s="7">
         <f>IF($D80="","",LOOKUP($D80,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3758,7 +5411,7 @@
       <c r="P80" s="5"/>
       <c r="Q80" s="5"/>
       <c r="R80" s="8">
-        <f>IF(COUNTA($A80:$F80,I80:P80,Q80)=0,"",IF(AND($A80&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A80,4))="FSS-",MID($A80,LEN($A80)-2,1)="/",ISNUMBER(VALUE(RIGHT($A80,2))),VALUE(MID($A80,5,LEN($A80)-7))&gt;=1,VALUE(MID($A80,5,LEN($A80)-7))=INT(VALUE(MID($A80,5,LEN($A80)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B80="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B80&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C80="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C80&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D80="","Nedostaje godište",IF($G80="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E80="","Nedostaje pol",IF($F80="","Nedostaje pojas",IF(COUNTA(I80:P80)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I80:P80&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G80),I80:P80)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G80,IF(AND(COUNTIF(I80:P80,"Fudokan sport kumite")&gt;0,Q80=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I80:P80,"Fudokan sport kumite")=0,Q80&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A80:$F80))+SUMPRODUCT(LEN(I80:P80))+LEN(Q80)=0,"",IF(AND($A80&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A80,4))="FSS-",MID($A80,LEN($A80)-2,1)="/",ISNUMBER(VALUE(RIGHT($A80,2))),VALUE(MID($A80,5,LEN($A80)-7))&gt;=1,VALUE(MID($A80,5,LEN($A80)-7))=INT(VALUE(MID($A80,5,LEN($A80)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A80&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A80&lt;&gt;"",$U80=0,$B80=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U80&gt;0,$V80=0,$B80=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U80)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B80="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B80&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C80="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C80&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D80="","Nedostaje godište",IF($G80="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E80="","Nedostaje pol",IF($F80="","Nedostaje pojas",IF(COUNTA(I80:P80)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I80:P80&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G80),I80:P80)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G80,IF(AND(COUNTIF(I80:P80,"Fudokan sport kumite")&gt;0,Q80=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I80:P80,"Fudokan sport kumite")=0,Q80&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S80">
@@ -3769,14 +5422,37 @@
         <f>IF(OR($G80="",$E80=""),"sve_kilaze","kg_"&amp;$G80&amp;"_"&amp;IF($E80="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="81" spans="1:20">
+      <c r="U80">
+        <f>IF($A80="",0,IFERROR(MATCH(TRIM($A80),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V80">
+        <f>IF($U80=0,0,IF(TRIM(INDEX(spisak_klub,$U80))=TRIM($B$4),$U80,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22">
       <c r="A81" s="5"/>
-      <c r="B81" s="5"/>
-      <c r="C81" s="5"/>
-      <c r="D81" s="5"/>
-      <c r="E81" s="5"/>
-      <c r="F81" s="5"/>
+      <c r="B81" s="5">
+        <f>IF($V81=0,"",INDEX(spisak_ime,$V81)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C81" s="5">
+        <f>IF($V81=0,"",INDEX(spisak_prezime,$V81)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D81" s="5">
+        <f>IF($V81=0,"",INDEX(spisak_godiste,$V81))</f>
+        <v/>
+      </c>
+      <c r="E81" s="5">
+        <f>IF($V81=0,"",INDEX(spisak_pol,$V81)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F81" s="5">
+        <f>IF($V81=0,"",INDEX(spisak_pojas,$V81)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G81" s="7">
         <f>IF($D81="","",LOOKUP($D81,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3795,7 +5471,7 @@
       <c r="P81" s="5"/>
       <c r="Q81" s="5"/>
       <c r="R81" s="8">
-        <f>IF(COUNTA($A81:$F81,I81:P81,Q81)=0,"",IF(AND($A81&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A81,4))="FSS-",MID($A81,LEN($A81)-2,1)="/",ISNUMBER(VALUE(RIGHT($A81,2))),VALUE(MID($A81,5,LEN($A81)-7))&gt;=1,VALUE(MID($A81,5,LEN($A81)-7))=INT(VALUE(MID($A81,5,LEN($A81)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B81="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B81&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C81="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C81&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D81="","Nedostaje godište",IF($G81="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E81="","Nedostaje pol",IF($F81="","Nedostaje pojas",IF(COUNTA(I81:P81)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I81:P81&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G81),I81:P81)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G81,IF(AND(COUNTIF(I81:P81,"Fudokan sport kumite")&gt;0,Q81=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I81:P81,"Fudokan sport kumite")=0,Q81&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A81:$F81))+SUMPRODUCT(LEN(I81:P81))+LEN(Q81)=0,"",IF(AND($A81&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A81,4))="FSS-",MID($A81,LEN($A81)-2,1)="/",ISNUMBER(VALUE(RIGHT($A81,2))),VALUE(MID($A81,5,LEN($A81)-7))&gt;=1,VALUE(MID($A81,5,LEN($A81)-7))=INT(VALUE(MID($A81,5,LEN($A81)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A81&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A81&lt;&gt;"",$U81=0,$B81=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U81&gt;0,$V81=0,$B81=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U81)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B81="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B81&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C81="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C81&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D81="","Nedostaje godište",IF($G81="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E81="","Nedostaje pol",IF($F81="","Nedostaje pojas",IF(COUNTA(I81:P81)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I81:P81&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G81),I81:P81)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G81,IF(AND(COUNTIF(I81:P81,"Fudokan sport kumite")&gt;0,Q81=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I81:P81,"Fudokan sport kumite")=0,Q81&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S81">
@@ -3806,14 +5482,37 @@
         <f>IF(OR($G81="",$E81=""),"sve_kilaze","kg_"&amp;$G81&amp;"_"&amp;IF($E81="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="82" spans="1:20">
+      <c r="U81">
+        <f>IF($A81="",0,IFERROR(MATCH(TRIM($A81),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V81">
+        <f>IF($U81=0,0,IF(TRIM(INDEX(spisak_klub,$U81))=TRIM($B$4),$U81,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22">
       <c r="A82" s="5"/>
-      <c r="B82" s="5"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="5"/>
-      <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
+      <c r="B82" s="5">
+        <f>IF($V82=0,"",INDEX(spisak_ime,$V82)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C82" s="5">
+        <f>IF($V82=0,"",INDEX(spisak_prezime,$V82)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D82" s="5">
+        <f>IF($V82=0,"",INDEX(spisak_godiste,$V82))</f>
+        <v/>
+      </c>
+      <c r="E82" s="5">
+        <f>IF($V82=0,"",INDEX(spisak_pol,$V82)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F82" s="5">
+        <f>IF($V82=0,"",INDEX(spisak_pojas,$V82)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G82" s="7">
         <f>IF($D82="","",LOOKUP($D82,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3832,7 +5531,7 @@
       <c r="P82" s="5"/>
       <c r="Q82" s="5"/>
       <c r="R82" s="8">
-        <f>IF(COUNTA($A82:$F82,I82:P82,Q82)=0,"",IF(AND($A82&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A82,4))="FSS-",MID($A82,LEN($A82)-2,1)="/",ISNUMBER(VALUE(RIGHT($A82,2))),VALUE(MID($A82,5,LEN($A82)-7))&gt;=1,VALUE(MID($A82,5,LEN($A82)-7))=INT(VALUE(MID($A82,5,LEN($A82)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B82="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B82&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C82="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C82&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D82="","Nedostaje godište",IF($G82="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E82="","Nedostaje pol",IF($F82="","Nedostaje pojas",IF(COUNTA(I82:P82)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I82:P82&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G82),I82:P82)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G82,IF(AND(COUNTIF(I82:P82,"Fudokan sport kumite")&gt;0,Q82=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I82:P82,"Fudokan sport kumite")=0,Q82&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A82:$F82))+SUMPRODUCT(LEN(I82:P82))+LEN(Q82)=0,"",IF(AND($A82&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A82,4))="FSS-",MID($A82,LEN($A82)-2,1)="/",ISNUMBER(VALUE(RIGHT($A82,2))),VALUE(MID($A82,5,LEN($A82)-7))&gt;=1,VALUE(MID($A82,5,LEN($A82)-7))=INT(VALUE(MID($A82,5,LEN($A82)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A82&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A82&lt;&gt;"",$U82=0,$B82=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U82&gt;0,$V82=0,$B82=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U82)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B82="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B82&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C82="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C82&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D82="","Nedostaje godište",IF($G82="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E82="","Nedostaje pol",IF($F82="","Nedostaje pojas",IF(COUNTA(I82:P82)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I82:P82&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G82),I82:P82)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G82,IF(AND(COUNTIF(I82:P82,"Fudokan sport kumite")&gt;0,Q82=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I82:P82,"Fudokan sport kumite")=0,Q82&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S82">
@@ -3843,14 +5542,37 @@
         <f>IF(OR($G82="",$E82=""),"sve_kilaze","kg_"&amp;$G82&amp;"_"&amp;IF($E82="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="83" spans="1:20">
+      <c r="U82">
+        <f>IF($A82="",0,IFERROR(MATCH(TRIM($A82),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V82">
+        <f>IF($U82=0,0,IF(TRIM(INDEX(spisak_klub,$U82))=TRIM($B$4),$U82,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22">
       <c r="A83" s="5"/>
-      <c r="B83" s="5"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="5"/>
-      <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
+      <c r="B83" s="5">
+        <f>IF($V83=0,"",INDEX(spisak_ime,$V83)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C83" s="5">
+        <f>IF($V83=0,"",INDEX(spisak_prezime,$V83)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D83" s="5">
+        <f>IF($V83=0,"",INDEX(spisak_godiste,$V83))</f>
+        <v/>
+      </c>
+      <c r="E83" s="5">
+        <f>IF($V83=0,"",INDEX(spisak_pol,$V83)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F83" s="5">
+        <f>IF($V83=0,"",INDEX(spisak_pojas,$V83)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G83" s="7">
         <f>IF($D83="","",LOOKUP($D83,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3869,7 +5591,7 @@
       <c r="P83" s="5"/>
       <c r="Q83" s="5"/>
       <c r="R83" s="8">
-        <f>IF(COUNTA($A83:$F83,I83:P83,Q83)=0,"",IF(AND($A83&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A83,4))="FSS-",MID($A83,LEN($A83)-2,1)="/",ISNUMBER(VALUE(RIGHT($A83,2))),VALUE(MID($A83,5,LEN($A83)-7))&gt;=1,VALUE(MID($A83,5,LEN($A83)-7))=INT(VALUE(MID($A83,5,LEN($A83)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B83="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B83&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C83="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C83&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D83="","Nedostaje godište",IF($G83="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E83="","Nedostaje pol",IF($F83="","Nedostaje pojas",IF(COUNTA(I83:P83)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I83:P83&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G83),I83:P83)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G83,IF(AND(COUNTIF(I83:P83,"Fudokan sport kumite")&gt;0,Q83=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I83:P83,"Fudokan sport kumite")=0,Q83&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A83:$F83))+SUMPRODUCT(LEN(I83:P83))+LEN(Q83)=0,"",IF(AND($A83&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A83,4))="FSS-",MID($A83,LEN($A83)-2,1)="/",ISNUMBER(VALUE(RIGHT($A83,2))),VALUE(MID($A83,5,LEN($A83)-7))&gt;=1,VALUE(MID($A83,5,LEN($A83)-7))=INT(VALUE(MID($A83,5,LEN($A83)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A83&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A83&lt;&gt;"",$U83=0,$B83=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U83&gt;0,$V83=0,$B83=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U83)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B83="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B83&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C83="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C83&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D83="","Nedostaje godište",IF($G83="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E83="","Nedostaje pol",IF($F83="","Nedostaje pojas",IF(COUNTA(I83:P83)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I83:P83&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G83),I83:P83)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G83,IF(AND(COUNTIF(I83:P83,"Fudokan sport kumite")&gt;0,Q83=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I83:P83,"Fudokan sport kumite")=0,Q83&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S83">
@@ -3880,14 +5602,37 @@
         <f>IF(OR($G83="",$E83=""),"sve_kilaze","kg_"&amp;$G83&amp;"_"&amp;IF($E83="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="84" spans="1:20">
+      <c r="U83">
+        <f>IF($A83="",0,IFERROR(MATCH(TRIM($A83),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V83">
+        <f>IF($U83=0,0,IF(TRIM(INDEX(spisak_klub,$U83))=TRIM($B$4),$U83,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22">
       <c r="A84" s="5"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="5"/>
-      <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
+      <c r="B84" s="5">
+        <f>IF($V84=0,"",INDEX(spisak_ime,$V84)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C84" s="5">
+        <f>IF($V84=0,"",INDEX(spisak_prezime,$V84)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D84" s="5">
+        <f>IF($V84=0,"",INDEX(spisak_godiste,$V84))</f>
+        <v/>
+      </c>
+      <c r="E84" s="5">
+        <f>IF($V84=0,"",INDEX(spisak_pol,$V84)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F84" s="5">
+        <f>IF($V84=0,"",INDEX(spisak_pojas,$V84)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G84" s="7">
         <f>IF($D84="","",LOOKUP($D84,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3906,7 +5651,7 @@
       <c r="P84" s="5"/>
       <c r="Q84" s="5"/>
       <c r="R84" s="8">
-        <f>IF(COUNTA($A84:$F84,I84:P84,Q84)=0,"",IF(AND($A84&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A84,4))="FSS-",MID($A84,LEN($A84)-2,1)="/",ISNUMBER(VALUE(RIGHT($A84,2))),VALUE(MID($A84,5,LEN($A84)-7))&gt;=1,VALUE(MID($A84,5,LEN($A84)-7))=INT(VALUE(MID($A84,5,LEN($A84)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B84="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B84&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C84="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C84&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D84="","Nedostaje godište",IF($G84="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E84="","Nedostaje pol",IF($F84="","Nedostaje pojas",IF(COUNTA(I84:P84)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I84:P84&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G84),I84:P84)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G84,IF(AND(COUNTIF(I84:P84,"Fudokan sport kumite")&gt;0,Q84=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I84:P84,"Fudokan sport kumite")=0,Q84&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A84:$F84))+SUMPRODUCT(LEN(I84:P84))+LEN(Q84)=0,"",IF(AND($A84&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A84,4))="FSS-",MID($A84,LEN($A84)-2,1)="/",ISNUMBER(VALUE(RIGHT($A84,2))),VALUE(MID($A84,5,LEN($A84)-7))&gt;=1,VALUE(MID($A84,5,LEN($A84)-7))=INT(VALUE(MID($A84,5,LEN($A84)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A84&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A84&lt;&gt;"",$U84=0,$B84=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U84&gt;0,$V84=0,$B84=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U84)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B84="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B84&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C84="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C84&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D84="","Nedostaje godište",IF($G84="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E84="","Nedostaje pol",IF($F84="","Nedostaje pojas",IF(COUNTA(I84:P84)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I84:P84&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G84),I84:P84)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G84,IF(AND(COUNTIF(I84:P84,"Fudokan sport kumite")&gt;0,Q84=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I84:P84,"Fudokan sport kumite")=0,Q84&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S84">
@@ -3917,14 +5662,37 @@
         <f>IF(OR($G84="",$E84=""),"sve_kilaze","kg_"&amp;$G84&amp;"_"&amp;IF($E84="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="85" spans="1:20">
+      <c r="U84">
+        <f>IF($A84="",0,IFERROR(MATCH(TRIM($A84),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V84">
+        <f>IF($U84=0,0,IF(TRIM(INDEX(spisak_klub,$U84))=TRIM($B$4),$U84,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22">
       <c r="A85" s="5"/>
-      <c r="B85" s="5"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="5"/>
-      <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
+      <c r="B85" s="5">
+        <f>IF($V85=0,"",INDEX(spisak_ime,$V85)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C85" s="5">
+        <f>IF($V85=0,"",INDEX(spisak_prezime,$V85)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D85" s="5">
+        <f>IF($V85=0,"",INDEX(spisak_godiste,$V85))</f>
+        <v/>
+      </c>
+      <c r="E85" s="5">
+        <f>IF($V85=0,"",INDEX(spisak_pol,$V85)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F85" s="5">
+        <f>IF($V85=0,"",INDEX(spisak_pojas,$V85)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G85" s="7">
         <f>IF($D85="","",LOOKUP($D85,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3943,7 +5711,7 @@
       <c r="P85" s="5"/>
       <c r="Q85" s="5"/>
       <c r="R85" s="8">
-        <f>IF(COUNTA($A85:$F85,I85:P85,Q85)=0,"",IF(AND($A85&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A85,4))="FSS-",MID($A85,LEN($A85)-2,1)="/",ISNUMBER(VALUE(RIGHT($A85,2))),VALUE(MID($A85,5,LEN($A85)-7))&gt;=1,VALUE(MID($A85,5,LEN($A85)-7))=INT(VALUE(MID($A85,5,LEN($A85)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B85="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B85&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C85="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C85&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D85="","Nedostaje godište",IF($G85="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E85="","Nedostaje pol",IF($F85="","Nedostaje pojas",IF(COUNTA(I85:P85)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I85:P85&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G85),I85:P85)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G85,IF(AND(COUNTIF(I85:P85,"Fudokan sport kumite")&gt;0,Q85=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I85:P85,"Fudokan sport kumite")=0,Q85&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A85:$F85))+SUMPRODUCT(LEN(I85:P85))+LEN(Q85)=0,"",IF(AND($A85&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A85,4))="FSS-",MID($A85,LEN($A85)-2,1)="/",ISNUMBER(VALUE(RIGHT($A85,2))),VALUE(MID($A85,5,LEN($A85)-7))&gt;=1,VALUE(MID($A85,5,LEN($A85)-7))=INT(VALUE(MID($A85,5,LEN($A85)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A85&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A85&lt;&gt;"",$U85=0,$B85=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U85&gt;0,$V85=0,$B85=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U85)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B85="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B85&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C85="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C85&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D85="","Nedostaje godište",IF($G85="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E85="","Nedostaje pol",IF($F85="","Nedostaje pojas",IF(COUNTA(I85:P85)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I85:P85&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G85),I85:P85)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G85,IF(AND(COUNTIF(I85:P85,"Fudokan sport kumite")&gt;0,Q85=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I85:P85,"Fudokan sport kumite")=0,Q85&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S85">
@@ -3954,14 +5722,37 @@
         <f>IF(OR($G85="",$E85=""),"sve_kilaze","kg_"&amp;$G85&amp;"_"&amp;IF($E85="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="86" spans="1:20">
+      <c r="U85">
+        <f>IF($A85="",0,IFERROR(MATCH(TRIM($A85),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V85">
+        <f>IF($U85=0,0,IF(TRIM(INDEX(spisak_klub,$U85))=TRIM($B$4),$U85,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22">
       <c r="A86" s="5"/>
-      <c r="B86" s="5"/>
-      <c r="C86" s="5"/>
-      <c r="D86" s="5"/>
-      <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
+      <c r="B86" s="5">
+        <f>IF($V86=0,"",INDEX(spisak_ime,$V86)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C86" s="5">
+        <f>IF($V86=0,"",INDEX(spisak_prezime,$V86)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D86" s="5">
+        <f>IF($V86=0,"",INDEX(spisak_godiste,$V86))</f>
+        <v/>
+      </c>
+      <c r="E86" s="5">
+        <f>IF($V86=0,"",INDEX(spisak_pol,$V86)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F86" s="5">
+        <f>IF($V86=0,"",INDEX(spisak_pojas,$V86)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G86" s="7">
         <f>IF($D86="","",LOOKUP($D86,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -3980,7 +5771,7 @@
       <c r="P86" s="5"/>
       <c r="Q86" s="5"/>
       <c r="R86" s="8">
-        <f>IF(COUNTA($A86:$F86,I86:P86,Q86)=0,"",IF(AND($A86&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A86,4))="FSS-",MID($A86,LEN($A86)-2,1)="/",ISNUMBER(VALUE(RIGHT($A86,2))),VALUE(MID($A86,5,LEN($A86)-7))&gt;=1,VALUE(MID($A86,5,LEN($A86)-7))=INT(VALUE(MID($A86,5,LEN($A86)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B86="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B86&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C86="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C86&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D86="","Nedostaje godište",IF($G86="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E86="","Nedostaje pol",IF($F86="","Nedostaje pojas",IF(COUNTA(I86:P86)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I86:P86&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G86),I86:P86)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G86,IF(AND(COUNTIF(I86:P86,"Fudokan sport kumite")&gt;0,Q86=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I86:P86,"Fudokan sport kumite")=0,Q86&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A86:$F86))+SUMPRODUCT(LEN(I86:P86))+LEN(Q86)=0,"",IF(AND($A86&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A86,4))="FSS-",MID($A86,LEN($A86)-2,1)="/",ISNUMBER(VALUE(RIGHT($A86,2))),VALUE(MID($A86,5,LEN($A86)-7))&gt;=1,VALUE(MID($A86,5,LEN($A86)-7))=INT(VALUE(MID($A86,5,LEN($A86)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A86&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A86&lt;&gt;"",$U86=0,$B86=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U86&gt;0,$V86=0,$B86=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U86)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B86="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B86&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C86="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C86&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D86="","Nedostaje godište",IF($G86="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E86="","Nedostaje pol",IF($F86="","Nedostaje pojas",IF(COUNTA(I86:P86)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I86:P86&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G86),I86:P86)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G86,IF(AND(COUNTIF(I86:P86,"Fudokan sport kumite")&gt;0,Q86=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I86:P86,"Fudokan sport kumite")=0,Q86&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S86">
@@ -3991,14 +5782,37 @@
         <f>IF(OR($G86="",$E86=""),"sve_kilaze","kg_"&amp;$G86&amp;"_"&amp;IF($E86="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="87" spans="1:20">
+      <c r="U86">
+        <f>IF($A86="",0,IFERROR(MATCH(TRIM($A86),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V86">
+        <f>IF($U86=0,0,IF(TRIM(INDEX(spisak_klub,$U86))=TRIM($B$4),$U86,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22">
       <c r="A87" s="5"/>
-      <c r="B87" s="5"/>
-      <c r="C87" s="5"/>
-      <c r="D87" s="5"/>
-      <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
+      <c r="B87" s="5">
+        <f>IF($V87=0,"",INDEX(spisak_ime,$V87)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C87" s="5">
+        <f>IF($V87=0,"",INDEX(spisak_prezime,$V87)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D87" s="5">
+        <f>IF($V87=0,"",INDEX(spisak_godiste,$V87))</f>
+        <v/>
+      </c>
+      <c r="E87" s="5">
+        <f>IF($V87=0,"",INDEX(spisak_pol,$V87)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F87" s="5">
+        <f>IF($V87=0,"",INDEX(spisak_pojas,$V87)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G87" s="7">
         <f>IF($D87="","",LOOKUP($D87,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4017,7 +5831,7 @@
       <c r="P87" s="5"/>
       <c r="Q87" s="5"/>
       <c r="R87" s="8">
-        <f>IF(COUNTA($A87:$F87,I87:P87,Q87)=0,"",IF(AND($A87&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A87,4))="FSS-",MID($A87,LEN($A87)-2,1)="/",ISNUMBER(VALUE(RIGHT($A87,2))),VALUE(MID($A87,5,LEN($A87)-7))&gt;=1,VALUE(MID($A87,5,LEN($A87)-7))=INT(VALUE(MID($A87,5,LEN($A87)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B87="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B87&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C87="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C87&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D87="","Nedostaje godište",IF($G87="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E87="","Nedostaje pol",IF($F87="","Nedostaje pojas",IF(COUNTA(I87:P87)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I87:P87&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G87),I87:P87)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G87,IF(AND(COUNTIF(I87:P87,"Fudokan sport kumite")&gt;0,Q87=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I87:P87,"Fudokan sport kumite")=0,Q87&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A87:$F87))+SUMPRODUCT(LEN(I87:P87))+LEN(Q87)=0,"",IF(AND($A87&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A87,4))="FSS-",MID($A87,LEN($A87)-2,1)="/",ISNUMBER(VALUE(RIGHT($A87,2))),VALUE(MID($A87,5,LEN($A87)-7))&gt;=1,VALUE(MID($A87,5,LEN($A87)-7))=INT(VALUE(MID($A87,5,LEN($A87)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A87&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A87&lt;&gt;"",$U87=0,$B87=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U87&gt;0,$V87=0,$B87=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U87)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B87="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B87&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C87="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C87&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D87="","Nedostaje godište",IF($G87="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E87="","Nedostaje pol",IF($F87="","Nedostaje pojas",IF(COUNTA(I87:P87)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I87:P87&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G87),I87:P87)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G87,IF(AND(COUNTIF(I87:P87,"Fudokan sport kumite")&gt;0,Q87=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I87:P87,"Fudokan sport kumite")=0,Q87&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S87">
@@ -4028,14 +5842,37 @@
         <f>IF(OR($G87="",$E87=""),"sve_kilaze","kg_"&amp;$G87&amp;"_"&amp;IF($E87="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="88" spans="1:20">
+      <c r="U87">
+        <f>IF($A87="",0,IFERROR(MATCH(TRIM($A87),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V87">
+        <f>IF($U87=0,0,IF(TRIM(INDEX(spisak_klub,$U87))=TRIM($B$4),$U87,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22">
       <c r="A88" s="5"/>
-      <c r="B88" s="5"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="5"/>
-      <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
+      <c r="B88" s="5">
+        <f>IF($V88=0,"",INDEX(spisak_ime,$V88)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C88" s="5">
+        <f>IF($V88=0,"",INDEX(spisak_prezime,$V88)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D88" s="5">
+        <f>IF($V88=0,"",INDEX(spisak_godiste,$V88))</f>
+        <v/>
+      </c>
+      <c r="E88" s="5">
+        <f>IF($V88=0,"",INDEX(spisak_pol,$V88)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F88" s="5">
+        <f>IF($V88=0,"",INDEX(spisak_pojas,$V88)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G88" s="7">
         <f>IF($D88="","",LOOKUP($D88,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4054,7 +5891,7 @@
       <c r="P88" s="5"/>
       <c r="Q88" s="5"/>
       <c r="R88" s="8">
-        <f>IF(COUNTA($A88:$F88,I88:P88,Q88)=0,"",IF(AND($A88&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A88,4))="FSS-",MID($A88,LEN($A88)-2,1)="/",ISNUMBER(VALUE(RIGHT($A88,2))),VALUE(MID($A88,5,LEN($A88)-7))&gt;=1,VALUE(MID($A88,5,LEN($A88)-7))=INT(VALUE(MID($A88,5,LEN($A88)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B88="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B88&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C88="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C88&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D88="","Nedostaje godište",IF($G88="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E88="","Nedostaje pol",IF($F88="","Nedostaje pojas",IF(COUNTA(I88:P88)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I88:P88&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G88),I88:P88)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G88,IF(AND(COUNTIF(I88:P88,"Fudokan sport kumite")&gt;0,Q88=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I88:P88,"Fudokan sport kumite")=0,Q88&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A88:$F88))+SUMPRODUCT(LEN(I88:P88))+LEN(Q88)=0,"",IF(AND($A88&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A88,4))="FSS-",MID($A88,LEN($A88)-2,1)="/",ISNUMBER(VALUE(RIGHT($A88,2))),VALUE(MID($A88,5,LEN($A88)-7))&gt;=1,VALUE(MID($A88,5,LEN($A88)-7))=INT(VALUE(MID($A88,5,LEN($A88)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A88&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A88&lt;&gt;"",$U88=0,$B88=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U88&gt;0,$V88=0,$B88=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U88)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B88="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B88&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C88="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C88&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D88="","Nedostaje godište",IF($G88="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E88="","Nedostaje pol",IF($F88="","Nedostaje pojas",IF(COUNTA(I88:P88)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I88:P88&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G88),I88:P88)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G88,IF(AND(COUNTIF(I88:P88,"Fudokan sport kumite")&gt;0,Q88=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I88:P88,"Fudokan sport kumite")=0,Q88&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S88">
@@ -4065,14 +5902,37 @@
         <f>IF(OR($G88="",$E88=""),"sve_kilaze","kg_"&amp;$G88&amp;"_"&amp;IF($E88="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="89" spans="1:20">
+      <c r="U88">
+        <f>IF($A88="",0,IFERROR(MATCH(TRIM($A88),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V88">
+        <f>IF($U88=0,0,IF(TRIM(INDEX(spisak_klub,$U88))=TRIM($B$4),$U88,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22">
       <c r="A89" s="5"/>
-      <c r="B89" s="5"/>
-      <c r="C89" s="5"/>
-      <c r="D89" s="5"/>
-      <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
+      <c r="B89" s="5">
+        <f>IF($V89=0,"",INDEX(spisak_ime,$V89)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C89" s="5">
+        <f>IF($V89=0,"",INDEX(spisak_prezime,$V89)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D89" s="5">
+        <f>IF($V89=0,"",INDEX(spisak_godiste,$V89))</f>
+        <v/>
+      </c>
+      <c r="E89" s="5">
+        <f>IF($V89=0,"",INDEX(spisak_pol,$V89)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F89" s="5">
+        <f>IF($V89=0,"",INDEX(spisak_pojas,$V89)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G89" s="7">
         <f>IF($D89="","",LOOKUP($D89,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4091,7 +5951,7 @@
       <c r="P89" s="5"/>
       <c r="Q89" s="5"/>
       <c r="R89" s="8">
-        <f>IF(COUNTA($A89:$F89,I89:P89,Q89)=0,"",IF(AND($A89&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A89,4))="FSS-",MID($A89,LEN($A89)-2,1)="/",ISNUMBER(VALUE(RIGHT($A89,2))),VALUE(MID($A89,5,LEN($A89)-7))&gt;=1,VALUE(MID($A89,5,LEN($A89)-7))=INT(VALUE(MID($A89,5,LEN($A89)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B89="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B89&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C89="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C89&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D89="","Nedostaje godište",IF($G89="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E89="","Nedostaje pol",IF($F89="","Nedostaje pojas",IF(COUNTA(I89:P89)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I89:P89&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G89),I89:P89)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G89,IF(AND(COUNTIF(I89:P89,"Fudokan sport kumite")&gt;0,Q89=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I89:P89,"Fudokan sport kumite")=0,Q89&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A89:$F89))+SUMPRODUCT(LEN(I89:P89))+LEN(Q89)=0,"",IF(AND($A89&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A89,4))="FSS-",MID($A89,LEN($A89)-2,1)="/",ISNUMBER(VALUE(RIGHT($A89,2))),VALUE(MID($A89,5,LEN($A89)-7))&gt;=1,VALUE(MID($A89,5,LEN($A89)-7))=INT(VALUE(MID($A89,5,LEN($A89)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A89&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A89&lt;&gt;"",$U89=0,$B89=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U89&gt;0,$V89=0,$B89=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U89)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B89="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B89&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C89="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C89&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D89="","Nedostaje godište",IF($G89="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E89="","Nedostaje pol",IF($F89="","Nedostaje pojas",IF(COUNTA(I89:P89)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I89:P89&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G89),I89:P89)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G89,IF(AND(COUNTIF(I89:P89,"Fudokan sport kumite")&gt;0,Q89=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I89:P89,"Fudokan sport kumite")=0,Q89&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S89">
@@ -4102,14 +5962,37 @@
         <f>IF(OR($G89="",$E89=""),"sve_kilaze","kg_"&amp;$G89&amp;"_"&amp;IF($E89="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="90" spans="1:20">
+      <c r="U89">
+        <f>IF($A89="",0,IFERROR(MATCH(TRIM($A89),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V89">
+        <f>IF($U89=0,0,IF(TRIM(INDEX(spisak_klub,$U89))=TRIM($B$4),$U89,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22">
       <c r="A90" s="5"/>
-      <c r="B90" s="5"/>
-      <c r="C90" s="5"/>
-      <c r="D90" s="5"/>
-      <c r="E90" s="5"/>
-      <c r="F90" s="5"/>
+      <c r="B90" s="5">
+        <f>IF($V90=0,"",INDEX(spisak_ime,$V90)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C90" s="5">
+        <f>IF($V90=0,"",INDEX(spisak_prezime,$V90)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D90" s="5">
+        <f>IF($V90=0,"",INDEX(spisak_godiste,$V90))</f>
+        <v/>
+      </c>
+      <c r="E90" s="5">
+        <f>IF($V90=0,"",INDEX(spisak_pol,$V90)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F90" s="5">
+        <f>IF($V90=0,"",INDEX(spisak_pojas,$V90)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G90" s="7">
         <f>IF($D90="","",LOOKUP($D90,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4128,7 +6011,7 @@
       <c r="P90" s="5"/>
       <c r="Q90" s="5"/>
       <c r="R90" s="8">
-        <f>IF(COUNTA($A90:$F90,I90:P90,Q90)=0,"",IF(AND($A90&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A90,4))="FSS-",MID($A90,LEN($A90)-2,1)="/",ISNUMBER(VALUE(RIGHT($A90,2))),VALUE(MID($A90,5,LEN($A90)-7))&gt;=1,VALUE(MID($A90,5,LEN($A90)-7))=INT(VALUE(MID($A90,5,LEN($A90)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B90="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B90&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C90="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C90&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D90="","Nedostaje godište",IF($G90="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E90="","Nedostaje pol",IF($F90="","Nedostaje pojas",IF(COUNTA(I90:P90)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I90:P90&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G90),I90:P90)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G90,IF(AND(COUNTIF(I90:P90,"Fudokan sport kumite")&gt;0,Q90=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I90:P90,"Fudokan sport kumite")=0,Q90&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A90:$F90))+SUMPRODUCT(LEN(I90:P90))+LEN(Q90)=0,"",IF(AND($A90&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A90,4))="FSS-",MID($A90,LEN($A90)-2,1)="/",ISNUMBER(VALUE(RIGHT($A90,2))),VALUE(MID($A90,5,LEN($A90)-7))&gt;=1,VALUE(MID($A90,5,LEN($A90)-7))=INT(VALUE(MID($A90,5,LEN($A90)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A90&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A90&lt;&gt;"",$U90=0,$B90=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U90&gt;0,$V90=0,$B90=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U90)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B90="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B90&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C90="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C90&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D90="","Nedostaje godište",IF($G90="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E90="","Nedostaje pol",IF($F90="","Nedostaje pojas",IF(COUNTA(I90:P90)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I90:P90&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G90),I90:P90)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G90,IF(AND(COUNTIF(I90:P90,"Fudokan sport kumite")&gt;0,Q90=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I90:P90,"Fudokan sport kumite")=0,Q90&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S90">
@@ -4139,14 +6022,37 @@
         <f>IF(OR($G90="",$E90=""),"sve_kilaze","kg_"&amp;$G90&amp;"_"&amp;IF($E90="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="91" spans="1:20">
+      <c r="U90">
+        <f>IF($A90="",0,IFERROR(MATCH(TRIM($A90),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V90">
+        <f>IF($U90=0,0,IF(TRIM(INDEX(spisak_klub,$U90))=TRIM($B$4),$U90,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22">
       <c r="A91" s="5"/>
-      <c r="B91" s="5"/>
-      <c r="C91" s="5"/>
-      <c r="D91" s="5"/>
-      <c r="E91" s="5"/>
-      <c r="F91" s="5"/>
+      <c r="B91" s="5">
+        <f>IF($V91=0,"",INDEX(spisak_ime,$V91)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C91" s="5">
+        <f>IF($V91=0,"",INDEX(spisak_prezime,$V91)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D91" s="5">
+        <f>IF($V91=0,"",INDEX(spisak_godiste,$V91))</f>
+        <v/>
+      </c>
+      <c r="E91" s="5">
+        <f>IF($V91=0,"",INDEX(spisak_pol,$V91)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F91" s="5">
+        <f>IF($V91=0,"",INDEX(spisak_pojas,$V91)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G91" s="7">
         <f>IF($D91="","",LOOKUP($D91,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4165,7 +6071,7 @@
       <c r="P91" s="5"/>
       <c r="Q91" s="5"/>
       <c r="R91" s="8">
-        <f>IF(COUNTA($A91:$F91,I91:P91,Q91)=0,"",IF(AND($A91&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A91,4))="FSS-",MID($A91,LEN($A91)-2,1)="/",ISNUMBER(VALUE(RIGHT($A91,2))),VALUE(MID($A91,5,LEN($A91)-7))&gt;=1,VALUE(MID($A91,5,LEN($A91)-7))=INT(VALUE(MID($A91,5,LEN($A91)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B91="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B91&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C91="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C91&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D91="","Nedostaje godište",IF($G91="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E91="","Nedostaje pol",IF($F91="","Nedostaje pojas",IF(COUNTA(I91:P91)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I91:P91&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G91),I91:P91)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G91,IF(AND(COUNTIF(I91:P91,"Fudokan sport kumite")&gt;0,Q91=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I91:P91,"Fudokan sport kumite")=0,Q91&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A91:$F91))+SUMPRODUCT(LEN(I91:P91))+LEN(Q91)=0,"",IF(AND($A91&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A91,4))="FSS-",MID($A91,LEN($A91)-2,1)="/",ISNUMBER(VALUE(RIGHT($A91,2))),VALUE(MID($A91,5,LEN($A91)-7))&gt;=1,VALUE(MID($A91,5,LEN($A91)-7))=INT(VALUE(MID($A91,5,LEN($A91)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A91&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A91&lt;&gt;"",$U91=0,$B91=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U91&gt;0,$V91=0,$B91=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U91)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B91="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B91&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C91="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C91&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D91="","Nedostaje godište",IF($G91="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E91="","Nedostaje pol",IF($F91="","Nedostaje pojas",IF(COUNTA(I91:P91)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I91:P91&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G91),I91:P91)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G91,IF(AND(COUNTIF(I91:P91,"Fudokan sport kumite")&gt;0,Q91=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I91:P91,"Fudokan sport kumite")=0,Q91&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S91">
@@ -4176,14 +6082,37 @@
         <f>IF(OR($G91="",$E91=""),"sve_kilaze","kg_"&amp;$G91&amp;"_"&amp;IF($E91="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="92" spans="1:20">
+      <c r="U91">
+        <f>IF($A91="",0,IFERROR(MATCH(TRIM($A91),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V91">
+        <f>IF($U91=0,0,IF(TRIM(INDEX(spisak_klub,$U91))=TRIM($B$4),$U91,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22">
       <c r="A92" s="5"/>
-      <c r="B92" s="5"/>
-      <c r="C92" s="5"/>
-      <c r="D92" s="5"/>
-      <c r="E92" s="5"/>
-      <c r="F92" s="5"/>
+      <c r="B92" s="5">
+        <f>IF($V92=0,"",INDEX(spisak_ime,$V92)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C92" s="5">
+        <f>IF($V92=0,"",INDEX(spisak_prezime,$V92)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D92" s="5">
+        <f>IF($V92=0,"",INDEX(spisak_godiste,$V92))</f>
+        <v/>
+      </c>
+      <c r="E92" s="5">
+        <f>IF($V92=0,"",INDEX(spisak_pol,$V92)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F92" s="5">
+        <f>IF($V92=0,"",INDEX(spisak_pojas,$V92)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G92" s="7">
         <f>IF($D92="","",LOOKUP($D92,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4202,7 +6131,7 @@
       <c r="P92" s="5"/>
       <c r="Q92" s="5"/>
       <c r="R92" s="8">
-        <f>IF(COUNTA($A92:$F92,I92:P92,Q92)=0,"",IF(AND($A92&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A92,4))="FSS-",MID($A92,LEN($A92)-2,1)="/",ISNUMBER(VALUE(RIGHT($A92,2))),VALUE(MID($A92,5,LEN($A92)-7))&gt;=1,VALUE(MID($A92,5,LEN($A92)-7))=INT(VALUE(MID($A92,5,LEN($A92)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B92="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B92&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C92="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C92&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D92="","Nedostaje godište",IF($G92="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E92="","Nedostaje pol",IF($F92="","Nedostaje pojas",IF(COUNTA(I92:P92)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I92:P92&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G92),I92:P92)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G92,IF(AND(COUNTIF(I92:P92,"Fudokan sport kumite")&gt;0,Q92=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I92:P92,"Fudokan sport kumite")=0,Q92&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A92:$F92))+SUMPRODUCT(LEN(I92:P92))+LEN(Q92)=0,"",IF(AND($A92&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A92,4))="FSS-",MID($A92,LEN($A92)-2,1)="/",ISNUMBER(VALUE(RIGHT($A92,2))),VALUE(MID($A92,5,LEN($A92)-7))&gt;=1,VALUE(MID($A92,5,LEN($A92)-7))=INT(VALUE(MID($A92,5,LEN($A92)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A92&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A92&lt;&gt;"",$U92=0,$B92=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U92&gt;0,$V92=0,$B92=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U92)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B92="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B92&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C92="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C92&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D92="","Nedostaje godište",IF($G92="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E92="","Nedostaje pol",IF($F92="","Nedostaje pojas",IF(COUNTA(I92:P92)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I92:P92&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G92),I92:P92)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G92,IF(AND(COUNTIF(I92:P92,"Fudokan sport kumite")&gt;0,Q92=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I92:P92,"Fudokan sport kumite")=0,Q92&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S92">
@@ -4213,14 +6142,37 @@
         <f>IF(OR($G92="",$E92=""),"sve_kilaze","kg_"&amp;$G92&amp;"_"&amp;IF($E92="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="93" spans="1:20">
+      <c r="U92">
+        <f>IF($A92="",0,IFERROR(MATCH(TRIM($A92),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V92">
+        <f>IF($U92=0,0,IF(TRIM(INDEX(spisak_klub,$U92))=TRIM($B$4),$U92,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22">
       <c r="A93" s="5"/>
-      <c r="B93" s="5"/>
-      <c r="C93" s="5"/>
-      <c r="D93" s="5"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
+      <c r="B93" s="5">
+        <f>IF($V93=0,"",INDEX(spisak_ime,$V93)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C93" s="5">
+        <f>IF($V93=0,"",INDEX(spisak_prezime,$V93)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D93" s="5">
+        <f>IF($V93=0,"",INDEX(spisak_godiste,$V93))</f>
+        <v/>
+      </c>
+      <c r="E93" s="5">
+        <f>IF($V93=0,"",INDEX(spisak_pol,$V93)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F93" s="5">
+        <f>IF($V93=0,"",INDEX(spisak_pojas,$V93)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G93" s="7">
         <f>IF($D93="","",LOOKUP($D93,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4239,7 +6191,7 @@
       <c r="P93" s="5"/>
       <c r="Q93" s="5"/>
       <c r="R93" s="8">
-        <f>IF(COUNTA($A93:$F93,I93:P93,Q93)=0,"",IF(AND($A93&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A93,4))="FSS-",MID($A93,LEN($A93)-2,1)="/",ISNUMBER(VALUE(RIGHT($A93,2))),VALUE(MID($A93,5,LEN($A93)-7))&gt;=1,VALUE(MID($A93,5,LEN($A93)-7))=INT(VALUE(MID($A93,5,LEN($A93)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B93="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B93&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C93="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C93&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D93="","Nedostaje godište",IF($G93="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E93="","Nedostaje pol",IF($F93="","Nedostaje pojas",IF(COUNTA(I93:P93)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I93:P93&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G93),I93:P93)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G93,IF(AND(COUNTIF(I93:P93,"Fudokan sport kumite")&gt;0,Q93=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I93:P93,"Fudokan sport kumite")=0,Q93&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A93:$F93))+SUMPRODUCT(LEN(I93:P93))+LEN(Q93)=0,"",IF(AND($A93&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A93,4))="FSS-",MID($A93,LEN($A93)-2,1)="/",ISNUMBER(VALUE(RIGHT($A93,2))),VALUE(MID($A93,5,LEN($A93)-7))&gt;=1,VALUE(MID($A93,5,LEN($A93)-7))=INT(VALUE(MID($A93,5,LEN($A93)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A93&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A93&lt;&gt;"",$U93=0,$B93=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U93&gt;0,$V93=0,$B93=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U93)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B93="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B93&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C93="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C93&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D93="","Nedostaje godište",IF($G93="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E93="","Nedostaje pol",IF($F93="","Nedostaje pojas",IF(COUNTA(I93:P93)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I93:P93&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G93),I93:P93)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G93,IF(AND(COUNTIF(I93:P93,"Fudokan sport kumite")&gt;0,Q93=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I93:P93,"Fudokan sport kumite")=0,Q93&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S93">
@@ -4250,14 +6202,37 @@
         <f>IF(OR($G93="",$E93=""),"sve_kilaze","kg_"&amp;$G93&amp;"_"&amp;IF($E93="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="94" spans="1:20">
+      <c r="U93">
+        <f>IF($A93="",0,IFERROR(MATCH(TRIM($A93),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V93">
+        <f>IF($U93=0,0,IF(TRIM(INDEX(spisak_klub,$U93))=TRIM($B$4),$U93,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22">
       <c r="A94" s="5"/>
-      <c r="B94" s="5"/>
-      <c r="C94" s="5"/>
-      <c r="D94" s="5"/>
-      <c r="E94" s="5"/>
-      <c r="F94" s="5"/>
+      <c r="B94" s="5">
+        <f>IF($V94=0,"",INDEX(spisak_ime,$V94)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C94" s="5">
+        <f>IF($V94=0,"",INDEX(spisak_prezime,$V94)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D94" s="5">
+        <f>IF($V94=0,"",INDEX(spisak_godiste,$V94))</f>
+        <v/>
+      </c>
+      <c r="E94" s="5">
+        <f>IF($V94=0,"",INDEX(spisak_pol,$V94)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F94" s="5">
+        <f>IF($V94=0,"",INDEX(spisak_pojas,$V94)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G94" s="7">
         <f>IF($D94="","",LOOKUP($D94,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4276,7 +6251,7 @@
       <c r="P94" s="5"/>
       <c r="Q94" s="5"/>
       <c r="R94" s="8">
-        <f>IF(COUNTA($A94:$F94,I94:P94,Q94)=0,"",IF(AND($A94&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A94,4))="FSS-",MID($A94,LEN($A94)-2,1)="/",ISNUMBER(VALUE(RIGHT($A94,2))),VALUE(MID($A94,5,LEN($A94)-7))&gt;=1,VALUE(MID($A94,5,LEN($A94)-7))=INT(VALUE(MID($A94,5,LEN($A94)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B94="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B94&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C94="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C94&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D94="","Nedostaje godište",IF($G94="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E94="","Nedostaje pol",IF($F94="","Nedostaje pojas",IF(COUNTA(I94:P94)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I94:P94&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G94),I94:P94)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G94,IF(AND(COUNTIF(I94:P94,"Fudokan sport kumite")&gt;0,Q94=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I94:P94,"Fudokan sport kumite")=0,Q94&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A94:$F94))+SUMPRODUCT(LEN(I94:P94))+LEN(Q94)=0,"",IF(AND($A94&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A94,4))="FSS-",MID($A94,LEN($A94)-2,1)="/",ISNUMBER(VALUE(RIGHT($A94,2))),VALUE(MID($A94,5,LEN($A94)-7))&gt;=1,VALUE(MID($A94,5,LEN($A94)-7))=INT(VALUE(MID($A94,5,LEN($A94)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A94&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A94&lt;&gt;"",$U94=0,$B94=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U94&gt;0,$V94=0,$B94=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U94)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B94="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B94&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C94="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C94&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D94="","Nedostaje godište",IF($G94="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E94="","Nedostaje pol",IF($F94="","Nedostaje pojas",IF(COUNTA(I94:P94)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I94:P94&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G94),I94:P94)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G94,IF(AND(COUNTIF(I94:P94,"Fudokan sport kumite")&gt;0,Q94=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I94:P94,"Fudokan sport kumite")=0,Q94&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S94">
@@ -4287,14 +6262,37 @@
         <f>IF(OR($G94="",$E94=""),"sve_kilaze","kg_"&amp;$G94&amp;"_"&amp;IF($E94="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="95" spans="1:20">
+      <c r="U94">
+        <f>IF($A94="",0,IFERROR(MATCH(TRIM($A94),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V94">
+        <f>IF($U94=0,0,IF(TRIM(INDEX(spisak_klub,$U94))=TRIM($B$4),$U94,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22">
       <c r="A95" s="5"/>
-      <c r="B95" s="5"/>
-      <c r="C95" s="5"/>
-      <c r="D95" s="5"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
+      <c r="B95" s="5">
+        <f>IF($V95=0,"",INDEX(spisak_ime,$V95)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C95" s="5">
+        <f>IF($V95=0,"",INDEX(spisak_prezime,$V95)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D95" s="5">
+        <f>IF($V95=0,"",INDEX(spisak_godiste,$V95))</f>
+        <v/>
+      </c>
+      <c r="E95" s="5">
+        <f>IF($V95=0,"",INDEX(spisak_pol,$V95)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F95" s="5">
+        <f>IF($V95=0,"",INDEX(spisak_pojas,$V95)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G95" s="7">
         <f>IF($D95="","",LOOKUP($D95,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4313,7 +6311,7 @@
       <c r="P95" s="5"/>
       <c r="Q95" s="5"/>
       <c r="R95" s="8">
-        <f>IF(COUNTA($A95:$F95,I95:P95,Q95)=0,"",IF(AND($A95&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A95,4))="FSS-",MID($A95,LEN($A95)-2,1)="/",ISNUMBER(VALUE(RIGHT($A95,2))),VALUE(MID($A95,5,LEN($A95)-7))&gt;=1,VALUE(MID($A95,5,LEN($A95)-7))=INT(VALUE(MID($A95,5,LEN($A95)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B95="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B95&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C95="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C95&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D95="","Nedostaje godište",IF($G95="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E95="","Nedostaje pol",IF($F95="","Nedostaje pojas",IF(COUNTA(I95:P95)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I95:P95&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G95),I95:P95)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G95,IF(AND(COUNTIF(I95:P95,"Fudokan sport kumite")&gt;0,Q95=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I95:P95,"Fudokan sport kumite")=0,Q95&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A95:$F95))+SUMPRODUCT(LEN(I95:P95))+LEN(Q95)=0,"",IF(AND($A95&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A95,4))="FSS-",MID($A95,LEN($A95)-2,1)="/",ISNUMBER(VALUE(RIGHT($A95,2))),VALUE(MID($A95,5,LEN($A95)-7))&gt;=1,VALUE(MID($A95,5,LEN($A95)-7))=INT(VALUE(MID($A95,5,LEN($A95)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A95&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A95&lt;&gt;"",$U95=0,$B95=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U95&gt;0,$V95=0,$B95=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U95)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B95="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B95&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C95="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C95&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D95="","Nedostaje godište",IF($G95="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E95="","Nedostaje pol",IF($F95="","Nedostaje pojas",IF(COUNTA(I95:P95)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I95:P95&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G95),I95:P95)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G95,IF(AND(COUNTIF(I95:P95,"Fudokan sport kumite")&gt;0,Q95=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I95:P95,"Fudokan sport kumite")=0,Q95&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S95">
@@ -4324,14 +6322,37 @@
         <f>IF(OR($G95="",$E95=""),"sve_kilaze","kg_"&amp;$G95&amp;"_"&amp;IF($E95="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="96" spans="1:20">
+      <c r="U95">
+        <f>IF($A95="",0,IFERROR(MATCH(TRIM($A95),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V95">
+        <f>IF($U95=0,0,IF(TRIM(INDEX(spisak_klub,$U95))=TRIM($B$4),$U95,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22">
       <c r="A96" s="5"/>
-      <c r="B96" s="5"/>
-      <c r="C96" s="5"/>
-      <c r="D96" s="5"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="5"/>
+      <c r="B96" s="5">
+        <f>IF($V96=0,"",INDEX(spisak_ime,$V96)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C96" s="5">
+        <f>IF($V96=0,"",INDEX(spisak_prezime,$V96)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D96" s="5">
+        <f>IF($V96=0,"",INDEX(spisak_godiste,$V96))</f>
+        <v/>
+      </c>
+      <c r="E96" s="5">
+        <f>IF($V96=0,"",INDEX(spisak_pol,$V96)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F96" s="5">
+        <f>IF($V96=0,"",INDEX(spisak_pojas,$V96)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G96" s="7">
         <f>IF($D96="","",LOOKUP($D96,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4350,7 +6371,7 @@
       <c r="P96" s="5"/>
       <c r="Q96" s="5"/>
       <c r="R96" s="8">
-        <f>IF(COUNTA($A96:$F96,I96:P96,Q96)=0,"",IF(AND($A96&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A96,4))="FSS-",MID($A96,LEN($A96)-2,1)="/",ISNUMBER(VALUE(RIGHT($A96,2))),VALUE(MID($A96,5,LEN($A96)-7))&gt;=1,VALUE(MID($A96,5,LEN($A96)-7))=INT(VALUE(MID($A96,5,LEN($A96)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B96="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B96&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C96="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C96&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D96="","Nedostaje godište",IF($G96="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E96="","Nedostaje pol",IF($F96="","Nedostaje pojas",IF(COUNTA(I96:P96)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I96:P96&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G96),I96:P96)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G96,IF(AND(COUNTIF(I96:P96,"Fudokan sport kumite")&gt;0,Q96=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I96:P96,"Fudokan sport kumite")=0,Q96&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A96:$F96))+SUMPRODUCT(LEN(I96:P96))+LEN(Q96)=0,"",IF(AND($A96&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A96,4))="FSS-",MID($A96,LEN($A96)-2,1)="/",ISNUMBER(VALUE(RIGHT($A96,2))),VALUE(MID($A96,5,LEN($A96)-7))&gt;=1,VALUE(MID($A96,5,LEN($A96)-7))=INT(VALUE(MID($A96,5,LEN($A96)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A96&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A96&lt;&gt;"",$U96=0,$B96=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U96&gt;0,$V96=0,$B96=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U96)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B96="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B96&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C96="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C96&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D96="","Nedostaje godište",IF($G96="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E96="","Nedostaje pol",IF($F96="","Nedostaje pojas",IF(COUNTA(I96:P96)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I96:P96&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G96),I96:P96)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G96,IF(AND(COUNTIF(I96:P96,"Fudokan sport kumite")&gt;0,Q96=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I96:P96,"Fudokan sport kumite")=0,Q96&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S96">
@@ -4361,14 +6382,37 @@
         <f>IF(OR($G96="",$E96=""),"sve_kilaze","kg_"&amp;$G96&amp;"_"&amp;IF($E96="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="97" spans="1:20">
+      <c r="U96">
+        <f>IF($A96="",0,IFERROR(MATCH(TRIM($A96),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V96">
+        <f>IF($U96=0,0,IF(TRIM(INDEX(spisak_klub,$U96))=TRIM($B$4),$U96,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22">
       <c r="A97" s="5"/>
-      <c r="B97" s="5"/>
-      <c r="C97" s="5"/>
-      <c r="D97" s="5"/>
-      <c r="E97" s="5"/>
-      <c r="F97" s="5"/>
+      <c r="B97" s="5">
+        <f>IF($V97=0,"",INDEX(spisak_ime,$V97)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C97" s="5">
+        <f>IF($V97=0,"",INDEX(spisak_prezime,$V97)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D97" s="5">
+        <f>IF($V97=0,"",INDEX(spisak_godiste,$V97))</f>
+        <v/>
+      </c>
+      <c r="E97" s="5">
+        <f>IF($V97=0,"",INDEX(spisak_pol,$V97)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F97" s="5">
+        <f>IF($V97=0,"",INDEX(spisak_pojas,$V97)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G97" s="7">
         <f>IF($D97="","",LOOKUP($D97,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4387,7 +6431,7 @@
       <c r="P97" s="5"/>
       <c r="Q97" s="5"/>
       <c r="R97" s="8">
-        <f>IF(COUNTA($A97:$F97,I97:P97,Q97)=0,"",IF(AND($A97&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A97,4))="FSS-",MID($A97,LEN($A97)-2,1)="/",ISNUMBER(VALUE(RIGHT($A97,2))),VALUE(MID($A97,5,LEN($A97)-7))&gt;=1,VALUE(MID($A97,5,LEN($A97)-7))=INT(VALUE(MID($A97,5,LEN($A97)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B97="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B97&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C97="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C97&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D97="","Nedostaje godište",IF($G97="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E97="","Nedostaje pol",IF($F97="","Nedostaje pojas",IF(COUNTA(I97:P97)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I97:P97&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G97),I97:P97)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G97,IF(AND(COUNTIF(I97:P97,"Fudokan sport kumite")&gt;0,Q97=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I97:P97,"Fudokan sport kumite")=0,Q97&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A97:$F97))+SUMPRODUCT(LEN(I97:P97))+LEN(Q97)=0,"",IF(AND($A97&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A97,4))="FSS-",MID($A97,LEN($A97)-2,1)="/",ISNUMBER(VALUE(RIGHT($A97,2))),VALUE(MID($A97,5,LEN($A97)-7))&gt;=1,VALUE(MID($A97,5,LEN($A97)-7))=INT(VALUE(MID($A97,5,LEN($A97)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A97&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A97&lt;&gt;"",$U97=0,$B97=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U97&gt;0,$V97=0,$B97=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U97)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B97="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B97&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C97="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C97&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D97="","Nedostaje godište",IF($G97="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E97="","Nedostaje pol",IF($F97="","Nedostaje pojas",IF(COUNTA(I97:P97)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I97:P97&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G97),I97:P97)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G97,IF(AND(COUNTIF(I97:P97,"Fudokan sport kumite")&gt;0,Q97=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I97:P97,"Fudokan sport kumite")=0,Q97&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S97">
@@ -4398,14 +6442,37 @@
         <f>IF(OR($G97="",$E97=""),"sve_kilaze","kg_"&amp;$G97&amp;"_"&amp;IF($E97="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="98" spans="1:20">
+      <c r="U97">
+        <f>IF($A97="",0,IFERROR(MATCH(TRIM($A97),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V97">
+        <f>IF($U97=0,0,IF(TRIM(INDEX(spisak_klub,$U97))=TRIM($B$4),$U97,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22">
       <c r="A98" s="5"/>
-      <c r="B98" s="5"/>
-      <c r="C98" s="5"/>
-      <c r="D98" s="5"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
+      <c r="B98" s="5">
+        <f>IF($V98=0,"",INDEX(spisak_ime,$V98)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C98" s="5">
+        <f>IF($V98=0,"",INDEX(spisak_prezime,$V98)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D98" s="5">
+        <f>IF($V98=0,"",INDEX(spisak_godiste,$V98))</f>
+        <v/>
+      </c>
+      <c r="E98" s="5">
+        <f>IF($V98=0,"",INDEX(spisak_pol,$V98)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F98" s="5">
+        <f>IF($V98=0,"",INDEX(spisak_pojas,$V98)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G98" s="7">
         <f>IF($D98="","",LOOKUP($D98,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4424,7 +6491,7 @@
       <c r="P98" s="5"/>
       <c r="Q98" s="5"/>
       <c r="R98" s="8">
-        <f>IF(COUNTA($A98:$F98,I98:P98,Q98)=0,"",IF(AND($A98&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A98,4))="FSS-",MID($A98,LEN($A98)-2,1)="/",ISNUMBER(VALUE(RIGHT($A98,2))),VALUE(MID($A98,5,LEN($A98)-7))&gt;=1,VALUE(MID($A98,5,LEN($A98)-7))=INT(VALUE(MID($A98,5,LEN($A98)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B98="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B98&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C98="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C98&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D98="","Nedostaje godište",IF($G98="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E98="","Nedostaje pol",IF($F98="","Nedostaje pojas",IF(COUNTA(I98:P98)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I98:P98&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G98),I98:P98)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G98,IF(AND(COUNTIF(I98:P98,"Fudokan sport kumite")&gt;0,Q98=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I98:P98,"Fudokan sport kumite")=0,Q98&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A98:$F98))+SUMPRODUCT(LEN(I98:P98))+LEN(Q98)=0,"",IF(AND($A98&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A98,4))="FSS-",MID($A98,LEN($A98)-2,1)="/",ISNUMBER(VALUE(RIGHT($A98,2))),VALUE(MID($A98,5,LEN($A98)-7))&gt;=1,VALUE(MID($A98,5,LEN($A98)-7))=INT(VALUE(MID($A98,5,LEN($A98)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A98&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A98&lt;&gt;"",$U98=0,$B98=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U98&gt;0,$V98=0,$B98=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U98)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B98="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B98&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C98="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C98&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D98="","Nedostaje godište",IF($G98="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E98="","Nedostaje pol",IF($F98="","Nedostaje pojas",IF(COUNTA(I98:P98)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I98:P98&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G98),I98:P98)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G98,IF(AND(COUNTIF(I98:P98,"Fudokan sport kumite")&gt;0,Q98=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I98:P98,"Fudokan sport kumite")=0,Q98&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S98">
@@ -4435,14 +6502,37 @@
         <f>IF(OR($G98="",$E98=""),"sve_kilaze","kg_"&amp;$G98&amp;"_"&amp;IF($E98="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="99" spans="1:20">
+      <c r="U98">
+        <f>IF($A98="",0,IFERROR(MATCH(TRIM($A98),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V98">
+        <f>IF($U98=0,0,IF(TRIM(INDEX(spisak_klub,$U98))=TRIM($B$4),$U98,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:22">
       <c r="A99" s="5"/>
-      <c r="B99" s="5"/>
-      <c r="C99" s="5"/>
-      <c r="D99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
+      <c r="B99" s="5">
+        <f>IF($V99=0,"",INDEX(spisak_ime,$V99)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C99" s="5">
+        <f>IF($V99=0,"",INDEX(spisak_prezime,$V99)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D99" s="5">
+        <f>IF($V99=0,"",INDEX(spisak_godiste,$V99))</f>
+        <v/>
+      </c>
+      <c r="E99" s="5">
+        <f>IF($V99=0,"",INDEX(spisak_pol,$V99)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F99" s="5">
+        <f>IF($V99=0,"",INDEX(spisak_pojas,$V99)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G99" s="7">
         <f>IF($D99="","",LOOKUP($D99,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4461,7 +6551,7 @@
       <c r="P99" s="5"/>
       <c r="Q99" s="5"/>
       <c r="R99" s="8">
-        <f>IF(COUNTA($A99:$F99,I99:P99,Q99)=0,"",IF(AND($A99&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A99,4))="FSS-",MID($A99,LEN($A99)-2,1)="/",ISNUMBER(VALUE(RIGHT($A99,2))),VALUE(MID($A99,5,LEN($A99)-7))&gt;=1,VALUE(MID($A99,5,LEN($A99)-7))=INT(VALUE(MID($A99,5,LEN($A99)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B99="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B99&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C99="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C99&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D99="","Nedostaje godište",IF($G99="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E99="","Nedostaje pol",IF($F99="","Nedostaje pojas",IF(COUNTA(I99:P99)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I99:P99&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G99),I99:P99)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G99,IF(AND(COUNTIF(I99:P99,"Fudokan sport kumite")&gt;0,Q99=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I99:P99,"Fudokan sport kumite")=0,Q99&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A99:$F99))+SUMPRODUCT(LEN(I99:P99))+LEN(Q99)=0,"",IF(AND($A99&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A99,4))="FSS-",MID($A99,LEN($A99)-2,1)="/",ISNUMBER(VALUE(RIGHT($A99,2))),VALUE(MID($A99,5,LEN($A99)-7))&gt;=1,VALUE(MID($A99,5,LEN($A99)-7))=INT(VALUE(MID($A99,5,LEN($A99)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A99&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A99&lt;&gt;"",$U99=0,$B99=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U99&gt;0,$V99=0,$B99=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U99)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B99="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B99&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C99="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C99&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D99="","Nedostaje godište",IF($G99="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E99="","Nedostaje pol",IF($F99="","Nedostaje pojas",IF(COUNTA(I99:P99)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I99:P99&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G99),I99:P99)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G99,IF(AND(COUNTIF(I99:P99,"Fudokan sport kumite")&gt;0,Q99=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I99:P99,"Fudokan sport kumite")=0,Q99&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S99">
@@ -4472,14 +6562,37 @@
         <f>IF(OR($G99="",$E99=""),"sve_kilaze","kg_"&amp;$G99&amp;"_"&amp;IF($E99="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="100" spans="1:20">
+      <c r="U99">
+        <f>IF($A99="",0,IFERROR(MATCH(TRIM($A99),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V99">
+        <f>IF($U99=0,0,IF(TRIM(INDEX(spisak_klub,$U99))=TRIM($B$4),$U99,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22">
       <c r="A100" s="5"/>
-      <c r="B100" s="5"/>
-      <c r="C100" s="5"/>
-      <c r="D100" s="5"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="5"/>
+      <c r="B100" s="5">
+        <f>IF($V100=0,"",INDEX(spisak_ime,$V100)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C100" s="5">
+        <f>IF($V100=0,"",INDEX(spisak_prezime,$V100)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D100" s="5">
+        <f>IF($V100=0,"",INDEX(spisak_godiste,$V100))</f>
+        <v/>
+      </c>
+      <c r="E100" s="5">
+        <f>IF($V100=0,"",INDEX(spisak_pol,$V100)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F100" s="5">
+        <f>IF($V100=0,"",INDEX(spisak_pojas,$V100)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G100" s="7">
         <f>IF($D100="","",LOOKUP($D100,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4498,7 +6611,7 @@
       <c r="P100" s="5"/>
       <c r="Q100" s="5"/>
       <c r="R100" s="8">
-        <f>IF(COUNTA($A100:$F100,I100:P100,Q100)=0,"",IF(AND($A100&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A100,4))="FSS-",MID($A100,LEN($A100)-2,1)="/",ISNUMBER(VALUE(RIGHT($A100,2))),VALUE(MID($A100,5,LEN($A100)-7))&gt;=1,VALUE(MID($A100,5,LEN($A100)-7))=INT(VALUE(MID($A100,5,LEN($A100)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B100="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B100&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C100="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C100&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D100="","Nedostaje godište",IF($G100="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E100="","Nedostaje pol",IF($F100="","Nedostaje pojas",IF(COUNTA(I100:P100)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I100:P100&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G100),I100:P100)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G100,IF(AND(COUNTIF(I100:P100,"Fudokan sport kumite")&gt;0,Q100=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I100:P100,"Fudokan sport kumite")=0,Q100&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A100:$F100))+SUMPRODUCT(LEN(I100:P100))+LEN(Q100)=0,"",IF(AND($A100&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A100,4))="FSS-",MID($A100,LEN($A100)-2,1)="/",ISNUMBER(VALUE(RIGHT($A100,2))),VALUE(MID($A100,5,LEN($A100)-7))&gt;=1,VALUE(MID($A100,5,LEN($A100)-7))=INT(VALUE(MID($A100,5,LEN($A100)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A100&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A100&lt;&gt;"",$U100=0,$B100=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U100&gt;0,$V100=0,$B100=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U100)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B100="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B100&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C100="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C100&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D100="","Nedostaje godište",IF($G100="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E100="","Nedostaje pol",IF($F100="","Nedostaje pojas",IF(COUNTA(I100:P100)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I100:P100&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G100),I100:P100)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G100,IF(AND(COUNTIF(I100:P100,"Fudokan sport kumite")&gt;0,Q100=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I100:P100,"Fudokan sport kumite")=0,Q100&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S100">
@@ -4509,14 +6622,37 @@
         <f>IF(OR($G100="",$E100=""),"sve_kilaze","kg_"&amp;$G100&amp;"_"&amp;IF($E100="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="101" spans="1:20">
+      <c r="U100">
+        <f>IF($A100="",0,IFERROR(MATCH(TRIM($A100),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V100">
+        <f>IF($U100=0,0,IF(TRIM(INDEX(spisak_klub,$U100))=TRIM($B$4),$U100,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22">
       <c r="A101" s="5"/>
-      <c r="B101" s="5"/>
-      <c r="C101" s="5"/>
-      <c r="D101" s="5"/>
-      <c r="E101" s="5"/>
-      <c r="F101" s="5"/>
+      <c r="B101" s="5">
+        <f>IF($V101=0,"",INDEX(spisak_ime,$V101)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C101" s="5">
+        <f>IF($V101=0,"",INDEX(spisak_prezime,$V101)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D101" s="5">
+        <f>IF($V101=0,"",INDEX(spisak_godiste,$V101))</f>
+        <v/>
+      </c>
+      <c r="E101" s="5">
+        <f>IF($V101=0,"",INDEX(spisak_pol,$V101)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F101" s="5">
+        <f>IF($V101=0,"",INDEX(spisak_pojas,$V101)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G101" s="7">
         <f>IF($D101="","",LOOKUP($D101,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4535,7 +6671,7 @@
       <c r="P101" s="5"/>
       <c r="Q101" s="5"/>
       <c r="R101" s="8">
-        <f>IF(COUNTA($A101:$F101,I101:P101,Q101)=0,"",IF(AND($A101&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A101,4))="FSS-",MID($A101,LEN($A101)-2,1)="/",ISNUMBER(VALUE(RIGHT($A101,2))),VALUE(MID($A101,5,LEN($A101)-7))&gt;=1,VALUE(MID($A101,5,LEN($A101)-7))=INT(VALUE(MID($A101,5,LEN($A101)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B101="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B101&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C101="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C101&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D101="","Nedostaje godište",IF($G101="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E101="","Nedostaje pol",IF($F101="","Nedostaje pojas",IF(COUNTA(I101:P101)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I101:P101&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G101),I101:P101)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G101,IF(AND(COUNTIF(I101:P101,"Fudokan sport kumite")&gt;0,Q101=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I101:P101,"Fudokan sport kumite")=0,Q101&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A101:$F101))+SUMPRODUCT(LEN(I101:P101))+LEN(Q101)=0,"",IF(AND($A101&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A101,4))="FSS-",MID($A101,LEN($A101)-2,1)="/",ISNUMBER(VALUE(RIGHT($A101,2))),VALUE(MID($A101,5,LEN($A101)-7))&gt;=1,VALUE(MID($A101,5,LEN($A101)-7))=INT(VALUE(MID($A101,5,LEN($A101)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A101&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A101&lt;&gt;"",$U101=0,$B101=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U101&gt;0,$V101=0,$B101=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U101)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B101="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B101&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C101="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C101&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D101="","Nedostaje godište",IF($G101="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E101="","Nedostaje pol",IF($F101="","Nedostaje pojas",IF(COUNTA(I101:P101)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I101:P101&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G101),I101:P101)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G101,IF(AND(COUNTIF(I101:P101,"Fudokan sport kumite")&gt;0,Q101=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I101:P101,"Fudokan sport kumite")=0,Q101&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S101">
@@ -4546,14 +6682,37 @@
         <f>IF(OR($G101="",$E101=""),"sve_kilaze","kg_"&amp;$G101&amp;"_"&amp;IF($E101="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="102" spans="1:20">
+      <c r="U101">
+        <f>IF($A101="",0,IFERROR(MATCH(TRIM($A101),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V101">
+        <f>IF($U101=0,0,IF(TRIM(INDEX(spisak_klub,$U101))=TRIM($B$4),$U101,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:22">
       <c r="A102" s="5"/>
-      <c r="B102" s="5"/>
-      <c r="C102" s="5"/>
-      <c r="D102" s="5"/>
-      <c r="E102" s="5"/>
-      <c r="F102" s="5"/>
+      <c r="B102" s="5">
+        <f>IF($V102=0,"",INDEX(spisak_ime,$V102)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C102" s="5">
+        <f>IF($V102=0,"",INDEX(spisak_prezime,$V102)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D102" s="5">
+        <f>IF($V102=0,"",INDEX(spisak_godiste,$V102))</f>
+        <v/>
+      </c>
+      <c r="E102" s="5">
+        <f>IF($V102=0,"",INDEX(spisak_pol,$V102)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F102" s="5">
+        <f>IF($V102=0,"",INDEX(spisak_pojas,$V102)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G102" s="7">
         <f>IF($D102="","",LOOKUP($D102,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4572,7 +6731,7 @@
       <c r="P102" s="5"/>
       <c r="Q102" s="5"/>
       <c r="R102" s="8">
-        <f>IF(COUNTA($A102:$F102,I102:P102,Q102)=0,"",IF(AND($A102&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A102,4))="FSS-",MID($A102,LEN($A102)-2,1)="/",ISNUMBER(VALUE(RIGHT($A102,2))),VALUE(MID($A102,5,LEN($A102)-7))&gt;=1,VALUE(MID($A102,5,LEN($A102)-7))=INT(VALUE(MID($A102,5,LEN($A102)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B102="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B102&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C102="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C102&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D102="","Nedostaje godište",IF($G102="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E102="","Nedostaje pol",IF($F102="","Nedostaje pojas",IF(COUNTA(I102:P102)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I102:P102&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G102),I102:P102)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G102,IF(AND(COUNTIF(I102:P102,"Fudokan sport kumite")&gt;0,Q102=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I102:P102,"Fudokan sport kumite")=0,Q102&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A102:$F102))+SUMPRODUCT(LEN(I102:P102))+LEN(Q102)=0,"",IF(AND($A102&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A102,4))="FSS-",MID($A102,LEN($A102)-2,1)="/",ISNUMBER(VALUE(RIGHT($A102,2))),VALUE(MID($A102,5,LEN($A102)-7))&gt;=1,VALUE(MID($A102,5,LEN($A102)-7))=INT(VALUE(MID($A102,5,LEN($A102)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A102&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A102&lt;&gt;"",$U102=0,$B102=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U102&gt;0,$V102=0,$B102=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U102)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B102="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B102&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C102="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C102&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D102="","Nedostaje godište",IF($G102="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E102="","Nedostaje pol",IF($F102="","Nedostaje pojas",IF(COUNTA(I102:P102)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I102:P102&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G102),I102:P102)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G102,IF(AND(COUNTIF(I102:P102,"Fudokan sport kumite")&gt;0,Q102=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I102:P102,"Fudokan sport kumite")=0,Q102&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S102">
@@ -4583,14 +6742,37 @@
         <f>IF(OR($G102="",$E102=""),"sve_kilaze","kg_"&amp;$G102&amp;"_"&amp;IF($E102="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="103" spans="1:20">
+      <c r="U102">
+        <f>IF($A102="",0,IFERROR(MATCH(TRIM($A102),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V102">
+        <f>IF($U102=0,0,IF(TRIM(INDEX(spisak_klub,$U102))=TRIM($B$4),$U102,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22">
       <c r="A103" s="5"/>
-      <c r="B103" s="5"/>
-      <c r="C103" s="5"/>
-      <c r="D103" s="5"/>
-      <c r="E103" s="5"/>
-      <c r="F103" s="5"/>
+      <c r="B103" s="5">
+        <f>IF($V103=0,"",INDEX(spisak_ime,$V103)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C103" s="5">
+        <f>IF($V103=0,"",INDEX(spisak_prezime,$V103)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D103" s="5">
+        <f>IF($V103=0,"",INDEX(spisak_godiste,$V103))</f>
+        <v/>
+      </c>
+      <c r="E103" s="5">
+        <f>IF($V103=0,"",INDEX(spisak_pol,$V103)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F103" s="5">
+        <f>IF($V103=0,"",INDEX(spisak_pojas,$V103)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G103" s="7">
         <f>IF($D103="","",LOOKUP($D103,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4609,7 +6791,7 @@
       <c r="P103" s="5"/>
       <c r="Q103" s="5"/>
       <c r="R103" s="8">
-        <f>IF(COUNTA($A103:$F103,I103:P103,Q103)=0,"",IF(AND($A103&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A103,4))="FSS-",MID($A103,LEN($A103)-2,1)="/",ISNUMBER(VALUE(RIGHT($A103,2))),VALUE(MID($A103,5,LEN($A103)-7))&gt;=1,VALUE(MID($A103,5,LEN($A103)-7))=INT(VALUE(MID($A103,5,LEN($A103)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B103="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B103&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C103="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C103&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D103="","Nedostaje godište",IF($G103="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E103="","Nedostaje pol",IF($F103="","Nedostaje pojas",IF(COUNTA(I103:P103)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I103:P103&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G103),I103:P103)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G103,IF(AND(COUNTIF(I103:P103,"Fudokan sport kumite")&gt;0,Q103=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I103:P103,"Fudokan sport kumite")=0,Q103&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A103:$F103))+SUMPRODUCT(LEN(I103:P103))+LEN(Q103)=0,"",IF(AND($A103&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A103,4))="FSS-",MID($A103,LEN($A103)-2,1)="/",ISNUMBER(VALUE(RIGHT($A103,2))),VALUE(MID($A103,5,LEN($A103)-7))&gt;=1,VALUE(MID($A103,5,LEN($A103)-7))=INT(VALUE(MID($A103,5,LEN($A103)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A103&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A103&lt;&gt;"",$U103=0,$B103=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U103&gt;0,$V103=0,$B103=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U103)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B103="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B103&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C103="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C103&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D103="","Nedostaje godište",IF($G103="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E103="","Nedostaje pol",IF($F103="","Nedostaje pojas",IF(COUNTA(I103:P103)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I103:P103&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G103),I103:P103)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G103,IF(AND(COUNTIF(I103:P103,"Fudokan sport kumite")&gt;0,Q103=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I103:P103,"Fudokan sport kumite")=0,Q103&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S103">
@@ -4620,14 +6802,37 @@
         <f>IF(OR($G103="",$E103=""),"sve_kilaze","kg_"&amp;$G103&amp;"_"&amp;IF($E103="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="104" spans="1:20">
+      <c r="U103">
+        <f>IF($A103="",0,IFERROR(MATCH(TRIM($A103),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V103">
+        <f>IF($U103=0,0,IF(TRIM(INDEX(spisak_klub,$U103))=TRIM($B$4),$U103,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:22">
       <c r="A104" s="5"/>
-      <c r="B104" s="5"/>
-      <c r="C104" s="5"/>
-      <c r="D104" s="5"/>
-      <c r="E104" s="5"/>
-      <c r="F104" s="5"/>
+      <c r="B104" s="5">
+        <f>IF($V104=0,"",INDEX(spisak_ime,$V104)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C104" s="5">
+        <f>IF($V104=0,"",INDEX(spisak_prezime,$V104)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D104" s="5">
+        <f>IF($V104=0,"",INDEX(spisak_godiste,$V104))</f>
+        <v/>
+      </c>
+      <c r="E104" s="5">
+        <f>IF($V104=0,"",INDEX(spisak_pol,$V104)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F104" s="5">
+        <f>IF($V104=0,"",INDEX(spisak_pojas,$V104)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G104" s="7">
         <f>IF($D104="","",LOOKUP($D104,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4646,7 +6851,7 @@
       <c r="P104" s="5"/>
       <c r="Q104" s="5"/>
       <c r="R104" s="8">
-        <f>IF(COUNTA($A104:$F104,I104:P104,Q104)=0,"",IF(AND($A104&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A104,4))="FSS-",MID($A104,LEN($A104)-2,1)="/",ISNUMBER(VALUE(RIGHT($A104,2))),VALUE(MID($A104,5,LEN($A104)-7))&gt;=1,VALUE(MID($A104,5,LEN($A104)-7))=INT(VALUE(MID($A104,5,LEN($A104)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B104="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B104&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C104="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C104&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D104="","Nedostaje godište",IF($G104="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E104="","Nedostaje pol",IF($F104="","Nedostaje pojas",IF(COUNTA(I104:P104)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I104:P104&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G104),I104:P104)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G104,IF(AND(COUNTIF(I104:P104,"Fudokan sport kumite")&gt;0,Q104=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I104:P104,"Fudokan sport kumite")=0,Q104&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A104:$F104))+SUMPRODUCT(LEN(I104:P104))+LEN(Q104)=0,"",IF(AND($A104&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A104,4))="FSS-",MID($A104,LEN($A104)-2,1)="/",ISNUMBER(VALUE(RIGHT($A104,2))),VALUE(MID($A104,5,LEN($A104)-7))&gt;=1,VALUE(MID($A104,5,LEN($A104)-7))=INT(VALUE(MID($A104,5,LEN($A104)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A104&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A104&lt;&gt;"",$U104=0,$B104=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U104&gt;0,$V104=0,$B104=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U104)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B104="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B104&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C104="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C104&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D104="","Nedostaje godište",IF($G104="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E104="","Nedostaje pol",IF($F104="","Nedostaje pojas",IF(COUNTA(I104:P104)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I104:P104&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G104),I104:P104)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G104,IF(AND(COUNTIF(I104:P104,"Fudokan sport kumite")&gt;0,Q104=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I104:P104,"Fudokan sport kumite")=0,Q104&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S104">
@@ -4657,14 +6862,37 @@
         <f>IF(OR($G104="",$E104=""),"sve_kilaze","kg_"&amp;$G104&amp;"_"&amp;IF($E104="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="105" spans="1:20">
+      <c r="U104">
+        <f>IF($A104="",0,IFERROR(MATCH(TRIM($A104),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V104">
+        <f>IF($U104=0,0,IF(TRIM(INDEX(spisak_klub,$U104))=TRIM($B$4),$U104,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:22">
       <c r="A105" s="5"/>
-      <c r="B105" s="5"/>
-      <c r="C105" s="5"/>
-      <c r="D105" s="5"/>
-      <c r="E105" s="5"/>
-      <c r="F105" s="5"/>
+      <c r="B105" s="5">
+        <f>IF($V105=0,"",INDEX(spisak_ime,$V105)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C105" s="5">
+        <f>IF($V105=0,"",INDEX(spisak_prezime,$V105)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D105" s="5">
+        <f>IF($V105=0,"",INDEX(spisak_godiste,$V105))</f>
+        <v/>
+      </c>
+      <c r="E105" s="5">
+        <f>IF($V105=0,"",INDEX(spisak_pol,$V105)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F105" s="5">
+        <f>IF($V105=0,"",INDEX(spisak_pojas,$V105)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G105" s="7">
         <f>IF($D105="","",LOOKUP($D105,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4683,7 +6911,7 @@
       <c r="P105" s="5"/>
       <c r="Q105" s="5"/>
       <c r="R105" s="8">
-        <f>IF(COUNTA($A105:$F105,I105:P105,Q105)=0,"",IF(AND($A105&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A105,4))="FSS-",MID($A105,LEN($A105)-2,1)="/",ISNUMBER(VALUE(RIGHT($A105,2))),VALUE(MID($A105,5,LEN($A105)-7))&gt;=1,VALUE(MID($A105,5,LEN($A105)-7))=INT(VALUE(MID($A105,5,LEN($A105)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B105="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B105&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C105="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C105&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D105="","Nedostaje godište",IF($G105="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E105="","Nedostaje pol",IF($F105="","Nedostaje pojas",IF(COUNTA(I105:P105)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I105:P105&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G105),I105:P105)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G105,IF(AND(COUNTIF(I105:P105,"Fudokan sport kumite")&gt;0,Q105=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I105:P105,"Fudokan sport kumite")=0,Q105&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A105:$F105))+SUMPRODUCT(LEN(I105:P105))+LEN(Q105)=0,"",IF(AND($A105&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A105,4))="FSS-",MID($A105,LEN($A105)-2,1)="/",ISNUMBER(VALUE(RIGHT($A105,2))),VALUE(MID($A105,5,LEN($A105)-7))&gt;=1,VALUE(MID($A105,5,LEN($A105)-7))=INT(VALUE(MID($A105,5,LEN($A105)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A105&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A105&lt;&gt;"",$U105=0,$B105=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U105&gt;0,$V105=0,$B105=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U105)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B105="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B105&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C105="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C105&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D105="","Nedostaje godište",IF($G105="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E105="","Nedostaje pol",IF($F105="","Nedostaje pojas",IF(COUNTA(I105:P105)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I105:P105&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G105),I105:P105)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G105,IF(AND(COUNTIF(I105:P105,"Fudokan sport kumite")&gt;0,Q105=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I105:P105,"Fudokan sport kumite")=0,Q105&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S105">
@@ -4694,14 +6922,37 @@
         <f>IF(OR($G105="",$E105=""),"sve_kilaze","kg_"&amp;$G105&amp;"_"&amp;IF($E105="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="106" spans="1:20">
+      <c r="U105">
+        <f>IF($A105="",0,IFERROR(MATCH(TRIM($A105),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V105">
+        <f>IF($U105=0,0,IF(TRIM(INDEX(spisak_klub,$U105))=TRIM($B$4),$U105,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:22">
       <c r="A106" s="5"/>
-      <c r="B106" s="5"/>
-      <c r="C106" s="5"/>
-      <c r="D106" s="5"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
+      <c r="B106" s="5">
+        <f>IF($V106=0,"",INDEX(spisak_ime,$V106)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C106" s="5">
+        <f>IF($V106=0,"",INDEX(spisak_prezime,$V106)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D106" s="5">
+        <f>IF($V106=0,"",INDEX(spisak_godiste,$V106))</f>
+        <v/>
+      </c>
+      <c r="E106" s="5">
+        <f>IF($V106=0,"",INDEX(spisak_pol,$V106)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F106" s="5">
+        <f>IF($V106=0,"",INDEX(spisak_pojas,$V106)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G106" s="7">
         <f>IF($D106="","",LOOKUP($D106,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4720,7 +6971,7 @@
       <c r="P106" s="5"/>
       <c r="Q106" s="5"/>
       <c r="R106" s="8">
-        <f>IF(COUNTA($A106:$F106,I106:P106,Q106)=0,"",IF(AND($A106&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A106,4))="FSS-",MID($A106,LEN($A106)-2,1)="/",ISNUMBER(VALUE(RIGHT($A106,2))),VALUE(MID($A106,5,LEN($A106)-7))&gt;=1,VALUE(MID($A106,5,LEN($A106)-7))=INT(VALUE(MID($A106,5,LEN($A106)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B106="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B106&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C106="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C106&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D106="","Nedostaje godište",IF($G106="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E106="","Nedostaje pol",IF($F106="","Nedostaje pojas",IF(COUNTA(I106:P106)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I106:P106&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G106),I106:P106)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G106,IF(AND(COUNTIF(I106:P106,"Fudokan sport kumite")&gt;0,Q106=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I106:P106,"Fudokan sport kumite")=0,Q106&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A106:$F106))+SUMPRODUCT(LEN(I106:P106))+LEN(Q106)=0,"",IF(AND($A106&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A106,4))="FSS-",MID($A106,LEN($A106)-2,1)="/",ISNUMBER(VALUE(RIGHT($A106,2))),VALUE(MID($A106,5,LEN($A106)-7))&gt;=1,VALUE(MID($A106,5,LEN($A106)-7))=INT(VALUE(MID($A106,5,LEN($A106)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A106&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A106&lt;&gt;"",$U106=0,$B106=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U106&gt;0,$V106=0,$B106=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U106)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B106="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B106&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C106="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C106&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D106="","Nedostaje godište",IF($G106="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E106="","Nedostaje pol",IF($F106="","Nedostaje pojas",IF(COUNTA(I106:P106)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I106:P106&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G106),I106:P106)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G106,IF(AND(COUNTIF(I106:P106,"Fudokan sport kumite")&gt;0,Q106=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I106:P106,"Fudokan sport kumite")=0,Q106&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S106">
@@ -4731,14 +6982,37 @@
         <f>IF(OR($G106="",$E106=""),"sve_kilaze","kg_"&amp;$G106&amp;"_"&amp;IF($E106="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="107" spans="1:20">
+      <c r="U106">
+        <f>IF($A106="",0,IFERROR(MATCH(TRIM($A106),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V106">
+        <f>IF($U106=0,0,IF(TRIM(INDEX(spisak_klub,$U106))=TRIM($B$4),$U106,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:22">
       <c r="A107" s="5"/>
-      <c r="B107" s="5"/>
-      <c r="C107" s="5"/>
-      <c r="D107" s="5"/>
-      <c r="E107" s="5"/>
-      <c r="F107" s="5"/>
+      <c r="B107" s="5">
+        <f>IF($V107=0,"",INDEX(spisak_ime,$V107)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C107" s="5">
+        <f>IF($V107=0,"",INDEX(spisak_prezime,$V107)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D107" s="5">
+        <f>IF($V107=0,"",INDEX(spisak_godiste,$V107))</f>
+        <v/>
+      </c>
+      <c r="E107" s="5">
+        <f>IF($V107=0,"",INDEX(spisak_pol,$V107)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F107" s="5">
+        <f>IF($V107=0,"",INDEX(spisak_pojas,$V107)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G107" s="7">
         <f>IF($D107="","",LOOKUP($D107,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4757,7 +7031,7 @@
       <c r="P107" s="5"/>
       <c r="Q107" s="5"/>
       <c r="R107" s="8">
-        <f>IF(COUNTA($A107:$F107,I107:P107,Q107)=0,"",IF(AND($A107&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A107,4))="FSS-",MID($A107,LEN($A107)-2,1)="/",ISNUMBER(VALUE(RIGHT($A107,2))),VALUE(MID($A107,5,LEN($A107)-7))&gt;=1,VALUE(MID($A107,5,LEN($A107)-7))=INT(VALUE(MID($A107,5,LEN($A107)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B107="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B107&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C107="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C107&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D107="","Nedostaje godište",IF($G107="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E107="","Nedostaje pol",IF($F107="","Nedostaje pojas",IF(COUNTA(I107:P107)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I107:P107&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G107),I107:P107)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G107,IF(AND(COUNTIF(I107:P107,"Fudokan sport kumite")&gt;0,Q107=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I107:P107,"Fudokan sport kumite")=0,Q107&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A107:$F107))+SUMPRODUCT(LEN(I107:P107))+LEN(Q107)=0,"",IF(AND($A107&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A107,4))="FSS-",MID($A107,LEN($A107)-2,1)="/",ISNUMBER(VALUE(RIGHT($A107,2))),VALUE(MID($A107,5,LEN($A107)-7))&gt;=1,VALUE(MID($A107,5,LEN($A107)-7))=INT(VALUE(MID($A107,5,LEN($A107)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A107&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A107&lt;&gt;"",$U107=0,$B107=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U107&gt;0,$V107=0,$B107=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U107)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B107="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B107&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C107="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C107&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D107="","Nedostaje godište",IF($G107="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E107="","Nedostaje pol",IF($F107="","Nedostaje pojas",IF(COUNTA(I107:P107)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I107:P107&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G107),I107:P107)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G107,IF(AND(COUNTIF(I107:P107,"Fudokan sport kumite")&gt;0,Q107=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I107:P107,"Fudokan sport kumite")=0,Q107&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S107">
@@ -4768,14 +7042,37 @@
         <f>IF(OR($G107="",$E107=""),"sve_kilaze","kg_"&amp;$G107&amp;"_"&amp;IF($E107="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="108" spans="1:20">
+      <c r="U107">
+        <f>IF($A107="",0,IFERROR(MATCH(TRIM($A107),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V107">
+        <f>IF($U107=0,0,IF(TRIM(INDEX(spisak_klub,$U107))=TRIM($B$4),$U107,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:22">
       <c r="A108" s="5"/>
-      <c r="B108" s="5"/>
-      <c r="C108" s="5"/>
-      <c r="D108" s="5"/>
-      <c r="E108" s="5"/>
-      <c r="F108" s="5"/>
+      <c r="B108" s="5">
+        <f>IF($V108=0,"",INDEX(spisak_ime,$V108)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C108" s="5">
+        <f>IF($V108=0,"",INDEX(spisak_prezime,$V108)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D108" s="5">
+        <f>IF($V108=0,"",INDEX(spisak_godiste,$V108))</f>
+        <v/>
+      </c>
+      <c r="E108" s="5">
+        <f>IF($V108=0,"",INDEX(spisak_pol,$V108)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F108" s="5">
+        <f>IF($V108=0,"",INDEX(spisak_pojas,$V108)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G108" s="7">
         <f>IF($D108="","",LOOKUP($D108,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4794,7 +7091,7 @@
       <c r="P108" s="5"/>
       <c r="Q108" s="5"/>
       <c r="R108" s="8">
-        <f>IF(COUNTA($A108:$F108,I108:P108,Q108)=0,"",IF(AND($A108&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A108,4))="FSS-",MID($A108,LEN($A108)-2,1)="/",ISNUMBER(VALUE(RIGHT($A108,2))),VALUE(MID($A108,5,LEN($A108)-7))&gt;=1,VALUE(MID($A108,5,LEN($A108)-7))=INT(VALUE(MID($A108,5,LEN($A108)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B108="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B108&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C108="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C108&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D108="","Nedostaje godište",IF($G108="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E108="","Nedostaje pol",IF($F108="","Nedostaje pojas",IF(COUNTA(I108:P108)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I108:P108&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G108),I108:P108)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G108,IF(AND(COUNTIF(I108:P108,"Fudokan sport kumite")&gt;0,Q108=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I108:P108,"Fudokan sport kumite")=0,Q108&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A108:$F108))+SUMPRODUCT(LEN(I108:P108))+LEN(Q108)=0,"",IF(AND($A108&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A108,4))="FSS-",MID($A108,LEN($A108)-2,1)="/",ISNUMBER(VALUE(RIGHT($A108,2))),VALUE(MID($A108,5,LEN($A108)-7))&gt;=1,VALUE(MID($A108,5,LEN($A108)-7))=INT(VALUE(MID($A108,5,LEN($A108)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A108&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A108&lt;&gt;"",$U108=0,$B108=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U108&gt;0,$V108=0,$B108=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U108)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B108="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B108&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C108="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C108&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D108="","Nedostaje godište",IF($G108="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E108="","Nedostaje pol",IF($F108="","Nedostaje pojas",IF(COUNTA(I108:P108)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I108:P108&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G108),I108:P108)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G108,IF(AND(COUNTIF(I108:P108,"Fudokan sport kumite")&gt;0,Q108=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I108:P108,"Fudokan sport kumite")=0,Q108&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S108">
@@ -4805,14 +7102,37 @@
         <f>IF(OR($G108="",$E108=""),"sve_kilaze","kg_"&amp;$G108&amp;"_"&amp;IF($E108="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="109" spans="1:20">
+      <c r="U108">
+        <f>IF($A108="",0,IFERROR(MATCH(TRIM($A108),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V108">
+        <f>IF($U108=0,0,IF(TRIM(INDEX(spisak_klub,$U108))=TRIM($B$4),$U108,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:22">
       <c r="A109" s="5"/>
-      <c r="B109" s="5"/>
-      <c r="C109" s="5"/>
-      <c r="D109" s="5"/>
-      <c r="E109" s="5"/>
-      <c r="F109" s="5"/>
+      <c r="B109" s="5">
+        <f>IF($V109=0,"",INDEX(spisak_ime,$V109)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C109" s="5">
+        <f>IF($V109=0,"",INDEX(spisak_prezime,$V109)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D109" s="5">
+        <f>IF($V109=0,"",INDEX(spisak_godiste,$V109))</f>
+        <v/>
+      </c>
+      <c r="E109" s="5">
+        <f>IF($V109=0,"",INDEX(spisak_pol,$V109)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F109" s="5">
+        <f>IF($V109=0,"",INDEX(spisak_pojas,$V109)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G109" s="7">
         <f>IF($D109="","",LOOKUP($D109,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4831,7 +7151,7 @@
       <c r="P109" s="5"/>
       <c r="Q109" s="5"/>
       <c r="R109" s="8">
-        <f>IF(COUNTA($A109:$F109,I109:P109,Q109)=0,"",IF(AND($A109&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A109,4))="FSS-",MID($A109,LEN($A109)-2,1)="/",ISNUMBER(VALUE(RIGHT($A109,2))),VALUE(MID($A109,5,LEN($A109)-7))&gt;=1,VALUE(MID($A109,5,LEN($A109)-7))=INT(VALUE(MID($A109,5,LEN($A109)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B109="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B109&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C109="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C109&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D109="","Nedostaje godište",IF($G109="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E109="","Nedostaje pol",IF($F109="","Nedostaje pojas",IF(COUNTA(I109:P109)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I109:P109&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G109),I109:P109)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G109,IF(AND(COUNTIF(I109:P109,"Fudokan sport kumite")&gt;0,Q109=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I109:P109,"Fudokan sport kumite")=0,Q109&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A109:$F109))+SUMPRODUCT(LEN(I109:P109))+LEN(Q109)=0,"",IF(AND($A109&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A109,4))="FSS-",MID($A109,LEN($A109)-2,1)="/",ISNUMBER(VALUE(RIGHT($A109,2))),VALUE(MID($A109,5,LEN($A109)-7))&gt;=1,VALUE(MID($A109,5,LEN($A109)-7))=INT(VALUE(MID($A109,5,LEN($A109)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A109&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A109&lt;&gt;"",$U109=0,$B109=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U109&gt;0,$V109=0,$B109=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U109)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B109="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B109&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C109="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C109&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D109="","Nedostaje godište",IF($G109="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E109="","Nedostaje pol",IF($F109="","Nedostaje pojas",IF(COUNTA(I109:P109)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I109:P109&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G109),I109:P109)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G109,IF(AND(COUNTIF(I109:P109,"Fudokan sport kumite")&gt;0,Q109=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I109:P109,"Fudokan sport kumite")=0,Q109&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S109">
@@ -4842,14 +7162,37 @@
         <f>IF(OR($G109="",$E109=""),"sve_kilaze","kg_"&amp;$G109&amp;"_"&amp;IF($E109="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="110" spans="1:20">
+      <c r="U109">
+        <f>IF($A109="",0,IFERROR(MATCH(TRIM($A109),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V109">
+        <f>IF($U109=0,0,IF(TRIM(INDEX(spisak_klub,$U109))=TRIM($B$4),$U109,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:22">
       <c r="A110" s="5"/>
-      <c r="B110" s="5"/>
-      <c r="C110" s="5"/>
-      <c r="D110" s="5"/>
-      <c r="E110" s="5"/>
-      <c r="F110" s="5"/>
+      <c r="B110" s="5">
+        <f>IF($V110=0,"",INDEX(spisak_ime,$V110)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C110" s="5">
+        <f>IF($V110=0,"",INDEX(spisak_prezime,$V110)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D110" s="5">
+        <f>IF($V110=0,"",INDEX(spisak_godiste,$V110))</f>
+        <v/>
+      </c>
+      <c r="E110" s="5">
+        <f>IF($V110=0,"",INDEX(spisak_pol,$V110)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F110" s="5">
+        <f>IF($V110=0,"",INDEX(spisak_pojas,$V110)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G110" s="7">
         <f>IF($D110="","",LOOKUP($D110,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4868,7 +7211,7 @@
       <c r="P110" s="5"/>
       <c r="Q110" s="5"/>
       <c r="R110" s="8">
-        <f>IF(COUNTA($A110:$F110,I110:P110,Q110)=0,"",IF(AND($A110&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A110,4))="FSS-",MID($A110,LEN($A110)-2,1)="/",ISNUMBER(VALUE(RIGHT($A110,2))),VALUE(MID($A110,5,LEN($A110)-7))&gt;=1,VALUE(MID($A110,5,LEN($A110)-7))=INT(VALUE(MID($A110,5,LEN($A110)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B110="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B110&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C110="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C110&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D110="","Nedostaje godište",IF($G110="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E110="","Nedostaje pol",IF($F110="","Nedostaje pojas",IF(COUNTA(I110:P110)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I110:P110&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G110),I110:P110)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G110,IF(AND(COUNTIF(I110:P110,"Fudokan sport kumite")&gt;0,Q110=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I110:P110,"Fudokan sport kumite")=0,Q110&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A110:$F110))+SUMPRODUCT(LEN(I110:P110))+LEN(Q110)=0,"",IF(AND($A110&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A110,4))="FSS-",MID($A110,LEN($A110)-2,1)="/",ISNUMBER(VALUE(RIGHT($A110,2))),VALUE(MID($A110,5,LEN($A110)-7))&gt;=1,VALUE(MID($A110,5,LEN($A110)-7))=INT(VALUE(MID($A110,5,LEN($A110)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A110&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A110&lt;&gt;"",$U110=0,$B110=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U110&gt;0,$V110=0,$B110=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U110)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B110="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B110&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C110="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C110&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D110="","Nedostaje godište",IF($G110="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E110="","Nedostaje pol",IF($F110="","Nedostaje pojas",IF(COUNTA(I110:P110)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I110:P110&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G110),I110:P110)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G110,IF(AND(COUNTIF(I110:P110,"Fudokan sport kumite")&gt;0,Q110=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I110:P110,"Fudokan sport kumite")=0,Q110&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S110">
@@ -4879,14 +7222,37 @@
         <f>IF(OR($G110="",$E110=""),"sve_kilaze","kg_"&amp;$G110&amp;"_"&amp;IF($E110="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="111" spans="1:20">
+      <c r="U110">
+        <f>IF($A110="",0,IFERROR(MATCH(TRIM($A110),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V110">
+        <f>IF($U110=0,0,IF(TRIM(INDEX(spisak_klub,$U110))=TRIM($B$4),$U110,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:22">
       <c r="A111" s="5"/>
-      <c r="B111" s="5"/>
-      <c r="C111" s="5"/>
-      <c r="D111" s="5"/>
-      <c r="E111" s="5"/>
-      <c r="F111" s="5"/>
+      <c r="B111" s="5">
+        <f>IF($V111=0,"",INDEX(spisak_ime,$V111)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C111" s="5">
+        <f>IF($V111=0,"",INDEX(spisak_prezime,$V111)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D111" s="5">
+        <f>IF($V111=0,"",INDEX(spisak_godiste,$V111))</f>
+        <v/>
+      </c>
+      <c r="E111" s="5">
+        <f>IF($V111=0,"",INDEX(spisak_pol,$V111)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F111" s="5">
+        <f>IF($V111=0,"",INDEX(spisak_pojas,$V111)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G111" s="7">
         <f>IF($D111="","",LOOKUP($D111,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4905,7 +7271,7 @@
       <c r="P111" s="5"/>
       <c r="Q111" s="5"/>
       <c r="R111" s="8">
-        <f>IF(COUNTA($A111:$F111,I111:P111,Q111)=0,"",IF(AND($A111&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A111,4))="FSS-",MID($A111,LEN($A111)-2,1)="/",ISNUMBER(VALUE(RIGHT($A111,2))),VALUE(MID($A111,5,LEN($A111)-7))&gt;=1,VALUE(MID($A111,5,LEN($A111)-7))=INT(VALUE(MID($A111,5,LEN($A111)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B111="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B111&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C111="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C111&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D111="","Nedostaje godište",IF($G111="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E111="","Nedostaje pol",IF($F111="","Nedostaje pojas",IF(COUNTA(I111:P111)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I111:P111&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G111),I111:P111)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G111,IF(AND(COUNTIF(I111:P111,"Fudokan sport kumite")&gt;0,Q111=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I111:P111,"Fudokan sport kumite")=0,Q111&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A111:$F111))+SUMPRODUCT(LEN(I111:P111))+LEN(Q111)=0,"",IF(AND($A111&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A111,4))="FSS-",MID($A111,LEN($A111)-2,1)="/",ISNUMBER(VALUE(RIGHT($A111,2))),VALUE(MID($A111,5,LEN($A111)-7))&gt;=1,VALUE(MID($A111,5,LEN($A111)-7))=INT(VALUE(MID($A111,5,LEN($A111)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A111&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A111&lt;&gt;"",$U111=0,$B111=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U111&gt;0,$V111=0,$B111=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U111)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B111="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B111&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C111="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C111&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D111="","Nedostaje godište",IF($G111="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E111="","Nedostaje pol",IF($F111="","Nedostaje pojas",IF(COUNTA(I111:P111)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I111:P111&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G111),I111:P111)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G111,IF(AND(COUNTIF(I111:P111,"Fudokan sport kumite")&gt;0,Q111=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I111:P111,"Fudokan sport kumite")=0,Q111&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S111">
@@ -4916,14 +7282,37 @@
         <f>IF(OR($G111="",$E111=""),"sve_kilaze","kg_"&amp;$G111&amp;"_"&amp;IF($E111="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="112" spans="1:20">
+      <c r="U111">
+        <f>IF($A111="",0,IFERROR(MATCH(TRIM($A111),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V111">
+        <f>IF($U111=0,0,IF(TRIM(INDEX(spisak_klub,$U111))=TRIM($B$4),$U111,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:22">
       <c r="A112" s="5"/>
-      <c r="B112" s="5"/>
-      <c r="C112" s="5"/>
-      <c r="D112" s="5"/>
-      <c r="E112" s="5"/>
-      <c r="F112" s="5"/>
+      <c r="B112" s="5">
+        <f>IF($V112=0,"",INDEX(spisak_ime,$V112)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C112" s="5">
+        <f>IF($V112=0,"",INDEX(spisak_prezime,$V112)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D112" s="5">
+        <f>IF($V112=0,"",INDEX(spisak_godiste,$V112))</f>
+        <v/>
+      </c>
+      <c r="E112" s="5">
+        <f>IF($V112=0,"",INDEX(spisak_pol,$V112)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F112" s="5">
+        <f>IF($V112=0,"",INDEX(spisak_pojas,$V112)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G112" s="7">
         <f>IF($D112="","",LOOKUP($D112,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4942,7 +7331,7 @@
       <c r="P112" s="5"/>
       <c r="Q112" s="5"/>
       <c r="R112" s="8">
-        <f>IF(COUNTA($A112:$F112,I112:P112,Q112)=0,"",IF(AND($A112&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A112,4))="FSS-",MID($A112,LEN($A112)-2,1)="/",ISNUMBER(VALUE(RIGHT($A112,2))),VALUE(MID($A112,5,LEN($A112)-7))&gt;=1,VALUE(MID($A112,5,LEN($A112)-7))=INT(VALUE(MID($A112,5,LEN($A112)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B112="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B112&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C112="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C112&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D112="","Nedostaje godište",IF($G112="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E112="","Nedostaje pol",IF($F112="","Nedostaje pojas",IF(COUNTA(I112:P112)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I112:P112&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G112),I112:P112)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G112,IF(AND(COUNTIF(I112:P112,"Fudokan sport kumite")&gt;0,Q112=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I112:P112,"Fudokan sport kumite")=0,Q112&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A112:$F112))+SUMPRODUCT(LEN(I112:P112))+LEN(Q112)=0,"",IF(AND($A112&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A112,4))="FSS-",MID($A112,LEN($A112)-2,1)="/",ISNUMBER(VALUE(RIGHT($A112,2))),VALUE(MID($A112,5,LEN($A112)-7))&gt;=1,VALUE(MID($A112,5,LEN($A112)-7))=INT(VALUE(MID($A112,5,LEN($A112)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A112&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A112&lt;&gt;"",$U112=0,$B112=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U112&gt;0,$V112=0,$B112=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U112)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B112="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B112&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C112="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C112&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D112="","Nedostaje godište",IF($G112="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E112="","Nedostaje pol",IF($F112="","Nedostaje pojas",IF(COUNTA(I112:P112)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I112:P112&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G112),I112:P112)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G112,IF(AND(COUNTIF(I112:P112,"Fudokan sport kumite")&gt;0,Q112=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I112:P112,"Fudokan sport kumite")=0,Q112&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S112">
@@ -4953,14 +7342,37 @@
         <f>IF(OR($G112="",$E112=""),"sve_kilaze","kg_"&amp;$G112&amp;"_"&amp;IF($E112="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="113" spans="1:20">
+      <c r="U112">
+        <f>IF($A112="",0,IFERROR(MATCH(TRIM($A112),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V112">
+        <f>IF($U112=0,0,IF(TRIM(INDEX(spisak_klub,$U112))=TRIM($B$4),$U112,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:22">
       <c r="A113" s="5"/>
-      <c r="B113" s="5"/>
-      <c r="C113" s="5"/>
-      <c r="D113" s="5"/>
-      <c r="E113" s="5"/>
-      <c r="F113" s="5"/>
+      <c r="B113" s="5">
+        <f>IF($V113=0,"",INDEX(spisak_ime,$V113)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C113" s="5">
+        <f>IF($V113=0,"",INDEX(spisak_prezime,$V113)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D113" s="5">
+        <f>IF($V113=0,"",INDEX(spisak_godiste,$V113))</f>
+        <v/>
+      </c>
+      <c r="E113" s="5">
+        <f>IF($V113=0,"",INDEX(spisak_pol,$V113)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F113" s="5">
+        <f>IF($V113=0,"",INDEX(spisak_pojas,$V113)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G113" s="7">
         <f>IF($D113="","",LOOKUP($D113,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -4979,7 +7391,7 @@
       <c r="P113" s="5"/>
       <c r="Q113" s="5"/>
       <c r="R113" s="8">
-        <f>IF(COUNTA($A113:$F113,I113:P113,Q113)=0,"",IF(AND($A113&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A113,4))="FSS-",MID($A113,LEN($A113)-2,1)="/",ISNUMBER(VALUE(RIGHT($A113,2))),VALUE(MID($A113,5,LEN($A113)-7))&gt;=1,VALUE(MID($A113,5,LEN($A113)-7))=INT(VALUE(MID($A113,5,LEN($A113)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B113="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B113&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C113="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C113&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D113="","Nedostaje godište",IF($G113="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E113="","Nedostaje pol",IF($F113="","Nedostaje pojas",IF(COUNTA(I113:P113)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I113:P113&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G113),I113:P113)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G113,IF(AND(COUNTIF(I113:P113,"Fudokan sport kumite")&gt;0,Q113=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I113:P113,"Fudokan sport kumite")=0,Q113&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A113:$F113))+SUMPRODUCT(LEN(I113:P113))+LEN(Q113)=0,"",IF(AND($A113&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A113,4))="FSS-",MID($A113,LEN($A113)-2,1)="/",ISNUMBER(VALUE(RIGHT($A113,2))),VALUE(MID($A113,5,LEN($A113)-7))&gt;=1,VALUE(MID($A113,5,LEN($A113)-7))=INT(VALUE(MID($A113,5,LEN($A113)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A113&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A113&lt;&gt;"",$U113=0,$B113=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U113&gt;0,$V113=0,$B113=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U113)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B113="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B113&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C113="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C113&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D113="","Nedostaje godište",IF($G113="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E113="","Nedostaje pol",IF($F113="","Nedostaje pojas",IF(COUNTA(I113:P113)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I113:P113&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G113),I113:P113)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G113,IF(AND(COUNTIF(I113:P113,"Fudokan sport kumite")&gt;0,Q113=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I113:P113,"Fudokan sport kumite")=0,Q113&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S113">
@@ -4990,14 +7402,37 @@
         <f>IF(OR($G113="",$E113=""),"sve_kilaze","kg_"&amp;$G113&amp;"_"&amp;IF($E113="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="114" spans="1:20">
+      <c r="U113">
+        <f>IF($A113="",0,IFERROR(MATCH(TRIM($A113),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V113">
+        <f>IF($U113=0,0,IF(TRIM(INDEX(spisak_klub,$U113))=TRIM($B$4),$U113,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:22">
       <c r="A114" s="5"/>
-      <c r="B114" s="5"/>
-      <c r="C114" s="5"/>
-      <c r="D114" s="5"/>
-      <c r="E114" s="5"/>
-      <c r="F114" s="5"/>
+      <c r="B114" s="5">
+        <f>IF($V114=0,"",INDEX(spisak_ime,$V114)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C114" s="5">
+        <f>IF($V114=0,"",INDEX(spisak_prezime,$V114)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D114" s="5">
+        <f>IF($V114=0,"",INDEX(spisak_godiste,$V114))</f>
+        <v/>
+      </c>
+      <c r="E114" s="5">
+        <f>IF($V114=0,"",INDEX(spisak_pol,$V114)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F114" s="5">
+        <f>IF($V114=0,"",INDEX(spisak_pojas,$V114)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G114" s="7">
         <f>IF($D114="","",LOOKUP($D114,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -5016,7 +7451,7 @@
       <c r="P114" s="5"/>
       <c r="Q114" s="5"/>
       <c r="R114" s="8">
-        <f>IF(COUNTA($A114:$F114,I114:P114,Q114)=0,"",IF(AND($A114&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A114,4))="FSS-",MID($A114,LEN($A114)-2,1)="/",ISNUMBER(VALUE(RIGHT($A114,2))),VALUE(MID($A114,5,LEN($A114)-7))&gt;=1,VALUE(MID($A114,5,LEN($A114)-7))=INT(VALUE(MID($A114,5,LEN($A114)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B114="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B114&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C114="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C114&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D114="","Nedostaje godište",IF($G114="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E114="","Nedostaje pol",IF($F114="","Nedostaje pojas",IF(COUNTA(I114:P114)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I114:P114&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G114),I114:P114)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G114,IF(AND(COUNTIF(I114:P114,"Fudokan sport kumite")&gt;0,Q114=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I114:P114,"Fudokan sport kumite")=0,Q114&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A114:$F114))+SUMPRODUCT(LEN(I114:P114))+LEN(Q114)=0,"",IF(AND($A114&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A114,4))="FSS-",MID($A114,LEN($A114)-2,1)="/",ISNUMBER(VALUE(RIGHT($A114,2))),VALUE(MID($A114,5,LEN($A114)-7))&gt;=1,VALUE(MID($A114,5,LEN($A114)-7))=INT(VALUE(MID($A114,5,LEN($A114)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A114&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A114&lt;&gt;"",$U114=0,$B114=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U114&gt;0,$V114=0,$B114=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U114)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B114="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B114&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C114="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C114&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D114="","Nedostaje godište",IF($G114="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E114="","Nedostaje pol",IF($F114="","Nedostaje pojas",IF(COUNTA(I114:P114)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I114:P114&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G114),I114:P114)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G114,IF(AND(COUNTIF(I114:P114,"Fudokan sport kumite")&gt;0,Q114=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I114:P114,"Fudokan sport kumite")=0,Q114&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S114">
@@ -5027,14 +7462,37 @@
         <f>IF(OR($G114="",$E114=""),"sve_kilaze","kg_"&amp;$G114&amp;"_"&amp;IF($E114="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="115" spans="1:20">
+      <c r="U114">
+        <f>IF($A114="",0,IFERROR(MATCH(TRIM($A114),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V114">
+        <f>IF($U114=0,0,IF(TRIM(INDEX(spisak_klub,$U114))=TRIM($B$4),$U114,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:22">
       <c r="A115" s="5"/>
-      <c r="B115" s="5"/>
-      <c r="C115" s="5"/>
-      <c r="D115" s="5"/>
-      <c r="E115" s="5"/>
-      <c r="F115" s="5"/>
+      <c r="B115" s="5">
+        <f>IF($V115=0,"",INDEX(spisak_ime,$V115)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C115" s="5">
+        <f>IF($V115=0,"",INDEX(spisak_prezime,$V115)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D115" s="5">
+        <f>IF($V115=0,"",INDEX(spisak_godiste,$V115))</f>
+        <v/>
+      </c>
+      <c r="E115" s="5">
+        <f>IF($V115=0,"",INDEX(spisak_pol,$V115)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F115" s="5">
+        <f>IF($V115=0,"",INDEX(spisak_pojas,$V115)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G115" s="7">
         <f>IF($D115="","",LOOKUP($D115,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -5053,7 +7511,7 @@
       <c r="P115" s="5"/>
       <c r="Q115" s="5"/>
       <c r="R115" s="8">
-        <f>IF(COUNTA($A115:$F115,I115:P115,Q115)=0,"",IF(AND($A115&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A115,4))="FSS-",MID($A115,LEN($A115)-2,1)="/",ISNUMBER(VALUE(RIGHT($A115,2))),VALUE(MID($A115,5,LEN($A115)-7))&gt;=1,VALUE(MID($A115,5,LEN($A115)-7))=INT(VALUE(MID($A115,5,LEN($A115)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B115="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B115&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C115="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C115&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D115="","Nedostaje godište",IF($G115="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E115="","Nedostaje pol",IF($F115="","Nedostaje pojas",IF(COUNTA(I115:P115)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I115:P115&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G115),I115:P115)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G115,IF(AND(COUNTIF(I115:P115,"Fudokan sport kumite")&gt;0,Q115=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I115:P115,"Fudokan sport kumite")=0,Q115&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A115:$F115))+SUMPRODUCT(LEN(I115:P115))+LEN(Q115)=0,"",IF(AND($A115&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A115,4))="FSS-",MID($A115,LEN($A115)-2,1)="/",ISNUMBER(VALUE(RIGHT($A115,2))),VALUE(MID($A115,5,LEN($A115)-7))&gt;=1,VALUE(MID($A115,5,LEN($A115)-7))=INT(VALUE(MID($A115,5,LEN($A115)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A115&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A115&lt;&gt;"",$U115=0,$B115=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U115&gt;0,$V115=0,$B115=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U115)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B115="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B115&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C115="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C115&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D115="","Nedostaje godište",IF($G115="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E115="","Nedostaje pol",IF($F115="","Nedostaje pojas",IF(COUNTA(I115:P115)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I115:P115&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G115),I115:P115)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G115,IF(AND(COUNTIF(I115:P115,"Fudokan sport kumite")&gt;0,Q115=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I115:P115,"Fudokan sport kumite")=0,Q115&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S115">
@@ -5064,14 +7522,37 @@
         <f>IF(OR($G115="",$E115=""),"sve_kilaze","kg_"&amp;$G115&amp;"_"&amp;IF($E115="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="116" spans="1:20">
+      <c r="U115">
+        <f>IF($A115="",0,IFERROR(MATCH(TRIM($A115),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V115">
+        <f>IF($U115=0,0,IF(TRIM(INDEX(spisak_klub,$U115))=TRIM($B$4),$U115,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:22">
       <c r="A116" s="5"/>
-      <c r="B116" s="5"/>
-      <c r="C116" s="5"/>
-      <c r="D116" s="5"/>
-      <c r="E116" s="5"/>
-      <c r="F116" s="5"/>
+      <c r="B116" s="5">
+        <f>IF($V116=0,"",INDEX(spisak_ime,$V116)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C116" s="5">
+        <f>IF($V116=0,"",INDEX(spisak_prezime,$V116)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D116" s="5">
+        <f>IF($V116=0,"",INDEX(spisak_godiste,$V116))</f>
+        <v/>
+      </c>
+      <c r="E116" s="5">
+        <f>IF($V116=0,"",INDEX(spisak_pol,$V116)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F116" s="5">
+        <f>IF($V116=0,"",INDEX(spisak_pojas,$V116)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G116" s="7">
         <f>IF($D116="","",LOOKUP($D116,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -5090,7 +7571,7 @@
       <c r="P116" s="5"/>
       <c r="Q116" s="5"/>
       <c r="R116" s="8">
-        <f>IF(COUNTA($A116:$F116,I116:P116,Q116)=0,"",IF(AND($A116&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A116,4))="FSS-",MID($A116,LEN($A116)-2,1)="/",ISNUMBER(VALUE(RIGHT($A116,2))),VALUE(MID($A116,5,LEN($A116)-7))&gt;=1,VALUE(MID($A116,5,LEN($A116)-7))=INT(VALUE(MID($A116,5,LEN($A116)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B116="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B116&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C116="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C116&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D116="","Nedostaje godište",IF($G116="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E116="","Nedostaje pol",IF($F116="","Nedostaje pojas",IF(COUNTA(I116:P116)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I116:P116&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G116),I116:P116)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G116,IF(AND(COUNTIF(I116:P116,"Fudokan sport kumite")&gt;0,Q116=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I116:P116,"Fudokan sport kumite")=0,Q116&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A116:$F116))+SUMPRODUCT(LEN(I116:P116))+LEN(Q116)=0,"",IF(AND($A116&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A116,4))="FSS-",MID($A116,LEN($A116)-2,1)="/",ISNUMBER(VALUE(RIGHT($A116,2))),VALUE(MID($A116,5,LEN($A116)-7))&gt;=1,VALUE(MID($A116,5,LEN($A116)-7))=INT(VALUE(MID($A116,5,LEN($A116)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A116&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A116&lt;&gt;"",$U116=0,$B116=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U116&gt;0,$V116=0,$B116=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U116)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B116="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B116&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C116="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C116&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D116="","Nedostaje godište",IF($G116="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E116="","Nedostaje pol",IF($F116="","Nedostaje pojas",IF(COUNTA(I116:P116)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I116:P116&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G116),I116:P116)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G116,IF(AND(COUNTIF(I116:P116,"Fudokan sport kumite")&gt;0,Q116=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I116:P116,"Fudokan sport kumite")=0,Q116&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S116">
@@ -5101,14 +7582,37 @@
         <f>IF(OR($G116="",$E116=""),"sve_kilaze","kg_"&amp;$G116&amp;"_"&amp;IF($E116="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="117" spans="1:20">
+      <c r="U116">
+        <f>IF($A116="",0,IFERROR(MATCH(TRIM($A116),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V116">
+        <f>IF($U116=0,0,IF(TRIM(INDEX(spisak_klub,$U116))=TRIM($B$4),$U116,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:22">
       <c r="A117" s="5"/>
-      <c r="B117" s="5"/>
-      <c r="C117" s="5"/>
-      <c r="D117" s="5"/>
-      <c r="E117" s="5"/>
-      <c r="F117" s="5"/>
+      <c r="B117" s="5">
+        <f>IF($V117=0,"",INDEX(spisak_ime,$V117)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C117" s="5">
+        <f>IF($V117=0,"",INDEX(spisak_prezime,$V117)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D117" s="5">
+        <f>IF($V117=0,"",INDEX(spisak_godiste,$V117))</f>
+        <v/>
+      </c>
+      <c r="E117" s="5">
+        <f>IF($V117=0,"",INDEX(spisak_pol,$V117)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F117" s="5">
+        <f>IF($V117=0,"",INDEX(spisak_pojas,$V117)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G117" s="7">
         <f>IF($D117="","",LOOKUP($D117,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -5127,7 +7631,7 @@
       <c r="P117" s="5"/>
       <c r="Q117" s="5"/>
       <c r="R117" s="8">
-        <f>IF(COUNTA($A117:$F117,I117:P117,Q117)=0,"",IF(AND($A117&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A117,4))="FSS-",MID($A117,LEN($A117)-2,1)="/",ISNUMBER(VALUE(RIGHT($A117,2))),VALUE(MID($A117,5,LEN($A117)-7))&gt;=1,VALUE(MID($A117,5,LEN($A117)-7))=INT(VALUE(MID($A117,5,LEN($A117)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B117="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B117&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C117="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C117&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D117="","Nedostaje godište",IF($G117="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E117="","Nedostaje pol",IF($F117="","Nedostaje pojas",IF(COUNTA(I117:P117)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I117:P117&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G117),I117:P117)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G117,IF(AND(COUNTIF(I117:P117,"Fudokan sport kumite")&gt;0,Q117=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I117:P117,"Fudokan sport kumite")=0,Q117&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A117:$F117))+SUMPRODUCT(LEN(I117:P117))+LEN(Q117)=0,"",IF(AND($A117&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A117,4))="FSS-",MID($A117,LEN($A117)-2,1)="/",ISNUMBER(VALUE(RIGHT($A117,2))),VALUE(MID($A117,5,LEN($A117)-7))&gt;=1,VALUE(MID($A117,5,LEN($A117)-7))=INT(VALUE(MID($A117,5,LEN($A117)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A117&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A117&lt;&gt;"",$U117=0,$B117=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U117&gt;0,$V117=0,$B117=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U117)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B117="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B117&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C117="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C117&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D117="","Nedostaje godište",IF($G117="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E117="","Nedostaje pol",IF($F117="","Nedostaje pojas",IF(COUNTA(I117:P117)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I117:P117&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G117),I117:P117)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G117,IF(AND(COUNTIF(I117:P117,"Fudokan sport kumite")&gt;0,Q117=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I117:P117,"Fudokan sport kumite")=0,Q117&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S117">
@@ -5138,14 +7642,37 @@
         <f>IF(OR($G117="",$E117=""),"sve_kilaze","kg_"&amp;$G117&amp;"_"&amp;IF($E117="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="118" spans="1:20">
+      <c r="U117">
+        <f>IF($A117="",0,IFERROR(MATCH(TRIM($A117),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V117">
+        <f>IF($U117=0,0,IF(TRIM(INDEX(spisak_klub,$U117))=TRIM($B$4),$U117,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:22">
       <c r="A118" s="5"/>
-      <c r="B118" s="5"/>
-      <c r="C118" s="5"/>
-      <c r="D118" s="5"/>
-      <c r="E118" s="5"/>
-      <c r="F118" s="5"/>
+      <c r="B118" s="5">
+        <f>IF($V118=0,"",INDEX(spisak_ime,$V118)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C118" s="5">
+        <f>IF($V118=0,"",INDEX(spisak_prezime,$V118)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D118" s="5">
+        <f>IF($V118=0,"",INDEX(spisak_godiste,$V118))</f>
+        <v/>
+      </c>
+      <c r="E118" s="5">
+        <f>IF($V118=0,"",INDEX(spisak_pol,$V118)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F118" s="5">
+        <f>IF($V118=0,"",INDEX(spisak_pojas,$V118)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G118" s="7">
         <f>IF($D118="","",LOOKUP($D118,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -5164,7 +7691,7 @@
       <c r="P118" s="5"/>
       <c r="Q118" s="5"/>
       <c r="R118" s="8">
-        <f>IF(COUNTA($A118:$F118,I118:P118,Q118)=0,"",IF(AND($A118&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A118,4))="FSS-",MID($A118,LEN($A118)-2,1)="/",ISNUMBER(VALUE(RIGHT($A118,2))),VALUE(MID($A118,5,LEN($A118)-7))&gt;=1,VALUE(MID($A118,5,LEN($A118)-7))=INT(VALUE(MID($A118,5,LEN($A118)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B118="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B118&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C118="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C118&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D118="","Nedostaje godište",IF($G118="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E118="","Nedostaje pol",IF($F118="","Nedostaje pojas",IF(COUNTA(I118:P118)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I118:P118&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G118),I118:P118)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G118,IF(AND(COUNTIF(I118:P118,"Fudokan sport kumite")&gt;0,Q118=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I118:P118,"Fudokan sport kumite")=0,Q118&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A118:$F118))+SUMPRODUCT(LEN(I118:P118))+LEN(Q118)=0,"",IF(AND($A118&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A118,4))="FSS-",MID($A118,LEN($A118)-2,1)="/",ISNUMBER(VALUE(RIGHT($A118,2))),VALUE(MID($A118,5,LEN($A118)-7))&gt;=1,VALUE(MID($A118,5,LEN($A118)-7))=INT(VALUE(MID($A118,5,LEN($A118)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A118&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A118&lt;&gt;"",$U118=0,$B118=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U118&gt;0,$V118=0,$B118=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U118)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B118="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B118&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C118="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C118&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D118="","Nedostaje godište",IF($G118="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E118="","Nedostaje pol",IF($F118="","Nedostaje pojas",IF(COUNTA(I118:P118)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I118:P118&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G118),I118:P118)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G118,IF(AND(COUNTIF(I118:P118,"Fudokan sport kumite")&gt;0,Q118=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I118:P118,"Fudokan sport kumite")=0,Q118&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S118">
@@ -5175,14 +7702,37 @@
         <f>IF(OR($G118="",$E118=""),"sve_kilaze","kg_"&amp;$G118&amp;"_"&amp;IF($E118="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="119" spans="1:20">
+      <c r="U118">
+        <f>IF($A118="",0,IFERROR(MATCH(TRIM($A118),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V118">
+        <f>IF($U118=0,0,IF(TRIM(INDEX(spisak_klub,$U118))=TRIM($B$4),$U118,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:22">
       <c r="A119" s="5"/>
-      <c r="B119" s="5"/>
-      <c r="C119" s="5"/>
-      <c r="D119" s="5"/>
-      <c r="E119" s="5"/>
-      <c r="F119" s="5"/>
+      <c r="B119" s="5">
+        <f>IF($V119=0,"",INDEX(spisak_ime,$V119)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C119" s="5">
+        <f>IF($V119=0,"",INDEX(spisak_prezime,$V119)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D119" s="5">
+        <f>IF($V119=0,"",INDEX(spisak_godiste,$V119))</f>
+        <v/>
+      </c>
+      <c r="E119" s="5">
+        <f>IF($V119=0,"",INDEX(spisak_pol,$V119)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F119" s="5">
+        <f>IF($V119=0,"",INDEX(spisak_pojas,$V119)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G119" s="7">
         <f>IF($D119="","",LOOKUP($D119,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -5201,7 +7751,7 @@
       <c r="P119" s="5"/>
       <c r="Q119" s="5"/>
       <c r="R119" s="8">
-        <f>IF(COUNTA($A119:$F119,I119:P119,Q119)=0,"",IF(AND($A119&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A119,4))="FSS-",MID($A119,LEN($A119)-2,1)="/",ISNUMBER(VALUE(RIGHT($A119,2))),VALUE(MID($A119,5,LEN($A119)-7))&gt;=1,VALUE(MID($A119,5,LEN($A119)-7))=INT(VALUE(MID($A119,5,LEN($A119)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B119="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B119&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C119="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C119&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D119="","Nedostaje godište",IF($G119="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E119="","Nedostaje pol",IF($F119="","Nedostaje pojas",IF(COUNTA(I119:P119)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I119:P119&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G119),I119:P119)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G119,IF(AND(COUNTIF(I119:P119,"Fudokan sport kumite")&gt;0,Q119=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I119:P119,"Fudokan sport kumite")=0,Q119&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A119:$F119))+SUMPRODUCT(LEN(I119:P119))+LEN(Q119)=0,"",IF(AND($A119&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A119,4))="FSS-",MID($A119,LEN($A119)-2,1)="/",ISNUMBER(VALUE(RIGHT($A119,2))),VALUE(MID($A119,5,LEN($A119)-7))&gt;=1,VALUE(MID($A119,5,LEN($A119)-7))=INT(VALUE(MID($A119,5,LEN($A119)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A119&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A119&lt;&gt;"",$U119=0,$B119=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U119&gt;0,$V119=0,$B119=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U119)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B119="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B119&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C119="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C119&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D119="","Nedostaje godište",IF($G119="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E119="","Nedostaje pol",IF($F119="","Nedostaje pojas",IF(COUNTA(I119:P119)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I119:P119&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G119),I119:P119)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G119,IF(AND(COUNTIF(I119:P119,"Fudokan sport kumite")&gt;0,Q119=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I119:P119,"Fudokan sport kumite")=0,Q119&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S119">
@@ -5212,14 +7762,37 @@
         <f>IF(OR($G119="",$E119=""),"sve_kilaze","kg_"&amp;$G119&amp;"_"&amp;IF($E119="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="120" spans="1:20">
+      <c r="U119">
+        <f>IF($A119="",0,IFERROR(MATCH(TRIM($A119),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V119">
+        <f>IF($U119=0,0,IF(TRIM(INDEX(spisak_klub,$U119))=TRIM($B$4),$U119,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:22">
       <c r="A120" s="5"/>
-      <c r="B120" s="5"/>
-      <c r="C120" s="5"/>
-      <c r="D120" s="5"/>
-      <c r="E120" s="5"/>
-      <c r="F120" s="5"/>
+      <c r="B120" s="5">
+        <f>IF($V120=0,"",INDEX(spisak_ime,$V120)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C120" s="5">
+        <f>IF($V120=0,"",INDEX(spisak_prezime,$V120)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D120" s="5">
+        <f>IF($V120=0,"",INDEX(spisak_godiste,$V120))</f>
+        <v/>
+      </c>
+      <c r="E120" s="5">
+        <f>IF($V120=0,"",INDEX(spisak_pol,$V120)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F120" s="5">
+        <f>IF($V120=0,"",INDEX(spisak_pojas,$V120)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G120" s="7">
         <f>IF($D120="","",LOOKUP($D120,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -5238,7 +7811,7 @@
       <c r="P120" s="5"/>
       <c r="Q120" s="5"/>
       <c r="R120" s="8">
-        <f>IF(COUNTA($A120:$F120,I120:P120,Q120)=0,"",IF(AND($A120&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A120,4))="FSS-",MID($A120,LEN($A120)-2,1)="/",ISNUMBER(VALUE(RIGHT($A120,2))),VALUE(MID($A120,5,LEN($A120)-7))&gt;=1,VALUE(MID($A120,5,LEN($A120)-7))=INT(VALUE(MID($A120,5,LEN($A120)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B120="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B120&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C120="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C120&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D120="","Nedostaje godište",IF($G120="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E120="","Nedostaje pol",IF($F120="","Nedostaje pojas",IF(COUNTA(I120:P120)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I120:P120&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G120),I120:P120)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G120,IF(AND(COUNTIF(I120:P120,"Fudokan sport kumite")&gt;0,Q120=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I120:P120,"Fudokan sport kumite")=0,Q120&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A120:$F120))+SUMPRODUCT(LEN(I120:P120))+LEN(Q120)=0,"",IF(AND($A120&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A120,4))="FSS-",MID($A120,LEN($A120)-2,1)="/",ISNUMBER(VALUE(RIGHT($A120,2))),VALUE(MID($A120,5,LEN($A120)-7))&gt;=1,VALUE(MID($A120,5,LEN($A120)-7))=INT(VALUE(MID($A120,5,LEN($A120)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A120&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A120&lt;&gt;"",$U120=0,$B120=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U120&gt;0,$V120=0,$B120=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U120)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B120="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B120&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C120="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C120&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D120="","Nedostaje godište",IF($G120="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E120="","Nedostaje pol",IF($F120="","Nedostaje pojas",IF(COUNTA(I120:P120)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I120:P120&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G120),I120:P120)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G120,IF(AND(COUNTIF(I120:P120,"Fudokan sport kumite")&gt;0,Q120=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I120:P120,"Fudokan sport kumite")=0,Q120&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S120">
@@ -5249,14 +7822,37 @@
         <f>IF(OR($G120="",$E120=""),"sve_kilaze","kg_"&amp;$G120&amp;"_"&amp;IF($E120="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="121" spans="1:20">
+      <c r="U120">
+        <f>IF($A120="",0,IFERROR(MATCH(TRIM($A120),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V120">
+        <f>IF($U120=0,0,IF(TRIM(INDEX(spisak_klub,$U120))=TRIM($B$4),$U120,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:22">
       <c r="A121" s="5"/>
-      <c r="B121" s="5"/>
-      <c r="C121" s="5"/>
-      <c r="D121" s="5"/>
-      <c r="E121" s="5"/>
-      <c r="F121" s="5"/>
+      <c r="B121" s="5">
+        <f>IF($V121=0,"",INDEX(spisak_ime,$V121)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C121" s="5">
+        <f>IF($V121=0,"",INDEX(spisak_prezime,$V121)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D121" s="5">
+        <f>IF($V121=0,"",INDEX(spisak_godiste,$V121))</f>
+        <v/>
+      </c>
+      <c r="E121" s="5">
+        <f>IF($V121=0,"",INDEX(spisak_pol,$V121)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F121" s="5">
+        <f>IF($V121=0,"",INDEX(spisak_pojas,$V121)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G121" s="7">
         <f>IF($D121="","",LOOKUP($D121,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -5275,7 +7871,7 @@
       <c r="P121" s="5"/>
       <c r="Q121" s="5"/>
       <c r="R121" s="8">
-        <f>IF(COUNTA($A121:$F121,I121:P121,Q121)=0,"",IF(AND($A121&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A121,4))="FSS-",MID($A121,LEN($A121)-2,1)="/",ISNUMBER(VALUE(RIGHT($A121,2))),VALUE(MID($A121,5,LEN($A121)-7))&gt;=1,VALUE(MID($A121,5,LEN($A121)-7))=INT(VALUE(MID($A121,5,LEN($A121)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B121="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B121&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C121="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C121&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D121="","Nedostaje godište",IF($G121="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E121="","Nedostaje pol",IF($F121="","Nedostaje pojas",IF(COUNTA(I121:P121)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I121:P121&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G121),I121:P121)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G121,IF(AND(COUNTIF(I121:P121,"Fudokan sport kumite")&gt;0,Q121=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I121:P121,"Fudokan sport kumite")=0,Q121&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A121:$F121))+SUMPRODUCT(LEN(I121:P121))+LEN(Q121)=0,"",IF(AND($A121&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A121,4))="FSS-",MID($A121,LEN($A121)-2,1)="/",ISNUMBER(VALUE(RIGHT($A121,2))),VALUE(MID($A121,5,LEN($A121)-7))&gt;=1,VALUE(MID($A121,5,LEN($A121)-7))=INT(VALUE(MID($A121,5,LEN($A121)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A121&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A121&lt;&gt;"",$U121=0,$B121=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U121&gt;0,$V121=0,$B121=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U121)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B121="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B121&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C121="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C121&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D121="","Nedostaje godište",IF($G121="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E121="","Nedostaje pol",IF($F121="","Nedostaje pojas",IF(COUNTA(I121:P121)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I121:P121&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G121),I121:P121)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G121,IF(AND(COUNTIF(I121:P121,"Fudokan sport kumite")&gt;0,Q121=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I121:P121,"Fudokan sport kumite")=0,Q121&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S121">
@@ -5286,14 +7882,37 @@
         <f>IF(OR($G121="",$E121=""),"sve_kilaze","kg_"&amp;$G121&amp;"_"&amp;IF($E121="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="122" spans="1:20">
+      <c r="U121">
+        <f>IF($A121="",0,IFERROR(MATCH(TRIM($A121),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V121">
+        <f>IF($U121=0,0,IF(TRIM(INDEX(spisak_klub,$U121))=TRIM($B$4),$U121,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:22">
       <c r="A122" s="5"/>
-      <c r="B122" s="5"/>
-      <c r="C122" s="5"/>
-      <c r="D122" s="5"/>
-      <c r="E122" s="5"/>
-      <c r="F122" s="5"/>
+      <c r="B122" s="5">
+        <f>IF($V122=0,"",INDEX(spisak_ime,$V122)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C122" s="5">
+        <f>IF($V122=0,"",INDEX(spisak_prezime,$V122)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D122" s="5">
+        <f>IF($V122=0,"",INDEX(spisak_godiste,$V122))</f>
+        <v/>
+      </c>
+      <c r="E122" s="5">
+        <f>IF($V122=0,"",INDEX(spisak_pol,$V122)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F122" s="5">
+        <f>IF($V122=0,"",INDEX(spisak_pojas,$V122)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G122" s="7">
         <f>IF($D122="","",LOOKUP($D122,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -5312,7 +7931,7 @@
       <c r="P122" s="5"/>
       <c r="Q122" s="5"/>
       <c r="R122" s="8">
-        <f>IF(COUNTA($A122:$F122,I122:P122,Q122)=0,"",IF(AND($A122&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A122,4))="FSS-",MID($A122,LEN($A122)-2,1)="/",ISNUMBER(VALUE(RIGHT($A122,2))),VALUE(MID($A122,5,LEN($A122)-7))&gt;=1,VALUE(MID($A122,5,LEN($A122)-7))=INT(VALUE(MID($A122,5,LEN($A122)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B122="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B122&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C122="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C122&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D122="","Nedostaje godište",IF($G122="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E122="","Nedostaje pol",IF($F122="","Nedostaje pojas",IF(COUNTA(I122:P122)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I122:P122&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G122),I122:P122)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G122,IF(AND(COUNTIF(I122:P122,"Fudokan sport kumite")&gt;0,Q122=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I122:P122,"Fudokan sport kumite")=0,Q122&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A122:$F122))+SUMPRODUCT(LEN(I122:P122))+LEN(Q122)=0,"",IF(AND($A122&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A122,4))="FSS-",MID($A122,LEN($A122)-2,1)="/",ISNUMBER(VALUE(RIGHT($A122,2))),VALUE(MID($A122,5,LEN($A122)-7))&gt;=1,VALUE(MID($A122,5,LEN($A122)-7))=INT(VALUE(MID($A122,5,LEN($A122)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A122&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A122&lt;&gt;"",$U122=0,$B122=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U122&gt;0,$V122=0,$B122=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U122)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B122="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B122&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C122="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C122&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D122="","Nedostaje godište",IF($G122="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E122="","Nedostaje pol",IF($F122="","Nedostaje pojas",IF(COUNTA(I122:P122)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I122:P122&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G122),I122:P122)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G122,IF(AND(COUNTIF(I122:P122,"Fudokan sport kumite")&gt;0,Q122=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I122:P122,"Fudokan sport kumite")=0,Q122&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S122">
@@ -5323,14 +7942,37 @@
         <f>IF(OR($G122="",$E122=""),"sve_kilaze","kg_"&amp;$G122&amp;"_"&amp;IF($E122="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="123" spans="1:20">
+      <c r="U122">
+        <f>IF($A122="",0,IFERROR(MATCH(TRIM($A122),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V122">
+        <f>IF($U122=0,0,IF(TRIM(INDEX(spisak_klub,$U122))=TRIM($B$4),$U122,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:22">
       <c r="A123" s="5"/>
-      <c r="B123" s="5"/>
-      <c r="C123" s="5"/>
-      <c r="D123" s="5"/>
-      <c r="E123" s="5"/>
-      <c r="F123" s="5"/>
+      <c r="B123" s="5">
+        <f>IF($V123=0,"",INDEX(spisak_ime,$V123)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C123" s="5">
+        <f>IF($V123=0,"",INDEX(spisak_prezime,$V123)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D123" s="5">
+        <f>IF($V123=0,"",INDEX(spisak_godiste,$V123))</f>
+        <v/>
+      </c>
+      <c r="E123" s="5">
+        <f>IF($V123=0,"",INDEX(spisak_pol,$V123)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F123" s="5">
+        <f>IF($V123=0,"",INDEX(spisak_pojas,$V123)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G123" s="7">
         <f>IF($D123="","",LOOKUP($D123,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -5349,7 +7991,7 @@
       <c r="P123" s="5"/>
       <c r="Q123" s="5"/>
       <c r="R123" s="8">
-        <f>IF(COUNTA($A123:$F123,I123:P123,Q123)=0,"",IF(AND($A123&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A123,4))="FSS-",MID($A123,LEN($A123)-2,1)="/",ISNUMBER(VALUE(RIGHT($A123,2))),VALUE(MID($A123,5,LEN($A123)-7))&gt;=1,VALUE(MID($A123,5,LEN($A123)-7))=INT(VALUE(MID($A123,5,LEN($A123)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B123="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B123&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C123="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C123&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D123="","Nedostaje godište",IF($G123="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E123="","Nedostaje pol",IF($F123="","Nedostaje pojas",IF(COUNTA(I123:P123)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I123:P123&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G123),I123:P123)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G123,IF(AND(COUNTIF(I123:P123,"Fudokan sport kumite")&gt;0,Q123=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I123:P123,"Fudokan sport kumite")=0,Q123&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A123:$F123))+SUMPRODUCT(LEN(I123:P123))+LEN(Q123)=0,"",IF(AND($A123&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A123,4))="FSS-",MID($A123,LEN($A123)-2,1)="/",ISNUMBER(VALUE(RIGHT($A123,2))),VALUE(MID($A123,5,LEN($A123)-7))&gt;=1,VALUE(MID($A123,5,LEN($A123)-7))=INT(VALUE(MID($A123,5,LEN($A123)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A123&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A123&lt;&gt;"",$U123=0,$B123=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U123&gt;0,$V123=0,$B123=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U123)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B123="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B123&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C123="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C123&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D123="","Nedostaje godište",IF($G123="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E123="","Nedostaje pol",IF($F123="","Nedostaje pojas",IF(COUNTA(I123:P123)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I123:P123&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G123),I123:P123)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G123,IF(AND(COUNTIF(I123:P123,"Fudokan sport kumite")&gt;0,Q123=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I123:P123,"Fudokan sport kumite")=0,Q123&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S123">
@@ -5360,14 +8002,37 @@
         <f>IF(OR($G123="",$E123=""),"sve_kilaze","kg_"&amp;$G123&amp;"_"&amp;IF($E123="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="124" spans="1:20">
+      <c r="U123">
+        <f>IF($A123="",0,IFERROR(MATCH(TRIM($A123),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V123">
+        <f>IF($U123=0,0,IF(TRIM(INDEX(spisak_klub,$U123))=TRIM($B$4),$U123,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:22">
       <c r="A124" s="5"/>
-      <c r="B124" s="5"/>
-      <c r="C124" s="5"/>
-      <c r="D124" s="5"/>
-      <c r="E124" s="5"/>
-      <c r="F124" s="5"/>
+      <c r="B124" s="5">
+        <f>IF($V124=0,"",INDEX(spisak_ime,$V124)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C124" s="5">
+        <f>IF($V124=0,"",INDEX(spisak_prezime,$V124)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D124" s="5">
+        <f>IF($V124=0,"",INDEX(spisak_godiste,$V124))</f>
+        <v/>
+      </c>
+      <c r="E124" s="5">
+        <f>IF($V124=0,"",INDEX(spisak_pol,$V124)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F124" s="5">
+        <f>IF($V124=0,"",INDEX(spisak_pojas,$V124)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G124" s="7">
         <f>IF($D124="","",LOOKUP($D124,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -5386,7 +8051,7 @@
       <c r="P124" s="5"/>
       <c r="Q124" s="5"/>
       <c r="R124" s="8">
-        <f>IF(COUNTA($A124:$F124,I124:P124,Q124)=0,"",IF(AND($A124&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A124,4))="FSS-",MID($A124,LEN($A124)-2,1)="/",ISNUMBER(VALUE(RIGHT($A124,2))),VALUE(MID($A124,5,LEN($A124)-7))&gt;=1,VALUE(MID($A124,5,LEN($A124)-7))=INT(VALUE(MID($A124,5,LEN($A124)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B124="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B124&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C124="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C124&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D124="","Nedostaje godište",IF($G124="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E124="","Nedostaje pol",IF($F124="","Nedostaje pojas",IF(COUNTA(I124:P124)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I124:P124&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G124),I124:P124)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G124,IF(AND(COUNTIF(I124:P124,"Fudokan sport kumite")&gt;0,Q124=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I124:P124,"Fudokan sport kumite")=0,Q124&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A124:$F124))+SUMPRODUCT(LEN(I124:P124))+LEN(Q124)=0,"",IF(AND($A124&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A124,4))="FSS-",MID($A124,LEN($A124)-2,1)="/",ISNUMBER(VALUE(RIGHT($A124,2))),VALUE(MID($A124,5,LEN($A124)-7))&gt;=1,VALUE(MID($A124,5,LEN($A124)-7))=INT(VALUE(MID($A124,5,LEN($A124)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A124&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A124&lt;&gt;"",$U124=0,$B124=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U124&gt;0,$V124=0,$B124=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U124)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B124="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B124&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C124="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C124&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D124="","Nedostaje godište",IF($G124="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E124="","Nedostaje pol",IF($F124="","Nedostaje pojas",IF(COUNTA(I124:P124)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I124:P124&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G124),I124:P124)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G124,IF(AND(COUNTIF(I124:P124,"Fudokan sport kumite")&gt;0,Q124=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I124:P124,"Fudokan sport kumite")=0,Q124&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S124">
@@ -5397,14 +8062,37 @@
         <f>IF(OR($G124="",$E124=""),"sve_kilaze","kg_"&amp;$G124&amp;"_"&amp;IF($E124="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="125" spans="1:20">
+      <c r="U124">
+        <f>IF($A124="",0,IFERROR(MATCH(TRIM($A124),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V124">
+        <f>IF($U124=0,0,IF(TRIM(INDEX(spisak_klub,$U124))=TRIM($B$4),$U124,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:22">
       <c r="A125" s="5"/>
-      <c r="B125" s="5"/>
-      <c r="C125" s="5"/>
-      <c r="D125" s="5"/>
-      <c r="E125" s="5"/>
-      <c r="F125" s="5"/>
+      <c r="B125" s="5">
+        <f>IF($V125=0,"",INDEX(spisak_ime,$V125)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C125" s="5">
+        <f>IF($V125=0,"",INDEX(spisak_prezime,$V125)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D125" s="5">
+        <f>IF($V125=0,"",INDEX(spisak_godiste,$V125))</f>
+        <v/>
+      </c>
+      <c r="E125" s="5">
+        <f>IF($V125=0,"",INDEX(spisak_pol,$V125)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F125" s="5">
+        <f>IF($V125=0,"",INDEX(spisak_pojas,$V125)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G125" s="7">
         <f>IF($D125="","",LOOKUP($D125,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -5423,7 +8111,7 @@
       <c r="P125" s="5"/>
       <c r="Q125" s="5"/>
       <c r="R125" s="8">
-        <f>IF(COUNTA($A125:$F125,I125:P125,Q125)=0,"",IF(AND($A125&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A125,4))="FSS-",MID($A125,LEN($A125)-2,1)="/",ISNUMBER(VALUE(RIGHT($A125,2))),VALUE(MID($A125,5,LEN($A125)-7))&gt;=1,VALUE(MID($A125,5,LEN($A125)-7))=INT(VALUE(MID($A125,5,LEN($A125)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B125="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B125&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C125="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C125&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D125="","Nedostaje godište",IF($G125="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E125="","Nedostaje pol",IF($F125="","Nedostaje pojas",IF(COUNTA(I125:P125)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I125:P125&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G125),I125:P125)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G125,IF(AND(COUNTIF(I125:P125,"Fudokan sport kumite")&gt;0,Q125=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I125:P125,"Fudokan sport kumite")=0,Q125&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A125:$F125))+SUMPRODUCT(LEN(I125:P125))+LEN(Q125)=0,"",IF(AND($A125&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A125,4))="FSS-",MID($A125,LEN($A125)-2,1)="/",ISNUMBER(VALUE(RIGHT($A125,2))),VALUE(MID($A125,5,LEN($A125)-7))&gt;=1,VALUE(MID($A125,5,LEN($A125)-7))=INT(VALUE(MID($A125,5,LEN($A125)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A125&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A125&lt;&gt;"",$U125=0,$B125=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U125&gt;0,$V125=0,$B125=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U125)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B125="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B125&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C125="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C125&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D125="","Nedostaje godište",IF($G125="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E125="","Nedostaje pol",IF($F125="","Nedostaje pojas",IF(COUNTA(I125:P125)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I125:P125&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G125),I125:P125)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G125,IF(AND(COUNTIF(I125:P125,"Fudokan sport kumite")&gt;0,Q125=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I125:P125,"Fudokan sport kumite")=0,Q125&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S125">
@@ -5434,14 +8122,37 @@
         <f>IF(OR($G125="",$E125=""),"sve_kilaze","kg_"&amp;$G125&amp;"_"&amp;IF($E125="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="126" spans="1:20">
+      <c r="U125">
+        <f>IF($A125="",0,IFERROR(MATCH(TRIM($A125),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V125">
+        <f>IF($U125=0,0,IF(TRIM(INDEX(spisak_klub,$U125))=TRIM($B$4),$U125,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:22">
       <c r="A126" s="5"/>
-      <c r="B126" s="5"/>
-      <c r="C126" s="5"/>
-      <c r="D126" s="5"/>
-      <c r="E126" s="5"/>
-      <c r="F126" s="5"/>
+      <c r="B126" s="5">
+        <f>IF($V126=0,"",INDEX(spisak_ime,$V126)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C126" s="5">
+        <f>IF($V126=0,"",INDEX(spisak_prezime,$V126)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D126" s="5">
+        <f>IF($V126=0,"",INDEX(spisak_godiste,$V126))</f>
+        <v/>
+      </c>
+      <c r="E126" s="5">
+        <f>IF($V126=0,"",INDEX(spisak_pol,$V126)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F126" s="5">
+        <f>IF($V126=0,"",INDEX(spisak_pojas,$V126)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G126" s="7">
         <f>IF($D126="","",LOOKUP($D126,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -5460,7 +8171,7 @@
       <c r="P126" s="5"/>
       <c r="Q126" s="5"/>
       <c r="R126" s="8">
-        <f>IF(COUNTA($A126:$F126,I126:P126,Q126)=0,"",IF(AND($A126&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A126,4))="FSS-",MID($A126,LEN($A126)-2,1)="/",ISNUMBER(VALUE(RIGHT($A126,2))),VALUE(MID($A126,5,LEN($A126)-7))&gt;=1,VALUE(MID($A126,5,LEN($A126)-7))=INT(VALUE(MID($A126,5,LEN($A126)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B126="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B126&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C126="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C126&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D126="","Nedostaje godište",IF($G126="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E126="","Nedostaje pol",IF($F126="","Nedostaje pojas",IF(COUNTA(I126:P126)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I126:P126&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G126),I126:P126)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G126,IF(AND(COUNTIF(I126:P126,"Fudokan sport kumite")&gt;0,Q126=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I126:P126,"Fudokan sport kumite")=0,Q126&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A126:$F126))+SUMPRODUCT(LEN(I126:P126))+LEN(Q126)=0,"",IF(AND($A126&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A126,4))="FSS-",MID($A126,LEN($A126)-2,1)="/",ISNUMBER(VALUE(RIGHT($A126,2))),VALUE(MID($A126,5,LEN($A126)-7))&gt;=1,VALUE(MID($A126,5,LEN($A126)-7))=INT(VALUE(MID($A126,5,LEN($A126)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A126&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A126&lt;&gt;"",$U126=0,$B126=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U126&gt;0,$V126=0,$B126=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U126)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B126="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B126&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C126="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C126&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D126="","Nedostaje godište",IF($G126="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E126="","Nedostaje pol",IF($F126="","Nedostaje pojas",IF(COUNTA(I126:P126)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I126:P126&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G126),I126:P126)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G126,IF(AND(COUNTIF(I126:P126,"Fudokan sport kumite")&gt;0,Q126=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I126:P126,"Fudokan sport kumite")=0,Q126&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S126">
@@ -5471,14 +8182,37 @@
         <f>IF(OR($G126="",$E126=""),"sve_kilaze","kg_"&amp;$G126&amp;"_"&amp;IF($E126="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="127" spans="1:20">
+      <c r="U126">
+        <f>IF($A126="",0,IFERROR(MATCH(TRIM($A126),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V126">
+        <f>IF($U126=0,0,IF(TRIM(INDEX(spisak_klub,$U126))=TRIM($B$4),$U126,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:22">
       <c r="A127" s="5"/>
-      <c r="B127" s="5"/>
-      <c r="C127" s="5"/>
-      <c r="D127" s="5"/>
-      <c r="E127" s="5"/>
-      <c r="F127" s="5"/>
+      <c r="B127" s="5">
+        <f>IF($V127=0,"",INDEX(spisak_ime,$V127)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C127" s="5">
+        <f>IF($V127=0,"",INDEX(spisak_prezime,$V127)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D127" s="5">
+        <f>IF($V127=0,"",INDEX(spisak_godiste,$V127))</f>
+        <v/>
+      </c>
+      <c r="E127" s="5">
+        <f>IF($V127=0,"",INDEX(spisak_pol,$V127)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F127" s="5">
+        <f>IF($V127=0,"",INDEX(spisak_pojas,$V127)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G127" s="7">
         <f>IF($D127="","",LOOKUP($D127,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -5497,7 +8231,7 @@
       <c r="P127" s="5"/>
       <c r="Q127" s="5"/>
       <c r="R127" s="8">
-        <f>IF(COUNTA($A127:$F127,I127:P127,Q127)=0,"",IF(AND($A127&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A127,4))="FSS-",MID($A127,LEN($A127)-2,1)="/",ISNUMBER(VALUE(RIGHT($A127,2))),VALUE(MID($A127,5,LEN($A127)-7))&gt;=1,VALUE(MID($A127,5,LEN($A127)-7))=INT(VALUE(MID($A127,5,LEN($A127)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B127="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B127&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C127="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C127&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D127="","Nedostaje godište",IF($G127="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E127="","Nedostaje pol",IF($F127="","Nedostaje pojas",IF(COUNTA(I127:P127)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I127:P127&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G127),I127:P127)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G127,IF(AND(COUNTIF(I127:P127,"Fudokan sport kumite")&gt;0,Q127=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I127:P127,"Fudokan sport kumite")=0,Q127&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A127:$F127))+SUMPRODUCT(LEN(I127:P127))+LEN(Q127)=0,"",IF(AND($A127&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A127,4))="FSS-",MID($A127,LEN($A127)-2,1)="/",ISNUMBER(VALUE(RIGHT($A127,2))),VALUE(MID($A127,5,LEN($A127)-7))&gt;=1,VALUE(MID($A127,5,LEN($A127)-7))=INT(VALUE(MID($A127,5,LEN($A127)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A127&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A127&lt;&gt;"",$U127=0,$B127=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U127&gt;0,$V127=0,$B127=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U127)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B127="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B127&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C127="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C127&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D127="","Nedostaje godište",IF($G127="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E127="","Nedostaje pol",IF($F127="","Nedostaje pojas",IF(COUNTA(I127:P127)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I127:P127&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G127),I127:P127)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G127,IF(AND(COUNTIF(I127:P127,"Fudokan sport kumite")&gt;0,Q127=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I127:P127,"Fudokan sport kumite")=0,Q127&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S127">
@@ -5508,14 +8242,37 @@
         <f>IF(OR($G127="",$E127=""),"sve_kilaze","kg_"&amp;$G127&amp;"_"&amp;IF($E127="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="128" spans="1:20">
+      <c r="U127">
+        <f>IF($A127="",0,IFERROR(MATCH(TRIM($A127),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V127">
+        <f>IF($U127=0,0,IF(TRIM(INDEX(spisak_klub,$U127))=TRIM($B$4),$U127,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:22">
       <c r="A128" s="5"/>
-      <c r="B128" s="5"/>
-      <c r="C128" s="5"/>
-      <c r="D128" s="5"/>
-      <c r="E128" s="5"/>
-      <c r="F128" s="5"/>
+      <c r="B128" s="5">
+        <f>IF($V128=0,"",INDEX(spisak_ime,$V128)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C128" s="5">
+        <f>IF($V128=0,"",INDEX(spisak_prezime,$V128)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D128" s="5">
+        <f>IF($V128=0,"",INDEX(spisak_godiste,$V128))</f>
+        <v/>
+      </c>
+      <c r="E128" s="5">
+        <f>IF($V128=0,"",INDEX(spisak_pol,$V128)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F128" s="5">
+        <f>IF($V128=0,"",INDEX(spisak_pojas,$V128)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G128" s="7">
         <f>IF($D128="","",LOOKUP($D128,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -5534,7 +8291,7 @@
       <c r="P128" s="5"/>
       <c r="Q128" s="5"/>
       <c r="R128" s="8">
-        <f>IF(COUNTA($A128:$F128,I128:P128,Q128)=0,"",IF(AND($A128&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A128,4))="FSS-",MID($A128,LEN($A128)-2,1)="/",ISNUMBER(VALUE(RIGHT($A128,2))),VALUE(MID($A128,5,LEN($A128)-7))&gt;=1,VALUE(MID($A128,5,LEN($A128)-7))=INT(VALUE(MID($A128,5,LEN($A128)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B128="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B128&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C128="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C128&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D128="","Nedostaje godište",IF($G128="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E128="","Nedostaje pol",IF($F128="","Nedostaje pojas",IF(COUNTA(I128:P128)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I128:P128&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G128),I128:P128)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G128,IF(AND(COUNTIF(I128:P128,"Fudokan sport kumite")&gt;0,Q128=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I128:P128,"Fudokan sport kumite")=0,Q128&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A128:$F128))+SUMPRODUCT(LEN(I128:P128))+LEN(Q128)=0,"",IF(AND($A128&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A128,4))="FSS-",MID($A128,LEN($A128)-2,1)="/",ISNUMBER(VALUE(RIGHT($A128,2))),VALUE(MID($A128,5,LEN($A128)-7))&gt;=1,VALUE(MID($A128,5,LEN($A128)-7))=INT(VALUE(MID($A128,5,LEN($A128)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A128&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A128&lt;&gt;"",$U128=0,$B128=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U128&gt;0,$V128=0,$B128=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U128)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B128="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B128&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C128="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C128&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D128="","Nedostaje godište",IF($G128="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E128="","Nedostaje pol",IF($F128="","Nedostaje pojas",IF(COUNTA(I128:P128)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I128:P128&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G128),I128:P128)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G128,IF(AND(COUNTIF(I128:P128,"Fudokan sport kumite")&gt;0,Q128=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I128:P128,"Fudokan sport kumite")=0,Q128&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S128">
@@ -5545,14 +8302,37 @@
         <f>IF(OR($G128="",$E128=""),"sve_kilaze","kg_"&amp;$G128&amp;"_"&amp;IF($E128="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="129" spans="1:20">
+      <c r="U128">
+        <f>IF($A128="",0,IFERROR(MATCH(TRIM($A128),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V128">
+        <f>IF($U128=0,0,IF(TRIM(INDEX(spisak_klub,$U128))=TRIM($B$4),$U128,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:22">
       <c r="A129" s="5"/>
-      <c r="B129" s="5"/>
-      <c r="C129" s="5"/>
-      <c r="D129" s="5"/>
-      <c r="E129" s="5"/>
-      <c r="F129" s="5"/>
+      <c r="B129" s="5">
+        <f>IF($V129=0,"",INDEX(spisak_ime,$V129)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C129" s="5">
+        <f>IF($V129=0,"",INDEX(spisak_prezime,$V129)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D129" s="5">
+        <f>IF($V129=0,"",INDEX(spisak_godiste,$V129))</f>
+        <v/>
+      </c>
+      <c r="E129" s="5">
+        <f>IF($V129=0,"",INDEX(spisak_pol,$V129)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F129" s="5">
+        <f>IF($V129=0,"",INDEX(spisak_pojas,$V129)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G129" s="7">
         <f>IF($D129="","",LOOKUP($D129,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -5571,7 +8351,7 @@
       <c r="P129" s="5"/>
       <c r="Q129" s="5"/>
       <c r="R129" s="8">
-        <f>IF(COUNTA($A129:$F129,I129:P129,Q129)=0,"",IF(AND($A129&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A129,4))="FSS-",MID($A129,LEN($A129)-2,1)="/",ISNUMBER(VALUE(RIGHT($A129,2))),VALUE(MID($A129,5,LEN($A129)-7))&gt;=1,VALUE(MID($A129,5,LEN($A129)-7))=INT(VALUE(MID($A129,5,LEN($A129)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B129="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B129&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C129="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C129&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D129="","Nedostaje godište",IF($G129="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E129="","Nedostaje pol",IF($F129="","Nedostaje pojas",IF(COUNTA(I129:P129)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I129:P129&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G129),I129:P129)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G129,IF(AND(COUNTIF(I129:P129,"Fudokan sport kumite")&gt;0,Q129=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I129:P129,"Fudokan sport kumite")=0,Q129&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A129:$F129))+SUMPRODUCT(LEN(I129:P129))+LEN(Q129)=0,"",IF(AND($A129&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A129,4))="FSS-",MID($A129,LEN($A129)-2,1)="/",ISNUMBER(VALUE(RIGHT($A129,2))),VALUE(MID($A129,5,LEN($A129)-7))&gt;=1,VALUE(MID($A129,5,LEN($A129)-7))=INT(VALUE(MID($A129,5,LEN($A129)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A129&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A129&lt;&gt;"",$U129=0,$B129=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U129&gt;0,$V129=0,$B129=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U129)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B129="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B129&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C129="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C129&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D129="","Nedostaje godište",IF($G129="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E129="","Nedostaje pol",IF($F129="","Nedostaje pojas",IF(COUNTA(I129:P129)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I129:P129&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G129),I129:P129)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G129,IF(AND(COUNTIF(I129:P129,"Fudokan sport kumite")&gt;0,Q129=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I129:P129,"Fudokan sport kumite")=0,Q129&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S129">
@@ -5582,14 +8362,37 @@
         <f>IF(OR($G129="",$E129=""),"sve_kilaze","kg_"&amp;$G129&amp;"_"&amp;IF($E129="ženski","Z","M"))</f>
         <v/>
       </c>
-    </row>
-    <row r="130" spans="1:20">
+      <c r="U129">
+        <f>IF($A129="",0,IFERROR(MATCH(TRIM($A129),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V129">
+        <f>IF($U129=0,0,IF(TRIM(INDEX(spisak_klub,$U129))=TRIM($B$4),$U129,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:22">
       <c r="A130" s="5"/>
-      <c r="B130" s="5"/>
-      <c r="C130" s="5"/>
-      <c r="D130" s="5"/>
-      <c r="E130" s="5"/>
-      <c r="F130" s="5"/>
+      <c r="B130" s="5">
+        <f>IF($V130=0,"",INDEX(spisak_ime,$V130)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="C130" s="5">
+        <f>IF($V130=0,"",INDEX(spisak_prezime,$V130)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="D130" s="5">
+        <f>IF($V130=0,"",INDEX(spisak_godiste,$V130))</f>
+        <v/>
+      </c>
+      <c r="E130" s="5">
+        <f>IF($V130=0,"",INDEX(spisak_pol,$V130)&amp;"")</f>
+        <v/>
+      </c>
+      <c r="F130" s="5">
+        <f>IF($V130=0,"",INDEX(spisak_pojas,$V130)&amp;"")</f>
+        <v/>
+      </c>
       <c r="G130" s="7">
         <f>IF($D130="","",LOOKUP($D130,INDEX(grupe,0,1),INDEX(grupe,0,2)))</f>
         <v/>
@@ -5608,7 +8411,7 @@
       <c r="P130" s="5"/>
       <c r="Q130" s="5"/>
       <c r="R130" s="8">
-        <f>IF(COUNTA($A130:$F130,I130:P130,Q130)=0,"",IF(AND($A130&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A130,4))="FSS-",MID($A130,LEN($A130)-2,1)="/",ISNUMBER(VALUE(RIGHT($A130,2))),VALUE(MID($A130,5,LEN($A130)-7))&gt;=1,VALUE(MID($A130,5,LEN($A130)-7))=INT(VALUE(MID($A130,5,LEN($A130)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF($B130="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B130&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C130="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C130&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D130="","Nedostaje godište",IF($G130="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E130="","Nedostaje pol",IF($F130="","Nedostaje pojas",IF(COUNTA(I130:P130)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I130:P130&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G130),I130:P130)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G130,IF(AND(COUNTIF(I130:P130,"Fudokan sport kumite")&gt;0,Q130=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I130:P130,"Fudokan sport kumite")=0,Q130&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna"))))))))))))))</f>
+        <f>IF(SUMPRODUCT(LEN($A130:$F130))+SUMPRODUCT(LEN(I130:P130))+LEN(Q130)=0,"",IF(AND($A130&lt;&gt;"",NOT(IFERROR(AND(UPPER(LEFT($A130,4))="FSS-",MID($A130,LEN($A130)-2,1)="/",ISNUMBER(VALUE(RIGHT($A130,2))),VALUE(MID($A130,5,LEN($A130)-7))&gt;=1,VALUE(MID($A130,5,LEN($A130)-7))=INT(VALUE(MID($A130,5,LEN($A130)-7)))),FALSE))),"FSS ID se upisuje u obliku FSS-12/26",IF(AND($A130&lt;&gt;"",TRIM($B$4)=""),"Klub nije izabran u zaglavlju — bez njega se red ne popunjava",IF(AND($A130&lt;&gt;"",$U130=0,$B130=""),"FSS ID nije na spisku saveza — upiši ime, prezime i ostale podatke",IF(AND($U130&gt;0,$V130=0,$B130=""),"FSS ID pripada takmičaru kluba "&amp;INDEX(spisak_klub,$U130)&amp;" — ako je prešao u vaš klub, upiši ime i prezime",IF($B130="","Nedostaje ime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($B130&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Ime sadrži znakove koji nisu slova",IF($C130="","Nedostaje prezime",IF(NOT(SUMPRODUCT(--ISERROR(FIND(MID($C130&amp;REPT("a",60),ROW($A$1:$A$60),1),"ABCDEFGHIJKLMNOPQRSTUVWXYZabcdefghijklmnopqrstuvwxyzČĆĐŠŽčćđšž -'")))=0),"Prezime sadrži znakove koji nisu slova",IF($D130="","Nedostaje godište",IF($G130="","Godište nije obuhvaćeno uzrasnom tabelom",IF($E130="","Nedostaje pol",IF($F130="","Nedostaje pojas",IF(COUNTA(I130:P130)=0,"Nije izabrana nijedna disciplina",IF(SUMPRODUCT(--(I130:P130&lt;&gt;""),--(COUNTIF(INDIRECT("disc_"&amp;$G130),I130:P130)=0))&gt;0,"Izabrana disciplina nije moguća za uzrast "&amp;$G130,IF(AND(COUNTIF(I130:P130,"Fudokan sport kumite")&gt;0,Q130=""),"Nedostaje telesna težina za Fudokan sport kumite",IF(AND(COUNTIF(I130:P130,"Fudokan sport kumite")=0,Q130&lt;&gt;""),"Telesna težina se unosi isključivo uz Fudokan sport kumite","prijava je kompletna")))))))))))))))))</f>
         <v/>
       </c>
       <c r="S130">
@@ -5618,6 +8421,14 @@
       <c r="T130">
         <f>IF(OR($G130="",$E130=""),"sve_kilaze","kg_"&amp;$G130&amp;"_"&amp;IF($E130="ženski","Z","M"))</f>
         <v/>
+      </c>
+      <c r="U130">
+        <f>IF($A130="",0,IFERROR(MATCH(TRIM($A130),spisak_id,0),0))</f>
+        <v>0</v>
+      </c>
+      <c r="V130">
+        <f>IF($U130=0,0,IF(TRIM(INDEX(spisak_klub,$U130))=TRIM($B$4),$U130,0))</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5625,7 +8436,10 @@
   <mergeCells count="1">
     <mergeCell ref="A3:R3"/>
   </mergeCells>
-  <dataValidations count="7">
+  <dataValidations count="8">
+    <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Klub" error="Ovog kluba nema na spisku saveza. Ako je klub nov, potvrdi upis." sqref="B4">
+      <formula1>klubovi</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Godište" error="Godište se bira iz padajućeg menija." sqref="D11:D130">
       <formula1>godista</formula1>
     </dataValidation>
@@ -11639,4 +14453,106 @@
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="I2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="I3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="I4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="I5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="I6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="I7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="I8" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="I9" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="I10" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="I11" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="I12" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="I13" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="I14" t="s">
+        <v>198</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>